--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rb4ffef5a3b434c64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rd79d825d050e4be8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R96a315c450eb4144"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R07ae9b8364ff414b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rc4526b72fdf94aac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Ra03ebc26e4f842e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R206732953606436b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R4c9b1bbd34ef473d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-07T00:43:44.962Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-07T08:19:57.914Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>ec066f78b134a4ab41e86b94133226ce6f6438520682c580b116eb56ed715fc9</x:v>
+        <x:v>682cddfb34b9ba0867e0152518ab5a1ad129de7bbb8828a58f64d23cf072cc71</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>99ba5edfb5f5ec7966456e3ad66285380fe1c91036b9f85ff7846b14c7fd32f2</x:v>
+        <x:v>4139f272a1dd534c1fd927881b22bba0c4b16ce3b4162f405c44d3aab380f491</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3372,7 +3372,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e028815d0034f9f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bee93c2adad49e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5800,7 +5800,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79f1f0a39d664290"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d94463f8bf6492d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11276,7 +11276,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2ef70e0f5e648d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f401a13229a4d76"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rc4526b72fdf94aac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Ra03ebc26e4f842e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R206732953606436b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R4c9b1bbd34ef473d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Re13fb4a751eb4150"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R1435b0bda9224bc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R610fd805035248c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R808ccab6fbb74281"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -251,7 +251,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G230" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G240" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Route ID"/>
     <x:tableColumn id="2" name="Vertex"/>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-07T08:19:57.914Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-07T12:10:03.268Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>682cddfb34b9ba0867e0152518ab5a1ad129de7bbb8828a58f64d23cf072cc71</x:v>
+        <x:v>43d938ca7f8fb8bab04793528cf39b516a7cfa3e6f752cefca7203bfeafa0aac</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>4139f272a1dd534c1fd927881b22bba0c4b16ce3b4162f405c44d3aab380f491</x:v>
+        <x:v>a162fc27119841a75190b0bc0153cc17495a8bc432ad574a535e8a6799eb9a3d</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3372,7 +3372,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bee93c2adad49e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R424c09d9175c4b15"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3671,8 +3671,8 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I7" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A7,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>72.597</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A7,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>64.02913031117919</x:v>
       </x:c>
       <x:c r="J7" s="11"/>
       <x:c r="K7" s="11" t="str">
@@ -3689,7 +3689,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P7" s="8" t="str">
-        <x:v>Concealed wall band above openings; ceiling containment at wing returns</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q7" s="9"/>
       <x:c r="R7" s="9"/>
@@ -3730,8 +3730,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A8,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>10.549110166147116</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A8,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>11.286909264308505</x:v>
       </x:c>
       <x:c r="J8" s="11"/>
       <x:c r="K8" s="11" t="str">
@@ -3748,7 +3748,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P8" s="8" t="str">
-        <x:v>Wall / beam or roof containment, then pendant connection</x:v>
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
       </x:c>
       <x:c r="Q8" s="9"/>
       <x:c r="R8" s="9"/>
@@ -3791,8 +3791,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A9,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>10.549110166147116</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A9,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>11.286909264308505</x:v>
       </x:c>
       <x:c r="J9" s="11"/>
       <x:c r="K9" s="11" t="str">
@@ -3809,7 +3809,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P9" s="8" t="str">
-        <x:v>Wall / beam or roof containment, then pendant connection</x:v>
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
       </x:c>
       <x:c r="Q9" s="9"/>
       <x:c r="R9" s="9"/>
@@ -3852,8 +3852,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A10,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>10.539110166147115</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A10,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>11.276909264308502</x:v>
       </x:c>
       <x:c r="J10" s="11"/>
       <x:c r="K10" s="11" t="str">
@@ -3870,7 +3870,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P10" s="8" t="str">
-        <x:v>Wall / beam or roof containment, then pendant connection</x:v>
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
       </x:c>
       <x:c r="Q10" s="9"/>
       <x:c r="R10" s="9"/>
@@ -3913,8 +3913,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A11,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>10.549110166147116</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A11,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>11.286909264308504</x:v>
       </x:c>
       <x:c r="J11" s="11"/>
       <x:c r="K11" s="11" t="str">
@@ -3931,7 +3931,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P11" s="8" t="str">
-        <x:v>Wall / beam or roof containment, then pendant connection</x:v>
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
       </x:c>
       <x:c r="Q11" s="9"/>
       <x:c r="R11" s="9"/>
@@ -3974,8 +3974,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A12,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>10.549110166147116</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A12,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>11.286909264308504</x:v>
       </x:c>
       <x:c r="J12" s="11"/>
       <x:c r="K12" s="11" t="str">
@@ -3992,7 +3992,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P12" s="8" t="str">
-        <x:v>Wall / beam or roof containment, then pendant connection</x:v>
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
       </x:c>
       <x:c r="Q12" s="9"/>
       <x:c r="R12" s="9"/>
@@ -4035,8 +4035,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I13" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A13,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>10.549110166147116</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A13,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>11.286909264308504</x:v>
       </x:c>
       <x:c r="J13" s="11"/>
       <x:c r="K13" s="11" t="str">
@@ -4053,7 +4053,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P13" s="8" t="str">
-        <x:v>Wall / beam or roof containment, then pendant connection</x:v>
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
       </x:c>
       <x:c r="Q13" s="9"/>
       <x:c r="R13" s="9"/>
@@ -4096,8 +4096,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I14" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A14,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>10.539110166147118</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A14,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>11.276909264308506</x:v>
       </x:c>
       <x:c r="J14" s="11"/>
       <x:c r="K14" s="11" t="str">
@@ -4114,7 +4114,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P14" s="8" t="str">
-        <x:v>Wall / beam or roof containment, then pendant connection</x:v>
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
       </x:c>
       <x:c r="Q14" s="9"/>
       <x:c r="R14" s="9"/>
@@ -4157,8 +4157,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I15" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A15,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>10.054759999999991</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A15,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>7.73309922680412</x:v>
       </x:c>
       <x:c r="J15" s="11"/>
       <x:c r="K15" s="11" t="str">
@@ -4175,7 +4175,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P15" s="8" t="str">
-        <x:v>Wall / beam or roof containment, then pendant connection</x:v>
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
       </x:c>
       <x:c r="Q15" s="9"/>
       <x:c r="R15" s="9"/>
@@ -4218,8 +4218,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I16" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A16,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>10.007540000000002</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A16,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>7.733099226804125</x:v>
       </x:c>
       <x:c r="J16" s="11"/>
       <x:c r="K16" s="11" t="str">
@@ -4236,7 +4236,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P16" s="8" t="str">
-        <x:v>Wall / beam or roof containment, then pendant connection</x:v>
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
       </x:c>
       <x:c r="Q16" s="9"/>
       <x:c r="R16" s="9"/>
@@ -4287,8 +4287,8 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I17" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A17,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>79.797</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A17,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>70.62913031117918</x:v>
       </x:c>
       <x:c r="J17" s="11"/>
       <x:c r="K17" s="11" t="str">
@@ -4305,7 +4305,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P17" s="8" t="str">
-        <x:v>Concealed wall band above openings; ceiling containment at wing returns</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q17" s="9"/>
       <x:c r="R17" s="9"/>
@@ -4346,8 +4346,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I18" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A18,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>10.549110166147116</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A18,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>11.286909264308505</x:v>
       </x:c>
       <x:c r="J18" s="11"/>
       <x:c r="K18" s="11" t="str">
@@ -4364,7 +4364,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P18" s="8" t="str">
-        <x:v>Wall / beam or roof containment, then pendant connection</x:v>
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
       </x:c>
       <x:c r="Q18" s="9"/>
       <x:c r="R18" s="9"/>
@@ -4407,8 +4407,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I19" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A19,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>10.549110166147116</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A19,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>11.286909264308505</x:v>
       </x:c>
       <x:c r="J19" s="11"/>
       <x:c r="K19" s="11" t="str">
@@ -4425,7 +4425,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P19" s="8" t="str">
-        <x:v>Wall / beam or roof containment, then pendant connection</x:v>
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
       </x:c>
       <x:c r="Q19" s="9"/>
       <x:c r="R19" s="9"/>
@@ -4468,8 +4468,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I20" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A20,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>10.539110166147115</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A20,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>11.276909264308502</x:v>
       </x:c>
       <x:c r="J20" s="11"/>
       <x:c r="K20" s="11" t="str">
@@ -4486,7 +4486,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P20" s="8" t="str">
-        <x:v>Wall / beam or roof containment, then pendant connection</x:v>
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
       </x:c>
       <x:c r="Q20" s="9"/>
       <x:c r="R20" s="9"/>
@@ -4529,8 +4529,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I21" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A21,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>10.549110166147116</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A21,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>11.286909264308504</x:v>
       </x:c>
       <x:c r="J21" s="11"/>
       <x:c r="K21" s="11" t="str">
@@ -4547,7 +4547,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P21" s="8" t="str">
-        <x:v>Wall / beam or roof containment, then pendant connection</x:v>
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
       </x:c>
       <x:c r="Q21" s="9"/>
       <x:c r="R21" s="9"/>
@@ -4590,8 +4590,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I22" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A22,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>10.549110166147116</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A22,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>11.286909264308504</x:v>
       </x:c>
       <x:c r="J22" s="11"/>
       <x:c r="K22" s="11" t="str">
@@ -4608,7 +4608,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P22" s="8" t="str">
-        <x:v>Wall / beam or roof containment, then pendant connection</x:v>
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
       </x:c>
       <x:c r="Q22" s="9"/>
       <x:c r="R22" s="9"/>
@@ -4651,8 +4651,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I23" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A23,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>10.549110166147116</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A23,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>11.286909264308504</x:v>
       </x:c>
       <x:c r="J23" s="11"/>
       <x:c r="K23" s="11" t="str">
@@ -4669,7 +4669,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P23" s="8" t="str">
-        <x:v>Wall / beam or roof containment, then pendant connection</x:v>
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
       </x:c>
       <x:c r="Q23" s="9"/>
       <x:c r="R23" s="9"/>
@@ -4712,8 +4712,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I24" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A24,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>10.539110166147118</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A24,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>11.276909264308506</x:v>
       </x:c>
       <x:c r="J24" s="11"/>
       <x:c r="K24" s="11" t="str">
@@ -4730,7 +4730,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P24" s="8" t="str">
-        <x:v>Wall / beam or roof containment, then pendant connection</x:v>
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
       </x:c>
       <x:c r="Q24" s="9"/>
       <x:c r="R24" s="9"/>
@@ -4773,8 +4773,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I25" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A25,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>10.054759999999991</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A25,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>7.73309922680412</x:v>
       </x:c>
       <x:c r="J25" s="11"/>
       <x:c r="K25" s="11" t="str">
@@ -4791,7 +4791,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P25" s="8" t="str">
-        <x:v>Wall / beam or roof containment, then pendant connection</x:v>
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
       </x:c>
       <x:c r="Q25" s="9"/>
       <x:c r="R25" s="9"/>
@@ -4834,8 +4834,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I26" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A26,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>10.007540000000002</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A26,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>7.733099226804125</x:v>
       </x:c>
       <x:c r="J26" s="11"/>
       <x:c r="K26" s="11" t="str">
@@ -4852,7 +4852,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P26" s="8" t="str">
-        <x:v>Wall / beam or roof containment, then pendant connection</x:v>
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
       </x:c>
       <x:c r="Q26" s="9"/>
       <x:c r="R26" s="9"/>
@@ -4895,8 +4895,8 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I27" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A27,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>11.971</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A27,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>12.517</x:v>
       </x:c>
       <x:c r="J27" s="11"/>
       <x:c r="K27" s="11" t="str">
@@ -4913,7 +4913,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P27" s="8" t="str">
-        <x:v>Concealed wall band above openings; ceiling containment at wing returns</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q27" s="9"/>
       <x:c r="R27" s="9"/>
@@ -4954,8 +4954,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I28" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A28,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>7.3833921494717325</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A28,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>7.91542691446789</x:v>
       </x:c>
       <x:c r="J28" s="11"/>
       <x:c r="K28" s="11" t="str">
@@ -4972,7 +4972,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P28" s="8" t="str">
-        <x:v>Concealed pier / wall drop, local termination</x:v>
+        <x:v>Concealed entrance wall band, solid pier and local termination.</x:v>
       </x:c>
       <x:c r="Q28" s="9"/>
       <x:c r="R28" s="9"/>
@@ -5015,8 +5015,8 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I29" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A29,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>18.571</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A29,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>19.117</x:v>
       </x:c>
       <x:c r="J29" s="11"/>
       <x:c r="K29" s="11" t="str">
@@ -5033,7 +5033,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P29" s="8" t="str">
-        <x:v>Concealed wall band above openings; ceiling containment at wing returns</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q29" s="9"/>
       <x:c r="R29" s="9"/>
@@ -5074,8 +5074,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I30" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A30,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>7.3833921494717325</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A30,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>7.91542691446789</x:v>
       </x:c>
       <x:c r="J30" s="11"/>
       <x:c r="K30" s="11" t="str">
@@ -5092,7 +5092,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P30" s="8" t="str">
-        <x:v>Concealed pier / wall drop, local termination</x:v>
+        <x:v>Concealed entrance wall band, solid pier and local termination.</x:v>
       </x:c>
       <x:c r="Q30" s="9"/>
       <x:c r="R30" s="9"/>
@@ -5139,8 +5139,8 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I31" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A31,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>76.203</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A31,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>67.54713031117919</x:v>
       </x:c>
       <x:c r="J31" s="11"/>
       <x:c r="K31" s="11" t="str">
@@ -5157,7 +5157,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P31" s="8" t="str">
-        <x:v>Concealed wall band above openings; ceiling containment at wing returns</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q31" s="9"/>
       <x:c r="R31" s="9"/>
@@ -5198,8 +5198,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I32" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A32,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>7.782000000000003</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A32,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>8.69282092938182</x:v>
       </x:c>
       <x:c r="J32" s="11"/>
       <x:c r="K32" s="11" t="str">
@@ -5216,7 +5216,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P32" s="8" t="str">
-        <x:v>Concealed pier / wall drop, local termination</x:v>
+        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
       </x:c>
       <x:c r="Q32" s="9"/>
       <x:c r="R32" s="9"/>
@@ -5259,8 +5259,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I33" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A33,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>9.382000000000003</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A33,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>11.831150261440472</x:v>
       </x:c>
       <x:c r="J33" s="11"/>
       <x:c r="K33" s="11" t="str">
@@ -5277,7 +5277,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P33" s="8" t="str">
-        <x:v>Concealed pier / wall drop, local termination</x:v>
+        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
       </x:c>
       <x:c r="Q33" s="9"/>
       <x:c r="R33" s="9"/>
@@ -5320,8 +5320,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I34" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A34,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>1.121999999999999</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A34,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>6.973264175257731</x:v>
       </x:c>
       <x:c r="J34" s="11"/>
       <x:c r="K34" s="11" t="str">
@@ -5338,7 +5338,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P34" s="8" t="str">
-        <x:v>Concealed pier / wall drop, local termination</x:v>
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
       </x:c>
       <x:c r="Q34" s="9"/>
       <x:c r="R34" s="9"/>
@@ -5381,8 +5381,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I35" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A35,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>1.121999999999999</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A35,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>6.973264175257731</x:v>
       </x:c>
       <x:c r="J35" s="11"/>
       <x:c r="K35" s="11" t="str">
@@ -5399,7 +5399,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P35" s="8" t="str">
-        <x:v>Concealed pier / wall drop, local termination</x:v>
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
       </x:c>
       <x:c r="Q35" s="9"/>
       <x:c r="R35" s="9"/>
@@ -5442,8 +5442,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I36" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A36,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>10.718</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A36,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="J36" s="11"/>
       <x:c r="K36" s="11" t="str">
@@ -5460,7 +5460,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P36" s="8" t="str">
-        <x:v>Concealed pier / wall drop, local termination</x:v>
+        <x:v>Rear-wall band and local termination; gable / weatherproof entry details pending.</x:v>
       </x:c>
       <x:c r="Q36" s="9"/>
       <x:c r="R36" s="9"/>
@@ -5506,8 +5506,8 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I37" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A37,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>83.403</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A37,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>74.14713031117918</x:v>
       </x:c>
       <x:c r="J37" s="11"/>
       <x:c r="K37" s="11" t="str">
@@ -5524,7 +5524,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P37" s="8" t="str">
-        <x:v>Concealed wall band above openings; ceiling containment at wing returns</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q37" s="9"/>
       <x:c r="R37" s="9"/>
@@ -5565,8 +5565,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I38" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A38,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>9.382000000000003</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A38,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>11.831150261440472</x:v>
       </x:c>
       <x:c r="J38" s="11"/>
       <x:c r="K38" s="11" t="str">
@@ -5583,7 +5583,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P38" s="8" t="str">
-        <x:v>Concealed pier / wall drop, local termination</x:v>
+        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
       </x:c>
       <x:c r="Q38" s="9"/>
       <x:c r="R38" s="9"/>
@@ -5626,8 +5626,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I39" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A39,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>7.782000000000003</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A39,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>8.69282092938182</x:v>
       </x:c>
       <x:c r="J39" s="11"/>
       <x:c r="K39" s="11" t="str">
@@ -5644,7 +5644,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P39" s="8" t="str">
-        <x:v>Concealed pier / wall drop, local termination</x:v>
+        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
       </x:c>
       <x:c r="Q39" s="9"/>
       <x:c r="R39" s="9"/>
@@ -5687,8 +5687,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I40" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A40,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>1.121999999999999</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A40,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>6.973264175257731</x:v>
       </x:c>
       <x:c r="J40" s="11"/>
       <x:c r="K40" s="11" t="str">
@@ -5705,7 +5705,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P40" s="8" t="str">
-        <x:v>Concealed pier / wall drop, local termination</x:v>
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
       </x:c>
       <x:c r="Q40" s="9"/>
       <x:c r="R40" s="9"/>
@@ -5748,8 +5748,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I41" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$230,A41,'Route Points'!$F$7:$F$230)</x:f>
-        <x:v>1.121999999999999</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$240,A41,'Route Points'!$F$7:$F$240)</x:f>
+        <x:v>6.973264175257731</x:v>
       </x:c>
       <x:c r="J41" s="11"/>
       <x:c r="K41" s="11" t="str">
@@ -5766,7 +5766,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P41" s="8" t="str">
-        <x:v>Concealed pier / wall drop, local termination</x:v>
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
       </x:c>
       <x:c r="Q41" s="9"/>
       <x:c r="R41" s="9"/>
@@ -5800,7 +5800,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d94463f8bf6492d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c43e5566c624a59"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5977,14 +5977,14 @@
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
         <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
         <x:f>SQRT((C10-C9)^2+(D10-D9)^2+(E10-E9)^2)</x:f>
-        <x:v>2.0699999999999994</x:v>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="G10" s="8" t="str">
         <x:v>Current</x:v>
@@ -6001,14 +6001,14 @@
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
         <x:f>SQRT((C11-C10)^2+(D11-D10)^2+(E11-E10)^2)</x:f>
-        <x:v>1.3599999999999999</x:v>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G11" s="8" t="str">
         <x:v>Current</x:v>
@@ -6022,17 +6022,17 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
         <x:f>SQRT((C12-C11)^2+(D12-D11)^2+(E12-E11)^2)</x:f>
-        <x:v>4.314999999999998</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G12" s="8" t="str">
         <x:v>Current</x:v>
@@ -6046,17 +6046,17 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
         <x:f>SQRT((C13-C12)^2+(D13-D12)^2+(E13-E12)^2)</x:f>
-        <x:v>2.5120000000000005</x:v>
+        <x:v>1.6740000000000004</x:v>
       </x:c>
       <x:c r="G13" s="8" t="str">
         <x:v>Current</x:v>
@@ -6070,17 +6070,17 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
         <x:f>SQRT((C14-C13)^2+(D14-D13)^2+(E14-E13)^2)</x:f>
-        <x:v>3.7600000000000002</x:v>
+        <x:v>4.0600000000000005</x:v>
       </x:c>
       <x:c r="G14" s="8" t="str">
         <x:v>Current</x:v>
@@ -6097,14 +6097,14 @@
         <x:v>44.175</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
         <x:f>SQRT((C15-C14)^2+(D15-D14)^2+(E15-E14)^2)</x:f>
-        <x:v>8.875</x:v>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G15" s="8" t="str">
         <x:v>Current</x:v>
@@ -6121,14 +6121,14 @@
         <x:v>44.175</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
-        <x:v>-13.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
         <x:f>SQRT((C16-C15)^2+(D16-D15)^2+(E16-E15)^2)</x:f>
-        <x:v>5.88</x:v>
+        <x:v>1.0359999999999996</x:v>
       </x:c>
       <x:c r="G16" s="8" t="str">
         <x:v>Current</x:v>
@@ -6142,17 +6142,17 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
-        <x:v>-13.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
         <x:f>SQRT((C17-C16)^2+(D17-D16)^2+(E17-E16)^2)</x:f>
-        <x:v>7.199999999999996</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G17" s="8" t="str">
         <x:v>Current</x:v>
@@ -6166,17 +6166,17 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C18" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
         <x:f>SQRT((C18-C17)^2+(D18-D17)^2+(E18-E17)^2)</x:f>
-        <x:v>5.88</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G18" s="8" t="str">
         <x:v>Current</x:v>
@@ -6190,17 +6190,17 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C19" s="11" t="n">
-        <x:v>9.03</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
         <x:f>SQRT((C19-C18)^2+(D19-D18)^2+(E19-E18)^2)</x:f>
-        <x:v>27.945</x:v>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G19" s="8" t="str">
         <x:v>Current</x:v>
@@ -6208,23 +6208,23 @@
     </x:row>
     <x:row r="20" ht="32" customHeight="1">
       <x:c r="A20" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F226</x:v>
+        <x:v>trunk:FC1:F1:fan:-1</x:v>
       </x:c>
       <x:c r="B20" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
-        <x:v>9.03</x:v>
+        <x:v>37.695</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>6.950412371134018</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C20-C19)^2+(D20-D19)^2+(E20-E19)^2)</x:f>
+        <x:v>3.697957107375376</x:v>
       </x:c>
       <x:c r="G20" s="8" t="str">
         <x:v>Current</x:v>
@@ -6232,23 +6232,23 @@
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
       <x:c r="A21" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F226</x:v>
+        <x:v>trunk:FC1:F1:fan:-1</x:v>
       </x:c>
       <x:c r="B21" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
-        <x:v>9.03</x:v>
+        <x:v>37.615</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>7.02</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
         <x:f>SQRT((C21-C20)^2+(D21-D20)^2+(E21-E20)^2)</x:f>
-        <x:v>0.48799999999999955</x:v>
+        <x:v>0.12010804821421713</x:v>
       </x:c>
       <x:c r="G21" s="8" t="str">
         <x:v>Current</x:v>
@@ -6256,23 +6256,23 @@
     </x:row>
     <x:row r="22" ht="32" customHeight="1">
       <x:c r="A22" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F226</x:v>
+        <x:v>trunk:FC1:F1:fan:-1</x:v>
       </x:c>
       <x:c r="B22" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
-        <x:v>9.03</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:v>-7.05</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
         <x:f>SQRT((C22-C21)^2+(D22-D21)^2+(E22-E21)^2)</x:f>
-        <x:v>0.3132494925336704</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G22" s="8" t="str">
         <x:v>Current</x:v>
@@ -6280,23 +6280,23 @@
     </x:row>
     <x:row r="23" ht="32" customHeight="1">
       <x:c r="A23" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F226</x:v>
+        <x:v>trunk:FC1:F1:fan:-1</x:v>
       </x:c>
       <x:c r="B23" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C23" s="11" t="n">
-        <x:v>7.725</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>-7.05</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
         <x:f>SQRT((C23-C22)^2+(D23-D22)^2+(E23-E22)^2)</x:f>
-        <x:v>1.3049999999999997</x:v>
+        <x:v>1.0359999999999996</x:v>
       </x:c>
       <x:c r="G23" s="8" t="str">
         <x:v>Current</x:v>
@@ -6304,23 +6304,23 @@
     </x:row>
     <x:row r="24" ht="32" customHeight="1">
       <x:c r="A24" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F226</x:v>
+        <x:v>trunk:FC1:F1:fan:-1</x:v>
       </x:c>
       <x:c r="B24" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
-        <x:v>7.725</x:v>
+        <x:v>9.030000000000001</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>8.988413043478262</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>-4.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
         <x:f>SQRT((C24-C23)^2+(D24-D23)^2+(E24-E23)^2)</x:f>
-        <x:v>3.2744476301351852</x:v>
+        <x:v>27.945</x:v>
       </x:c>
       <x:c r="G24" s="8" t="str">
         <x:v>Current</x:v>
@@ -6331,20 +6331,20 @@
         <x:v>drop:FC1:F1:fan:-1:F226</x:v>
       </x:c>
       <x:c r="B25" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
-        <x:v>7.725</x:v>
+        <x:v>9.030000000000001</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>9.028413043478261</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>-4.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:f>SQRT((C25-C24)^2+(D25-D24)^2+(E25-E24)^2)</x:f>
-        <x:v>0.03999999999999915</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G25" s="8" t="str">
         <x:v>Current</x:v>
@@ -6355,20 +6355,20 @@
         <x:v>drop:FC1:F1:fan:-1:F226</x:v>
       </x:c>
       <x:c r="B26" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
-        <x:v>7.725</x:v>
+        <x:v>9.030000000000001</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>3.9</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:v>-4.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
         <x:f>SQRT((C26-C25)^2+(D26-D25)^2+(E26-E25)^2)</x:f>
-        <x:v>5.128413043478261</x:v>
+        <x:v>1.0359999999999996</x:v>
       </x:c>
       <x:c r="G26" s="8" t="str">
         <x:v>Current</x:v>
@@ -6376,23 +6376,23 @@
     </x:row>
     <x:row r="27" ht="32" customHeight="1">
       <x:c r="A27" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F228</x:v>
+        <x:v>drop:FC1:F1:fan:-1:F226</x:v>
       </x:c>
       <x:c r="B27" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C27" s="11" t="n">
-        <x:v>13.53</x:v>
+        <x:v>7.725</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C27-C26)^2+(D27-D26)^2+(E27-E26)^2)</x:f>
+        <x:v>1.3050000000000015</x:v>
       </x:c>
       <x:c r="G27" s="8" t="str">
         <x:v>Current</x:v>
@@ -6400,23 +6400,23 @@
     </x:row>
     <x:row r="28" ht="32" customHeight="1">
       <x:c r="A28" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F228</x:v>
+        <x:v>drop:FC1:F1:fan:-1:F226</x:v>
       </x:c>
       <x:c r="B28" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C28" s="11" t="n">
-        <x:v>13.53</x:v>
+        <x:v>7.725</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>7.02</x:v>
+        <x:v>9.18841304347826</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-4.4</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
         <x:f>SQRT((C28-C27)^2+(D28-D27)^2+(E28-E27)^2)</x:f>
-        <x:v>0.48799999999999955</x:v>
+        <x:v>3.6574962208302444</x:v>
       </x:c>
       <x:c r="G28" s="8" t="str">
         <x:v>Current</x:v>
@@ -6424,23 +6424,23 @@
     </x:row>
     <x:row r="29" ht="32" customHeight="1">
       <x:c r="A29" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F228</x:v>
+        <x:v>drop:FC1:F1:fan:-1:F226</x:v>
       </x:c>
       <x:c r="B29" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
-        <x:v>13.53</x:v>
+        <x:v>7.725</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>9.028413043478261</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>-7.05</x:v>
+        <x:v>-4.4</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
         <x:f>SQRT((C29-C28)^2+(D29-D28)^2+(E29-E28)^2)</x:f>
-        <x:v>0.3132494925336704</x:v>
+        <x:v>0.15999999999999837</x:v>
       </x:c>
       <x:c r="G29" s="8" t="str">
         <x:v>Current</x:v>
@@ -6448,23 +6448,23 @@
     </x:row>
     <x:row r="30" ht="32" customHeight="1">
       <x:c r="A30" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F228</x:v>
+        <x:v>drop:FC1:F1:fan:-1:F226</x:v>
       </x:c>
       <x:c r="B30" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
-        <x:v>12.225</x:v>
+        <x:v>7.725</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>3.9</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>-7.05</x:v>
+        <x:v>-4.4</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
         <x:f>SQRT((C30-C29)^2+(D30-D29)^2+(E30-E29)^2)</x:f>
-        <x:v>1.3049999999999997</x:v>
+        <x:v>5.128413043478261</x:v>
       </x:c>
       <x:c r="G30" s="8" t="str">
         <x:v>Current</x:v>
@@ -6475,20 +6475,20 @@
         <x:v>drop:FC1:F1:fan:-1:F228</x:v>
       </x:c>
       <x:c r="B31" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C31" s="11" t="n">
-        <x:v>12.225</x:v>
+        <x:v>13.530000000000001</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>8.988413043478262</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>-4.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:f>SQRT((C31-C30)^2+(D31-D30)^2+(E31-E30)^2)</x:f>
-        <x:v>3.2744476301351852</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G31" s="8" t="str">
         <x:v>Current</x:v>
@@ -6499,20 +6499,20 @@
         <x:v>drop:FC1:F1:fan:-1:F228</x:v>
       </x:c>
       <x:c r="B32" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C32" s="11" t="n">
-        <x:v>12.225</x:v>
+        <x:v>13.530000000000001</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
-        <x:v>9.028413043478261</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>-4.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
         <x:f>SQRT((C32-C31)^2+(D32-D31)^2+(E32-E31)^2)</x:f>
-        <x:v>0.03999999999999915</x:v>
+        <x:v>1.0359999999999996</x:v>
       </x:c>
       <x:c r="G32" s="8" t="str">
         <x:v>Current</x:v>
@@ -6523,20 +6523,20 @@
         <x:v>drop:FC1:F1:fan:-1:F228</x:v>
       </x:c>
       <x:c r="B33" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C33" s="11" t="n">
         <x:v>12.225</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
-        <x:v>3.9</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>-4.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
         <x:f>SQRT((C33-C32)^2+(D33-D32)^2+(E33-E32)^2)</x:f>
-        <x:v>5.128413043478261</x:v>
+        <x:v>1.3050000000000015</x:v>
       </x:c>
       <x:c r="G33" s="8" t="str">
         <x:v>Current</x:v>
@@ -6544,23 +6544,23 @@
     </x:row>
     <x:row r="34" ht="32" customHeight="1">
       <x:c r="A34" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F230</x:v>
+        <x:v>drop:FC1:F1:fan:-1:F228</x:v>
       </x:c>
       <x:c r="B34" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C34" s="11" t="n">
-        <x:v>18.02</x:v>
+        <x:v>12.225</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>9.18841304347826</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-4.4</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C34-C33)^2+(D34-D33)^2+(E34-E33)^2)</x:f>
+        <x:v>3.6574962208302444</x:v>
       </x:c>
       <x:c r="G34" s="8" t="str">
         <x:v>Current</x:v>
@@ -6568,23 +6568,23 @@
     </x:row>
     <x:row r="35" ht="32" customHeight="1">
       <x:c r="A35" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F230</x:v>
+        <x:v>drop:FC1:F1:fan:-1:F228</x:v>
       </x:c>
       <x:c r="B35" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C35" s="11" t="n">
-        <x:v>18.02</x:v>
+        <x:v>12.225</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
-        <x:v>7.02</x:v>
+        <x:v>9.028413043478261</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-4.4</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
         <x:f>SQRT((C35-C34)^2+(D35-D34)^2+(E35-E34)^2)</x:f>
-        <x:v>0.48799999999999955</x:v>
+        <x:v>0.15999999999999837</x:v>
       </x:c>
       <x:c r="G35" s="8" t="str">
         <x:v>Current</x:v>
@@ -6592,23 +6592,23 @@
     </x:row>
     <x:row r="36" ht="32" customHeight="1">
       <x:c r="A36" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F230</x:v>
+        <x:v>drop:FC1:F1:fan:-1:F228</x:v>
       </x:c>
       <x:c r="B36" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C36" s="11" t="n">
-        <x:v>18.02</x:v>
+        <x:v>12.225</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>3.9</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>-7.05</x:v>
+        <x:v>-4.4</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
         <x:f>SQRT((C36-C35)^2+(D36-D35)^2+(E36-E35)^2)</x:f>
-        <x:v>0.3132494925336704</x:v>
+        <x:v>5.128413043478261</x:v>
       </x:c>
       <x:c r="G36" s="8" t="str">
         <x:v>Current</x:v>
@@ -6619,20 +6619,20 @@
         <x:v>drop:FC1:F1:fan:-1:F230</x:v>
       </x:c>
       <x:c r="B37" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C37" s="11" t="n">
-        <x:v>16.725</x:v>
+        <x:v>18.02</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>-7.05</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:f>SQRT((C37-C36)^2+(D37-D36)^2+(E37-E36)^2)</x:f>
-        <x:v>1.2949999999999982</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G37" s="8" t="str">
         <x:v>Current</x:v>
@@ -6643,20 +6643,20 @@
         <x:v>drop:FC1:F1:fan:-1:F230</x:v>
       </x:c>
       <x:c r="B38" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C38" s="11" t="n">
-        <x:v>16.725</x:v>
+        <x:v>18.02</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
-        <x:v>8.988413043478262</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>-4.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
         <x:f>SQRT((C38-C37)^2+(D38-D37)^2+(E38-E37)^2)</x:f>
-        <x:v>3.2744476301351852</x:v>
+        <x:v>1.0359999999999996</x:v>
       </x:c>
       <x:c r="G38" s="8" t="str">
         <x:v>Current</x:v>
@@ -6667,20 +6667,20 @@
         <x:v>drop:FC1:F1:fan:-1:F230</x:v>
       </x:c>
       <x:c r="B39" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C39" s="11" t="n">
         <x:v>16.725</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
-        <x:v>9.028413043478261</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>-4.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
         <x:f>SQRT((C39-C38)^2+(D39-D38)^2+(E39-E38)^2)</x:f>
-        <x:v>0.03999999999999915</x:v>
+        <x:v>1.2949999999999982</x:v>
       </x:c>
       <x:c r="G39" s="8" t="str">
         <x:v>Current</x:v>
@@ -6691,20 +6691,20 @@
         <x:v>drop:FC1:F1:fan:-1:F230</x:v>
       </x:c>
       <x:c r="B40" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
         <x:v>16.725</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
-        <x:v>3.9</x:v>
+        <x:v>9.18841304347826</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
         <x:v>-4.4</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
         <x:f>SQRT((C40-C39)^2+(D40-D39)^2+(E40-E39)^2)</x:f>
-        <x:v>5.128413043478261</x:v>
+        <x:v>3.6574962208302444</x:v>
       </x:c>
       <x:c r="G40" s="8" t="str">
         <x:v>Current</x:v>
@@ -6712,23 +6712,23 @@
     </x:row>
     <x:row r="41" ht="32" customHeight="1">
       <x:c r="A41" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F232</x:v>
+        <x:v>drop:FC1:F1:fan:-1:F230</x:v>
       </x:c>
       <x:c r="B41" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C41" s="11" t="n">
-        <x:v>22.53</x:v>
+        <x:v>16.725</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>9.028413043478261</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-4.4</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C41-C40)^2+(D41-D40)^2+(E41-E40)^2)</x:f>
+        <x:v>0.15999999999999837</x:v>
       </x:c>
       <x:c r="G41" s="8" t="str">
         <x:v>Current</x:v>
@@ -6736,23 +6736,23 @@
     </x:row>
     <x:row r="42" ht="32" customHeight="1">
       <x:c r="A42" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F232</x:v>
+        <x:v>drop:FC1:F1:fan:-1:F230</x:v>
       </x:c>
       <x:c r="B42" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C42" s="11" t="n">
-        <x:v>22.53</x:v>
+        <x:v>16.725</x:v>
       </x:c>
       <x:c r="D42" s="11" t="n">
-        <x:v>7.02</x:v>
+        <x:v>3.9</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-4.4</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
         <x:f>SQRT((C42-C41)^2+(D42-D41)^2+(E42-E41)^2)</x:f>
-        <x:v>0.48799999999999955</x:v>
+        <x:v>5.128413043478261</x:v>
       </x:c>
       <x:c r="G42" s="8" t="str">
         <x:v>Current</x:v>
@@ -6763,20 +6763,20 @@
         <x:v>drop:FC1:F1:fan:-1:F232</x:v>
       </x:c>
       <x:c r="B43" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C43" s="11" t="n">
         <x:v>22.53</x:v>
       </x:c>
       <x:c r="D43" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E43" s="11" t="n">
-        <x:v>-7.05</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
-        <x:f>SQRT((C43-C42)^2+(D43-D42)^2+(E43-E42)^2)</x:f>
-        <x:v>0.3132494925336704</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G43" s="8" t="str">
         <x:v>Current</x:v>
@@ -6787,20 +6787,20 @@
         <x:v>drop:FC1:F1:fan:-1:F232</x:v>
       </x:c>
       <x:c r="B44" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C44" s="11" t="n">
-        <x:v>21.225</x:v>
+        <x:v>22.53</x:v>
       </x:c>
       <x:c r="D44" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E44" s="11" t="n">
-        <x:v>-7.05</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F44" s="11" t="n">
         <x:f>SQRT((C44-C43)^2+(D44-D43)^2+(E44-E43)^2)</x:f>
-        <x:v>1.3049999999999997</x:v>
+        <x:v>1.0359999999999996</x:v>
       </x:c>
       <x:c r="G44" s="8" t="str">
         <x:v>Current</x:v>
@@ -6811,20 +6811,20 @@
         <x:v>drop:FC1:F1:fan:-1:F232</x:v>
       </x:c>
       <x:c r="B45" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C45" s="11" t="n">
         <x:v>21.225</x:v>
       </x:c>
       <x:c r="D45" s="11" t="n">
-        <x:v>8.988413043478262</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E45" s="11" t="n">
-        <x:v>-4.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F45" s="11" t="n">
         <x:f>SQRT((C45-C44)^2+(D45-D44)^2+(E45-E44)^2)</x:f>
-        <x:v>3.2744476301351852</x:v>
+        <x:v>1.3049999999999997</x:v>
       </x:c>
       <x:c r="G45" s="8" t="str">
         <x:v>Current</x:v>
@@ -6835,20 +6835,20 @@
         <x:v>drop:FC1:F1:fan:-1:F232</x:v>
       </x:c>
       <x:c r="B46" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C46" s="11" t="n">
         <x:v>21.225</x:v>
       </x:c>
       <x:c r="D46" s="11" t="n">
-        <x:v>9.028413043478261</x:v>
+        <x:v>9.18841304347826</x:v>
       </x:c>
       <x:c r="E46" s="11" t="n">
         <x:v>-4.4</x:v>
       </x:c>
       <x:c r="F46" s="11" t="n">
         <x:f>SQRT((C46-C45)^2+(D46-D45)^2+(E46-E45)^2)</x:f>
-        <x:v>0.03999999999999915</x:v>
+        <x:v>3.6574962208302444</x:v>
       </x:c>
       <x:c r="G46" s="8" t="str">
         <x:v>Current</x:v>
@@ -6859,20 +6859,20 @@
         <x:v>drop:FC1:F1:fan:-1:F232</x:v>
       </x:c>
       <x:c r="B47" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C47" s="11" t="n">
         <x:v>21.225</x:v>
       </x:c>
       <x:c r="D47" s="11" t="n">
-        <x:v>3.9</x:v>
+        <x:v>9.028413043478261</x:v>
       </x:c>
       <x:c r="E47" s="11" t="n">
         <x:v>-4.4</x:v>
       </x:c>
       <x:c r="F47" s="11" t="n">
         <x:f>SQRT((C47-C46)^2+(D47-D46)^2+(E47-E46)^2)</x:f>
-        <x:v>5.128413043478261</x:v>
+        <x:v>0.15999999999999837</x:v>
       </x:c>
       <x:c r="G47" s="8" t="str">
         <x:v>Current</x:v>
@@ -6880,23 +6880,23 @@
     </x:row>
     <x:row r="48" ht="32" customHeight="1">
       <x:c r="A48" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F234</x:v>
+        <x:v>drop:FC1:F1:fan:-1:F232</x:v>
       </x:c>
       <x:c r="B48" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C48" s="11" t="n">
-        <x:v>27.03</x:v>
+        <x:v>21.225</x:v>
       </x:c>
       <x:c r="D48" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>3.9</x:v>
       </x:c>
       <x:c r="E48" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-4.4</x:v>
       </x:c>
       <x:c r="F48" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C48-C47)^2+(D48-D47)^2+(E48-E47)^2)</x:f>
+        <x:v>5.128413043478261</x:v>
       </x:c>
       <x:c r="G48" s="8" t="str">
         <x:v>Current</x:v>
@@ -6907,20 +6907,20 @@
         <x:v>drop:FC1:F1:fan:-1:F234</x:v>
       </x:c>
       <x:c r="B49" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C49" s="11" t="n">
         <x:v>27.03</x:v>
       </x:c>
       <x:c r="D49" s="11" t="n">
-        <x:v>7.02</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E49" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F49" s="11" t="n">
-        <x:f>SQRT((C49-C48)^2+(D49-D48)^2+(E49-E48)^2)</x:f>
-        <x:v>0.48799999999999955</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G49" s="8" t="str">
         <x:v>Current</x:v>
@@ -6931,20 +6931,20 @@
         <x:v>drop:FC1:F1:fan:-1:F234</x:v>
       </x:c>
       <x:c r="B50" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C50" s="11" t="n">
         <x:v>27.03</x:v>
       </x:c>
       <x:c r="D50" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E50" s="11" t="n">
-        <x:v>-7.05</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F50" s="11" t="n">
         <x:f>SQRT((C50-C49)^2+(D50-D49)^2+(E50-E49)^2)</x:f>
-        <x:v>0.3132494925336704</x:v>
+        <x:v>1.0359999999999996</x:v>
       </x:c>
       <x:c r="G50" s="8" t="str">
         <x:v>Current</x:v>
@@ -6955,16 +6955,16 @@
         <x:v>drop:FC1:F1:fan:-1:F234</x:v>
       </x:c>
       <x:c r="B51" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C51" s="11" t="n">
         <x:v>25.725</x:v>
       </x:c>
       <x:c r="D51" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E51" s="11" t="n">
-        <x:v>-7.05</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F51" s="11" t="n">
         <x:f>SQRT((C51-C50)^2+(D51-D50)^2+(E51-E50)^2)</x:f>
@@ -6979,20 +6979,20 @@
         <x:v>drop:FC1:F1:fan:-1:F234</x:v>
       </x:c>
       <x:c r="B52" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C52" s="11" t="n">
         <x:v>25.725</x:v>
       </x:c>
       <x:c r="D52" s="11" t="n">
-        <x:v>8.988413043478262</x:v>
+        <x:v>9.18841304347826</x:v>
       </x:c>
       <x:c r="E52" s="11" t="n">
         <x:v>-4.4</x:v>
       </x:c>
       <x:c r="F52" s="11" t="n">
         <x:f>SQRT((C52-C51)^2+(D52-D51)^2+(E52-E51)^2)</x:f>
-        <x:v>3.2744476301351852</x:v>
+        <x:v>3.6574962208302444</x:v>
       </x:c>
       <x:c r="G52" s="8" t="str">
         <x:v>Current</x:v>
@@ -7003,7 +7003,7 @@
         <x:v>drop:FC1:F1:fan:-1:F234</x:v>
       </x:c>
       <x:c r="B53" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C53" s="11" t="n">
         <x:v>25.725</x:v>
@@ -7016,7 +7016,7 @@
       </x:c>
       <x:c r="F53" s="11" t="n">
         <x:f>SQRT((C53-C52)^2+(D53-D52)^2+(E53-E52)^2)</x:f>
-        <x:v>0.03999999999999915</x:v>
+        <x:v>0.15999999999999837</x:v>
       </x:c>
       <x:c r="G53" s="8" t="str">
         <x:v>Current</x:v>
@@ -7027,7 +7027,7 @@
         <x:v>drop:FC1:F1:fan:-1:F234</x:v>
       </x:c>
       <x:c r="B54" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C54" s="11" t="n">
         <x:v>25.725</x:v>
@@ -7057,7 +7057,7 @@
         <x:v>31.53</x:v>
       </x:c>
       <x:c r="D55" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E55" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -7081,14 +7081,14 @@
         <x:v>31.53</x:v>
       </x:c>
       <x:c r="D56" s="11" t="n">
-        <x:v>7.02</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E56" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F56" s="11" t="n">
         <x:f>SQRT((C56-C55)^2+(D56-D55)^2+(E56-E55)^2)</x:f>
-        <x:v>0.48799999999999955</x:v>
+        <x:v>1.0359999999999996</x:v>
       </x:c>
       <x:c r="G56" s="8" t="str">
         <x:v>Current</x:v>
@@ -7102,17 +7102,17 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C57" s="11" t="n">
-        <x:v>31.53</x:v>
+        <x:v>30.225</x:v>
       </x:c>
       <x:c r="D57" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E57" s="11" t="n">
-        <x:v>-7.05</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F57" s="11" t="n">
         <x:f>SQRT((C57-C56)^2+(D57-D56)^2+(E57-E56)^2)</x:f>
-        <x:v>0.3132494925336704</x:v>
+        <x:v>1.3049999999999997</x:v>
       </x:c>
       <x:c r="G57" s="8" t="str">
         <x:v>Current</x:v>
@@ -7129,14 +7129,14 @@
         <x:v>30.225</x:v>
       </x:c>
       <x:c r="D58" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>9.18841304347826</x:v>
       </x:c>
       <x:c r="E58" s="11" t="n">
-        <x:v>-7.05</x:v>
+        <x:v>-4.4</x:v>
       </x:c>
       <x:c r="F58" s="11" t="n">
         <x:f>SQRT((C58-C57)^2+(D58-D57)^2+(E58-E57)^2)</x:f>
-        <x:v>1.3049999999999997</x:v>
+        <x:v>3.6574962208302444</x:v>
       </x:c>
       <x:c r="G58" s="8" t="str">
         <x:v>Current</x:v>
@@ -7153,14 +7153,14 @@
         <x:v>30.225</x:v>
       </x:c>
       <x:c r="D59" s="11" t="n">
-        <x:v>8.988413043478262</x:v>
+        <x:v>9.028413043478261</x:v>
       </x:c>
       <x:c r="E59" s="11" t="n">
         <x:v>-4.4</x:v>
       </x:c>
       <x:c r="F59" s="11" t="n">
         <x:f>SQRT((C59-C58)^2+(D59-D58)^2+(E59-E58)^2)</x:f>
-        <x:v>3.2744476301351852</x:v>
+        <x:v>0.15999999999999837</x:v>
       </x:c>
       <x:c r="G59" s="8" t="str">
         <x:v>Current</x:v>
@@ -7177,14 +7177,14 @@
         <x:v>30.225</x:v>
       </x:c>
       <x:c r="D60" s="11" t="n">
-        <x:v>9.028413043478261</x:v>
+        <x:v>3.9</x:v>
       </x:c>
       <x:c r="E60" s="11" t="n">
         <x:v>-4.4</x:v>
       </x:c>
       <x:c r="F60" s="11" t="n">
         <x:f>SQRT((C60-C59)^2+(D60-D59)^2+(E60-E59)^2)</x:f>
-        <x:v>0.03999999999999915</x:v>
+        <x:v>5.128413043478261</x:v>
       </x:c>
       <x:c r="G60" s="8" t="str">
         <x:v>Current</x:v>
@@ -7192,23 +7192,23 @@
     </x:row>
     <x:row r="61" ht="32" customHeight="1">
       <x:c r="A61" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F236</x:v>
+        <x:v>drop:FC1:F1:fan:-1:F238</x:v>
       </x:c>
       <x:c r="B61" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C61" s="11" t="n">
-        <x:v>30.225</x:v>
+        <x:v>36.02</x:v>
       </x:c>
       <x:c r="D61" s="11" t="n">
-        <x:v>3.9</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E61" s="11" t="n">
-        <x:v>-4.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F61" s="11" t="n">
-        <x:f>SQRT((C61-C60)^2+(D61-D60)^2+(E61-E60)^2)</x:f>
-        <x:v>5.128413043478261</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G61" s="8" t="str">
         <x:v>Current</x:v>
@@ -7219,20 +7219,20 @@
         <x:v>drop:FC1:F1:fan:-1:F238</x:v>
       </x:c>
       <x:c r="B62" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C62" s="11" t="n">
         <x:v>36.02</x:v>
       </x:c>
       <x:c r="D62" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E62" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F62" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C62-C61)^2+(D62-D61)^2+(E62-E61)^2)</x:f>
+        <x:v>1.0359999999999996</x:v>
       </x:c>
       <x:c r="G62" s="8" t="str">
         <x:v>Current</x:v>
@@ -7243,20 +7243,20 @@
         <x:v>drop:FC1:F1:fan:-1:F238</x:v>
       </x:c>
       <x:c r="B63" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C63" s="11" t="n">
-        <x:v>36.02</x:v>
+        <x:v>34.725</x:v>
       </x:c>
       <x:c r="D63" s="11" t="n">
-        <x:v>7.02</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E63" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F63" s="11" t="n">
         <x:f>SQRT((C63-C62)^2+(D63-D62)^2+(E63-E62)^2)</x:f>
-        <x:v>0.48799999999999955</x:v>
+        <x:v>1.2950000000000017</x:v>
       </x:c>
       <x:c r="G63" s="8" t="str">
         <x:v>Current</x:v>
@@ -7267,20 +7267,20 @@
         <x:v>drop:FC1:F1:fan:-1:F238</x:v>
       </x:c>
       <x:c r="B64" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C64" s="11" t="n">
-        <x:v>36.02</x:v>
+        <x:v>34.725</x:v>
       </x:c>
       <x:c r="D64" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>9.18841304347826</x:v>
       </x:c>
       <x:c r="E64" s="11" t="n">
-        <x:v>-7.05</x:v>
+        <x:v>-4.4</x:v>
       </x:c>
       <x:c r="F64" s="11" t="n">
         <x:f>SQRT((C64-C63)^2+(D64-D63)^2+(E64-E63)^2)</x:f>
-        <x:v>0.3132494925336704</x:v>
+        <x:v>3.6574962208302444</x:v>
       </x:c>
       <x:c r="G64" s="8" t="str">
         <x:v>Current</x:v>
@@ -7291,20 +7291,20 @@
         <x:v>drop:FC1:F1:fan:-1:F238</x:v>
       </x:c>
       <x:c r="B65" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C65" s="11" t="n">
         <x:v>34.725</x:v>
       </x:c>
       <x:c r="D65" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>9.028413043478261</x:v>
       </x:c>
       <x:c r="E65" s="11" t="n">
-        <x:v>-7.05</x:v>
+        <x:v>-4.4</x:v>
       </x:c>
       <x:c r="F65" s="11" t="n">
         <x:f>SQRT((C65-C64)^2+(D65-D64)^2+(E65-E64)^2)</x:f>
-        <x:v>1.2950000000000017</x:v>
+        <x:v>0.15999999999999837</x:v>
       </x:c>
       <x:c r="G65" s="8" t="str">
         <x:v>Current</x:v>
@@ -7315,20 +7315,20 @@
         <x:v>drop:FC1:F1:fan:-1:F238</x:v>
       </x:c>
       <x:c r="B66" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C66" s="11" t="n">
         <x:v>34.725</x:v>
       </x:c>
       <x:c r="D66" s="11" t="n">
-        <x:v>8.988413043478262</x:v>
+        <x:v>3.9</x:v>
       </x:c>
       <x:c r="E66" s="11" t="n">
         <x:v>-4.4</x:v>
       </x:c>
       <x:c r="F66" s="11" t="n">
         <x:f>SQRT((C66-C65)^2+(D66-D65)^2+(E66-E65)^2)</x:f>
-        <x:v>3.2744476301351852</x:v>
+        <x:v>5.128413043478261</x:v>
       </x:c>
       <x:c r="G66" s="8" t="str">
         <x:v>Current</x:v>
@@ -7336,23 +7336,23 @@
     </x:row>
     <x:row r="67" ht="32" customHeight="1">
       <x:c r="A67" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F238</x:v>
+        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
       </x:c>
       <x:c r="B67" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C67" s="11" t="n">
-        <x:v>34.725</x:v>
+        <x:v>39.3</x:v>
       </x:c>
       <x:c r="D67" s="11" t="n">
-        <x:v>9.028413043478261</x:v>
+        <x:v>8.24309922680412</x:v>
       </x:c>
       <x:c r="E67" s="11" t="n">
-        <x:v>-4.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F67" s="11" t="n">
-        <x:f>SQRT((C67-C66)^2+(D67-D66)^2+(E67-E66)^2)</x:f>
-        <x:v>0.03999999999999915</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G67" s="8" t="str">
         <x:v>Current</x:v>
@@ -7360,23 +7360,23 @@
     </x:row>
     <x:row r="68" ht="32" customHeight="1">
       <x:c r="A68" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F238</x:v>
+        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
       </x:c>
       <x:c r="B68" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C68" s="11" t="n">
-        <x:v>34.725</x:v>
+        <x:v>39.3</x:v>
       </x:c>
       <x:c r="D68" s="11" t="n">
-        <x:v>3.9</x:v>
+        <x:v>8.24309922680412</x:v>
       </x:c>
       <x:c r="E68" s="11" t="n">
-        <x:v>-4.4</x:v>
+        <x:v>-10.15</x:v>
       </x:c>
       <x:c r="F68" s="11" t="n">
         <x:f>SQRT((C68-C67)^2+(D68-D67)^2+(E68-E67)^2)</x:f>
-        <x:v>5.128413043478261</x:v>
+        <x:v>2.79</x:v>
       </x:c>
       <x:c r="G68" s="8" t="str">
         <x:v>Current</x:v>
@@ -7387,68 +7387,68 @@
         <x:v>drop:FC1:F1:fan:-1:F240</x:v>
       </x:c>
       <x:c r="B69" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C69" s="11" t="n">
         <x:v>39.3</x:v>
       </x:c>
       <x:c r="D69" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="E69" s="11" t="n">
-        <x:v>-13.24</x:v>
+        <x:v>-10.15</x:v>
       </x:c>
       <x:c r="F69" s="11" t="n">
+        <x:f>SQRT((C69-C68)^2+(D69-D68)^2+(E69-E68)^2)</x:f>
+        <x:v>4.94309922680412</x:v>
+      </x:c>
+      <x:c r="G69" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="32" customHeight="1">
+      <x:c r="A70" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+      </x:c>
+      <x:c r="B70" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C70" s="11" t="n">
+        <x:v>41.85</x:v>
+      </x:c>
+      <x:c r="D70" s="11" t="n">
+        <x:v>8.243099226804118</x:v>
+      </x:c>
+      <x:c r="E70" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F70" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G69" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" ht="32" customHeight="1">
-      <x:c r="A70" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
-      </x:c>
-      <x:c r="B70" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C70" s="11" t="n">
-        <x:v>39.3</x:v>
-      </x:c>
-      <x:c r="D70" s="11" t="n">
-        <x:v>6.532</x:v>
-      </x:c>
-      <x:c r="E70" s="11" t="n">
-        <x:v>-10.15</x:v>
-      </x:c>
-      <x:c r="F70" s="11" t="n">
-        <x:f>SQRT((C70-C69)^2+(D70-D69)^2+(E70-E69)^2)</x:f>
-        <x:v>3.09</x:v>
-      </x:c>
       <x:c r="G70" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="32" customHeight="1">
       <x:c r="A71" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
+        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
       </x:c>
       <x:c r="B71" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C71" s="11" t="n">
-        <x:v>39.3</x:v>
+        <x:v>41.85</x:v>
       </x:c>
       <x:c r="D71" s="11" t="n">
-        <x:v>8.398379999999996</x:v>
+        <x:v>8.243099226804125</x:v>
       </x:c>
       <x:c r="E71" s="11" t="n">
         <x:v>-10.15</x:v>
       </x:c>
       <x:c r="F71" s="11" t="n">
         <x:f>SQRT((C71-C70)^2+(D71-D70)^2+(E71-E70)^2)</x:f>
-        <x:v>1.866379999999996</x:v>
+        <x:v>2.79</x:v>
       </x:c>
       <x:c r="G71" s="8" t="str">
         <x:v>Current</x:v>
@@ -7456,13 +7456,13 @@
     </x:row>
     <x:row r="72" ht="32" customHeight="1">
       <x:c r="A72" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
+        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
       </x:c>
       <x:c r="B72" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C72" s="11" t="n">
-        <x:v>39.3</x:v>
+        <x:v>41.85</x:v>
       </x:c>
       <x:c r="D72" s="11" t="n">
         <x:v>3.3</x:v>
@@ -7472,7 +7472,7 @@
       </x:c>
       <x:c r="F72" s="11" t="n">
         <x:f>SQRT((C72-C71)^2+(D72-D71)^2+(E72-E71)^2)</x:f>
-        <x:v>5.098379999999996</x:v>
+        <x:v>4.943099226804125</x:v>
       </x:c>
       <x:c r="G72" s="8" t="str">
         <x:v>Current</x:v>
@@ -7480,19 +7480,19 @@
     </x:row>
     <x:row r="73" ht="32" customHeight="1">
       <x:c r="A73" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+        <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
       <x:c r="B73" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C73" s="11" t="n">
-        <x:v>41.85</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D73" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E73" s="11" t="n">
-        <x:v>-13.24</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F73" s="11" t="n">
         <x:f>0</x:f>
@@ -7504,23 +7504,23 @@
     </x:row>
     <x:row r="74" ht="32" customHeight="1">
       <x:c r="A74" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+        <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
       <x:c r="B74" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C74" s="11" t="n">
-        <x:v>41.85</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D74" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E74" s="11" t="n">
-        <x:v>-10.15</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F74" s="11" t="n">
         <x:f>SQRT((C74-C73)^2+(D74-D73)^2+(E74-E73)^2)</x:f>
-        <x:v>3.09</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G74" s="8" t="str">
         <x:v>Current</x:v>
@@ -7528,23 +7528,23 @@
     </x:row>
     <x:row r="75" ht="32" customHeight="1">
       <x:c r="A75" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+        <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
       <x:c r="B75" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C75" s="11" t="n">
-        <x:v>41.85</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D75" s="11" t="n">
-        <x:v>8.374770000000002</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E75" s="11" t="n">
-        <x:v>-10.15</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F75" s="11" t="n">
         <x:f>SQRT((C75-C74)^2+(D75-D74)^2+(E75-E74)^2)</x:f>
-        <x:v>1.8427700000000016</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="G75" s="8" t="str">
         <x:v>Current</x:v>
@@ -7552,23 +7552,23 @@
     </x:row>
     <x:row r="76" ht="32" customHeight="1">
       <x:c r="A76" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+        <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
       <x:c r="B76" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C76" s="11" t="n">
-        <x:v>41.85</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D76" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E76" s="11" t="n">
-        <x:v>-10.15</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F76" s="11" t="n">
         <x:f>SQRT((C76-C75)^2+(D76-D75)^2+(E76-E75)^2)</x:f>
-        <x:v>5.074770000000002</x:v>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="G76" s="8" t="str">
         <x:v>Current</x:v>
@@ -7579,20 +7579,20 @@
         <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
       <x:c r="B77" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C77" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D77" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E77" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F77" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C77-C76)^2+(D77-D76)^2+(E77-E76)^2)</x:f>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G77" s="8" t="str">
         <x:v>Current</x:v>
@@ -7603,20 +7603,20 @@
         <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
       <x:c r="B78" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C78" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D78" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E78" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F78" s="11" t="n">
         <x:f>SQRT((C78-C77)^2+(D78-D77)^2+(E78-E77)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G78" s="8" t="str">
         <x:v>Current</x:v>
@@ -7627,20 +7627,20 @@
         <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
       <x:c r="B79" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C79" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D79" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E79" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F79" s="11" t="n">
         <x:f>SQRT((C79-C78)^2+(D79-D78)^2+(E79-E78)^2)</x:f>
-        <x:v>2.64</x:v>
+        <x:v>1.6740000000000004</x:v>
       </x:c>
       <x:c r="G79" s="8" t="str">
         <x:v>Current</x:v>
@@ -7651,20 +7651,20 @@
         <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
       <x:c r="B80" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C80" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D80" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E80" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F80" s="11" t="n">
         <x:f>SQRT((C80-C79)^2+(D80-D79)^2+(E80-E79)^2)</x:f>
-        <x:v>2.0699999999999994</x:v>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G80" s="8" t="str">
         <x:v>Current</x:v>
@@ -7675,20 +7675,20 @@
         <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
       <x:c r="B81" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C81" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D81" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E81" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F81" s="11" t="n">
         <x:f>SQRT((C81-C80)^2+(D81-D80)^2+(E81-E80)^2)</x:f>
-        <x:v>1.3599999999999999</x:v>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G81" s="8" t="str">
         <x:v>Current</x:v>
@@ -7699,20 +7699,20 @@
         <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
       <x:c r="B82" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C82" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D82" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E82" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F82" s="11" t="n">
         <x:f>SQRT((C82-C81)^2+(D82-D81)^2+(E82-E81)^2)</x:f>
-        <x:v>4.314999999999998</x:v>
+        <x:v>1.0359999999999996</x:v>
       </x:c>
       <x:c r="G82" s="8" t="str">
         <x:v>Current</x:v>
@@ -7723,20 +7723,20 @@
         <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
       <x:c r="B83" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C83" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D83" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E83" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F83" s="11" t="n">
         <x:f>SQRT((C83-C82)^2+(D83-D82)^2+(E83-E82)^2)</x:f>
-        <x:v>2.5120000000000005</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G83" s="8" t="str">
         <x:v>Current</x:v>
@@ -7747,20 +7747,20 @@
         <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
       <x:c r="B84" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C84" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D84" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E84" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F84" s="11" t="n">
         <x:f>SQRT((C84-C83)^2+(D84-D83)^2+(E84-E83)^2)</x:f>
-        <x:v>10.96</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G84" s="8" t="str">
         <x:v>Current</x:v>
@@ -7771,20 +7771,20 @@
         <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
       <x:c r="B85" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C85" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D85" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E85" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F85" s="11" t="n">
         <x:f>SQRT((C85-C84)^2+(D85-D84)^2+(E85-E84)^2)</x:f>
-        <x:v>8.875</x:v>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G85" s="8" t="str">
         <x:v>Current</x:v>
@@ -7795,20 +7795,20 @@
         <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
       <x:c r="B86" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C86" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>37.695</x:v>
       </x:c>
       <x:c r="D86" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>6.950412371134018</x:v>
       </x:c>
       <x:c r="E86" s="11" t="n">
-        <x:v>13.24</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F86" s="11" t="n">
         <x:f>SQRT((C86-C85)^2+(D86-D85)^2+(E86-E85)^2)</x:f>
-        <x:v>5.88</x:v>
+        <x:v>3.697957107375376</x:v>
       </x:c>
       <x:c r="G86" s="8" t="str">
         <x:v>Current</x:v>
@@ -7819,20 +7819,20 @@
         <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
       <x:c r="B87" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C87" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>37.615</x:v>
       </x:c>
       <x:c r="D87" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E87" s="11" t="n">
-        <x:v>13.24</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F87" s="11" t="n">
         <x:f>SQRT((C87-C86)^2+(D87-D86)^2+(E87-E86)^2)</x:f>
-        <x:v>7.199999999999996</x:v>
+        <x:v>0.12010804821421713</x:v>
       </x:c>
       <x:c r="G87" s="8" t="str">
         <x:v>Current</x:v>
@@ -7843,20 +7843,20 @@
         <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
       <x:c r="B88" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C88" s="11" t="n">
         <x:v>36.975</x:v>
       </x:c>
       <x:c r="D88" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E88" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F88" s="11" t="n">
         <x:f>SQRT((C88-C87)^2+(D88-D87)^2+(E88-E87)^2)</x:f>
-        <x:v>5.88</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G88" s="8" t="str">
         <x:v>Current</x:v>
@@ -7867,20 +7867,20 @@
         <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
       <x:c r="B89" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C89" s="11" t="n">
-        <x:v>9.03</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D89" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E89" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F89" s="11" t="n">
         <x:f>SQRT((C89-C88)^2+(D89-D88)^2+(E89-E88)^2)</x:f>
-        <x:v>27.945</x:v>
+        <x:v>1.0359999999999996</x:v>
       </x:c>
       <x:c r="G89" s="8" t="str">
         <x:v>Current</x:v>
@@ -7888,23 +7888,23 @@
     </x:row>
     <x:row r="90" ht="32" customHeight="1">
       <x:c r="A90" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F227</x:v>
+        <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
       <x:c r="B90" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C90" s="11" t="n">
-        <x:v>9.03</x:v>
+        <x:v>9.030000000000001</x:v>
       </x:c>
       <x:c r="D90" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E90" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F90" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C90-C89)^2+(D90-D89)^2+(E90-E89)^2)</x:f>
+        <x:v>27.945</x:v>
       </x:c>
       <x:c r="G90" s="8" t="str">
         <x:v>Current</x:v>
@@ -7915,20 +7915,20 @@
         <x:v>drop:FC1:F1:fan:1:F227</x:v>
       </x:c>
       <x:c r="B91" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C91" s="11" t="n">
-        <x:v>9.03</x:v>
+        <x:v>9.030000000000001</x:v>
       </x:c>
       <x:c r="D91" s="11" t="n">
-        <x:v>7.02</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E91" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F91" s="11" t="n">
-        <x:f>SQRT((C91-C90)^2+(D91-D90)^2+(E91-E90)^2)</x:f>
-        <x:v>0.48799999999999955</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G91" s="8" t="str">
         <x:v>Current</x:v>
@@ -7939,20 +7939,20 @@
         <x:v>drop:FC1:F1:fan:1:F227</x:v>
       </x:c>
       <x:c r="B92" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C92" s="11" t="n">
-        <x:v>9.03</x:v>
+        <x:v>9.030000000000001</x:v>
       </x:c>
       <x:c r="D92" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E92" s="11" t="n">
-        <x:v>7.05</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F92" s="11" t="n">
         <x:f>SQRT((C92-C91)^2+(D92-D91)^2+(E92-E91)^2)</x:f>
-        <x:v>0.3132494925336704</x:v>
+        <x:v>1.0359999999999996</x:v>
       </x:c>
       <x:c r="G92" s="8" t="str">
         <x:v>Current</x:v>
@@ -7963,20 +7963,20 @@
         <x:v>drop:FC1:F1:fan:1:F227</x:v>
       </x:c>
       <x:c r="B93" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C93" s="11" t="n">
         <x:v>7.725</x:v>
       </x:c>
       <x:c r="D93" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E93" s="11" t="n">
-        <x:v>7.05</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F93" s="11" t="n">
         <x:f>SQRT((C93-C92)^2+(D93-D92)^2+(E93-E92)^2)</x:f>
-        <x:v>1.3049999999999997</x:v>
+        <x:v>1.3050000000000015</x:v>
       </x:c>
       <x:c r="G93" s="8" t="str">
         <x:v>Current</x:v>
@@ -7987,20 +7987,20 @@
         <x:v>drop:FC1:F1:fan:1:F227</x:v>
       </x:c>
       <x:c r="B94" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C94" s="11" t="n">
         <x:v>7.725</x:v>
       </x:c>
       <x:c r="D94" s="11" t="n">
-        <x:v>8.988413043478262</x:v>
+        <x:v>9.18841304347826</x:v>
       </x:c>
       <x:c r="E94" s="11" t="n">
         <x:v>4.4</x:v>
       </x:c>
       <x:c r="F94" s="11" t="n">
         <x:f>SQRT((C94-C93)^2+(D94-D93)^2+(E94-E93)^2)</x:f>
-        <x:v>3.2744476301351852</x:v>
+        <x:v>3.6574962208302444</x:v>
       </x:c>
       <x:c r="G94" s="8" t="str">
         <x:v>Current</x:v>
@@ -8011,7 +8011,7 @@
         <x:v>drop:FC1:F1:fan:1:F227</x:v>
       </x:c>
       <x:c r="B95" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C95" s="11" t="n">
         <x:v>7.725</x:v>
@@ -8024,7 +8024,7 @@
       </x:c>
       <x:c r="F95" s="11" t="n">
         <x:f>SQRT((C95-C94)^2+(D95-D94)^2+(E95-E94)^2)</x:f>
-        <x:v>0.03999999999999915</x:v>
+        <x:v>0.15999999999999837</x:v>
       </x:c>
       <x:c r="G95" s="8" t="str">
         <x:v>Current</x:v>
@@ -8035,7 +8035,7 @@
         <x:v>drop:FC1:F1:fan:1:F227</x:v>
       </x:c>
       <x:c r="B96" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C96" s="11" t="n">
         <x:v>7.725</x:v>
@@ -8062,10 +8062,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C97" s="11" t="n">
-        <x:v>13.53</x:v>
+        <x:v>13.530000000000001</x:v>
       </x:c>
       <x:c r="D97" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E97" s="11" t="n">
         <x:v>7.36</x:v>
@@ -8086,17 +8086,17 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C98" s="11" t="n">
-        <x:v>13.53</x:v>
+        <x:v>13.530000000000001</x:v>
       </x:c>
       <x:c r="D98" s="11" t="n">
-        <x:v>7.02</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E98" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F98" s="11" t="n">
         <x:f>SQRT((C98-C97)^2+(D98-D97)^2+(E98-E97)^2)</x:f>
-        <x:v>0.48799999999999955</x:v>
+        <x:v>1.0359999999999996</x:v>
       </x:c>
       <x:c r="G98" s="8" t="str">
         <x:v>Current</x:v>
@@ -8110,17 +8110,17 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C99" s="11" t="n">
-        <x:v>13.53</x:v>
+        <x:v>12.225</x:v>
       </x:c>
       <x:c r="D99" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E99" s="11" t="n">
-        <x:v>7.05</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F99" s="11" t="n">
         <x:f>SQRT((C99-C98)^2+(D99-D98)^2+(E99-E98)^2)</x:f>
-        <x:v>0.3132494925336704</x:v>
+        <x:v>1.3050000000000015</x:v>
       </x:c>
       <x:c r="G99" s="8" t="str">
         <x:v>Current</x:v>
@@ -8137,14 +8137,14 @@
         <x:v>12.225</x:v>
       </x:c>
       <x:c r="D100" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>9.18841304347826</x:v>
       </x:c>
       <x:c r="E100" s="11" t="n">
-        <x:v>7.05</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="F100" s="11" t="n">
         <x:f>SQRT((C100-C99)^2+(D100-D99)^2+(E100-E99)^2)</x:f>
-        <x:v>1.3049999999999997</x:v>
+        <x:v>3.6574962208302444</x:v>
       </x:c>
       <x:c r="G100" s="8" t="str">
         <x:v>Current</x:v>
@@ -8161,14 +8161,14 @@
         <x:v>12.225</x:v>
       </x:c>
       <x:c r="D101" s="11" t="n">
-        <x:v>8.988413043478262</x:v>
+        <x:v>9.028413043478261</x:v>
       </x:c>
       <x:c r="E101" s="11" t="n">
         <x:v>4.4</x:v>
       </x:c>
       <x:c r="F101" s="11" t="n">
         <x:f>SQRT((C101-C100)^2+(D101-D100)^2+(E101-E100)^2)</x:f>
-        <x:v>3.2744476301351852</x:v>
+        <x:v>0.15999999999999837</x:v>
       </x:c>
       <x:c r="G101" s="8" t="str">
         <x:v>Current</x:v>
@@ -8185,14 +8185,14 @@
         <x:v>12.225</x:v>
       </x:c>
       <x:c r="D102" s="11" t="n">
-        <x:v>9.028413043478261</x:v>
+        <x:v>3.9</x:v>
       </x:c>
       <x:c r="E102" s="11" t="n">
         <x:v>4.4</x:v>
       </x:c>
       <x:c r="F102" s="11" t="n">
         <x:f>SQRT((C102-C101)^2+(D102-D101)^2+(E102-E101)^2)</x:f>
-        <x:v>0.03999999999999915</x:v>
+        <x:v>5.128413043478261</x:v>
       </x:c>
       <x:c r="G102" s="8" t="str">
         <x:v>Current</x:v>
@@ -8200,23 +8200,23 @@
     </x:row>
     <x:row r="103" ht="32" customHeight="1">
       <x:c r="A103" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F229</x:v>
+        <x:v>drop:FC1:F1:fan:1:F231</x:v>
       </x:c>
       <x:c r="B103" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C103" s="11" t="n">
-        <x:v>12.225</x:v>
+        <x:v>18.02</x:v>
       </x:c>
       <x:c r="D103" s="11" t="n">
-        <x:v>3.9</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E103" s="11" t="n">
-        <x:v>4.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F103" s="11" t="n">
-        <x:f>SQRT((C103-C102)^2+(D103-D102)^2+(E103-E102)^2)</x:f>
-        <x:v>5.128413043478261</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G103" s="8" t="str">
         <x:v>Current</x:v>
@@ -8227,20 +8227,20 @@
         <x:v>drop:FC1:F1:fan:1:F231</x:v>
       </x:c>
       <x:c r="B104" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C104" s="11" t="n">
         <x:v>18.02</x:v>
       </x:c>
       <x:c r="D104" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E104" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F104" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C104-C103)^2+(D104-D103)^2+(E104-E103)^2)</x:f>
+        <x:v>1.0359999999999996</x:v>
       </x:c>
       <x:c r="G104" s="8" t="str">
         <x:v>Current</x:v>
@@ -8251,20 +8251,20 @@
         <x:v>drop:FC1:F1:fan:1:F231</x:v>
       </x:c>
       <x:c r="B105" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C105" s="11" t="n">
-        <x:v>18.02</x:v>
+        <x:v>16.725</x:v>
       </x:c>
       <x:c r="D105" s="11" t="n">
-        <x:v>7.02</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E105" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F105" s="11" t="n">
         <x:f>SQRT((C105-C104)^2+(D105-D104)^2+(E105-E104)^2)</x:f>
-        <x:v>0.48799999999999955</x:v>
+        <x:v>1.2949999999999982</x:v>
       </x:c>
       <x:c r="G105" s="8" t="str">
         <x:v>Current</x:v>
@@ -8275,20 +8275,20 @@
         <x:v>drop:FC1:F1:fan:1:F231</x:v>
       </x:c>
       <x:c r="B106" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C106" s="11" t="n">
-        <x:v>18.02</x:v>
+        <x:v>16.725</x:v>
       </x:c>
       <x:c r="D106" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>9.18841304347826</x:v>
       </x:c>
       <x:c r="E106" s="11" t="n">
-        <x:v>7.05</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="F106" s="11" t="n">
         <x:f>SQRT((C106-C105)^2+(D106-D105)^2+(E106-E105)^2)</x:f>
-        <x:v>0.3132494925336704</x:v>
+        <x:v>3.6574962208302444</x:v>
       </x:c>
       <x:c r="G106" s="8" t="str">
         <x:v>Current</x:v>
@@ -8299,20 +8299,20 @@
         <x:v>drop:FC1:F1:fan:1:F231</x:v>
       </x:c>
       <x:c r="B107" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C107" s="11" t="n">
         <x:v>16.725</x:v>
       </x:c>
       <x:c r="D107" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>9.028413043478261</x:v>
       </x:c>
       <x:c r="E107" s="11" t="n">
-        <x:v>7.05</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="F107" s="11" t="n">
         <x:f>SQRT((C107-C106)^2+(D107-D106)^2+(E107-E106)^2)</x:f>
-        <x:v>1.2949999999999982</x:v>
+        <x:v>0.15999999999999837</x:v>
       </x:c>
       <x:c r="G107" s="8" t="str">
         <x:v>Current</x:v>
@@ -8323,20 +8323,20 @@
         <x:v>drop:FC1:F1:fan:1:F231</x:v>
       </x:c>
       <x:c r="B108" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C108" s="11" t="n">
         <x:v>16.725</x:v>
       </x:c>
       <x:c r="D108" s="11" t="n">
-        <x:v>8.988413043478262</x:v>
+        <x:v>3.9</x:v>
       </x:c>
       <x:c r="E108" s="11" t="n">
         <x:v>4.4</x:v>
       </x:c>
       <x:c r="F108" s="11" t="n">
         <x:f>SQRT((C108-C107)^2+(D108-D107)^2+(E108-E107)^2)</x:f>
-        <x:v>3.2744476301351852</x:v>
+        <x:v>5.128413043478261</x:v>
       </x:c>
       <x:c r="G108" s="8" t="str">
         <x:v>Current</x:v>
@@ -8344,23 +8344,23 @@
     </x:row>
     <x:row r="109" ht="32" customHeight="1">
       <x:c r="A109" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F231</x:v>
+        <x:v>drop:FC1:F1:fan:1:F233</x:v>
       </x:c>
       <x:c r="B109" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C109" s="11" t="n">
-        <x:v>16.725</x:v>
+        <x:v>22.53</x:v>
       </x:c>
       <x:c r="D109" s="11" t="n">
-        <x:v>9.028413043478261</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E109" s="11" t="n">
-        <x:v>4.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F109" s="11" t="n">
-        <x:f>SQRT((C109-C108)^2+(D109-D108)^2+(E109-E108)^2)</x:f>
-        <x:v>0.03999999999999915</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G109" s="8" t="str">
         <x:v>Current</x:v>
@@ -8368,23 +8368,23 @@
     </x:row>
     <x:row r="110" ht="32" customHeight="1">
       <x:c r="A110" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F231</x:v>
+        <x:v>drop:FC1:F1:fan:1:F233</x:v>
       </x:c>
       <x:c r="B110" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C110" s="11" t="n">
-        <x:v>16.725</x:v>
+        <x:v>22.53</x:v>
       </x:c>
       <x:c r="D110" s="11" t="n">
-        <x:v>3.9</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E110" s="11" t="n">
-        <x:v>4.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F110" s="11" t="n">
         <x:f>SQRT((C110-C109)^2+(D110-D109)^2+(E110-E109)^2)</x:f>
-        <x:v>5.128413043478261</x:v>
+        <x:v>1.0359999999999996</x:v>
       </x:c>
       <x:c r="G110" s="8" t="str">
         <x:v>Current</x:v>
@@ -8395,20 +8395,20 @@
         <x:v>drop:FC1:F1:fan:1:F233</x:v>
       </x:c>
       <x:c r="B111" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C111" s="11" t="n">
-        <x:v>22.53</x:v>
+        <x:v>21.225</x:v>
       </x:c>
       <x:c r="D111" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E111" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F111" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C111-C110)^2+(D111-D110)^2+(E111-E110)^2)</x:f>
+        <x:v>1.3049999999999997</x:v>
       </x:c>
       <x:c r="G111" s="8" t="str">
         <x:v>Current</x:v>
@@ -8419,20 +8419,20 @@
         <x:v>drop:FC1:F1:fan:1:F233</x:v>
       </x:c>
       <x:c r="B112" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C112" s="11" t="n">
-        <x:v>22.53</x:v>
+        <x:v>21.225</x:v>
       </x:c>
       <x:c r="D112" s="11" t="n">
-        <x:v>7.02</x:v>
+        <x:v>9.18841304347826</x:v>
       </x:c>
       <x:c r="E112" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="F112" s="11" t="n">
         <x:f>SQRT((C112-C111)^2+(D112-D111)^2+(E112-E111)^2)</x:f>
-        <x:v>0.48799999999999955</x:v>
+        <x:v>3.6574962208302444</x:v>
       </x:c>
       <x:c r="G112" s="8" t="str">
         <x:v>Current</x:v>
@@ -8443,20 +8443,20 @@
         <x:v>drop:FC1:F1:fan:1:F233</x:v>
       </x:c>
       <x:c r="B113" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C113" s="11" t="n">
-        <x:v>22.53</x:v>
+        <x:v>21.225</x:v>
       </x:c>
       <x:c r="D113" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>9.028413043478261</x:v>
       </x:c>
       <x:c r="E113" s="11" t="n">
-        <x:v>7.05</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="F113" s="11" t="n">
         <x:f>SQRT((C113-C112)^2+(D113-D112)^2+(E113-E112)^2)</x:f>
-        <x:v>0.3132494925336704</x:v>
+        <x:v>0.15999999999999837</x:v>
       </x:c>
       <x:c r="G113" s="8" t="str">
         <x:v>Current</x:v>
@@ -8467,20 +8467,20 @@
         <x:v>drop:FC1:F1:fan:1:F233</x:v>
       </x:c>
       <x:c r="B114" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C114" s="11" t="n">
         <x:v>21.225</x:v>
       </x:c>
       <x:c r="D114" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>3.9</x:v>
       </x:c>
       <x:c r="E114" s="11" t="n">
-        <x:v>7.05</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="F114" s="11" t="n">
         <x:f>SQRT((C114-C113)^2+(D114-D113)^2+(E114-E113)^2)</x:f>
-        <x:v>1.3049999999999997</x:v>
+        <x:v>5.128413043478261</x:v>
       </x:c>
       <x:c r="G114" s="8" t="str">
         <x:v>Current</x:v>
@@ -8488,23 +8488,23 @@
     </x:row>
     <x:row r="115" ht="32" customHeight="1">
       <x:c r="A115" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F233</x:v>
+        <x:v>drop:FC1:F1:fan:1:F235</x:v>
       </x:c>
       <x:c r="B115" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C115" s="11" t="n">
-        <x:v>21.225</x:v>
+        <x:v>27.03</x:v>
       </x:c>
       <x:c r="D115" s="11" t="n">
-        <x:v>8.988413043478262</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E115" s="11" t="n">
-        <x:v>4.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F115" s="11" t="n">
-        <x:f>SQRT((C115-C114)^2+(D115-D114)^2+(E115-E114)^2)</x:f>
-        <x:v>3.2744476301351852</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G115" s="8" t="str">
         <x:v>Current</x:v>
@@ -8512,23 +8512,23 @@
     </x:row>
     <x:row r="116" ht="32" customHeight="1">
       <x:c r="A116" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F233</x:v>
+        <x:v>drop:FC1:F1:fan:1:F235</x:v>
       </x:c>
       <x:c r="B116" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C116" s="11" t="n">
-        <x:v>21.225</x:v>
+        <x:v>27.03</x:v>
       </x:c>
       <x:c r="D116" s="11" t="n">
-        <x:v>9.028413043478261</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E116" s="11" t="n">
-        <x:v>4.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F116" s="11" t="n">
         <x:f>SQRT((C116-C115)^2+(D116-D115)^2+(E116-E115)^2)</x:f>
-        <x:v>0.03999999999999915</x:v>
+        <x:v>1.0359999999999996</x:v>
       </x:c>
       <x:c r="G116" s="8" t="str">
         <x:v>Current</x:v>
@@ -8536,23 +8536,23 @@
     </x:row>
     <x:row r="117" ht="32" customHeight="1">
       <x:c r="A117" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F233</x:v>
+        <x:v>drop:FC1:F1:fan:1:F235</x:v>
       </x:c>
       <x:c r="B117" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C117" s="11" t="n">
-        <x:v>21.225</x:v>
+        <x:v>25.725</x:v>
       </x:c>
       <x:c r="D117" s="11" t="n">
-        <x:v>3.9</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E117" s="11" t="n">
-        <x:v>4.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F117" s="11" t="n">
         <x:f>SQRT((C117-C116)^2+(D117-D116)^2+(E117-E116)^2)</x:f>
-        <x:v>5.128413043478261</x:v>
+        <x:v>1.3049999999999997</x:v>
       </x:c>
       <x:c r="G117" s="8" t="str">
         <x:v>Current</x:v>
@@ -8563,20 +8563,20 @@
         <x:v>drop:FC1:F1:fan:1:F235</x:v>
       </x:c>
       <x:c r="B118" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C118" s="11" t="n">
-        <x:v>27.03</x:v>
+        <x:v>25.725</x:v>
       </x:c>
       <x:c r="D118" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>9.18841304347826</x:v>
       </x:c>
       <x:c r="E118" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="F118" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C118-C117)^2+(D118-D117)^2+(E118-E117)^2)</x:f>
+        <x:v>3.6574962208302444</x:v>
       </x:c>
       <x:c r="G118" s="8" t="str">
         <x:v>Current</x:v>
@@ -8587,20 +8587,20 @@
         <x:v>drop:FC1:F1:fan:1:F235</x:v>
       </x:c>
       <x:c r="B119" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C119" s="11" t="n">
-        <x:v>27.03</x:v>
+        <x:v>25.725</x:v>
       </x:c>
       <x:c r="D119" s="11" t="n">
-        <x:v>7.02</x:v>
+        <x:v>9.028413043478261</x:v>
       </x:c>
       <x:c r="E119" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="F119" s="11" t="n">
         <x:f>SQRT((C119-C118)^2+(D119-D118)^2+(E119-E118)^2)</x:f>
-        <x:v>0.48799999999999955</x:v>
+        <x:v>0.15999999999999837</x:v>
       </x:c>
       <x:c r="G119" s="8" t="str">
         <x:v>Current</x:v>
@@ -8611,20 +8611,20 @@
         <x:v>drop:FC1:F1:fan:1:F235</x:v>
       </x:c>
       <x:c r="B120" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C120" s="11" t="n">
-        <x:v>27.03</x:v>
+        <x:v>25.725</x:v>
       </x:c>
       <x:c r="D120" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>3.9</x:v>
       </x:c>
       <x:c r="E120" s="11" t="n">
-        <x:v>7.05</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="F120" s="11" t="n">
         <x:f>SQRT((C120-C119)^2+(D120-D119)^2+(E120-E119)^2)</x:f>
-        <x:v>0.3132494925336704</x:v>
+        <x:v>5.128413043478261</x:v>
       </x:c>
       <x:c r="G120" s="8" t="str">
         <x:v>Current</x:v>
@@ -8632,23 +8632,23 @@
     </x:row>
     <x:row r="121" ht="32" customHeight="1">
       <x:c r="A121" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F235</x:v>
+        <x:v>drop:FC1:F1:fan:1:F237</x:v>
       </x:c>
       <x:c r="B121" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C121" s="11" t="n">
-        <x:v>25.725</x:v>
+        <x:v>31.53</x:v>
       </x:c>
       <x:c r="D121" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E121" s="11" t="n">
-        <x:v>7.05</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F121" s="11" t="n">
-        <x:f>SQRT((C121-C120)^2+(D121-D120)^2+(E121-E120)^2)</x:f>
-        <x:v>1.3049999999999997</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G121" s="8" t="str">
         <x:v>Current</x:v>
@@ -8656,23 +8656,23 @@
     </x:row>
     <x:row r="122" ht="32" customHeight="1">
       <x:c r="A122" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F235</x:v>
+        <x:v>drop:FC1:F1:fan:1:F237</x:v>
       </x:c>
       <x:c r="B122" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C122" s="11" t="n">
-        <x:v>25.725</x:v>
+        <x:v>31.53</x:v>
       </x:c>
       <x:c r="D122" s="11" t="n">
-        <x:v>8.988413043478262</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E122" s="11" t="n">
-        <x:v>4.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F122" s="11" t="n">
         <x:f>SQRT((C122-C121)^2+(D122-D121)^2+(E122-E121)^2)</x:f>
-        <x:v>3.2744476301351852</x:v>
+        <x:v>1.0359999999999996</x:v>
       </x:c>
       <x:c r="G122" s="8" t="str">
         <x:v>Current</x:v>
@@ -8680,23 +8680,23 @@
     </x:row>
     <x:row r="123" ht="32" customHeight="1">
       <x:c r="A123" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F235</x:v>
+        <x:v>drop:FC1:F1:fan:1:F237</x:v>
       </x:c>
       <x:c r="B123" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C123" s="11" t="n">
-        <x:v>25.725</x:v>
+        <x:v>30.225</x:v>
       </x:c>
       <x:c r="D123" s="11" t="n">
-        <x:v>9.028413043478261</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E123" s="11" t="n">
-        <x:v>4.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F123" s="11" t="n">
         <x:f>SQRT((C123-C122)^2+(D123-D122)^2+(E123-E122)^2)</x:f>
-        <x:v>0.03999999999999915</x:v>
+        <x:v>1.3049999999999997</x:v>
       </x:c>
       <x:c r="G123" s="8" t="str">
         <x:v>Current</x:v>
@@ -8704,23 +8704,23 @@
     </x:row>
     <x:row r="124" ht="32" customHeight="1">
       <x:c r="A124" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F235</x:v>
+        <x:v>drop:FC1:F1:fan:1:F237</x:v>
       </x:c>
       <x:c r="B124" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C124" s="11" t="n">
-        <x:v>25.725</x:v>
+        <x:v>30.225</x:v>
       </x:c>
       <x:c r="D124" s="11" t="n">
-        <x:v>3.9</x:v>
+        <x:v>9.18841304347826</x:v>
       </x:c>
       <x:c r="E124" s="11" t="n">
         <x:v>4.4</x:v>
       </x:c>
       <x:c r="F124" s="11" t="n">
         <x:f>SQRT((C124-C123)^2+(D124-D123)^2+(E124-E123)^2)</x:f>
-        <x:v>5.128413043478261</x:v>
+        <x:v>3.6574962208302444</x:v>
       </x:c>
       <x:c r="G124" s="8" t="str">
         <x:v>Current</x:v>
@@ -8731,20 +8731,20 @@
         <x:v>drop:FC1:F1:fan:1:F237</x:v>
       </x:c>
       <x:c r="B125" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C125" s="11" t="n">
-        <x:v>31.53</x:v>
+        <x:v>30.225</x:v>
       </x:c>
       <x:c r="D125" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>9.028413043478261</x:v>
       </x:c>
       <x:c r="E125" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="F125" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C125-C124)^2+(D125-D124)^2+(E125-E124)^2)</x:f>
+        <x:v>0.15999999999999837</x:v>
       </x:c>
       <x:c r="G125" s="8" t="str">
         <x:v>Current</x:v>
@@ -8755,20 +8755,20 @@
         <x:v>drop:FC1:F1:fan:1:F237</x:v>
       </x:c>
       <x:c r="B126" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C126" s="11" t="n">
-        <x:v>31.53</x:v>
+        <x:v>30.225</x:v>
       </x:c>
       <x:c r="D126" s="11" t="n">
-        <x:v>7.02</x:v>
+        <x:v>3.9</x:v>
       </x:c>
       <x:c r="E126" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="F126" s="11" t="n">
         <x:f>SQRT((C126-C125)^2+(D126-D125)^2+(E126-E125)^2)</x:f>
-        <x:v>0.48799999999999955</x:v>
+        <x:v>5.128413043478261</x:v>
       </x:c>
       <x:c r="G126" s="8" t="str">
         <x:v>Current</x:v>
@@ -8776,23 +8776,23 @@
     </x:row>
     <x:row r="127" ht="32" customHeight="1">
       <x:c r="A127" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F237</x:v>
+        <x:v>drop:FC1:F1:fan:1:F239</x:v>
       </x:c>
       <x:c r="B127" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C127" s="11" t="n">
-        <x:v>31.53</x:v>
+        <x:v>36.02</x:v>
       </x:c>
       <x:c r="D127" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>6.0040000000000004</x:v>
       </x:c>
       <x:c r="E127" s="11" t="n">
-        <x:v>7.05</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F127" s="11" t="n">
-        <x:f>SQRT((C127-C126)^2+(D127-D126)^2+(E127-E126)^2)</x:f>
-        <x:v>0.3132494925336704</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G127" s="8" t="str">
         <x:v>Current</x:v>
@@ -8800,23 +8800,23 @@
     </x:row>
     <x:row r="128" ht="32" customHeight="1">
       <x:c r="A128" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F237</x:v>
+        <x:v>drop:FC1:F1:fan:1:F239</x:v>
       </x:c>
       <x:c r="B128" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C128" s="11" t="n">
-        <x:v>30.225</x:v>
+        <x:v>36.02</x:v>
       </x:c>
       <x:c r="D128" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E128" s="11" t="n">
-        <x:v>7.05</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F128" s="11" t="n">
         <x:f>SQRT((C128-C127)^2+(D128-D127)^2+(E128-E127)^2)</x:f>
-        <x:v>1.3049999999999997</x:v>
+        <x:v>1.0359999999999996</x:v>
       </x:c>
       <x:c r="G128" s="8" t="str">
         <x:v>Current</x:v>
@@ -8824,23 +8824,23 @@
     </x:row>
     <x:row r="129" ht="32" customHeight="1">
       <x:c r="A129" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F237</x:v>
+        <x:v>drop:FC1:F1:fan:1:F239</x:v>
       </x:c>
       <x:c r="B129" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C129" s="11" t="n">
-        <x:v>30.225</x:v>
+        <x:v>34.725</x:v>
       </x:c>
       <x:c r="D129" s="11" t="n">
-        <x:v>8.988413043478262</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E129" s="11" t="n">
-        <x:v>4.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F129" s="11" t="n">
         <x:f>SQRT((C129-C128)^2+(D129-D128)^2+(E129-E128)^2)</x:f>
-        <x:v>3.2744476301351852</x:v>
+        <x:v>1.2950000000000017</x:v>
       </x:c>
       <x:c r="G129" s="8" t="str">
         <x:v>Current</x:v>
@@ -8848,23 +8848,23 @@
     </x:row>
     <x:row r="130" ht="32" customHeight="1">
       <x:c r="A130" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F237</x:v>
+        <x:v>drop:FC1:F1:fan:1:F239</x:v>
       </x:c>
       <x:c r="B130" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C130" s="11" t="n">
-        <x:v>30.225</x:v>
+        <x:v>34.725</x:v>
       </x:c>
       <x:c r="D130" s="11" t="n">
-        <x:v>9.028413043478261</x:v>
+        <x:v>9.18841304347826</x:v>
       </x:c>
       <x:c r="E130" s="11" t="n">
         <x:v>4.4</x:v>
       </x:c>
       <x:c r="F130" s="11" t="n">
         <x:f>SQRT((C130-C129)^2+(D130-D129)^2+(E130-E129)^2)</x:f>
-        <x:v>0.03999999999999915</x:v>
+        <x:v>3.6574962208302444</x:v>
       </x:c>
       <x:c r="G130" s="8" t="str">
         <x:v>Current</x:v>
@@ -8872,23 +8872,23 @@
     </x:row>
     <x:row r="131" ht="32" customHeight="1">
       <x:c r="A131" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F237</x:v>
+        <x:v>drop:FC1:F1:fan:1:F239</x:v>
       </x:c>
       <x:c r="B131" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C131" s="11" t="n">
-        <x:v>30.225</x:v>
+        <x:v>34.725</x:v>
       </x:c>
       <x:c r="D131" s="11" t="n">
-        <x:v>3.9</x:v>
+        <x:v>9.028413043478261</x:v>
       </x:c>
       <x:c r="E131" s="11" t="n">
         <x:v>4.4</x:v>
       </x:c>
       <x:c r="F131" s="11" t="n">
         <x:f>SQRT((C131-C130)^2+(D131-D130)^2+(E131-E130)^2)</x:f>
-        <x:v>5.128413043478261</x:v>
+        <x:v>0.15999999999999837</x:v>
       </x:c>
       <x:c r="G131" s="8" t="str">
         <x:v>Current</x:v>
@@ -8899,68 +8899,68 @@
         <x:v>drop:FC1:F1:fan:1:F239</x:v>
       </x:c>
       <x:c r="B132" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C132" s="11" t="n">
+        <x:v>34.725</x:v>
+      </x:c>
+      <x:c r="D132" s="11" t="n">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="E132" s="11" t="n">
+        <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="F132" s="11" t="n">
+        <x:f>SQRT((C132-C131)^2+(D132-D131)^2+(E132-E131)^2)</x:f>
+        <x:v>5.128413043478261</x:v>
+      </x:c>
+      <x:c r="G132" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="32" customHeight="1">
+      <x:c r="A133" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:1:F242</x:v>
+      </x:c>
+      <x:c r="B133" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C132" s="11" t="n">
-        <x:v>36.02</x:v>
-      </x:c>
-      <x:c r="D132" s="11" t="n">
-        <x:v>6.532</x:v>
-      </x:c>
-      <x:c r="E132" s="11" t="n">
+      <x:c r="C133" s="11" t="n">
+        <x:v>39.3</x:v>
+      </x:c>
+      <x:c r="D133" s="11" t="n">
+        <x:v>8.24309922680412</x:v>
+      </x:c>
+      <x:c r="E133" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
-      <x:c r="F132" s="11" t="n">
+      <x:c r="F133" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G132" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="133" ht="32" customHeight="1">
-      <x:c r="A133" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F239</x:v>
-      </x:c>
-      <x:c r="B133" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C133" s="11" t="n">
-        <x:v>36.02</x:v>
-      </x:c>
-      <x:c r="D133" s="11" t="n">
-        <x:v>7.02</x:v>
-      </x:c>
-      <x:c r="E133" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F133" s="11" t="n">
-        <x:f>SQRT((C133-C132)^2+(D133-D132)^2+(E133-E132)^2)</x:f>
-        <x:v>0.48799999999999955</x:v>
-      </x:c>
       <x:c r="G133" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="32" customHeight="1">
       <x:c r="A134" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F239</x:v>
+        <x:v>drop:FC1:F1:fan:1:F242</x:v>
       </x:c>
       <x:c r="B134" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C134" s="11" t="n">
-        <x:v>36.02</x:v>
+        <x:v>39.3</x:v>
       </x:c>
       <x:c r="D134" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>8.24309922680412</x:v>
       </x:c>
       <x:c r="E134" s="11" t="n">
-        <x:v>7.05</x:v>
+        <x:v>10.15</x:v>
       </x:c>
       <x:c r="F134" s="11" t="n">
         <x:f>SQRT((C134-C133)^2+(D134-D133)^2+(E134-E133)^2)</x:f>
-        <x:v>0.3132494925336704</x:v>
+        <x:v>2.79</x:v>
       </x:c>
       <x:c r="G134" s="8" t="str">
         <x:v>Current</x:v>
@@ -8968,23 +8968,23 @@
     </x:row>
     <x:row r="135" ht="32" customHeight="1">
       <x:c r="A135" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F239</x:v>
+        <x:v>drop:FC1:F1:fan:1:F242</x:v>
       </x:c>
       <x:c r="B135" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C135" s="11" t="n">
-        <x:v>34.725</x:v>
+        <x:v>39.3</x:v>
       </x:c>
       <x:c r="D135" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="E135" s="11" t="n">
-        <x:v>7.05</x:v>
+        <x:v>10.15</x:v>
       </x:c>
       <x:c r="F135" s="11" t="n">
         <x:f>SQRT((C135-C134)^2+(D135-D134)^2+(E135-E134)^2)</x:f>
-        <x:v>1.2950000000000017</x:v>
+        <x:v>4.94309922680412</x:v>
       </x:c>
       <x:c r="G135" s="8" t="str">
         <x:v>Current</x:v>
@@ -8992,23 +8992,23 @@
     </x:row>
     <x:row r="136" ht="32" customHeight="1">
       <x:c r="A136" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F239</x:v>
+        <x:v>drop:FC1:F1:fan:1:F243</x:v>
       </x:c>
       <x:c r="B136" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C136" s="11" t="n">
-        <x:v>34.725</x:v>
+        <x:v>41.85</x:v>
       </x:c>
       <x:c r="D136" s="11" t="n">
-        <x:v>8.988413043478262</x:v>
+        <x:v>8.243099226804118</x:v>
       </x:c>
       <x:c r="E136" s="11" t="n">
-        <x:v>4.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F136" s="11" t="n">
-        <x:f>SQRT((C136-C135)^2+(D136-D135)^2+(E136-E135)^2)</x:f>
-        <x:v>3.2744476301351852</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G136" s="8" t="str">
         <x:v>Current</x:v>
@@ -9016,23 +9016,23 @@
     </x:row>
     <x:row r="137" ht="32" customHeight="1">
       <x:c r="A137" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F239</x:v>
+        <x:v>drop:FC1:F1:fan:1:F243</x:v>
       </x:c>
       <x:c r="B137" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C137" s="11" t="n">
-        <x:v>34.725</x:v>
+        <x:v>41.85</x:v>
       </x:c>
       <x:c r="D137" s="11" t="n">
-        <x:v>9.028413043478261</x:v>
+        <x:v>8.243099226804125</x:v>
       </x:c>
       <x:c r="E137" s="11" t="n">
-        <x:v>4.4</x:v>
+        <x:v>10.15</x:v>
       </x:c>
       <x:c r="F137" s="11" t="n">
         <x:f>SQRT((C137-C136)^2+(D137-D136)^2+(E137-E136)^2)</x:f>
-        <x:v>0.03999999999999915</x:v>
+        <x:v>2.79</x:v>
       </x:c>
       <x:c r="G137" s="8" t="str">
         <x:v>Current</x:v>
@@ -9040,23 +9040,23 @@
     </x:row>
     <x:row r="138" ht="32" customHeight="1">
       <x:c r="A138" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F239</x:v>
+        <x:v>drop:FC1:F1:fan:1:F243</x:v>
       </x:c>
       <x:c r="B138" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C138" s="11" t="n">
-        <x:v>34.725</x:v>
+        <x:v>41.85</x:v>
       </x:c>
       <x:c r="D138" s="11" t="n">
-        <x:v>3.9</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="E138" s="11" t="n">
-        <x:v>4.4</x:v>
+        <x:v>10.15</x:v>
       </x:c>
       <x:c r="F138" s="11" t="n">
         <x:f>SQRT((C138-C137)^2+(D138-D137)^2+(E138-E137)^2)</x:f>
-        <x:v>5.128413043478261</x:v>
+        <x:v>4.943099226804125</x:v>
       </x:c>
       <x:c r="G138" s="8" t="str">
         <x:v>Current</x:v>
@@ -9064,19 +9064,19 @@
     </x:row>
     <x:row r="139" ht="32" customHeight="1">
       <x:c r="A139" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F242</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B139" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C139" s="11" t="n">
-        <x:v>39.3</x:v>
+        <x:v>2.73</x:v>
       </x:c>
       <x:c r="D139" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="E139" s="11" t="n">
-        <x:v>13.24</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F139" s="11" t="n">
         <x:f>0</x:f>
@@ -9088,23 +9088,23 @@
     </x:row>
     <x:row r="140" ht="32" customHeight="1">
       <x:c r="A140" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F242</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B140" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C140" s="11" t="n">
-        <x:v>39.3</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D140" s="11" t="n">
-        <x:v>6.532</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="E140" s="11" t="n">
-        <x:v>10.15</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F140" s="11" t="n">
         <x:f>SQRT((C140-C139)^2+(D140-D139)^2+(E140-E139)^2)</x:f>
-        <x:v>3.09</x:v>
+        <x:v>0.3799999999999999</x:v>
       </x:c>
       <x:c r="G140" s="8" t="str">
         <x:v>Current</x:v>
@@ -9112,23 +9112,23 @@
     </x:row>
     <x:row r="141" ht="32" customHeight="1">
       <x:c r="A141" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F242</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B141" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C141" s="11" t="n">
-        <x:v>39.3</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D141" s="11" t="n">
-        <x:v>8.398379999999996</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E141" s="11" t="n">
-        <x:v>10.15</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F141" s="11" t="n">
         <x:f>SQRT((C141-C140)^2+(D141-D140)^2+(E141-E140)^2)</x:f>
-        <x:v>1.866379999999996</x:v>
+        <x:v>6.15</x:v>
       </x:c>
       <x:c r="G141" s="8" t="str">
         <x:v>Current</x:v>
@@ -9136,23 +9136,23 @@
     </x:row>
     <x:row r="142" ht="32" customHeight="1">
       <x:c r="A142" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F242</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B142" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C142" s="11" t="n">
-        <x:v>39.3</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D142" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E142" s="11" t="n">
-        <x:v>10.15</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F142" s="11" t="n">
         <x:f>SQRT((C142-C141)^2+(D142-D141)^2+(E142-E141)^2)</x:f>
-        <x:v>5.098379999999996</x:v>
+        <x:v>4.0600000000000005</x:v>
       </x:c>
       <x:c r="G142" s="8" t="str">
         <x:v>Current</x:v>
@@ -9160,95 +9160,95 @@
     </x:row>
     <x:row r="143" ht="32" customHeight="1">
       <x:c r="A143" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F243</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B143" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C143" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D143" s="11" t="n">
+        <x:v>6.0280000000000005</x:v>
+      </x:c>
+      <x:c r="E143" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F143" s="11" t="n">
+        <x:f>SQRT((C143-C142)^2+(D143-D142)^2+(E143-E142)^2)</x:f>
+        <x:v>1.6219999999999999</x:v>
+      </x:c>
+      <x:c r="G143" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="32" customHeight="1">
+      <x:c r="A144" s="8" t="str">
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
+      </x:c>
+      <x:c r="B144" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C144" s="11" t="n">
+        <x:v>2.655</x:v>
+      </x:c>
+      <x:c r="D144" s="11" t="n">
+        <x:v>6.0280000000000005</x:v>
+      </x:c>
+      <x:c r="E144" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F144" s="11" t="n">
+        <x:f>SQRT((C144-C143)^2+(D144-D143)^2+(E144-E143)^2)</x:f>
+        <x:v>0.3049999999999997</x:v>
+      </x:c>
+      <x:c r="G144" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="32" customHeight="1">
+      <x:c r="A145" s="8" t="str">
+        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+      </x:c>
+      <x:c r="B145" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C143" s="11" t="n">
-        <x:v>41.85</x:v>
-      </x:c>
-      <x:c r="D143" s="11" t="n">
-        <x:v>6.532</x:v>
-      </x:c>
-      <x:c r="E143" s="11" t="n">
-        <x:v>13.24</x:v>
-      </x:c>
-      <x:c r="F143" s="11" t="n">
+      <x:c r="C145" s="11" t="n">
+        <x:v>2.655</x:v>
+      </x:c>
+      <x:c r="D145" s="11" t="n">
+        <x:v>6.0280000000000005</x:v>
+      </x:c>
+      <x:c r="E145" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F145" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G143" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="144" ht="32" customHeight="1">
-      <x:c r="A144" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F243</x:v>
-      </x:c>
-      <x:c r="B144" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C144" s="11" t="n">
-        <x:v>41.85</x:v>
-      </x:c>
-      <x:c r="D144" s="11" t="n">
-        <x:v>6.532</x:v>
-      </x:c>
-      <x:c r="E144" s="11" t="n">
-        <x:v>10.15</x:v>
-      </x:c>
-      <x:c r="F144" s="11" t="n">
-        <x:f>SQRT((C144-C143)^2+(D144-D143)^2+(E144-E143)^2)</x:f>
-        <x:v>3.09</x:v>
-      </x:c>
-      <x:c r="G144" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="145" ht="32" customHeight="1">
-      <x:c r="A145" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F243</x:v>
-      </x:c>
-      <x:c r="B145" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C145" s="11" t="n">
-        <x:v>41.85</x:v>
-      </x:c>
-      <x:c r="D145" s="11" t="n">
-        <x:v>8.374770000000002</x:v>
-      </x:c>
-      <x:c r="E145" s="11" t="n">
-        <x:v>10.15</x:v>
-      </x:c>
-      <x:c r="F145" s="11" t="n">
-        <x:f>SQRT((C145-C144)^2+(D145-D144)^2+(E145-E144)^2)</x:f>
-        <x:v>1.8427700000000016</x:v>
-      </x:c>
       <x:c r="G145" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="32" customHeight="1">
       <x:c r="A146" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F243</x:v>
+        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
       </x:c>
       <x:c r="B146" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C146" s="11" t="n">
-        <x:v>41.85</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D146" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E146" s="11" t="n">
-        <x:v>10.15</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F146" s="11" t="n">
         <x:f>SQRT((C146-C145)^2+(D146-D145)^2+(E146-E145)^2)</x:f>
-        <x:v>5.074770000000002</x:v>
+        <x:v>1.6504269144678898</x:v>
       </x:c>
       <x:c r="G146" s="8" t="str">
         <x:v>Current</x:v>
@@ -9256,119 +9256,119 @@
     </x:row>
     <x:row r="147" ht="32" customHeight="1">
       <x:c r="A147" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
+        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
       </x:c>
       <x:c r="B147" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C147" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D147" s="11" t="n">
+        <x:v>7.65</x:v>
+      </x:c>
+      <x:c r="E147" s="11" t="n">
+        <x:v>-3.05</x:v>
+      </x:c>
+      <x:c r="F147" s="11" t="n">
+        <x:f>SQRT((C147-C146)^2+(D147-D146)^2+(E147-E146)^2)</x:f>
+        <x:v>4.3100000000000005</x:v>
+      </x:c>
+      <x:c r="G147" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="32" customHeight="1">
+      <x:c r="A148" s="8" t="str">
+        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+      </x:c>
+      <x:c r="B148" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C148" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D148" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E148" s="11" t="n">
+        <x:v>-3.05</x:v>
+      </x:c>
+      <x:c r="F148" s="11" t="n">
+        <x:f>SQRT((C148-C147)^2+(D148-D147)^2+(E148-E147)^2)</x:f>
+        <x:v>1.6500000000000004</x:v>
+      </x:c>
+      <x:c r="G148" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="32" customHeight="1">
+      <x:c r="A149" s="8" t="str">
+        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+      </x:c>
+      <x:c r="B149" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C149" s="11" t="n">
+        <x:v>2.655</x:v>
+      </x:c>
+      <x:c r="D149" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E149" s="11" t="n">
+        <x:v>-3.05</x:v>
+      </x:c>
+      <x:c r="F149" s="11" t="n">
+        <x:f>SQRT((C149-C148)^2+(D149-D148)^2+(E149-E148)^2)</x:f>
+        <x:v>0.3049999999999997</x:v>
+      </x:c>
+      <x:c r="G149" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="32" customHeight="1">
+      <x:c r="A150" s="8" t="str">
+        <x:v>trunk:DB2:F4:fan:1</x:v>
+      </x:c>
+      <x:c r="B150" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C147" s="11" t="n">
+      <x:c r="C150" s="11" t="n">
         <x:v>2.73</x:v>
       </x:c>
-      <x:c r="D147" s="11" t="n">
+      <x:c r="D150" s="11" t="n">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="E147" s="11" t="n">
+      <x:c r="E150" s="11" t="n">
         <x:v>-3.3</x:v>
       </x:c>
-      <x:c r="F147" s="11" t="n">
+      <x:c r="F150" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G147" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="148" ht="32" customHeight="1">
-      <x:c r="A148" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
-      </x:c>
-      <x:c r="B148" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C148" s="11" t="n">
-        <x:v>2.35</x:v>
-      </x:c>
-      <x:c r="D148" s="11" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="E148" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F148" s="11" t="n">
-        <x:f>SQRT((C148-C147)^2+(D148-D147)^2+(E148-E147)^2)</x:f>
-        <x:v>0.3799999999999999</x:v>
-      </x:c>
-      <x:c r="G148" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="149" ht="32" customHeight="1">
-      <x:c r="A149" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
-      </x:c>
-      <x:c r="B149" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C149" s="11" t="n">
-        <x:v>2.35</x:v>
-      </x:c>
-      <x:c r="D149" s="11" t="n">
-        <x:v>7.65</x:v>
-      </x:c>
-      <x:c r="E149" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F149" s="11" t="n">
-        <x:f>SQRT((C149-C148)^2+(D149-D148)^2+(E149-E148)^2)</x:f>
-        <x:v>6.15</x:v>
-      </x:c>
-      <x:c r="G149" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="150" ht="32" customHeight="1">
-      <x:c r="A150" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
-      </x:c>
-      <x:c r="B150" s="8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C150" s="11" t="n">
-        <x:v>2.35</x:v>
-      </x:c>
-      <x:c r="D150" s="11" t="n">
-        <x:v>7.65</x:v>
-      </x:c>
-      <x:c r="E150" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F150" s="11" t="n">
-        <x:f>SQRT((C150-C149)^2+(D150-D149)^2+(E150-E149)^2)</x:f>
-        <x:v>4.0600000000000005</x:v>
-      </x:c>
       <x:c r="G150" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="32" customHeight="1">
       <x:c r="A151" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
+        <x:v>trunk:DB2:F4:fan:1</x:v>
       </x:c>
       <x:c r="B151" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C151" s="11" t="n">
         <x:v>2.35</x:v>
       </x:c>
       <x:c r="D151" s="11" t="n">
-        <x:v>6.574</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="E151" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F151" s="11" t="n">
         <x:f>SQRT((C151-C150)^2+(D151-D150)^2+(E151-E150)^2)</x:f>
-        <x:v>1.0760000000000005</x:v>
+        <x:v>0.3799999999999999</x:v>
       </x:c>
       <x:c r="G151" s="8" t="str">
         <x:v>Current</x:v>
@@ -9376,23 +9376,23 @@
     </x:row>
     <x:row r="152" ht="32" customHeight="1">
       <x:c r="A152" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
+        <x:v>trunk:DB2:F4:fan:1</x:v>
       </x:c>
       <x:c r="B152" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C152" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D152" s="11" t="n">
-        <x:v>6.574</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E152" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F152" s="11" t="n">
         <x:f>SQRT((C152-C151)^2+(D152-D151)^2+(E152-E151)^2)</x:f>
-        <x:v>0.3049999999999997</x:v>
+        <x:v>6.15</x:v>
       </x:c>
       <x:c r="G152" s="8" t="str">
         <x:v>Current</x:v>
@@ -9400,119 +9400,119 @@
     </x:row>
     <x:row r="153" ht="32" customHeight="1">
       <x:c r="A153" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+        <x:v>trunk:DB2:F4:fan:1</x:v>
       </x:c>
       <x:c r="B153" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C153" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D153" s="11" t="n">
+        <x:v>7.65</x:v>
+      </x:c>
+      <x:c r="E153" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F153" s="11" t="n">
+        <x:f>SQRT((C153-C152)^2+(D153-D152)^2+(E153-E152)^2)</x:f>
+        <x:v>10.66</x:v>
+      </x:c>
+      <x:c r="G153" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="32" customHeight="1">
+      <x:c r="A154" s="8" t="str">
+        <x:v>trunk:DB2:F4:fan:1</x:v>
+      </x:c>
+      <x:c r="B154" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C154" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D154" s="11" t="n">
+        <x:v>6.0280000000000005</x:v>
+      </x:c>
+      <x:c r="E154" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F154" s="11" t="n">
+        <x:f>SQRT((C154-C153)^2+(D154-D153)^2+(E154-E153)^2)</x:f>
+        <x:v>1.6219999999999999</x:v>
+      </x:c>
+      <x:c r="G154" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="32" customHeight="1">
+      <x:c r="A155" s="8" t="str">
+        <x:v>trunk:DB2:F4:fan:1</x:v>
+      </x:c>
+      <x:c r="B155" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C155" s="11" t="n">
+        <x:v>2.655</x:v>
+      </x:c>
+      <x:c r="D155" s="11" t="n">
+        <x:v>6.0280000000000005</x:v>
+      </x:c>
+      <x:c r="E155" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F155" s="11" t="n">
+        <x:f>SQRT((C155-C154)^2+(D155-D154)^2+(E155-E154)^2)</x:f>
+        <x:v>0.3049999999999997</x:v>
+      </x:c>
+      <x:c r="G155" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="32" customHeight="1">
+      <x:c r="A156" s="8" t="str">
+        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+      </x:c>
+      <x:c r="B156" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C153" s="11" t="n">
+      <x:c r="C156" s="11" t="n">
         <x:v>2.655</x:v>
       </x:c>
-      <x:c r="D153" s="11" t="n">
-        <x:v>6.574</x:v>
-      </x:c>
-      <x:c r="E153" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F153" s="11" t="n">
+      <x:c r="D156" s="11" t="n">
+        <x:v>6.0280000000000005</x:v>
+      </x:c>
+      <x:c r="E156" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F156" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G153" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="154" ht="32" customHeight="1">
-      <x:c r="A154" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
-      </x:c>
-      <x:c r="B154" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C154" s="11" t="n">
-        <x:v>2.35</x:v>
-      </x:c>
-      <x:c r="D154" s="11" t="n">
-        <x:v>7.65</x:v>
-      </x:c>
-      <x:c r="E154" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F154" s="11" t="n">
-        <x:f>SQRT((C154-C153)^2+(D154-D153)^2+(E154-E153)^2)</x:f>
-        <x:v>1.118392149471732</x:v>
-      </x:c>
-      <x:c r="G154" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="155" ht="32" customHeight="1">
-      <x:c r="A155" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
-      </x:c>
-      <x:c r="B155" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C155" s="11" t="n">
-        <x:v>2.35</x:v>
-      </x:c>
-      <x:c r="D155" s="11" t="n">
-        <x:v>7.65</x:v>
-      </x:c>
-      <x:c r="E155" s="11" t="n">
-        <x:v>-3.05</x:v>
-      </x:c>
-      <x:c r="F155" s="11" t="n">
-        <x:f>SQRT((C155-C154)^2+(D155-D154)^2+(E155-E154)^2)</x:f>
-        <x:v>4.3100000000000005</x:v>
-      </x:c>
-      <x:c r="G155" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="156" ht="32" customHeight="1">
-      <x:c r="A156" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
-      </x:c>
-      <x:c r="B156" s="8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C156" s="11" t="n">
-        <x:v>2.35</x:v>
-      </x:c>
-      <x:c r="D156" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E156" s="11" t="n">
-        <x:v>-3.05</x:v>
-      </x:c>
-      <x:c r="F156" s="11" t="n">
-        <x:f>SQRT((C156-C155)^2+(D156-D155)^2+(E156-E155)^2)</x:f>
-        <x:v>1.6500000000000004</x:v>
-      </x:c>
       <x:c r="G156" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="32" customHeight="1">
       <x:c r="A157" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+        <x:v>drop:DB2:F4:fan:1:F251</x:v>
       </x:c>
       <x:c r="B157" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C157" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D157" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E157" s="11" t="n">
-        <x:v>-3.05</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F157" s="11" t="n">
         <x:f>SQRT((C157-C156)^2+(D157-D156)^2+(E157-E156)^2)</x:f>
-        <x:v>0.3049999999999997</x:v>
+        <x:v>1.6504269144678898</x:v>
       </x:c>
       <x:c r="G157" s="8" t="str">
         <x:v>Current</x:v>
@@ -9520,119 +9520,119 @@
     </x:row>
     <x:row r="158" ht="32" customHeight="1">
       <x:c r="A158" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
+        <x:v>drop:DB2:F4:fan:1:F251</x:v>
       </x:c>
       <x:c r="B158" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C158" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D158" s="11" t="n">
+        <x:v>7.65</x:v>
+      </x:c>
+      <x:c r="E158" s="11" t="n">
+        <x:v>3.05</x:v>
+      </x:c>
+      <x:c r="F158" s="11" t="n">
+        <x:f>SQRT((C158-C157)^2+(D158-D157)^2+(E158-E157)^2)</x:f>
+        <x:v>4.3100000000000005</x:v>
+      </x:c>
+      <x:c r="G158" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="32" customHeight="1">
+      <x:c r="A159" s="8" t="str">
+        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+      </x:c>
+      <x:c r="B159" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C159" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D159" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E159" s="11" t="n">
+        <x:v>3.05</x:v>
+      </x:c>
+      <x:c r="F159" s="11" t="n">
+        <x:f>SQRT((C159-C158)^2+(D159-D158)^2+(E159-E158)^2)</x:f>
+        <x:v>1.6500000000000004</x:v>
+      </x:c>
+      <x:c r="G159" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="32" customHeight="1">
+      <x:c r="A160" s="8" t="str">
+        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+      </x:c>
+      <x:c r="B160" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C160" s="11" t="n">
+        <x:v>2.655</x:v>
+      </x:c>
+      <x:c r="D160" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E160" s="11" t="n">
+        <x:v>3.05</x:v>
+      </x:c>
+      <x:c r="F160" s="11" t="n">
+        <x:f>SQRT((C160-C159)^2+(D160-D159)^2+(E160-E159)^2)</x:f>
+        <x:v>0.3049999999999997</x:v>
+      </x:c>
+      <x:c r="G160" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="32" customHeight="1">
+      <x:c r="A161" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
+      </x:c>
+      <x:c r="B161" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C158" s="11" t="n">
-        <x:v>2.73</x:v>
-      </x:c>
-      <x:c r="D158" s="11" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="E158" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F158" s="11" t="n">
+      <x:c r="C161" s="11" t="n">
+        <x:v>48.895</x:v>
+      </x:c>
+      <x:c r="D161" s="11" t="n">
+        <x:v>1.95</x:v>
+      </x:c>
+      <x:c r="E161" s="11" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="F161" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G158" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="159" ht="32" customHeight="1">
-      <x:c r="A159" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
-      </x:c>
-      <x:c r="B159" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C159" s="11" t="n">
-        <x:v>2.35</x:v>
-      </x:c>
-      <x:c r="D159" s="11" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="E159" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F159" s="11" t="n">
-        <x:f>SQRT((C159-C158)^2+(D159-D158)^2+(E159-E158)^2)</x:f>
-        <x:v>0.3799999999999999</x:v>
-      </x:c>
-      <x:c r="G159" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="160" ht="32" customHeight="1">
-      <x:c r="A160" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
-      </x:c>
-      <x:c r="B160" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C160" s="11" t="n">
-        <x:v>2.35</x:v>
-      </x:c>
-      <x:c r="D160" s="11" t="n">
-        <x:v>7.65</x:v>
-      </x:c>
-      <x:c r="E160" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F160" s="11" t="n">
-        <x:f>SQRT((C160-C159)^2+(D160-D159)^2+(E160-E159)^2)</x:f>
-        <x:v>6.15</x:v>
-      </x:c>
-      <x:c r="G160" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161" ht="32" customHeight="1">
-      <x:c r="A161" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
-      </x:c>
-      <x:c r="B161" s="8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C161" s="11" t="n">
-        <x:v>2.35</x:v>
-      </x:c>
-      <x:c r="D161" s="11" t="n">
-        <x:v>7.65</x:v>
-      </x:c>
-      <x:c r="E161" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F161" s="11" t="n">
-        <x:f>SQRT((C161-C160)^2+(D161-D160)^2+(E161-E160)^2)</x:f>
-        <x:v>10.66</x:v>
-      </x:c>
       <x:c r="G161" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="32" customHeight="1">
       <x:c r="A162" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B162" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C162" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D162" s="11" t="n">
-        <x:v>6.574</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E162" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F162" s="11" t="n">
         <x:f>SQRT((C162-C161)^2+(D162-D161)^2+(E162-E161)^2)</x:f>
-        <x:v>1.0760000000000005</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G162" s="8" t="str">
         <x:v>Current</x:v>
@@ -9640,23 +9640,23 @@
     </x:row>
     <x:row r="163" ht="32" customHeight="1">
       <x:c r="A163" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B163" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C163" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D163" s="11" t="n">
-        <x:v>6.574</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E163" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F163" s="11" t="n">
         <x:f>SQRT((C163-C162)^2+(D163-D162)^2+(E163-E162)^2)</x:f>
-        <x:v>0.3049999999999997</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="G163" s="8" t="str">
         <x:v>Current</x:v>
@@ -9664,23 +9664,23 @@
     </x:row>
     <x:row r="164" ht="32" customHeight="1">
       <x:c r="A164" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B164" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C164" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D164" s="11" t="n">
-        <x:v>6.574</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E164" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F164" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C164-C163)^2+(D164-D163)^2+(E164-E163)^2)</x:f>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="G164" s="8" t="str">
         <x:v>Current</x:v>
@@ -9688,23 +9688,23 @@
     </x:row>
     <x:row r="165" ht="32" customHeight="1">
       <x:c r="A165" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B165" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C165" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D165" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E165" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F165" s="11" t="n">
         <x:f>SQRT((C165-C164)^2+(D165-D164)^2+(E165-E164)^2)</x:f>
-        <x:v>1.118392149471732</x:v>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G165" s="8" t="str">
         <x:v>Current</x:v>
@@ -9712,23 +9712,23 @@
     </x:row>
     <x:row r="166" ht="32" customHeight="1">
       <x:c r="A166" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B166" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C166" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D166" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E166" s="11" t="n">
-        <x:v>3.05</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F166" s="11" t="n">
         <x:f>SQRT((C166-C165)^2+(D166-D165)^2+(E166-E165)^2)</x:f>
-        <x:v>4.3100000000000005</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G166" s="8" t="str">
         <x:v>Current</x:v>
@@ -9736,23 +9736,23 @@
     </x:row>
     <x:row r="167" ht="32" customHeight="1">
       <x:c r="A167" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B167" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C167" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D167" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E167" s="11" t="n">
-        <x:v>3.05</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F167" s="11" t="n">
         <x:f>SQRT((C167-C166)^2+(D167-D166)^2+(E167-E166)^2)</x:f>
-        <x:v>1.6500000000000004</x:v>
+        <x:v>1.7060000000000004</x:v>
       </x:c>
       <x:c r="G167" s="8" t="str">
         <x:v>Current</x:v>
@@ -9760,23 +9760,23 @@
     </x:row>
     <x:row r="168" ht="32" customHeight="1">
       <x:c r="A168" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B168" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C168" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D168" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E168" s="11" t="n">
-        <x:v>3.05</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F168" s="11" t="n">
         <x:f>SQRT((C168-C167)^2+(D168-D167)^2+(E168-E167)^2)</x:f>
-        <x:v>0.3049999999999997</x:v>
+        <x:v>4.0600000000000005</x:v>
       </x:c>
       <x:c r="G168" s="8" t="str">
         <x:v>Current</x:v>
@@ -9787,20 +9787,20 @@
         <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B169" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C169" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D169" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E169" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F169" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C169-C168)^2+(D169-D168)^2+(E169-E168)^2)</x:f>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G169" s="8" t="str">
         <x:v>Current</x:v>
@@ -9811,20 +9811,20 @@
         <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B170" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C170" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D170" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E170" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F170" s="11" t="n">
         <x:f>SQRT((C170-C169)^2+(D170-D169)^2+(E170-E169)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
+        <x:v>1.0039999999999996</x:v>
       </x:c>
       <x:c r="G170" s="8" t="str">
         <x:v>Current</x:v>
@@ -9835,20 +9835,20 @@
         <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B171" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C171" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D171" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E171" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F171" s="11" t="n">
         <x:f>SQRT((C171-C170)^2+(D171-D170)^2+(E171-E170)^2)</x:f>
-        <x:v>2.64</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G171" s="8" t="str">
         <x:v>Current</x:v>
@@ -9859,20 +9859,20 @@
         <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B172" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C172" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D172" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E172" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F172" s="11" t="n">
         <x:f>SQRT((C172-C171)^2+(D172-D171)^2+(E172-E171)^2)</x:f>
-        <x:v>2.0699999999999994</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G172" s="8" t="str">
         <x:v>Current</x:v>
@@ -9883,20 +9883,20 @@
         <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B173" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C173" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D173" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E173" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F173" s="11" t="n">
         <x:f>SQRT((C173-C172)^2+(D173-D172)^2+(E173-E172)^2)</x:f>
-        <x:v>1.3599999999999999</x:v>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G173" s="8" t="str">
         <x:v>Current</x:v>
@@ -9907,20 +9907,20 @@
         <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B174" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C174" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>37.695</x:v>
       </x:c>
       <x:c r="D174" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>6.950412371134018</x:v>
       </x:c>
       <x:c r="E174" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F174" s="11" t="n">
         <x:f>SQRT((C174-C173)^2+(D174-D173)^2+(E174-E173)^2)</x:f>
-        <x:v>4.314999999999998</x:v>
+        <x:v>3.697957107375376</x:v>
       </x:c>
       <x:c r="G174" s="8" t="str">
         <x:v>Current</x:v>
@@ -9931,20 +9931,20 @@
         <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B175" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C175" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>37.615</x:v>
       </x:c>
       <x:c r="D175" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E175" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F175" s="11" t="n">
         <x:f>SQRT((C175-C174)^2+(D175-D174)^2+(E175-E174)^2)</x:f>
-        <x:v>2.5680000000000005</x:v>
+        <x:v>0.12010804821421713</x:v>
       </x:c>
       <x:c r="G175" s="8" t="str">
         <x:v>Current</x:v>
@@ -9955,20 +9955,20 @@
         <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B176" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C176" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D176" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E176" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F176" s="11" t="n">
         <x:f>SQRT((C176-C175)^2+(D176-D175)^2+(E176-E175)^2)</x:f>
-        <x:v>3.7600000000000002</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G176" s="8" t="str">
         <x:v>Current</x:v>
@@ -9979,20 +9979,20 @@
         <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B177" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C177" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D177" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E177" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F177" s="11" t="n">
         <x:f>SQRT((C177-C176)^2+(D177-D176)^2+(E177-E176)^2)</x:f>
-        <x:v>8.875</x:v>
+        <x:v>1.0039999999999996</x:v>
       </x:c>
       <x:c r="G177" s="8" t="str">
         <x:v>Current</x:v>
@@ -10003,20 +10003,20 @@
         <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B178" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C178" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D178" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E178" s="11" t="n">
-        <x:v>-13.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F178" s="11" t="n">
         <x:f>SQRT((C178-C177)^2+(D178-D177)^2+(E178-E177)^2)</x:f>
-        <x:v>5.88</x:v>
+        <x:v>31.495</x:v>
       </x:c>
       <x:c r="G178" s="8" t="str">
         <x:v>Current</x:v>
@@ -10024,23 +10024,23 @@
     </x:row>
     <x:row r="179" ht="32" customHeight="1">
       <x:c r="A179" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
       </x:c>
       <x:c r="B179" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C179" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D179" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E179" s="11" t="n">
-        <x:v>-13.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F179" s="11" t="n">
-        <x:f>SQRT((C179-C178)^2+(D179-D178)^2+(E179-E178)^2)</x:f>
-        <x:v>7.199999999999996</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G179" s="8" t="str">
         <x:v>Current</x:v>
@@ -10048,23 +10048,23 @@
     </x:row>
     <x:row r="180" ht="32" customHeight="1">
       <x:c r="A180" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
       </x:c>
       <x:c r="B180" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C180" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D180" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E180" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F180" s="11" t="n">
         <x:f>SQRT((C180-C179)^2+(D180-D179)^2+(E180-E179)^2)</x:f>
-        <x:v>5.88</x:v>
+        <x:v>1.0039999999999996</x:v>
       </x:c>
       <x:c r="G180" s="8" t="str">
         <x:v>Current</x:v>
@@ -10072,23 +10072,23 @@
     </x:row>
     <x:row r="181" ht="32" customHeight="1">
       <x:c r="A181" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
       </x:c>
       <x:c r="B181" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C181" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D181" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E181" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F181" s="11" t="n">
         <x:f>SQRT((C181-C180)^2+(D181-D180)^2+(E181-E180)^2)</x:f>
-        <x:v>31.495</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G181" s="8" t="str">
         <x:v>Current</x:v>
@@ -10099,20 +10099,20 @@
         <x:v>drop:FC1:V1:fan:-1:F252</x:v>
       </x:c>
       <x:c r="B182" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C182" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D182" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>10.64004347826087</x:v>
       </x:c>
       <x:c r="E182" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-2.3999999999999995</x:v>
       </x:c>
       <x:c r="F182" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C182-C181)^2+(D182-D181)^2+(E182-E181)^2)</x:f>
+        <x:v>6.128777451120952</x:v>
       </x:c>
       <x:c r="G182" s="8" t="str">
         <x:v>Current</x:v>
@@ -10123,20 +10123,20 @@
         <x:v>drop:FC1:V1:fan:-1:F252</x:v>
       </x:c>
       <x:c r="B183" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C183" s="11" t="n">
-        <x:v>5.475</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D183" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E183" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-2.4</x:v>
       </x:c>
       <x:c r="F183" s="11" t="n">
         <x:f>SQRT((C183-C182)^2+(D183-D182)^2+(E183-E182)^2)</x:f>
-        <x:v>0.005000000000000782</x:v>
+        <x:v>1.2400434782608691</x:v>
       </x:c>
       <x:c r="G183" s="8" t="str">
         <x:v>Current</x:v>
@@ -10147,20 +10147,20 @@
         <x:v>drop:FC1:V1:fan:-1:F252</x:v>
       </x:c>
       <x:c r="B184" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C184" s="11" t="n">
-        <x:v>5.475</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D184" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E184" s="11" t="n">
         <x:v>-2.4</x:v>
       </x:c>
       <x:c r="F184" s="11" t="n">
         <x:f>SQRT((C184-C183)^2+(D184-D183)^2+(E184-E183)^2)</x:f>
-        <x:v>4.960000000000001</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G184" s="8" t="str">
         <x:v>Current</x:v>
@@ -10168,23 +10168,23 @@
     </x:row>
     <x:row r="185" ht="32" customHeight="1">
       <x:c r="A185" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
       </x:c>
       <x:c r="B185" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C185" s="11" t="n">
-        <x:v>5.475</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D185" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E185" s="11" t="n">
-        <x:v>-2.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F185" s="11" t="n">
-        <x:f>SQRT((C185-C184)^2+(D185-D184)^2+(E185-E184)^2)</x:f>
-        <x:v>2.8120000000000003</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G185" s="8" t="str">
         <x:v>Current</x:v>
@@ -10192,23 +10192,23 @@
     </x:row>
     <x:row r="186" ht="32" customHeight="1">
       <x:c r="A186" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
       </x:c>
       <x:c r="B186" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C186" s="11" t="n">
         <x:v>5.48</x:v>
       </x:c>
       <x:c r="D186" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E186" s="11" t="n">
-        <x:v>-2.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F186" s="11" t="n">
         <x:f>SQRT((C186-C185)^2+(D186-D185)^2+(E186-E185)^2)</x:f>
-        <x:v>0.005000000000000782</x:v>
+        <x:v>1.0039999999999996</x:v>
       </x:c>
       <x:c r="G186" s="8" t="str">
         <x:v>Current</x:v>
@@ -10219,20 +10219,20 @@
         <x:v>drop:FC1:V1:fan:-1:F253</x:v>
       </x:c>
       <x:c r="B187" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C187" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D187" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E187" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F187" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C187-C186)^2+(D187-D186)^2+(E187-E186)^2)</x:f>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G187" s="8" t="str">
         <x:v>Current</x:v>
@@ -10243,20 +10243,20 @@
         <x:v>drop:FC1:V1:fan:-1:F253</x:v>
       </x:c>
       <x:c r="B188" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C188" s="11" t="n">
-        <x:v>5.475</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D188" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>11.801347826086957</x:v>
       </x:c>
       <x:c r="E188" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-0.7999999999999998</x:v>
       </x:c>
       <x:c r="F188" s="11" t="n">
         <x:f>SQRT((C188-C187)^2+(D188-D187)^2+(E188-E187)^2)</x:f>
-        <x:v>0.005000000000000782</x:v>
+        <x:v>8.105802435353516</x:v>
       </x:c>
       <x:c r="G188" s="8" t="str">
         <x:v>Current</x:v>
@@ -10267,20 +10267,20 @@
         <x:v>drop:FC1:V1:fan:-1:F253</x:v>
       </x:c>
       <x:c r="B189" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C189" s="11" t="n">
-        <x:v>5.475</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D189" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E189" s="11" t="n">
         <x:v>-0.8</x:v>
       </x:c>
       <x:c r="F189" s="11" t="n">
         <x:f>SQRT((C189-C188)^2+(D189-D188)^2+(E189-E188)^2)</x:f>
-        <x:v>6.5600000000000005</x:v>
+        <x:v>2.4013478260869565</x:v>
       </x:c>
       <x:c r="G189" s="8" t="str">
         <x:v>Current</x:v>
@@ -10291,10 +10291,10 @@
         <x:v>drop:FC1:V1:fan:-1:F253</x:v>
       </x:c>
       <x:c r="B190" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C190" s="11" t="n">
-        <x:v>5.475</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D190" s="11" t="n">
         <x:v>9.4</x:v>
@@ -10304,7 +10304,7 @@
       </x:c>
       <x:c r="F190" s="11" t="n">
         <x:f>SQRT((C190-C189)^2+(D190-D189)^2+(E190-E189)^2)</x:f>
-        <x:v>2.8120000000000003</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G190" s="8" t="str">
         <x:v>Current</x:v>
@@ -10312,23 +10312,23 @@
     </x:row>
     <x:row r="191" ht="32" customHeight="1">
       <x:c r="A191" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
       </x:c>
       <x:c r="B191" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C191" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D191" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>8.565264175257731</x:v>
       </x:c>
       <x:c r="E191" s="11" t="n">
-        <x:v>-0.8</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F191" s="11" t="n">
-        <x:f>SQRT((C191-C190)^2+(D191-D190)^2+(E191-E190)^2)</x:f>
-        <x:v>0.005000000000000782</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G191" s="8" t="str">
         <x:v>Current</x:v>
@@ -10339,20 +10339,20 @@
         <x:v>drop:FC1:V1:fan:-1:F256</x:v>
       </x:c>
       <x:c r="B192" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C192" s="11" t="n">
         <x:v>39.7</x:v>
       </x:c>
       <x:c r="D192" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>8.565264175257731</x:v>
       </x:c>
       <x:c r="E192" s="11" t="n">
-        <x:v>-13.24</x:v>
+        <x:v>-13.249</x:v>
       </x:c>
       <x:c r="F192" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C192-C191)^2+(D192-D191)^2+(E192-E191)^2)</x:f>
+        <x:v>5.889</x:v>
       </x:c>
       <x:c r="G192" s="8" t="str">
         <x:v>Current</x:v>
@@ -10363,7 +10363,7 @@
         <x:v>drop:FC1:V1:fan:-1:F256</x:v>
       </x:c>
       <x:c r="B193" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C193" s="11" t="n">
         <x:v>39.7</x:v>
@@ -10372,11 +10372,11 @@
         <x:v>7.6</x:v>
       </x:c>
       <x:c r="E193" s="11" t="n">
-        <x:v>-13.24</x:v>
+        <x:v>-13.249</x:v>
       </x:c>
       <x:c r="F193" s="11" t="n">
         <x:f>SQRT((C193-C192)^2+(D193-D192)^2+(E193-E192)^2)</x:f>
-        <x:v>1.0119999999999996</x:v>
+        <x:v>0.9652641752577313</x:v>
       </x:c>
       <x:c r="G193" s="8" t="str">
         <x:v>Current</x:v>
@@ -10387,7 +10387,7 @@
         <x:v>drop:FC1:V1:fan:-1:F256</x:v>
       </x:c>
       <x:c r="B194" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C194" s="11" t="n">
         <x:v>39.7</x:v>
@@ -10400,7 +10400,7 @@
       </x:c>
       <x:c r="F194" s="11" t="n">
         <x:f>SQRT((C194-C193)^2+(D194-D193)^2+(E194-E193)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
+        <x:v>0.11899999999999977</x:v>
       </x:c>
       <x:c r="G194" s="8" t="str">
         <x:v>Current</x:v>
@@ -10417,10 +10417,10 @@
         <x:v>41.45</x:v>
       </x:c>
       <x:c r="D195" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>8.565264175257724</x:v>
       </x:c>
       <x:c r="E195" s="11" t="n">
-        <x:v>-13.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F195" s="11" t="n">
         <x:f>0</x:f>
@@ -10441,14 +10441,14 @@
         <x:v>41.45</x:v>
       </x:c>
       <x:c r="D196" s="11" t="n">
-        <x:v>7.6</x:v>
+        <x:v>8.565264175257731</x:v>
       </x:c>
       <x:c r="E196" s="11" t="n">
-        <x:v>-13.24</x:v>
+        <x:v>-13.249</x:v>
       </x:c>
       <x:c r="F196" s="11" t="n">
         <x:f>SQRT((C196-C195)^2+(D196-D195)^2+(E196-E195)^2)</x:f>
-        <x:v>1.0119999999999996</x:v>
+        <x:v>5.889</x:v>
       </x:c>
       <x:c r="G196" s="8" t="str">
         <x:v>Current</x:v>
@@ -10468,11 +10468,11 @@
         <x:v>7.6</x:v>
       </x:c>
       <x:c r="E197" s="11" t="n">
-        <x:v>-13.13</x:v>
+        <x:v>-13.249</x:v>
       </x:c>
       <x:c r="F197" s="11" t="n">
         <x:f>SQRT((C197-C196)^2+(D197-D196)^2+(E197-E196)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
+        <x:v>0.9652641752577313</x:v>
       </x:c>
       <x:c r="G197" s="8" t="str">
         <x:v>Current</x:v>
@@ -10480,23 +10480,23 @@
     </x:row>
     <x:row r="198" ht="32" customHeight="1">
       <x:c r="A198" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
       </x:c>
       <x:c r="B198" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C198" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>41.45</x:v>
       </x:c>
       <x:c r="D198" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="E198" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-13.13</x:v>
       </x:c>
       <x:c r="F198" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C198-C197)^2+(D198-D197)^2+(E198-E197)^2)</x:f>
+        <x:v>0.11899999999999977</x:v>
       </x:c>
       <x:c r="G198" s="8" t="str">
         <x:v>Current</x:v>
@@ -10507,20 +10507,20 @@
         <x:v>drop:FC1:V1:fan:-1:F260</x:v>
       </x:c>
       <x:c r="B199" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C199" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D199" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E199" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F199" s="11" t="n">
-        <x:f>SQRT((C199-C198)^2+(D199-D198)^2+(E199-E198)^2)</x:f>
-        <x:v>3.2880000000000003</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G199" s="8" t="str">
         <x:v>Current</x:v>
@@ -10531,20 +10531,20 @@
         <x:v>drop:FC1:V1:fan:-1:F260</x:v>
       </x:c>
       <x:c r="B200" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C200" s="11" t="n">
-        <x:v>53.12</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D200" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E200" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F200" s="11" t="n">
         <x:f>SQRT((C200-C199)^2+(D200-D199)^2+(E200-E199)^2)</x:f>
-        <x:v>0.07000000000000028</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="G200" s="8" t="str">
         <x:v>Current</x:v>
@@ -10555,10 +10555,10 @@
         <x:v>drop:FC1:V1:fan:-1:F260</x:v>
       </x:c>
       <x:c r="B201" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C201" s="11" t="n">
-        <x:v>53.12</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D201" s="11" t="n">
         <x:v>3.3</x:v>
@@ -10568,7 +10568,7 @@
       </x:c>
       <x:c r="F201" s="11" t="n">
         <x:f>SQRT((C201-C200)^2+(D201-D200)^2+(E201-E200)^2)</x:f>
-        <x:v>7.36</x:v>
+        <x:v>2.7360000000000007</x:v>
       </x:c>
       <x:c r="G201" s="8" t="str">
         <x:v>Current</x:v>
@@ -10576,23 +10576,23 @@
     </x:row>
     <x:row r="202" ht="32" customHeight="1">
       <x:c r="A202" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
       </x:c>
       <x:c r="B202" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C202" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>53.12</x:v>
       </x:c>
       <x:c r="D202" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="E202" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F202" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C202-C201)^2+(D202-D201)^2+(E202-E201)^2)</x:f>
+        <x:v>0.1039999999999992</x:v>
       </x:c>
       <x:c r="G202" s="8" t="str">
         <x:v>Current</x:v>
@@ -10603,10 +10603,10 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B203" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C203" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D203" s="11" t="n">
         <x:v>1.95</x:v>
@@ -10615,8 +10615,8 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="F203" s="11" t="n">
-        <x:f>SQRT((C203-C202)^2+(D203-D202)^2+(E203-E202)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G203" s="8" t="str">
         <x:v>Current</x:v>
@@ -10627,7 +10627,7 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B204" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C204" s="11" t="n">
         <x:v>48.735</x:v>
@@ -10636,11 +10636,11 @@
         <x:v>1.95</x:v>
       </x:c>
       <x:c r="E204" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F204" s="11" t="n">
         <x:f>SQRT((C204-C203)^2+(D204-D203)^2+(E204-E203)^2)</x:f>
-        <x:v>2.64</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G204" s="8" t="str">
         <x:v>Current</x:v>
@@ -10651,20 +10651,20 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B205" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C205" s="11" t="n">
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D205" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E205" s="11" t="n">
         <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F205" s="11" t="n">
         <x:f>SQRT((C205-C204)^2+(D205-D204)^2+(E205-E204)^2)</x:f>
-        <x:v>2.0699999999999994</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="G205" s="8" t="str">
         <x:v>Current</x:v>
@@ -10675,20 +10675,20 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B206" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C206" s="11" t="n">
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D206" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E206" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F206" s="11" t="n">
         <x:f>SQRT((C206-C205)^2+(D206-D205)^2+(E206-E205)^2)</x:f>
-        <x:v>1.3599999999999999</x:v>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="G206" s="8" t="str">
         <x:v>Current</x:v>
@@ -10699,20 +10699,20 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B207" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C207" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D207" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E207" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F207" s="11" t="n">
         <x:f>SQRT((C207-C206)^2+(D207-D206)^2+(E207-E206)^2)</x:f>
-        <x:v>4.314999999999998</x:v>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G207" s="8" t="str">
         <x:v>Current</x:v>
@@ -10723,20 +10723,20 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B208" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C208" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D208" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E208" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F208" s="11" t="n">
         <x:f>SQRT((C208-C207)^2+(D208-D207)^2+(E208-E207)^2)</x:f>
-        <x:v>2.5680000000000005</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G208" s="8" t="str">
         <x:v>Current</x:v>
@@ -10747,20 +10747,20 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B209" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C209" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D209" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E209" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F209" s="11" t="n">
         <x:f>SQRT((C209-C208)^2+(D209-D208)^2+(E209-E208)^2)</x:f>
-        <x:v>10.96</x:v>
+        <x:v>1.7060000000000004</x:v>
       </x:c>
       <x:c r="G209" s="8" t="str">
         <x:v>Current</x:v>
@@ -10771,20 +10771,20 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B210" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C210" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D210" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E210" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F210" s="11" t="n">
         <x:f>SQRT((C210-C209)^2+(D210-D209)^2+(E210-E209)^2)</x:f>
-        <x:v>8.875</x:v>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G210" s="8" t="str">
         <x:v>Current</x:v>
@@ -10795,20 +10795,20 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B211" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C211" s="11" t="n">
         <x:v>44.175</x:v>
       </x:c>
       <x:c r="D211" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E211" s="11" t="n">
-        <x:v>13.24</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F211" s="11" t="n">
         <x:f>SQRT((C211-C210)^2+(D211-D210)^2+(E211-E210)^2)</x:f>
-        <x:v>5.88</x:v>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G211" s="8" t="str">
         <x:v>Current</x:v>
@@ -10819,20 +10819,20 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B212" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C212" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D212" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E212" s="11" t="n">
-        <x:v>13.24</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F212" s="11" t="n">
         <x:f>SQRT((C212-C211)^2+(D212-D211)^2+(E212-E211)^2)</x:f>
-        <x:v>7.199999999999996</x:v>
+        <x:v>1.0039999999999996</x:v>
       </x:c>
       <x:c r="G212" s="8" t="str">
         <x:v>Current</x:v>
@@ -10843,20 +10843,20 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B213" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C213" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D213" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E213" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F213" s="11" t="n">
         <x:f>SQRT((C213-C212)^2+(D213-D212)^2+(E213-E212)^2)</x:f>
-        <x:v>5.88</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G213" s="8" t="str">
         <x:v>Current</x:v>
@@ -10867,20 +10867,20 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B214" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C214" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D214" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E214" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F214" s="11" t="n">
         <x:f>SQRT((C214-C213)^2+(D214-D213)^2+(E214-E213)^2)</x:f>
-        <x:v>31.495</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G214" s="8" t="str">
         <x:v>Current</x:v>
@@ -10888,395 +10888,635 @@
     </x:row>
     <x:row r="215" ht="32" customHeight="1">
       <x:c r="A215" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B215" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C215" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D215" s="11" t="n">
-        <x:v>6.588</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E215" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F215" s="11" t="n">
+        <x:f>SQRT((C215-C214)^2+(D215-D214)^2+(E215-E214)^2)</x:f>
+        <x:v>3.6979571073753776</x:v>
+      </x:c>
+      <x:c r="G215" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" ht="32" customHeight="1">
+      <x:c r="A216" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+      <x:c r="B216" s="8" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C216" s="11" t="n">
+        <x:v>37.695</x:v>
+      </x:c>
+      <x:c r="D216" s="11" t="n">
+        <x:v>6.950412371134018</x:v>
+      </x:c>
+      <x:c r="E216" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F216" s="11" t="n">
+        <x:f>SQRT((C216-C215)^2+(D216-D215)^2+(E216-E215)^2)</x:f>
+        <x:v>3.697957107375376</x:v>
+      </x:c>
+      <x:c r="G216" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" ht="32" customHeight="1">
+      <x:c r="A217" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+      <x:c r="B217" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C217" s="11" t="n">
+        <x:v>37.615</x:v>
+      </x:c>
+      <x:c r="D217" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E217" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F217" s="11" t="n">
+        <x:f>SQRT((C217-C216)^2+(D217-D216)^2+(E217-E216)^2)</x:f>
+        <x:v>0.12010804821421713</x:v>
+      </x:c>
+      <x:c r="G217" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" ht="32" customHeight="1">
+      <x:c r="A218" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+      <x:c r="B218" s="8" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C218" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D218" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E218" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F218" s="11" t="n">
+        <x:f>SQRT((C218-C217)^2+(D218-D217)^2+(E218-E217)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G218" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" ht="32" customHeight="1">
+      <x:c r="A219" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+      <x:c r="B219" s="8" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C219" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D219" s="11" t="n">
+        <x:v>6.0360000000000005</x:v>
+      </x:c>
+      <x:c r="E219" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F219" s="11" t="n">
+        <x:f>SQRT((C219-C218)^2+(D219-D218)^2+(E219-E218)^2)</x:f>
+        <x:v>1.0039999999999996</x:v>
+      </x:c>
+      <x:c r="G219" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" ht="32" customHeight="1">
+      <x:c r="A220" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+      <x:c r="B220" s="8" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C220" s="11" t="n">
+        <x:v>5.48</x:v>
+      </x:c>
+      <x:c r="D220" s="11" t="n">
+        <x:v>6.0360000000000005</x:v>
+      </x:c>
+      <x:c r="E220" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F220" s="11" t="n">
+        <x:f>SQRT((C220-C219)^2+(D220-D219)^2+(E220-E219)^2)</x:f>
+        <x:v>31.495</x:v>
+      </x:c>
+      <x:c r="G220" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" ht="32" customHeight="1">
+      <x:c r="A221" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+      </x:c>
+      <x:c r="B221" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C221" s="11" t="n">
+        <x:v>5.48</x:v>
+      </x:c>
+      <x:c r="D221" s="11" t="n">
+        <x:v>6.0360000000000005</x:v>
+      </x:c>
+      <x:c r="E221" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F221" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G215" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="216" ht="32" customHeight="1">
-      <x:c r="A216" s="8" t="str">
+      <x:c r="G221" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" ht="32" customHeight="1">
+      <x:c r="A222" s="8" t="str">
         <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
-      <x:c r="B216" s="8" t="n">
+      <x:c r="B222" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C216" s="11" t="n">
-        <x:v>5.475</x:v>
-      </x:c>
-      <x:c r="D216" s="11" t="n">
-        <x:v>6.588</x:v>
-      </x:c>
-      <x:c r="E216" s="11" t="n">
+      <x:c r="C222" s="11" t="n">
+        <x:v>5.48</x:v>
+      </x:c>
+      <x:c r="D222" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E222" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
-      <x:c r="F216" s="11" t="n">
-        <x:f>SQRT((C216-C215)^2+(D216-D215)^2+(E216-E215)^2)</x:f>
-        <x:v>0.005000000000000782</x:v>
-      </x:c>
-      <x:c r="G216" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="217" ht="32" customHeight="1">
-      <x:c r="A217" s="8" t="str">
+      <x:c r="F222" s="11" t="n">
+        <x:f>SQRT((C222-C221)^2+(D222-D221)^2+(E222-E221)^2)</x:f>
+        <x:v>1.0039999999999996</x:v>
+      </x:c>
+      <x:c r="G222" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" ht="32" customHeight="1">
+      <x:c r="A223" s="8" t="str">
         <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
-      <x:c r="B217" s="8" t="n">
+      <x:c r="B223" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C217" s="11" t="n">
-        <x:v>5.475</x:v>
-      </x:c>
-      <x:c r="D217" s="11" t="n">
-        <x:v>6.588</x:v>
-      </x:c>
-      <x:c r="E217" s="11" t="n">
+      <x:c r="C223" s="11" t="n">
+        <x:v>5.32</x:v>
+      </x:c>
+      <x:c r="D223" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E223" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F223" s="11" t="n">
+        <x:f>SQRT((C223-C222)^2+(D223-D222)^2+(E223-E222)^2)</x:f>
+        <x:v>0.16000000000000014</x:v>
+      </x:c>
+      <x:c r="G223" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" ht="32" customHeight="1">
+      <x:c r="A224" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+      </x:c>
+      <x:c r="B224" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C224" s="11" t="n">
+        <x:v>5.32</x:v>
+      </x:c>
+      <x:c r="D224" s="11" t="n">
+        <x:v>11.801347826086957</x:v>
+      </x:c>
+      <x:c r="E224" s="11" t="n">
+        <x:v>0.7999999999999998</x:v>
+      </x:c>
+      <x:c r="F224" s="11" t="n">
+        <x:f>SQRT((C224-C223)^2+(D224-D223)^2+(E224-E223)^2)</x:f>
+        <x:v>8.105802435353516</x:v>
+      </x:c>
+      <x:c r="G224" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" ht="32" customHeight="1">
+      <x:c r="A225" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+      </x:c>
+      <x:c r="B225" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C225" s="11" t="n">
+        <x:v>5.32</x:v>
+      </x:c>
+      <x:c r="D225" s="11" t="n">
+        <x:v>9.4</x:v>
+      </x:c>
+      <x:c r="E225" s="11" t="n">
         <x:v>0.8</x:v>
       </x:c>
-      <x:c r="F217" s="11" t="n">
-        <x:f>SQRT((C217-C216)^2+(D217-D216)^2+(E217-E216)^2)</x:f>
-        <x:v>6.5600000000000005</x:v>
-      </x:c>
-      <x:c r="G217" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="218" ht="32" customHeight="1">
-      <x:c r="A218" s="8" t="str">
+      <x:c r="F225" s="11" t="n">
+        <x:f>SQRT((C225-C224)^2+(D225-D224)^2+(E225-E224)^2)</x:f>
+        <x:v>2.4013478260869565</x:v>
+      </x:c>
+      <x:c r="G225" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" ht="32" customHeight="1">
+      <x:c r="A226" s="8" t="str">
         <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
-      <x:c r="B218" s="8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C218" s="11" t="n">
-        <x:v>5.475</x:v>
-      </x:c>
-      <x:c r="D218" s="11" t="n">
+      <x:c r="B226" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C226" s="11" t="n">
+        <x:v>5.48</x:v>
+      </x:c>
+      <x:c r="D226" s="11" t="n">
         <x:v>9.4</x:v>
       </x:c>
-      <x:c r="E218" s="11" t="n">
+      <x:c r="E226" s="11" t="n">
         <x:v>0.8</x:v>
       </x:c>
-      <x:c r="F218" s="11" t="n">
-        <x:f>SQRT((C218-C217)^2+(D218-D217)^2+(E218-E217)^2)</x:f>
-        <x:v>2.8120000000000003</x:v>
-      </x:c>
-      <x:c r="G218" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="219" ht="32" customHeight="1">
-      <x:c r="A219" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
-      </x:c>
-      <x:c r="B219" s="8" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C219" s="11" t="n">
+      <x:c r="F226" s="11" t="n">
+        <x:f>SQRT((C226-C225)^2+(D226-D225)^2+(E226-E225)^2)</x:f>
+        <x:v>0.16000000000000014</x:v>
+      </x:c>
+      <x:c r="G226" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" ht="32" customHeight="1">
+      <x:c r="A227" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
+      </x:c>
+      <x:c r="B227" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C227" s="11" t="n">
         <x:v>5.48</x:v>
       </x:c>
-      <x:c r="D219" s="11" t="n">
-        <x:v>9.4</x:v>
-      </x:c>
-      <x:c r="E219" s="11" t="n">
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="F219" s="11" t="n">
-        <x:f>SQRT((C219-C218)^2+(D219-D218)^2+(E219-E218)^2)</x:f>
-        <x:v>0.005000000000000782</x:v>
-      </x:c>
-      <x:c r="G219" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="220" ht="32" customHeight="1">
-      <x:c r="A220" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
-      </x:c>
-      <x:c r="B220" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C220" s="11" t="n">
-        <x:v>5.48</x:v>
-      </x:c>
-      <x:c r="D220" s="11" t="n">
-        <x:v>6.588</x:v>
-      </x:c>
-      <x:c r="E220" s="11" t="n">
+      <x:c r="D227" s="11" t="n">
+        <x:v>6.0360000000000005</x:v>
+      </x:c>
+      <x:c r="E227" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
-      <x:c r="F220" s="11" t="n">
+      <x:c r="F227" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G220" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="221" ht="32" customHeight="1">
-      <x:c r="A221" s="8" t="str">
+      <x:c r="G227" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" ht="32" customHeight="1">
+      <x:c r="A228" s="8" t="str">
         <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
-      <x:c r="B221" s="8" t="n">
+      <x:c r="B228" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C221" s="11" t="n">
-        <x:v>5.475</x:v>
-      </x:c>
-      <x:c r="D221" s="11" t="n">
-        <x:v>6.588</x:v>
-      </x:c>
-      <x:c r="E221" s="11" t="n">
+      <x:c r="C228" s="11" t="n">
+        <x:v>5.48</x:v>
+      </x:c>
+      <x:c r="D228" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E228" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
-      <x:c r="F221" s="11" t="n">
-        <x:f>SQRT((C221-C220)^2+(D221-D220)^2+(E221-E220)^2)</x:f>
-        <x:v>0.005000000000000782</x:v>
-      </x:c>
-      <x:c r="G221" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="222" ht="32" customHeight="1">
-      <x:c r="A222" s="8" t="str">
+      <x:c r="F228" s="11" t="n">
+        <x:f>SQRT((C228-C227)^2+(D228-D227)^2+(E228-E227)^2)</x:f>
+        <x:v>1.0039999999999996</x:v>
+      </x:c>
+      <x:c r="G228" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" ht="32" customHeight="1">
+      <x:c r="A229" s="8" t="str">
         <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
-      <x:c r="B222" s="8" t="n">
+      <x:c r="B229" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C222" s="11" t="n">
-        <x:v>5.475</x:v>
-      </x:c>
-      <x:c r="D222" s="11" t="n">
-        <x:v>6.588</x:v>
-      </x:c>
-      <x:c r="E222" s="11" t="n">
+      <x:c r="C229" s="11" t="n">
+        <x:v>5.32</x:v>
+      </x:c>
+      <x:c r="D229" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E229" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F229" s="11" t="n">
+        <x:f>SQRT((C229-C228)^2+(D229-D228)^2+(E229-E228)^2)</x:f>
+        <x:v>0.16000000000000014</x:v>
+      </x:c>
+      <x:c r="G229" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" ht="32" customHeight="1">
+      <x:c r="A230" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
+      </x:c>
+      <x:c r="B230" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C230" s="11" t="n">
+        <x:v>5.32</x:v>
+      </x:c>
+      <x:c r="D230" s="11" t="n">
+        <x:v>10.64004347826087</x:v>
+      </x:c>
+      <x:c r="E230" s="11" t="n">
+        <x:v>2.3999999999999995</x:v>
+      </x:c>
+      <x:c r="F230" s="11" t="n">
+        <x:f>SQRT((C230-C229)^2+(D230-D229)^2+(E230-E229)^2)</x:f>
+        <x:v>6.128777451120952</x:v>
+      </x:c>
+      <x:c r="G230" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" ht="32" customHeight="1">
+      <x:c r="A231" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
+      </x:c>
+      <x:c r="B231" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C231" s="11" t="n">
+        <x:v>5.32</x:v>
+      </x:c>
+      <x:c r="D231" s="11" t="n">
+        <x:v>9.4</x:v>
+      </x:c>
+      <x:c r="E231" s="11" t="n">
         <x:v>2.4</x:v>
       </x:c>
-      <x:c r="F222" s="11" t="n">
-        <x:f>SQRT((C222-C221)^2+(D222-D221)^2+(E222-E221)^2)</x:f>
-        <x:v>4.960000000000001</x:v>
-      </x:c>
-      <x:c r="G222" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="223" ht="32" customHeight="1">
-      <x:c r="A223" s="8" t="str">
+      <x:c r="F231" s="11" t="n">
+        <x:f>SQRT((C231-C230)^2+(D231-D230)^2+(E231-E230)^2)</x:f>
+        <x:v>1.2400434782608691</x:v>
+      </x:c>
+      <x:c r="G231" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" ht="32" customHeight="1">
+      <x:c r="A232" s="8" t="str">
         <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
-      <x:c r="B223" s="8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C223" s="11" t="n">
-        <x:v>5.475</x:v>
-      </x:c>
-      <x:c r="D223" s="11" t="n">
+      <x:c r="B232" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C232" s="11" t="n">
+        <x:v>5.48</x:v>
+      </x:c>
+      <x:c r="D232" s="11" t="n">
         <x:v>9.4</x:v>
       </x:c>
-      <x:c r="E223" s="11" t="n">
+      <x:c r="E232" s="11" t="n">
         <x:v>2.4</x:v>
       </x:c>
-      <x:c r="F223" s="11" t="n">
-        <x:f>SQRT((C223-C222)^2+(D223-D222)^2+(E223-E222)^2)</x:f>
-        <x:v>2.8120000000000003</x:v>
-      </x:c>
-      <x:c r="G223" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="224" ht="32" customHeight="1">
-      <x:c r="A224" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
-      </x:c>
-      <x:c r="B224" s="8" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C224" s="11" t="n">
-        <x:v>5.48</x:v>
-      </x:c>
-      <x:c r="D224" s="11" t="n">
-        <x:v>9.4</x:v>
-      </x:c>
-      <x:c r="E224" s="11" t="n">
-        <x:v>2.4</x:v>
-      </x:c>
-      <x:c r="F224" s="11" t="n">
-        <x:f>SQRT((C224-C223)^2+(D224-D223)^2+(E224-E223)^2)</x:f>
-        <x:v>0.005000000000000782</x:v>
-      </x:c>
-      <x:c r="G224" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="225" ht="32" customHeight="1">
-      <x:c r="A225" s="8" t="str">
+      <x:c r="F232" s="11" t="n">
+        <x:f>SQRT((C232-C231)^2+(D232-D231)^2+(E232-E231)^2)</x:f>
+        <x:v>0.16000000000000014</x:v>
+      </x:c>
+      <x:c r="G232" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" ht="32" customHeight="1">
+      <x:c r="A233" s="8" t="str">
         <x:v>drop:FC1:V1:fan:1:F258</x:v>
       </x:c>
-      <x:c r="B225" s="8" t="n">
+      <x:c r="B233" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C225" s="11" t="n">
+      <x:c r="C233" s="11" t="n">
         <x:v>39.7</x:v>
       </x:c>
-      <x:c r="D225" s="11" t="n">
-        <x:v>6.588</x:v>
-      </x:c>
-      <x:c r="E225" s="11" t="n">
-        <x:v>13.24</x:v>
-      </x:c>
-      <x:c r="F225" s="11" t="n">
+      <x:c r="D233" s="11" t="n">
+        <x:v>8.565264175257731</x:v>
+      </x:c>
+      <x:c r="E233" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F233" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G225" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="226" ht="32" customHeight="1">
-      <x:c r="A226" s="8" t="str">
+      <x:c r="G233" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" ht="32" customHeight="1">
+      <x:c r="A234" s="8" t="str">
         <x:v>drop:FC1:V1:fan:1:F258</x:v>
       </x:c>
-      <x:c r="B226" s="8" t="n">
+      <x:c r="B234" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C226" s="11" t="n">
+      <x:c r="C234" s="11" t="n">
         <x:v>39.7</x:v>
       </x:c>
-      <x:c r="D226" s="11" t="n">
+      <x:c r="D234" s="11" t="n">
+        <x:v>8.565264175257731</x:v>
+      </x:c>
+      <x:c r="E234" s="11" t="n">
+        <x:v>13.249</x:v>
+      </x:c>
+      <x:c r="F234" s="11" t="n">
+        <x:f>SQRT((C234-C233)^2+(D234-D233)^2+(E234-E233)^2)</x:f>
+        <x:v>5.889</x:v>
+      </x:c>
+      <x:c r="G234" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" ht="32" customHeight="1">
+      <x:c r="A235" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F258</x:v>
+      </x:c>
+      <x:c r="B235" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C235" s="11" t="n">
+        <x:v>39.7</x:v>
+      </x:c>
+      <x:c r="D235" s="11" t="n">
         <x:v>7.6</x:v>
       </x:c>
-      <x:c r="E226" s="11" t="n">
-        <x:v>13.24</x:v>
-      </x:c>
-      <x:c r="F226" s="11" t="n">
-        <x:f>SQRT((C226-C225)^2+(D226-D225)^2+(E226-E225)^2)</x:f>
-        <x:v>1.0119999999999996</x:v>
-      </x:c>
-      <x:c r="G226" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="227" ht="32" customHeight="1">
-      <x:c r="A227" s="8" t="str">
+      <x:c r="E235" s="11" t="n">
+        <x:v>13.249</x:v>
+      </x:c>
+      <x:c r="F235" s="11" t="n">
+        <x:f>SQRT((C235-C234)^2+(D235-D234)^2+(E235-E234)^2)</x:f>
+        <x:v>0.9652641752577313</x:v>
+      </x:c>
+      <x:c r="G235" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" ht="32" customHeight="1">
+      <x:c r="A236" s="8" t="str">
         <x:v>drop:FC1:V1:fan:1:F258</x:v>
       </x:c>
-      <x:c r="B227" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C227" s="11" t="n">
+      <x:c r="B236" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C236" s="11" t="n">
         <x:v>39.7</x:v>
       </x:c>
-      <x:c r="D227" s="11" t="n">
+      <x:c r="D236" s="11" t="n">
         <x:v>7.6</x:v>
       </x:c>
-      <x:c r="E227" s="11" t="n">
+      <x:c r="E236" s="11" t="n">
         <x:v>13.13</x:v>
       </x:c>
-      <x:c r="F227" s="11" t="n">
-        <x:f>SQRT((C227-C226)^2+(D227-D226)^2+(E227-E226)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
-      </x:c>
-      <x:c r="G227" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="228" ht="32" customHeight="1">
-      <x:c r="A228" s="8" t="str">
+      <x:c r="F236" s="11" t="n">
+        <x:f>SQRT((C236-C235)^2+(D236-D235)^2+(E236-E235)^2)</x:f>
+        <x:v>0.11899999999999977</x:v>
+      </x:c>
+      <x:c r="G236" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" ht="32" customHeight="1">
+      <x:c r="A237" s="8" t="str">
         <x:v>drop:FC1:V1:fan:1:F259</x:v>
       </x:c>
-      <x:c r="B228" s="8" t="n">
+      <x:c r="B237" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C228" s="11" t="n">
+      <x:c r="C237" s="11" t="n">
         <x:v>41.45</x:v>
       </x:c>
-      <x:c r="D228" s="11" t="n">
-        <x:v>6.588</x:v>
-      </x:c>
-      <x:c r="E228" s="11" t="n">
-        <x:v>13.24</x:v>
-      </x:c>
-      <x:c r="F228" s="11" t="n">
+      <x:c r="D237" s="11" t="n">
+        <x:v>8.565264175257724</x:v>
+      </x:c>
+      <x:c r="E237" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F237" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G228" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="229" ht="32" customHeight="1">
-      <x:c r="A229" s="8" t="str">
+      <x:c r="G237" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" ht="32" customHeight="1">
+      <x:c r="A238" s="8" t="str">
         <x:v>drop:FC1:V1:fan:1:F259</x:v>
       </x:c>
-      <x:c r="B229" s="8" t="n">
+      <x:c r="B238" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C229" s="11" t="n">
+      <x:c r="C238" s="11" t="n">
         <x:v>41.45</x:v>
       </x:c>
-      <x:c r="D229" s="11" t="n">
+      <x:c r="D238" s="11" t="n">
+        <x:v>8.565264175257731</x:v>
+      </x:c>
+      <x:c r="E238" s="11" t="n">
+        <x:v>13.249</x:v>
+      </x:c>
+      <x:c r="F238" s="11" t="n">
+        <x:f>SQRT((C238-C237)^2+(D238-D237)^2+(E238-E237)^2)</x:f>
+        <x:v>5.889</x:v>
+      </x:c>
+      <x:c r="G238" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" ht="32" customHeight="1">
+      <x:c r="A239" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F259</x:v>
+      </x:c>
+      <x:c r="B239" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C239" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D239" s="11" t="n">
         <x:v>7.6</x:v>
       </x:c>
-      <x:c r="E229" s="11" t="n">
-        <x:v>13.24</x:v>
-      </x:c>
-      <x:c r="F229" s="11" t="n">
-        <x:f>SQRT((C229-C228)^2+(D229-D228)^2+(E229-E228)^2)</x:f>
-        <x:v>1.0119999999999996</x:v>
-      </x:c>
-      <x:c r="G229" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="230" ht="32" customHeight="1">
-      <x:c r="A230" s="8" t="str">
+      <x:c r="E239" s="11" t="n">
+        <x:v>13.249</x:v>
+      </x:c>
+      <x:c r="F239" s="11" t="n">
+        <x:f>SQRT((C239-C238)^2+(D239-D238)^2+(E239-E238)^2)</x:f>
+        <x:v>0.9652641752577313</x:v>
+      </x:c>
+      <x:c r="G239" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" ht="32" customHeight="1">
+      <x:c r="A240" s="8" t="str">
         <x:v>drop:FC1:V1:fan:1:F259</x:v>
       </x:c>
-      <x:c r="B230" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C230" s="11" t="n">
+      <x:c r="B240" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C240" s="11" t="n">
         <x:v>41.45</x:v>
       </x:c>
-      <x:c r="D230" s="11" t="n">
+      <x:c r="D240" s="11" t="n">
         <x:v>7.6</x:v>
       </x:c>
-      <x:c r="E230" s="11" t="n">
+      <x:c r="E240" s="11" t="n">
         <x:v>13.13</x:v>
       </x:c>
-      <x:c r="F230" s="11" t="n">
-        <x:f>SQRT((C230-C229)^2+(D230-D229)^2+(E230-E229)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
-      </x:c>
-      <x:c r="G230" s="8" t="str">
+      <x:c r="F240" s="11" t="n">
+        <x:f>SQRT((C240-C239)^2+(D240-D239)^2+(E240-E239)^2)</x:f>
+        <x:v>0.11899999999999977</x:v>
+      </x:c>
+      <x:c r="G240" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G7:G230">
+  <x:conditionalFormatting sqref="G7:G240">
     <x:cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f401a13229a4d76"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f16e682b7394b4b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R4aaad7373ef546e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rf8ff3002f9e84001"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Ra82da19164b944e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R03adced094b7448f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rb3b0736505764436"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rf70ceaec0af64720"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R9bb0772940044295"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rad4721993fb548c1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-08T22:16:25.645Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-09T01:06:21.478Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -496,7 +496,7 @@
       </x:c>
       <x:c r="B5" s="16" t="n">
         <x:f>COUNTIFS(Equipment!$AA$7:$AA$45,"Current")</x:f>
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
@@ -505,7 +505,7 @@
       </x:c>
       <x:c r="B6" s="16" t="n">
         <x:f>COUNTIFS('Electrical Lines'!$Y$7:$Y$59,"Current")</x:f>
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
@@ -514,7 +514,7 @@
       </x:c>
       <x:c r="B7" s="16" t="n">
         <x:f>COUNTIFS(Equipment!$AA$7:$AA$45,"Retired")+COUNTIFS('Electrical Lines'!$Y$7:$Y$59,"Retired")</x:f>
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>53ff13ffefd2679cbf8d12a1e21bde566f40af08275ae4f0ff95823f70ea1b77</x:v>
+        <x:v>d4067e8bb027f3bb435cc6fee67c0fc1d0e462a2d8802a6ada0bb37df793ab52</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>c883a38876b1d2b04788046ec5e1d87651113aa8dbfeb0f5415ba0b829f004ab</x:v>
+        <x:v>e2130aeffb518d934149fa35c32d858856db06e804d9cb98aac4f1896cd3b761</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1932,10 +1932,10 @@
         <x:v>F5</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>39.15</x:v>
+        <x:v>38.05</x:v>
       </x:c>
       <x:c r="G21" s="11" t="n">
-        <x:v>3.5</x:v>
+        <x:v>4.05</x:v>
       </x:c>
       <x:c r="H21" s="11" t="n">
         <x:v>-13.06</x:v>
@@ -1950,7 +1950,7 @@
         <x:v>On</x:v>
       </x:c>
       <x:c r="L21" s="8" t="str">
-        <x:v>460 × 490 × 490</x:v>
+        <x:v>665 × 490 × 490</x:v>
       </x:c>
       <x:c r="M21" s="8" t="str">
         <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
@@ -1959,10 +1959,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O21" s="11" t="n">
-        <x:v>97.66680426181422</x:v>
+        <x:v>72.99417126631943</x:v>
       </x:c>
       <x:c r="P21" s="11" t="n">
-        <x:v>-63.94867424281879</x:v>
+        <x:v>-51.090325667206876</x:v>
       </x:c>
       <x:c r="Q21" s="9"/>
       <x:c r="R21" s="9"/>
@@ -1981,7 +1981,7 @@
         <x:v>drop:FC1:F5:fan:-1:F240</x:v>
       </x:c>
       <x:c r="AC21" s="8" t="str">
-        <x:v>{"dim":1,"speed":1,"note":"ENGINEERING HOLD: 4 per wing at low speed cover 68/80 seats; noise and speech criteria fail. Gable anchors, concealment, sweep clearance and maintenance unapproved."}</x:v>
+        <x:v>{"dim":1,"speed":1,"note":"ENGINEERING HOLD: two fans per wing above window openings, clear of central saints strip. Same catalog flow/power/noise; extended bracket proxy unverified. Air, noise, speech, mounting, concealment an"}</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="96" customHeight="1">
@@ -2001,10 +2001,10 @@
         <x:v>F5</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>39.95</x:v>
+        <x:v>43.1</x:v>
       </x:c>
       <x:c r="G22" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>4.05</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
         <x:v>-13.06</x:v>
@@ -2019,7 +2019,7 @@
         <x:v>On</x:v>
       </x:c>
       <x:c r="L22" s="8" t="str">
-        <x:v>460 × 490 × 490</x:v>
+        <x:v>665 × 490 × 490</x:v>
       </x:c>
       <x:c r="M22" s="8" t="str">
         <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
@@ -2028,10 +2028,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O22" s="11" t="n">
-        <x:v>103.96981360840223</x:v>
+        <x:v>106.8256052315808</x:v>
       </x:c>
       <x:c r="P22" s="11" t="n">
-        <x:v>-30.04635493627147</x:v>
+        <x:v>-51.11711106599782</x:v>
       </x:c>
       <x:c r="Q22" s="9"/>
       <x:c r="R22" s="9"/>
@@ -2050,7 +2050,7 @@
         <x:v>drop:FC1:F5:fan:-1:F241</x:v>
       </x:c>
       <x:c r="AC22" s="8" t="str">
-        <x:v>{"dim":1,"speed":1,"note":"ENGINEERING HOLD: 4 per wing at low speed cover 68/80 seats; noise and speech criteria fail. Gable anchors, concealment, sweep clearance and maintenance unapproved."}</x:v>
+        <x:v>{"dim":1,"speed":1,"note":"ENGINEERING HOLD: two fans per wing above window openings, clear of central saints strip. Same catalog flow/power/noise; extended bracket proxy unverified. Air, noise, speech, mounting, concealment an"}</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="96" customHeight="1">
@@ -2070,10 +2070,10 @@
         <x:v>F5</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
-        <x:v>39.15</x:v>
+        <x:v>38.05</x:v>
       </x:c>
       <x:c r="G23" s="11" t="n">
-        <x:v>3.5</x:v>
+        <x:v>4.05</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
         <x:v>13.06</x:v>
@@ -2088,7 +2088,7 @@
         <x:v>On</x:v>
       </x:c>
       <x:c r="L23" s="8" t="str">
-        <x:v>460 × 490 × 490</x:v>
+        <x:v>665 × 490 × 490</x:v>
       </x:c>
       <x:c r="M23" s="8" t="str">
         <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
@@ -2097,10 +2097,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O23" s="11" t="n">
-        <x:v>-97.66680426181422</x:v>
+        <x:v>-72.99417126631943</x:v>
       </x:c>
       <x:c r="P23" s="11" t="n">
-        <x:v>-63.94867424281879</x:v>
+        <x:v>-51.090325667206876</x:v>
       </x:c>
       <x:c r="Q23" s="9"/>
       <x:c r="R23" s="9"/>
@@ -2119,7 +2119,7 @@
         <x:v>drop:FC1:F5:fan:1:F242</x:v>
       </x:c>
       <x:c r="AC23" s="8" t="str">
-        <x:v>{"dim":1,"speed":1,"note":"ENGINEERING HOLD: 4 per wing at low speed cover 68/80 seats; noise and speech criteria fail. Gable anchors, concealment, sweep clearance and maintenance unapproved."}</x:v>
+        <x:v>{"dim":1,"speed":1,"note":"ENGINEERING HOLD: two fans per wing above window openings, clear of central saints strip. Same catalog flow/power/noise; extended bracket proxy unverified. Air, noise, speech, mounting, concealment an"}</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="96" customHeight="1">
@@ -2139,10 +2139,10 @@
         <x:v>F5</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>39.95</x:v>
+        <x:v>43.1</x:v>
       </x:c>
       <x:c r="G24" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>4.05</x:v>
       </x:c>
       <x:c r="H24" s="11" t="n">
         <x:v>13.06</x:v>
@@ -2157,7 +2157,7 @@
         <x:v>On</x:v>
       </x:c>
       <x:c r="L24" s="8" t="str">
-        <x:v>460 × 490 × 490</x:v>
+        <x:v>665 × 490 × 490</x:v>
       </x:c>
       <x:c r="M24" s="8" t="str">
         <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
@@ -2166,10 +2166,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O24" s="11" t="n">
-        <x:v>-103.96981360840223</x:v>
+        <x:v>-106.8256052315808</x:v>
       </x:c>
       <x:c r="P24" s="11" t="n">
-        <x:v>-30.04635493627147</x:v>
+        <x:v>-51.11711106599782</x:v>
       </x:c>
       <x:c r="Q24" s="9"/>
       <x:c r="R24" s="9"/>
@@ -2188,7 +2188,7 @@
         <x:v>drop:FC1:F5:fan:1:F243</x:v>
       </x:c>
       <x:c r="AC24" s="8" t="str">
-        <x:v>{"dim":1,"speed":1,"note":"ENGINEERING HOLD: 4 per wing at low speed cover 68/80 seats; noise and speech criteria fail. Gable anchors, concealment, sweep clearance and maintenance unapproved."}</x:v>
+        <x:v>{"dim":1,"speed":1,"note":"ENGINEERING HOLD: two fans per wing above window openings, clear of central saints strip. Same catalog flow/power/noise; extended bracket proxy unverified. Air, noise, speech, mounting, concealment an"}</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="96" customHeight="1">
@@ -3424,7 +3424,7 @@
       <x:c r="Y42" s="13"/>
       <x:c r="Z42" s="9"/>
       <x:c r="AA42" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
       <x:c r="AB42" s="8" t="str">
         <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
@@ -3493,7 +3493,7 @@
       <x:c r="Y43" s="13"/>
       <x:c r="Z43" s="9"/>
       <x:c r="AA43" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
       <x:c r="AB43" s="8" t="str">
         <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
@@ -3562,7 +3562,7 @@
       <x:c r="Y44" s="13"/>
       <x:c r="Z44" s="9"/>
       <x:c r="AA44" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
       <x:c r="AB44" s="8" t="str">
         <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
@@ -3631,7 +3631,7 @@
       <x:c r="Y45" s="13"/>
       <x:c r="Z45" s="9"/>
       <x:c r="AA45" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
       <x:c r="AB45" s="8" t="str">
         <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15f81bb8e8a44bca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21ba3d8c79e149df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4921,9 +4921,7 @@
       </x:c>
       <x:c r="D23" s="8" t="str">
         <x:v>F240
-F241
-F-WING-B-3
-F-WING-B-4</x:v>
+F241</x:v>
       </x:c>
       <x:c r="E23" s="8" t="str">
         <x:v>DB1</x:v>
@@ -4939,7 +4937,7 @@
       </x:c>
       <x:c r="I23" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A23,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>32.419783516009694</x:v>
+        <x:v>33.83219768896557</x:v>
       </x:c>
       <x:c r="J23" s="11"/>
       <x:c r="K23" s="11" t="str">
@@ -4998,7 +4996,7 @@
       </x:c>
       <x:c r="I24" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A24,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>10.700287371134017</x:v>
+        <x:v>9.264333762886594</x:v>
       </x:c>
       <x:c r="J24" s="11"/>
       <x:c r="K24" s="11" t="str">
@@ -5059,7 +5057,7 @@
       </x:c>
       <x:c r="I25" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A25,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>12.144617268041237</x:v>
+        <x:v>9.264333762886599</x:v>
       </x:c>
       <x:c r="J25" s="11"/>
       <x:c r="K25" s="11" t="str">
@@ -5095,16 +5093,17 @@
     </x:row>
     <x:row r="26" ht="90" customHeight="1">
       <x:c r="A26" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+        <x:v>trunk:FC1:F5:fan:1</x:v>
       </x:c>
       <x:c r="B26" s="8" t="str">
-        <x:v>F5 → Wall fan · wing B · 3 · held review</x:v>
+        <x:v>F5 · H · circuit trunk</x:v>
       </x:c>
       <x:c r="C26" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D26" s="8" t="str">
-        <x:v>F-WING-B-3</x:v>
+        <x:v>F242
+F243</x:v>
       </x:c>
       <x:c r="E26" s="8" t="str">
         <x:v>DB1</x:v>
@@ -5116,11 +5115,11 @@
         <x:v>fan</x:v>
       </x:c>
       <x:c r="H26" s="8" t="str">
-        <x:v>drop</x:v>
+        <x:v>trunk</x:v>
       </x:c>
       <x:c r="I26" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A26,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>12.144617268041237</x:v>
+        <x:v>40.43219768896558</x:v>
       </x:c>
       <x:c r="J26" s="11"/>
       <x:c r="K26" s="11" t="str">
@@ -5137,7 +5136,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P26" s="8" t="str">
-        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q26" s="9"/>
       <x:c r="R26" s="9"/>
@@ -5150,22 +5149,20 @@
       <x:c r="Y26" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z26" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:-1</x:v>
-      </x:c>
+      <x:c r="Z26" s="8"/>
     </x:row>
     <x:row r="27" ht="90" customHeight="1">
       <x:c r="A27" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+        <x:v>drop:FC1:F5:fan:1:F242</x:v>
       </x:c>
       <x:c r="B27" s="8" t="str">
-        <x:v>F5 → Wall fan · wing B · 4 · held review</x:v>
+        <x:v>F5 → Wall fan · wing H · 1 · held review</x:v>
       </x:c>
       <x:c r="C27" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D27" s="8" t="str">
-        <x:v>F-WING-B-4</x:v>
+        <x:v>F242</x:v>
       </x:c>
       <x:c r="E27" s="8" t="str">
         <x:v>DB1</x:v>
@@ -5181,7 +5178,7 @@
       </x:c>
       <x:c r="I27" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A27,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>10.700287371134024</x:v>
+        <x:v>9.264333762886594</x:v>
       </x:c>
       <x:c r="J27" s="11"/>
       <x:c r="K27" s="11" t="str">
@@ -5212,24 +5209,21 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z27" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:-1</x:v>
+        <x:v>trunk:FC1:F5:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="90" customHeight="1">
       <x:c r="A28" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:1</x:v>
+        <x:v>drop:FC1:F5:fan:1:F243</x:v>
       </x:c>
       <x:c r="B28" s="8" t="str">
-        <x:v>F5 · H · circuit trunk</x:v>
+        <x:v>F5 → Wall fan · wing H · 2 · held review</x:v>
       </x:c>
       <x:c r="C28" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D28" s="8" t="str">
-        <x:v>F242
-F243
-F-WING-H-3
-F-WING-H-4</x:v>
+        <x:v>F243</x:v>
       </x:c>
       <x:c r="E28" s="8" t="str">
         <x:v>DB1</x:v>
@@ -5241,11 +5235,11 @@
         <x:v>fan</x:v>
       </x:c>
       <x:c r="H28" s="8" t="str">
-        <x:v>trunk</x:v>
+        <x:v>drop</x:v>
       </x:c>
       <x:c r="I28" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A28,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>39.0197835160097</x:v>
+        <x:v>9.264333762886599</x:v>
       </x:c>
       <x:c r="J28" s="11"/>
       <x:c r="K28" s="11" t="str">
@@ -5262,7 +5256,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P28" s="8" t="str">
-        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
       </x:c>
       <x:c r="Q28" s="9"/>
       <x:c r="R28" s="9"/>
@@ -5275,36 +5269,40 @@
       <x:c r="Y28" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z28" s="8"/>
+      <x:c r="Z28" s="8" t="str">
+        <x:v>trunk:FC1:F5:fan:1</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="90" customHeight="1">
       <x:c r="A29" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F242</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
       <x:c r="B29" s="8" t="str">
-        <x:v>F5 → Wall fan · wing H · 1 · held review</x:v>
+        <x:v>F2 · B · circuit trunk</x:v>
       </x:c>
       <x:c r="C29" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D29" s="8" t="str">
-        <x:v>F242</x:v>
+        <x:v>F244
+F246
+F248</x:v>
       </x:c>
       <x:c r="E29" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F29" s="8" t="str">
-        <x:v>F5</x:v>
+        <x:v>F2</x:v>
       </x:c>
       <x:c r="G29" s="8" t="str">
         <x:v>fan</x:v>
       </x:c>
       <x:c r="H29" s="8" t="str">
-        <x:v>drop</x:v>
+        <x:v>trunk</x:v>
       </x:c>
       <x:c r="I29" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A29,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>10.700287371134017</x:v>
+        <x:v>58.576130311179185</x:v>
       </x:c>
       <x:c r="J29" s="11"/>
       <x:c r="K29" s="11" t="str">
@@ -5321,7 +5319,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P29" s="8" t="str">
-        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q29" s="9"/>
       <x:c r="R29" s="9"/>
@@ -5334,28 +5332,26 @@
       <x:c r="Y29" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z29" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:1</x:v>
-      </x:c>
+      <x:c r="Z29" s="8"/>
     </x:row>
     <x:row r="30" ht="90" customHeight="1">
       <x:c r="A30" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F243</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F244</x:v>
       </x:c>
       <x:c r="B30" s="8" t="str">
-        <x:v>F5 → Wall fan · wing H · 2 · held review</x:v>
+        <x:v>F2 → Wall fan · axis 4 · B</x:v>
       </x:c>
       <x:c r="C30" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D30" s="8" t="str">
-        <x:v>F243</x:v>
+        <x:v>F244</x:v>
       </x:c>
       <x:c r="E30" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F30" s="8" t="str">
-        <x:v>F5</x:v>
+        <x:v>F2</x:v>
       </x:c>
       <x:c r="G30" s="8" t="str">
         <x:v>fan</x:v>
@@ -5365,7 +5361,7 @@
       </x:c>
       <x:c r="I30" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A30,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>12.144617268041237</x:v>
+        <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J30" s="11"/>
       <x:c r="K30" s="11" t="str">
@@ -5382,7 +5378,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P30" s="8" t="str">
-        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
       </x:c>
       <x:c r="Q30" s="9"/>
       <x:c r="R30" s="9"/>
@@ -5396,27 +5392,27 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z30" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:1</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="90" customHeight="1">
       <x:c r="A31" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F246</x:v>
       </x:c>
       <x:c r="B31" s="8" t="str">
-        <x:v>F5 → Wall fan · wing H · 3 · held review</x:v>
+        <x:v>F2 → Wall fan · axis 6 · B</x:v>
       </x:c>
       <x:c r="C31" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D31" s="8" t="str">
-        <x:v>F-WING-H-3</x:v>
+        <x:v>F246</x:v>
       </x:c>
       <x:c r="E31" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F31" s="8" t="str">
-        <x:v>F5</x:v>
+        <x:v>F2</x:v>
       </x:c>
       <x:c r="G31" s="8" t="str">
         <x:v>fan</x:v>
@@ -5426,7 +5422,7 @@
       </x:c>
       <x:c r="I31" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A31,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>12.144617268041237</x:v>
+        <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J31" s="11"/>
       <x:c r="K31" s="11" t="str">
@@ -5443,7 +5439,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P31" s="8" t="str">
-        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
       </x:c>
       <x:c r="Q31" s="9"/>
       <x:c r="R31" s="9"/>
@@ -5457,27 +5453,27 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z31" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:1</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="90" customHeight="1">
       <x:c r="A32" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F248</x:v>
       </x:c>
       <x:c r="B32" s="8" t="str">
-        <x:v>F5 → Wall fan · wing H · 4 · held review</x:v>
+        <x:v>F2 → Wall fan · axis 8 · B</x:v>
       </x:c>
       <x:c r="C32" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D32" s="8" t="str">
-        <x:v>F-WING-H-4</x:v>
+        <x:v>F248</x:v>
       </x:c>
       <x:c r="E32" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F32" s="8" t="str">
-        <x:v>F5</x:v>
+        <x:v>F2</x:v>
       </x:c>
       <x:c r="G32" s="8" t="str">
         <x:v>fan</x:v>
@@ -5487,7 +5483,7 @@
       </x:c>
       <x:c r="I32" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A32,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>10.700287371134024</x:v>
+        <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J32" s="11"/>
       <x:c r="K32" s="11" t="str">
@@ -5504,7 +5500,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P32" s="8" t="str">
-        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
       </x:c>
       <x:c r="Q32" s="9"/>
       <x:c r="R32" s="9"/>
@@ -5518,23 +5514,23 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z32" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:1</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="90" customHeight="1">
       <x:c r="A33" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B33" s="8" t="str">
-        <x:v>F2 · B · circuit trunk</x:v>
+        <x:v>F2 · H · circuit trunk</x:v>
       </x:c>
       <x:c r="C33" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D33" s="8" t="str">
-        <x:v>F244
-F246
-F248</x:v>
+        <x:v>F245
+F247
+F249</x:v>
       </x:c>
       <x:c r="E33" s="8" t="str">
         <x:v>DB1</x:v>
@@ -5550,7 +5546,7 @@
       </x:c>
       <x:c r="I33" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A33,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>58.576130311179185</x:v>
+        <x:v>65.17613031117918</x:v>
       </x:c>
       <x:c r="J33" s="11"/>
       <x:c r="K33" s="11" t="str">
@@ -5584,16 +5580,16 @@
     </x:row>
     <x:row r="34" ht="90" customHeight="1">
       <x:c r="A34" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:-1:F244</x:v>
+        <x:v>drop:FC1:F2:fan:1:F245</x:v>
       </x:c>
       <x:c r="B34" s="8" t="str">
-        <x:v>F2 → Wall fan · axis 4 · B</x:v>
+        <x:v>F2 → Wall fan · axis 4 · H</x:v>
       </x:c>
       <x:c r="C34" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D34" s="8" t="str">
-        <x:v>F244</x:v>
+        <x:v>F245</x:v>
       </x:c>
       <x:c r="E34" s="8" t="str">
         <x:v>DB1</x:v>
@@ -5640,21 +5636,21 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z34" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="90" customHeight="1">
       <x:c r="A35" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:-1:F246</x:v>
+        <x:v>drop:FC1:F2:fan:1:F247</x:v>
       </x:c>
       <x:c r="B35" s="8" t="str">
-        <x:v>F2 → Wall fan · axis 6 · B</x:v>
+        <x:v>F2 → Wall fan · axis 6 · H</x:v>
       </x:c>
       <x:c r="C35" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D35" s="8" t="str">
-        <x:v>F246</x:v>
+        <x:v>F247</x:v>
       </x:c>
       <x:c r="E35" s="8" t="str">
         <x:v>DB1</x:v>
@@ -5701,21 +5697,21 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z35" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="90" customHeight="1">
       <x:c r="A36" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:-1:F248</x:v>
+        <x:v>drop:FC1:F2:fan:1:F249</x:v>
       </x:c>
       <x:c r="B36" s="8" t="str">
-        <x:v>F2 → Wall fan · axis 8 · B</x:v>
+        <x:v>F2 → Wall fan · axis 8 · H</x:v>
       </x:c>
       <x:c r="C36" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D36" s="8" t="str">
-        <x:v>F248</x:v>
+        <x:v>F249</x:v>
       </x:c>
       <x:c r="E36" s="8" t="str">
         <x:v>DB1</x:v>
@@ -5762,29 +5758,27 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z36" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="90" customHeight="1">
       <x:c r="A37" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B37" s="8" t="str">
-        <x:v>F2 · H · circuit trunk</x:v>
+        <x:v>F4 · B · circuit trunk</x:v>
       </x:c>
       <x:c r="C37" s="8" t="str">
-        <x:v>FC1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="D37" s="8" t="str">
-        <x:v>F245
-F247
-F249</x:v>
+        <x:v>F250</x:v>
       </x:c>
       <x:c r="E37" s="8" t="str">
-        <x:v>DB1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="F37" s="8" t="str">
-        <x:v>F2</x:v>
+        <x:v>F4</x:v>
       </x:c>
       <x:c r="G37" s="8" t="str">
         <x:v>fan</x:v>
@@ -5794,7 +5788,7 @@
       </x:c>
       <x:c r="I37" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A37,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>65.17613031117918</x:v>
+        <x:v>12.517</x:v>
       </x:c>
       <x:c r="J37" s="11"/>
       <x:c r="K37" s="11" t="str">
@@ -5828,22 +5822,22 @@
     </x:row>
     <x:row r="38" ht="90" customHeight="1">
       <x:c r="A38" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F245</x:v>
+        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
       </x:c>
       <x:c r="B38" s="8" t="str">
-        <x:v>F2 → Wall fan · axis 4 · H</x:v>
+        <x:v>F4 → Entrance circulator · B</x:v>
       </x:c>
       <x:c r="C38" s="8" t="str">
-        <x:v>FC1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="D38" s="8" t="str">
-        <x:v>F245</x:v>
+        <x:v>F250</x:v>
       </x:c>
       <x:c r="E38" s="8" t="str">
-        <x:v>DB1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="F38" s="8" t="str">
-        <x:v>F2</x:v>
+        <x:v>F4</x:v>
       </x:c>
       <x:c r="G38" s="8" t="str">
         <x:v>fan</x:v>
@@ -5853,7 +5847,7 @@
       </x:c>
       <x:c r="I38" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A38,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>0.7520000000000007</x:v>
+        <x:v>7.91542691446789</x:v>
       </x:c>
       <x:c r="J38" s="11"/>
       <x:c r="K38" s="11" t="str">
@@ -5870,7 +5864,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P38" s="8" t="str">
-        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
+        <x:v>Concealed entrance wall band, solid pier and local termination.</x:v>
       </x:c>
       <x:c r="Q38" s="9"/>
       <x:c r="R38" s="9"/>
@@ -5884,37 +5878,37 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z38" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="90" customHeight="1">
       <x:c r="A39" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F247</x:v>
+        <x:v>trunk:DB2:F4:fan:1</x:v>
       </x:c>
       <x:c r="B39" s="8" t="str">
-        <x:v>F2 → Wall fan · axis 6 · H</x:v>
+        <x:v>F4 · H · circuit trunk</x:v>
       </x:c>
       <x:c r="C39" s="8" t="str">
-        <x:v>FC1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="D39" s="8" t="str">
-        <x:v>F247</x:v>
+        <x:v>F251</x:v>
       </x:c>
       <x:c r="E39" s="8" t="str">
-        <x:v>DB1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="F39" s="8" t="str">
-        <x:v>F2</x:v>
+        <x:v>F4</x:v>
       </x:c>
       <x:c r="G39" s="8" t="str">
         <x:v>fan</x:v>
       </x:c>
       <x:c r="H39" s="8" t="str">
-        <x:v>drop</x:v>
+        <x:v>trunk</x:v>
       </x:c>
       <x:c r="I39" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A39,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>0.7520000000000007</x:v>
+        <x:v>19.117</x:v>
       </x:c>
       <x:c r="J39" s="11"/>
       <x:c r="K39" s="11" t="str">
@@ -5931,7 +5925,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P39" s="8" t="str">
-        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q39" s="9"/>
       <x:c r="R39" s="9"/>
@@ -5944,28 +5938,26 @@
       <x:c r="Y39" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z39" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
-      </x:c>
+      <x:c r="Z39" s="8"/>
     </x:row>
     <x:row r="40" ht="90" customHeight="1">
       <x:c r="A40" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F249</x:v>
+        <x:v>drop:DB2:F4:fan:1:F251</x:v>
       </x:c>
       <x:c r="B40" s="8" t="str">
-        <x:v>F2 → Wall fan · axis 8 · H</x:v>
+        <x:v>F4 → Entrance circulator · H</x:v>
       </x:c>
       <x:c r="C40" s="8" t="str">
-        <x:v>FC1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="D40" s="8" t="str">
-        <x:v>F249</x:v>
+        <x:v>F251</x:v>
       </x:c>
       <x:c r="E40" s="8" t="str">
-        <x:v>DB1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="F40" s="8" t="str">
-        <x:v>F2</x:v>
+        <x:v>F4</x:v>
       </x:c>
       <x:c r="G40" s="8" t="str">
         <x:v>fan</x:v>
@@ -5975,7 +5967,7 @@
       </x:c>
       <x:c r="I40" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A40,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>0.7520000000000007</x:v>
+        <x:v>7.91542691446789</x:v>
       </x:c>
       <x:c r="J40" s="11"/>
       <x:c r="K40" s="11" t="str">
@@ -5992,7 +5984,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P40" s="8" t="str">
-        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
+        <x:v>Concealed entrance wall band, solid pier and local termination.</x:v>
       </x:c>
       <x:c r="Q40" s="9"/>
       <x:c r="R40" s="9"/>
@@ -6006,27 +5998,31 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z40" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>trunk:DB2:F4:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="90" customHeight="1">
       <x:c r="A41" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B41" s="8" t="str">
-        <x:v>F4 · B · circuit trunk</x:v>
+        <x:v>V1 · B · circuit trunk</x:v>
       </x:c>
       <x:c r="C41" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>FC1</x:v>
       </x:c>
       <x:c r="D41" s="8" t="str">
-        <x:v>F250</x:v>
+        <x:v>F252
+F253
+F256
+F257
+F260</x:v>
       </x:c>
       <x:c r="E41" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>DB1</x:v>
       </x:c>
       <x:c r="F41" s="8" t="str">
-        <x:v>F4</x:v>
+        <x:v>V1</x:v>
       </x:c>
       <x:c r="G41" s="8" t="str">
         <x:v>fan</x:v>
@@ -6036,7 +6032,7 @@
       </x:c>
       <x:c r="I41" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A41,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>12.517</x:v>
+        <x:v>67.54713031117919</x:v>
       </x:c>
       <x:c r="J41" s="11"/>
       <x:c r="K41" s="11" t="str">
@@ -6070,22 +6066,22 @@
     </x:row>
     <x:row r="42" ht="90" customHeight="1">
       <x:c r="A42" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
       </x:c>
       <x:c r="B42" s="8" t="str">
-        <x:v>F4 → Entrance circulator · B</x:v>
+        <x:v>V1 → Exhaust fan · front gable · B outer</x:v>
       </x:c>
       <x:c r="C42" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>FC1</x:v>
       </x:c>
       <x:c r="D42" s="8" t="str">
-        <x:v>F250</x:v>
+        <x:v>F252</x:v>
       </x:c>
       <x:c r="E42" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>DB1</x:v>
       </x:c>
       <x:c r="F42" s="8" t="str">
-        <x:v>F4</x:v>
+        <x:v>V1</x:v>
       </x:c>
       <x:c r="G42" s="8" t="str">
         <x:v>fan</x:v>
@@ -6095,7 +6091,7 @@
       </x:c>
       <x:c r="I42" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A42,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>7.91542691446789</x:v>
+        <x:v>8.69282092938182</x:v>
       </x:c>
       <x:c r="J42" s="11"/>
       <x:c r="K42" s="11" t="str">
@@ -6112,7 +6108,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P42" s="8" t="str">
-        <x:v>Concealed entrance wall band, solid pier and local termination.</x:v>
+        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
       </x:c>
       <x:c r="Q42" s="9"/>
       <x:c r="R42" s="9"/>
@@ -6126,37 +6122,37 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z42" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="90" customHeight="1">
       <x:c r="A43" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
       </x:c>
       <x:c r="B43" s="8" t="str">
-        <x:v>F4 · H · circuit trunk</x:v>
+        <x:v>V1 → Exhaust fan · front gable · B inner</x:v>
       </x:c>
       <x:c r="C43" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>FC1</x:v>
       </x:c>
       <x:c r="D43" s="8" t="str">
-        <x:v>F251</x:v>
+        <x:v>F253</x:v>
       </x:c>
       <x:c r="E43" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>DB1</x:v>
       </x:c>
       <x:c r="F43" s="8" t="str">
-        <x:v>F4</x:v>
+        <x:v>V1</x:v>
       </x:c>
       <x:c r="G43" s="8" t="str">
         <x:v>fan</x:v>
       </x:c>
       <x:c r="H43" s="8" t="str">
-        <x:v>trunk</x:v>
+        <x:v>drop</x:v>
       </x:c>
       <x:c r="I43" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A43,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>19.117</x:v>
+        <x:v>11.831150261440472</x:v>
       </x:c>
       <x:c r="J43" s="11"/>
       <x:c r="K43" s="11" t="str">
@@ -6173,7 +6169,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P43" s="8" t="str">
-        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
+        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
       </x:c>
       <x:c r="Q43" s="9"/>
       <x:c r="R43" s="9"/>
@@ -6186,26 +6182,28 @@
       <x:c r="Y43" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z43" s="8"/>
+      <x:c r="Z43" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="90" customHeight="1">
       <x:c r="A44" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
       </x:c>
       <x:c r="B44" s="8" t="str">
-        <x:v>F4 → Entrance circulator · H</x:v>
+        <x:v>V1 → Exhaust fan · wing gable B · front</x:v>
       </x:c>
       <x:c r="C44" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>FC1</x:v>
       </x:c>
       <x:c r="D44" s="8" t="str">
-        <x:v>F251</x:v>
+        <x:v>F256</x:v>
       </x:c>
       <x:c r="E44" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>DB1</x:v>
       </x:c>
       <x:c r="F44" s="8" t="str">
-        <x:v>F4</x:v>
+        <x:v>V1</x:v>
       </x:c>
       <x:c r="G44" s="8" t="str">
         <x:v>fan</x:v>
@@ -6215,7 +6213,7 @@
       </x:c>
       <x:c r="I44" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A44,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>7.91542691446789</x:v>
+        <x:v>6.973264175257731</x:v>
       </x:c>
       <x:c r="J44" s="11"/>
       <x:c r="K44" s="11" t="str">
@@ -6232,7 +6230,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P44" s="8" t="str">
-        <x:v>Concealed entrance wall band, solid pier and local termination.</x:v>
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
       </x:c>
       <x:c r="Q44" s="9"/>
       <x:c r="R44" s="9"/>
@@ -6246,25 +6244,21 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z44" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="90" customHeight="1">
       <x:c r="A45" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
       </x:c>
       <x:c r="B45" s="8" t="str">
-        <x:v>V1 · B · circuit trunk</x:v>
+        <x:v>V1 → Exhaust fan · wing gable B · rear</x:v>
       </x:c>
       <x:c r="C45" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D45" s="8" t="str">
-        <x:v>F252
-F253
-F256
-F257
-F260</x:v>
+        <x:v>F257</x:v>
       </x:c>
       <x:c r="E45" s="8" t="str">
         <x:v>DB1</x:v>
@@ -6276,11 +6270,11 @@
         <x:v>fan</x:v>
       </x:c>
       <x:c r="H45" s="8" t="str">
-        <x:v>trunk</x:v>
+        <x:v>drop</x:v>
       </x:c>
       <x:c r="I45" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A45,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>67.54713031117919</x:v>
+        <x:v>6.973264175257731</x:v>
       </x:c>
       <x:c r="J45" s="11"/>
       <x:c r="K45" s="11" t="str">
@@ -6297,7 +6291,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P45" s="8" t="str">
-        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
       </x:c>
       <x:c r="Q45" s="9"/>
       <x:c r="R45" s="9"/>
@@ -6310,20 +6304,22 @@
       <x:c r="Y45" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z45" s="8"/>
+      <x:c r="Z45" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="90" customHeight="1">
       <x:c r="A46" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
       </x:c>
       <x:c r="B46" s="8" t="str">
-        <x:v>V1 → Exhaust fan · front gable · B outer</x:v>
+        <x:v>V1 → Exhaust fan · service room</x:v>
       </x:c>
       <x:c r="C46" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D46" s="8" t="str">
-        <x:v>F252</x:v>
+        <x:v>F260</x:v>
       </x:c>
       <x:c r="E46" s="8" t="str">
         <x:v>DB1</x:v>
@@ -6339,7 +6335,7 @@
       </x:c>
       <x:c r="I46" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A46,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>8.69282092938182</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="J46" s="11"/>
       <x:c r="K46" s="11" t="str">
@@ -6356,7 +6352,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P46" s="8" t="str">
-        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
+        <x:v>Rear-wall band and local termination; gable / weatherproof entry details pending.</x:v>
       </x:c>
       <x:c r="Q46" s="9"/>
       <x:c r="R46" s="9"/>
@@ -6375,16 +6371,19 @@
     </x:row>
     <x:row r="47" ht="90" customHeight="1">
       <x:c r="A47" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B47" s="8" t="str">
-        <x:v>V1 → Exhaust fan · front gable · B inner</x:v>
+        <x:v>V1 · H · circuit trunk</x:v>
       </x:c>
       <x:c r="C47" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D47" s="8" t="str">
-        <x:v>F253</x:v>
+        <x:v>F254
+F255
+F258
+F259</x:v>
       </x:c>
       <x:c r="E47" s="8" t="str">
         <x:v>DB1</x:v>
@@ -6396,11 +6395,11 @@
         <x:v>fan</x:v>
       </x:c>
       <x:c r="H47" s="8" t="str">
-        <x:v>drop</x:v>
+        <x:v>trunk</x:v>
       </x:c>
       <x:c r="I47" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A47,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>11.831150261440472</x:v>
+        <x:v>74.14713031117918</x:v>
       </x:c>
       <x:c r="J47" s="11"/>
       <x:c r="K47" s="11" t="str">
@@ -6417,7 +6416,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P47" s="8" t="str">
-        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q47" s="9"/>
       <x:c r="R47" s="9"/>
@@ -6430,22 +6429,20 @@
       <x:c r="Y47" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z47" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
-      </x:c>
+      <x:c r="Z47" s="8"/>
     </x:row>
     <x:row r="48" ht="90" customHeight="1">
       <x:c r="A48" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B48" s="8" t="str">
-        <x:v>V1 → Exhaust fan · wing gable B · front</x:v>
+        <x:v>V1 → Exhaust fan · front gable · H inner</x:v>
       </x:c>
       <x:c r="C48" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D48" s="8" t="str">
-        <x:v>F256</x:v>
+        <x:v>F254</x:v>
       </x:c>
       <x:c r="E48" s="8" t="str">
         <x:v>DB1</x:v>
@@ -6461,7 +6458,7 @@
       </x:c>
       <x:c r="I48" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A48,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>6.973264175257731</x:v>
+        <x:v>11.831150261440472</x:v>
       </x:c>
       <x:c r="J48" s="11"/>
       <x:c r="K48" s="11" t="str">
@@ -6478,7 +6475,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P48" s="8" t="str">
-        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
       </x:c>
       <x:c r="Q48" s="9"/>
       <x:c r="R48" s="9"/>
@@ -6492,21 +6489,21 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z48" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="90" customHeight="1">
       <x:c r="A49" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B49" s="8" t="str">
-        <x:v>V1 → Exhaust fan · wing gable B · rear</x:v>
+        <x:v>V1 → Exhaust fan · front gable · H outer</x:v>
       </x:c>
       <x:c r="C49" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D49" s="8" t="str">
-        <x:v>F257</x:v>
+        <x:v>F255</x:v>
       </x:c>
       <x:c r="E49" s="8" t="str">
         <x:v>DB1</x:v>
@@ -6522,7 +6519,7 @@
       </x:c>
       <x:c r="I49" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A49,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>6.973264175257731</x:v>
+        <x:v>8.69282092938182</x:v>
       </x:c>
       <x:c r="J49" s="11"/>
       <x:c r="K49" s="11" t="str">
@@ -6539,7 +6536,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P49" s="8" t="str">
-        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
       </x:c>
       <x:c r="Q49" s="9"/>
       <x:c r="R49" s="9"/>
@@ -6553,21 +6550,21 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z49" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="90" customHeight="1">
       <x:c r="A50" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
+        <x:v>drop:FC1:V1:fan:1:F258</x:v>
       </x:c>
       <x:c r="B50" s="8" t="str">
-        <x:v>V1 → Exhaust fan · service room</x:v>
+        <x:v>V1 → Exhaust fan · wing gable H · front</x:v>
       </x:c>
       <x:c r="C50" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D50" s="8" t="str">
-        <x:v>F260</x:v>
+        <x:v>F258</x:v>
       </x:c>
       <x:c r="E50" s="8" t="str">
         <x:v>DB1</x:v>
@@ -6583,7 +6580,7 @@
       </x:c>
       <x:c r="I50" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A50,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>10.2</x:v>
+        <x:v>6.973264175257731</x:v>
       </x:c>
       <x:c r="J50" s="11"/>
       <x:c r="K50" s="11" t="str">
@@ -6600,7 +6597,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P50" s="8" t="str">
-        <x:v>Rear-wall band and local termination; gable / weatherproof entry details pending.</x:v>
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
       </x:c>
       <x:c r="Q50" s="9"/>
       <x:c r="R50" s="9"/>
@@ -6614,24 +6611,21 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z50" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="90" customHeight="1">
       <x:c r="A51" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F259</x:v>
       </x:c>
       <x:c r="B51" s="8" t="str">
-        <x:v>V1 · H · circuit trunk</x:v>
+        <x:v>V1 → Exhaust fan · wing gable H · rear</x:v>
       </x:c>
       <x:c r="C51" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D51" s="8" t="str">
-        <x:v>F254
-F255
-F258
-F259</x:v>
+        <x:v>F259</x:v>
       </x:c>
       <x:c r="E51" s="8" t="str">
         <x:v>DB1</x:v>
@@ -6643,11 +6637,11 @@
         <x:v>fan</x:v>
       </x:c>
       <x:c r="H51" s="8" t="str">
-        <x:v>trunk</x:v>
+        <x:v>drop</x:v>
       </x:c>
       <x:c r="I51" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A51,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>74.14713031117918</x:v>
+        <x:v>6.973264175257731</x:v>
       </x:c>
       <x:c r="J51" s="11"/>
       <x:c r="K51" s="11" t="str">
@@ -6664,7 +6658,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P51" s="8" t="str">
-        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
       </x:c>
       <x:c r="Q51" s="9"/>
       <x:c r="R51" s="9"/>
@@ -6677,26 +6671,28 @@
       <x:c r="Y51" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z51" s="8"/>
+      <x:c r="Z51" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="90" customHeight="1">
       <x:c r="A52" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
       </x:c>
       <x:c r="B52" s="8" t="str">
-        <x:v>V1 → Exhaust fan · front gable · H inner</x:v>
+        <x:v>F5 → Wall fan · wing B · 3 · held review</x:v>
       </x:c>
       <x:c r="C52" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D52" s="8" t="str">
-        <x:v>F254</x:v>
+        <x:v>F-WING-B-3</x:v>
       </x:c>
       <x:c r="E52" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F52" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>F5</x:v>
       </x:c>
       <x:c r="G52" s="8" t="str">
         <x:v>fan</x:v>
@@ -6706,7 +6702,7 @@
       </x:c>
       <x:c r="I52" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A52,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>11.831150261440472</x:v>
+        <x:v>12.144617268041237</x:v>
       </x:c>
       <x:c r="J52" s="11"/>
       <x:c r="K52" s="11" t="str">
@@ -6723,7 +6719,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P52" s="8" t="str">
-        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
       </x:c>
       <x:c r="Q52" s="9"/>
       <x:c r="R52" s="9"/>
@@ -6734,30 +6730,30 @@
       <x:c r="W52" s="9"/>
       <x:c r="X52" s="9"/>
       <x:c r="Y52" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
       <x:c r="Z52" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>trunk:FC1:F5:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="90" customHeight="1">
       <x:c r="A53" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
       </x:c>
       <x:c r="B53" s="8" t="str">
-        <x:v>V1 → Exhaust fan · front gable · H outer</x:v>
+        <x:v>F5 → Wall fan · wing B · 4 · held review</x:v>
       </x:c>
       <x:c r="C53" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D53" s="8" t="str">
-        <x:v>F255</x:v>
+        <x:v>F-WING-B-4</x:v>
       </x:c>
       <x:c r="E53" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F53" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>F5</x:v>
       </x:c>
       <x:c r="G53" s="8" t="str">
         <x:v>fan</x:v>
@@ -6767,7 +6763,7 @@
       </x:c>
       <x:c r="I53" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A53,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>8.69282092938182</x:v>
+        <x:v>10.700287371134024</x:v>
       </x:c>
       <x:c r="J53" s="11"/>
       <x:c r="K53" s="11" t="str">
@@ -6784,7 +6780,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P53" s="8" t="str">
-        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
       </x:c>
       <x:c r="Q53" s="9"/>
       <x:c r="R53" s="9"/>
@@ -6795,30 +6791,30 @@
       <x:c r="W53" s="9"/>
       <x:c r="X53" s="9"/>
       <x:c r="Y53" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
       <x:c r="Z53" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>trunk:FC1:F5:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="90" customHeight="1">
       <x:c r="A54" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F258</x:v>
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
       </x:c>
       <x:c r="B54" s="8" t="str">
-        <x:v>V1 → Exhaust fan · wing gable H · front</x:v>
+        <x:v>F5 → Wall fan · wing H · 3 · held review</x:v>
       </x:c>
       <x:c r="C54" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D54" s="8" t="str">
-        <x:v>F258</x:v>
+        <x:v>F-WING-H-3</x:v>
       </x:c>
       <x:c r="E54" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F54" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>F5</x:v>
       </x:c>
       <x:c r="G54" s="8" t="str">
         <x:v>fan</x:v>
@@ -6828,7 +6824,7 @@
       </x:c>
       <x:c r="I54" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A54,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>6.973264175257731</x:v>
+        <x:v>12.144617268041237</x:v>
       </x:c>
       <x:c r="J54" s="11"/>
       <x:c r="K54" s="11" t="str">
@@ -6856,30 +6852,30 @@
       <x:c r="W54" s="9"/>
       <x:c r="X54" s="9"/>
       <x:c r="Y54" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
       <x:c r="Z54" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>trunk:FC1:F5:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="90" customHeight="1">
       <x:c r="A55" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F259</x:v>
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
       </x:c>
       <x:c r="B55" s="8" t="str">
-        <x:v>V1 → Exhaust fan · wing gable H · rear</x:v>
+        <x:v>F5 → Wall fan · wing H · 4 · held review</x:v>
       </x:c>
       <x:c r="C55" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D55" s="8" t="str">
-        <x:v>F259</x:v>
+        <x:v>F-WING-H-4</x:v>
       </x:c>
       <x:c r="E55" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F55" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>F5</x:v>
       </x:c>
       <x:c r="G55" s="8" t="str">
         <x:v>fan</x:v>
@@ -6889,7 +6885,7 @@
       </x:c>
       <x:c r="I55" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$354,A55,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>6.973264175257731</x:v>
+        <x:v>10.700287371134024</x:v>
       </x:c>
       <x:c r="J55" s="11"/>
       <x:c r="K55" s="11" t="str">
@@ -6917,10 +6913,10 @@
       <x:c r="W55" s="9"/>
       <x:c r="X55" s="9"/>
       <x:c r="Y55" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
       <x:c r="Z55" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>trunk:FC1:F5:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="90" customHeight="1">
@@ -7184,7 +7180,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R164461c60b77468a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb28d14df9954578"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10478,17 +10474,17 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C140" s="11" t="n">
-        <x:v>39.15</x:v>
+        <x:v>38.05</x:v>
       </x:c>
       <x:c r="D140" s="11" t="n">
-        <x:v>8.122287371134018</x:v>
+        <x:v>7.236333762886593</x:v>
       </x:c>
       <x:c r="E140" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F140" s="11" t="n">
         <x:f>SQRT((C140-C139)^2+(D140-D139)^2+(E140-E139)^2)</x:f>
-        <x:v>1.8297183604201064</x:v>
+        <x:v>3.2421325333759836</x:v>
       </x:c>
       <x:c r="G140" s="8" t="str">
         <x:v>Current</x:v>
@@ -10502,10 +10498,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C141" s="11" t="n">
-        <x:v>39.15</x:v>
+        <x:v>38.05</x:v>
       </x:c>
       <x:c r="D141" s="11" t="n">
-        <x:v>8.122287371134018</x:v>
+        <x:v>7.236333762886593</x:v>
       </x:c>
       <x:c r="E141" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -10526,10 +10522,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C142" s="11" t="n">
-        <x:v>39.15</x:v>
+        <x:v>38.05</x:v>
       </x:c>
       <x:c r="D142" s="11" t="n">
-        <x:v>8.122287371134016</x:v>
+        <x:v>7.236333762886593</x:v>
       </x:c>
       <x:c r="E142" s="11" t="n">
         <x:v>-13.249</x:v>
@@ -10550,17 +10546,17 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C143" s="11" t="n">
-        <x:v>39.15</x:v>
+        <x:v>38.05</x:v>
       </x:c>
       <x:c r="D143" s="11" t="n">
-        <x:v>3.5</x:v>
+        <x:v>4.05</x:v>
       </x:c>
       <x:c r="E143" s="11" t="n">
         <x:v>-13.249</x:v>
       </x:c>
       <x:c r="F143" s="11" t="n">
         <x:f>SQRT((C143-C142)^2+(D143-D142)^2+(E143-E142)^2)</x:f>
-        <x:v>4.622287371134016</x:v>
+        <x:v>3.1863337628865933</x:v>
       </x:c>
       <x:c r="G143" s="8" t="str">
         <x:v>Current</x:v>
@@ -10574,10 +10570,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C144" s="11" t="n">
-        <x:v>39.15</x:v>
+        <x:v>38.05</x:v>
       </x:c>
       <x:c r="D144" s="11" t="n">
-        <x:v>3.5</x:v>
+        <x:v>4.05</x:v>
       </x:c>
       <x:c r="E144" s="11" t="n">
         <x:v>-13.06</x:v>
@@ -10598,10 +10594,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C145" s="11" t="n">
-        <x:v>39.95</x:v>
+        <x:v>43.1</x:v>
       </x:c>
       <x:c r="D145" s="11" t="n">
-        <x:v>8.766617268041237</x:v>
+        <x:v>7.236333762886598</x:v>
       </x:c>
       <x:c r="E145" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -10622,10 +10618,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C146" s="11" t="n">
-        <x:v>39.95</x:v>
+        <x:v>43.1</x:v>
       </x:c>
       <x:c r="D146" s="11" t="n">
-        <x:v>8.766617268041237</x:v>
+        <x:v>7.2363337628865985</x:v>
       </x:c>
       <x:c r="E146" s="11" t="n">
         <x:v>-13.249</x:v>
@@ -10646,17 +10642,17 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C147" s="11" t="n">
-        <x:v>39.95</x:v>
+        <x:v>43.1</x:v>
       </x:c>
       <x:c r="D147" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>4.05</x:v>
       </x:c>
       <x:c r="E147" s="11" t="n">
         <x:v>-13.249</x:v>
       </x:c>
       <x:c r="F147" s="11" t="n">
         <x:f>SQRT((C147-C146)^2+(D147-D146)^2+(E147-E146)^2)</x:f>
-        <x:v>6.066617268041237</x:v>
+        <x:v>3.1863337628865986</x:v>
       </x:c>
       <x:c r="G147" s="8" t="str">
         <x:v>Current</x:v>
@@ -10670,10 +10666,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C148" s="11" t="n">
-        <x:v>39.95</x:v>
+        <x:v>43.1</x:v>
       </x:c>
       <x:c r="D148" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>4.05</x:v>
       </x:c>
       <x:c r="E148" s="11" t="n">
         <x:v>-13.06</x:v>
@@ -10688,19 +10684,19 @@
     </x:row>
     <x:row r="149" ht="32" customHeight="1">
       <x:c r="A149" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+        <x:v>trunk:FC1:F5:fan:1</x:v>
       </x:c>
       <x:c r="B149" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C149" s="11" t="n">
-        <x:v>41.2</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D149" s="11" t="n">
-        <x:v>8.766617268041228</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E149" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F149" s="11" t="n">
         <x:f>0</x:f>
@@ -10712,23 +10708,23 @@
     </x:row>
     <x:row r="150" ht="32" customHeight="1">
       <x:c r="A150" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+        <x:v>trunk:FC1:F5:fan:1</x:v>
       </x:c>
       <x:c r="B150" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C150" s="11" t="n">
-        <x:v>41.2</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D150" s="11" t="n">
-        <x:v>8.766617268041237</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E150" s="11" t="n">
-        <x:v>-13.249</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F150" s="11" t="n">
         <x:f>SQRT((C150-C149)^2+(D150-D149)^2+(E150-E149)^2)</x:f>
-        <x:v>5.889</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G150" s="8" t="str">
         <x:v>Current</x:v>
@@ -10736,23 +10732,23 @@
     </x:row>
     <x:row r="151" ht="32" customHeight="1">
       <x:c r="A151" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+        <x:v>trunk:FC1:F5:fan:1</x:v>
       </x:c>
       <x:c r="B151" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C151" s="11" t="n">
-        <x:v>41.2</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D151" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E151" s="11" t="n">
-        <x:v>-13.249</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F151" s="11" t="n">
         <x:f>SQRT((C151-C150)^2+(D151-D150)^2+(E151-E150)^2)</x:f>
-        <x:v>6.066617268041237</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="G151" s="8" t="str">
         <x:v>Current</x:v>
@@ -10760,23 +10756,23 @@
     </x:row>
     <x:row r="152" ht="32" customHeight="1">
       <x:c r="A152" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+        <x:v>trunk:FC1:F5:fan:1</x:v>
       </x:c>
       <x:c r="B152" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C152" s="11" t="n">
-        <x:v>41.2</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D152" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E152" s="11" t="n">
-        <x:v>-13.06</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F152" s="11" t="n">
         <x:f>SQRT((C152-C151)^2+(D152-D151)^2+(E152-E151)^2)</x:f>
-        <x:v>0.18900000000000006</x:v>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="G152" s="8" t="str">
         <x:v>Current</x:v>
@@ -10784,23 +10780,23 @@
     </x:row>
     <x:row r="153" ht="32" customHeight="1">
       <x:c r="A153" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+        <x:v>trunk:FC1:F5:fan:1</x:v>
       </x:c>
       <x:c r="B153" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C153" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D153" s="11" t="n">
-        <x:v>8.122287371134018</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E153" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F153" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C153-C152)^2+(D153-D152)^2+(E153-E152)^2)</x:f>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G153" s="8" t="str">
         <x:v>Current</x:v>
@@ -10808,23 +10804,23 @@
     </x:row>
     <x:row r="154" ht="32" customHeight="1">
       <x:c r="A154" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+        <x:v>trunk:FC1:F5:fan:1</x:v>
       </x:c>
       <x:c r="B154" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C154" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D154" s="11" t="n">
-        <x:v>8.122287371134023</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E154" s="11" t="n">
-        <x:v>-13.249</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F154" s="11" t="n">
         <x:f>SQRT((C154-C153)^2+(D154-D153)^2+(E154-E153)^2)</x:f>
-        <x:v>5.889</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G154" s="8" t="str">
         <x:v>Current</x:v>
@@ -10832,23 +10828,23 @@
     </x:row>
     <x:row r="155" ht="32" customHeight="1">
       <x:c r="A155" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+        <x:v>trunk:FC1:F5:fan:1</x:v>
       </x:c>
       <x:c r="B155" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C155" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D155" s="11" t="n">
-        <x:v>3.5</x:v>
+        <x:v>6.1000000000000005</x:v>
       </x:c>
       <x:c r="E155" s="11" t="n">
-        <x:v>-13.249</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F155" s="11" t="n">
         <x:f>SQRT((C155-C154)^2+(D155-D154)^2+(E155-E154)^2)</x:f>
-        <x:v>4.622287371134023</x:v>
+        <x:v>1.7700000000000005</x:v>
       </x:c>
       <x:c r="G155" s="8" t="str">
         <x:v>Current</x:v>
@@ -10856,23 +10852,23 @@
     </x:row>
     <x:row r="156" ht="32" customHeight="1">
       <x:c r="A156" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+        <x:v>trunk:FC1:F5:fan:1</x:v>
       </x:c>
       <x:c r="B156" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C156" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D156" s="11" t="n">
-        <x:v>3.5</x:v>
+        <x:v>6.1000000000000005</x:v>
       </x:c>
       <x:c r="E156" s="11" t="n">
-        <x:v>-13.06</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F156" s="11" t="n">
         <x:f>SQRT((C156-C155)^2+(D156-D155)^2+(E156-E155)^2)</x:f>
-        <x:v>0.18900000000000006</x:v>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G156" s="8" t="str">
         <x:v>Current</x:v>
@@ -10883,20 +10879,20 @@
         <x:v>trunk:FC1:F5:fan:1</x:v>
       </x:c>
       <x:c r="B157" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C157" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D157" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>6.1000000000000005</x:v>
       </x:c>
       <x:c r="E157" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F157" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C157-C156)^2+(D157-D156)^2+(E157-E156)^2)</x:f>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G157" s="8" t="str">
         <x:v>Current</x:v>
@@ -10907,20 +10903,20 @@
         <x:v>trunk:FC1:F5:fan:1</x:v>
       </x:c>
       <x:c r="B158" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C158" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D158" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E158" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F158" s="11" t="n">
         <x:f>SQRT((C158-C157)^2+(D158-D157)^2+(E158-E157)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
+        <x:v>0.9399999999999995</x:v>
       </x:c>
       <x:c r="G158" s="8" t="str">
         <x:v>Current</x:v>
@@ -10931,20 +10927,20 @@
         <x:v>trunk:FC1:F5:fan:1</x:v>
       </x:c>
       <x:c r="B159" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C159" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D159" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E159" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F159" s="11" t="n">
         <x:f>SQRT((C159-C158)^2+(D159-D158)^2+(E159-E158)^2)</x:f>
-        <x:v>2.64</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G159" s="8" t="str">
         <x:v>Current</x:v>
@@ -10955,20 +10951,20 @@
         <x:v>trunk:FC1:F5:fan:1</x:v>
       </x:c>
       <x:c r="B160" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C160" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D160" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E160" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F160" s="11" t="n">
         <x:f>SQRT((C160-C159)^2+(D160-D159)^2+(E160-E159)^2)</x:f>
-        <x:v>2.38</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G160" s="8" t="str">
         <x:v>Current</x:v>
@@ -10979,20 +10975,20 @@
         <x:v>trunk:FC1:F5:fan:1</x:v>
       </x:c>
       <x:c r="B161" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C161" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D161" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E161" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F161" s="11" t="n">
         <x:f>SQRT((C161-C160)^2+(D161-D160)^2+(E161-E160)^2)</x:f>
-        <x:v>1.0599999999999996</x:v>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G161" s="8" t="str">
         <x:v>Current</x:v>
@@ -11003,20 +10999,20 @@
         <x:v>trunk:FC1:F5:fan:1</x:v>
       </x:c>
       <x:c r="B162" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C162" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>38.05</x:v>
       </x:c>
       <x:c r="D162" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>7.236333762886593</x:v>
       </x:c>
       <x:c r="E162" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F162" s="11" t="n">
         <x:f>SQRT((C162-C161)^2+(D162-D161)^2+(E162-E161)^2)</x:f>
-        <x:v>4.280999999999999</x:v>
+        <x:v>3.2421325333759836</x:v>
       </x:c>
       <x:c r="G162" s="8" t="str">
         <x:v>Current</x:v>
@@ -11024,23 +11020,23 @@
     </x:row>
     <x:row r="163" ht="32" customHeight="1">
       <x:c r="A163" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:1</x:v>
+        <x:v>drop:FC1:F5:fan:1:F242</x:v>
       </x:c>
       <x:c r="B163" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C163" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>38.05</x:v>
       </x:c>
       <x:c r="D163" s="11" t="n">
-        <x:v>6.1000000000000005</x:v>
+        <x:v>7.236333762886593</x:v>
       </x:c>
       <x:c r="E163" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F163" s="11" t="n">
-        <x:f>SQRT((C163-C162)^2+(D163-D162)^2+(E163-E162)^2)</x:f>
-        <x:v>1.7700000000000005</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G163" s="8" t="str">
         <x:v>Current</x:v>
@@ -11048,23 +11044,23 @@
     </x:row>
     <x:row r="164" ht="32" customHeight="1">
       <x:c r="A164" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:1</x:v>
+        <x:v>drop:FC1:F5:fan:1:F242</x:v>
       </x:c>
       <x:c r="B164" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C164" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>38.05</x:v>
       </x:c>
       <x:c r="D164" s="11" t="n">
-        <x:v>6.1000000000000005</x:v>
+        <x:v>7.236333762886593</x:v>
       </x:c>
       <x:c r="E164" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>13.249</x:v>
       </x:c>
       <x:c r="F164" s="11" t="n">
         <x:f>SQRT((C164-C163)^2+(D164-D163)^2+(E164-E163)^2)</x:f>
-        <x:v>10.66</x:v>
+        <x:v>5.889</x:v>
       </x:c>
       <x:c r="G164" s="8" t="str">
         <x:v>Current</x:v>
@@ -11072,23 +11068,23 @@
     </x:row>
     <x:row r="165" ht="32" customHeight="1">
       <x:c r="A165" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:1</x:v>
+        <x:v>drop:FC1:F5:fan:1:F242</x:v>
       </x:c>
       <x:c r="B165" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C165" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>38.05</x:v>
       </x:c>
       <x:c r="D165" s="11" t="n">
-        <x:v>6.1000000000000005</x:v>
+        <x:v>4.05</x:v>
       </x:c>
       <x:c r="E165" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>13.249</x:v>
       </x:c>
       <x:c r="F165" s="11" t="n">
         <x:f>SQRT((C165-C164)^2+(D165-D164)^2+(E165-E164)^2)</x:f>
-        <x:v>8.841000000000001</x:v>
+        <x:v>3.1863337628865933</x:v>
       </x:c>
       <x:c r="G165" s="8" t="str">
         <x:v>Current</x:v>
@@ -11096,23 +11092,23 @@
     </x:row>
     <x:row r="166" ht="32" customHeight="1">
       <x:c r="A166" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:1</x:v>
+        <x:v>drop:FC1:F5:fan:1:F242</x:v>
       </x:c>
       <x:c r="B166" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C166" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>38.05</x:v>
       </x:c>
       <x:c r="D166" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>4.05</x:v>
       </x:c>
       <x:c r="E166" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>13.06</x:v>
       </x:c>
       <x:c r="F166" s="11" t="n">
         <x:f>SQRT((C166-C165)^2+(D166-D165)^2+(E166-E165)^2)</x:f>
-        <x:v>0.9399999999999995</x:v>
+        <x:v>0.18900000000000006</x:v>
       </x:c>
       <x:c r="G166" s="8" t="str">
         <x:v>Current</x:v>
@@ -11120,23 +11116,23 @@
     </x:row>
     <x:row r="167" ht="32" customHeight="1">
       <x:c r="A167" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:1</x:v>
+        <x:v>drop:FC1:F5:fan:1:F243</x:v>
       </x:c>
       <x:c r="B167" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C167" s="11" t="n">
-        <x:v>43.535</x:v>
+        <x:v>43.1</x:v>
       </x:c>
       <x:c r="D167" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>7.236333762886598</x:v>
       </x:c>
       <x:c r="E167" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F167" s="11" t="n">
-        <x:f>SQRT((C167-C166)^2+(D167-D166)^2+(E167-E166)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G167" s="8" t="str">
         <x:v>Current</x:v>
@@ -11144,23 +11140,23 @@
     </x:row>
     <x:row r="168" ht="32" customHeight="1">
       <x:c r="A168" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:1</x:v>
+        <x:v>drop:FC1:F5:fan:1:F243</x:v>
       </x:c>
       <x:c r="B168" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C168" s="11" t="n">
-        <x:v>43.455</x:v>
+        <x:v>43.1</x:v>
       </x:c>
       <x:c r="D168" s="11" t="n">
-        <x:v>6.950412371134024</x:v>
+        <x:v>7.2363337628865985</x:v>
       </x:c>
       <x:c r="E168" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>13.249</x:v>
       </x:c>
       <x:c r="F168" s="11" t="n">
         <x:f>SQRT((C168-C167)^2+(D168-D167)^2+(E168-E167)^2)</x:f>
-        <x:v>0.12010804821421249</x:v>
+        <x:v>5.889</x:v>
       </x:c>
       <x:c r="G168" s="8" t="str">
         <x:v>Current</x:v>
@@ -11168,23 +11164,23 @@
     </x:row>
     <x:row r="169" ht="32" customHeight="1">
       <x:c r="A169" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:1</x:v>
+        <x:v>drop:FC1:F5:fan:1:F243</x:v>
       </x:c>
       <x:c r="B169" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C169" s="11" t="n">
-        <x:v>40.574999999999996</x:v>
+        <x:v>43.1</x:v>
       </x:c>
       <x:c r="D169" s="11" t="n">
-        <x:v>9.269999999999994</x:v>
+        <x:v>4.05</x:v>
       </x:c>
       <x:c r="E169" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>13.249</x:v>
       </x:c>
       <x:c r="F169" s="11" t="n">
         <x:f>SQRT((C169-C168)^2+(D169-D168)^2+(E169-E168)^2)</x:f>
-        <x:v>3.6979571073753776</x:v>
+        <x:v>3.1863337628865986</x:v>
       </x:c>
       <x:c r="G169" s="8" t="str">
         <x:v>Current</x:v>
@@ -11192,23 +11188,23 @@
     </x:row>
     <x:row r="170" ht="32" customHeight="1">
       <x:c r="A170" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:1</x:v>
+        <x:v>drop:FC1:F5:fan:1:F243</x:v>
       </x:c>
       <x:c r="B170" s="8" t="n">
-        <x:v>14</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C170" s="11" t="n">
-        <x:v>39.15</x:v>
+        <x:v>43.1</x:v>
       </x:c>
       <x:c r="D170" s="11" t="n">
-        <x:v>8.122287371134018</x:v>
+        <x:v>4.05</x:v>
       </x:c>
       <x:c r="E170" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>13.06</x:v>
       </x:c>
       <x:c r="F170" s="11" t="n">
         <x:f>SQRT((C170-C169)^2+(D170-D169)^2+(E170-E169)^2)</x:f>
-        <x:v>1.8297183604201064</x:v>
+        <x:v>0.18900000000000006</x:v>
       </x:c>
       <x:c r="G170" s="8" t="str">
         <x:v>Current</x:v>
@@ -11216,19 +11212,19 @@
     </x:row>
     <x:row r="171" ht="32" customHeight="1">
       <x:c r="A171" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F242</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
       <x:c r="B171" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C171" s="11" t="n">
-        <x:v>39.15</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D171" s="11" t="n">
-        <x:v>8.122287371134018</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E171" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F171" s="11" t="n">
         <x:f>0</x:f>
@@ -11240,23 +11236,23 @@
     </x:row>
     <x:row r="172" ht="32" customHeight="1">
       <x:c r="A172" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F242</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
       <x:c r="B172" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C172" s="11" t="n">
-        <x:v>39.15</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D172" s="11" t="n">
-        <x:v>8.122287371134016</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E172" s="11" t="n">
-        <x:v>13.249</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F172" s="11" t="n">
         <x:f>SQRT((C172-C171)^2+(D172-D171)^2+(E172-E171)^2)</x:f>
-        <x:v>5.889</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G172" s="8" t="str">
         <x:v>Current</x:v>
@@ -11264,23 +11260,23 @@
     </x:row>
     <x:row r="173" ht="32" customHeight="1">
       <x:c r="A173" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F242</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
       <x:c r="B173" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C173" s="11" t="n">
-        <x:v>39.15</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D173" s="11" t="n">
-        <x:v>3.5</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E173" s="11" t="n">
-        <x:v>13.249</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F173" s="11" t="n">
         <x:f>SQRT((C173-C172)^2+(D173-D172)^2+(E173-E172)^2)</x:f>
-        <x:v>4.622287371134016</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="G173" s="8" t="str">
         <x:v>Current</x:v>
@@ -11288,23 +11284,23 @@
     </x:row>
     <x:row r="174" ht="32" customHeight="1">
       <x:c r="A174" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F242</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
       <x:c r="B174" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C174" s="11" t="n">
-        <x:v>39.15</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D174" s="11" t="n">
-        <x:v>3.5</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E174" s="11" t="n">
-        <x:v>13.06</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F174" s="11" t="n">
         <x:f>SQRT((C174-C173)^2+(D174-D173)^2+(E174-E173)^2)</x:f>
-        <x:v>0.18900000000000006</x:v>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="G174" s="8" t="str">
         <x:v>Current</x:v>
@@ -11312,23 +11308,23 @@
     </x:row>
     <x:row r="175" ht="32" customHeight="1">
       <x:c r="A175" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F243</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
       <x:c r="B175" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C175" s="11" t="n">
-        <x:v>39.95</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D175" s="11" t="n">
-        <x:v>8.766617268041237</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E175" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F175" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C175-C174)^2+(D175-D174)^2+(E175-E174)^2)</x:f>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G175" s="8" t="str">
         <x:v>Current</x:v>
@@ -11336,23 +11332,23 @@
     </x:row>
     <x:row r="176" ht="32" customHeight="1">
       <x:c r="A176" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F243</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
       <x:c r="B176" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C176" s="11" t="n">
-        <x:v>39.95</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D176" s="11" t="n">
-        <x:v>8.766617268041237</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E176" s="11" t="n">
-        <x:v>13.249</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F176" s="11" t="n">
         <x:f>SQRT((C176-C175)^2+(D176-D175)^2+(E176-E175)^2)</x:f>
-        <x:v>5.889</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G176" s="8" t="str">
         <x:v>Current</x:v>
@@ -11360,23 +11356,23 @@
     </x:row>
     <x:row r="177" ht="32" customHeight="1">
       <x:c r="A177" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F243</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
       <x:c r="B177" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C177" s="11" t="n">
-        <x:v>39.95</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D177" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E177" s="11" t="n">
-        <x:v>13.249</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F177" s="11" t="n">
         <x:f>SQRT((C177-C176)^2+(D177-D176)^2+(E177-E176)^2)</x:f>
-        <x:v>6.066617268041237</x:v>
+        <x:v>1.6820000000000004</x:v>
       </x:c>
       <x:c r="G177" s="8" t="str">
         <x:v>Current</x:v>
@@ -11384,23 +11380,23 @@
     </x:row>
     <x:row r="178" ht="32" customHeight="1">
       <x:c r="A178" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F243</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
       <x:c r="B178" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C178" s="11" t="n">
-        <x:v>39.95</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D178" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E178" s="11" t="n">
-        <x:v>13.06</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F178" s="11" t="n">
         <x:f>SQRT((C178-C177)^2+(D178-D177)^2+(E178-E177)^2)</x:f>
-        <x:v>0.18900000000000006</x:v>
+        <x:v>4.0600000000000005</x:v>
       </x:c>
       <x:c r="G178" s="8" t="str">
         <x:v>Current</x:v>
@@ -11408,23 +11404,23 @@
     </x:row>
     <x:row r="179" ht="32" customHeight="1">
       <x:c r="A179" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
       <x:c r="B179" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C179" s="11" t="n">
-        <x:v>41.2</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D179" s="11" t="n">
-        <x:v>8.766617268041228</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E179" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F179" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C179-C178)^2+(D179-D178)^2+(E179-E178)^2)</x:f>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G179" s="8" t="str">
         <x:v>Current</x:v>
@@ -11432,23 +11428,23 @@
     </x:row>
     <x:row r="180" ht="32" customHeight="1">
       <x:c r="A180" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
       <x:c r="B180" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C180" s="11" t="n">
-        <x:v>41.2</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D180" s="11" t="n">
-        <x:v>8.766617268041237</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E180" s="11" t="n">
-        <x:v>13.249</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F180" s="11" t="n">
         <x:f>SQRT((C180-C179)^2+(D180-D179)^2+(E180-E179)^2)</x:f>
-        <x:v>5.889</x:v>
+        <x:v>1.0279999999999996</x:v>
       </x:c>
       <x:c r="G180" s="8" t="str">
         <x:v>Current</x:v>
@@ -11456,23 +11452,23 @@
     </x:row>
     <x:row r="181" ht="32" customHeight="1">
       <x:c r="A181" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
       <x:c r="B181" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C181" s="11" t="n">
-        <x:v>41.2</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D181" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E181" s="11" t="n">
-        <x:v>13.249</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F181" s="11" t="n">
         <x:f>SQRT((C181-C180)^2+(D181-D180)^2+(E181-E180)^2)</x:f>
-        <x:v>6.066617268041237</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G181" s="8" t="str">
         <x:v>Current</x:v>
@@ -11480,23 +11476,23 @@
     </x:row>
     <x:row r="182" ht="32" customHeight="1">
       <x:c r="A182" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
       <x:c r="B182" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C182" s="11" t="n">
-        <x:v>41.2</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D182" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E182" s="11" t="n">
-        <x:v>13.06</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F182" s="11" t="n">
         <x:f>SQRT((C182-C181)^2+(D182-D181)^2+(E182-E181)^2)</x:f>
-        <x:v>0.18900000000000006</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G182" s="8" t="str">
         <x:v>Current</x:v>
@@ -11504,23 +11500,23 @@
     </x:row>
     <x:row r="183" ht="32" customHeight="1">
       <x:c r="A183" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
       <x:c r="B183" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C183" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D183" s="11" t="n">
-        <x:v>8.122287371134018</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E183" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F183" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C183-C182)^2+(D183-D182)^2+(E183-E182)^2)</x:f>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G183" s="8" t="str">
         <x:v>Current</x:v>
@@ -11528,23 +11524,23 @@
     </x:row>
     <x:row r="184" ht="32" customHeight="1">
       <x:c r="A184" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
       <x:c r="B184" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C184" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>37.695</x:v>
       </x:c>
       <x:c r="D184" s="11" t="n">
-        <x:v>8.122287371134023</x:v>
+        <x:v>6.950412371134018</x:v>
       </x:c>
       <x:c r="E184" s="11" t="n">
-        <x:v>13.249</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F184" s="11" t="n">
         <x:f>SQRT((C184-C183)^2+(D184-D183)^2+(E184-E183)^2)</x:f>
-        <x:v>5.889</x:v>
+        <x:v>3.697957107375376</x:v>
       </x:c>
       <x:c r="G184" s="8" t="str">
         <x:v>Current</x:v>
@@ -11552,23 +11548,23 @@
     </x:row>
     <x:row r="185" ht="32" customHeight="1">
       <x:c r="A185" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
       <x:c r="B185" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C185" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>37.615</x:v>
       </x:c>
       <x:c r="D185" s="11" t="n">
-        <x:v>3.5</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E185" s="11" t="n">
-        <x:v>13.249</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F185" s="11" t="n">
         <x:f>SQRT((C185-C184)^2+(D185-D184)^2+(E185-E184)^2)</x:f>
-        <x:v>4.622287371134023</x:v>
+        <x:v>0.12010804821421713</x:v>
       </x:c>
       <x:c r="G185" s="8" t="str">
         <x:v>Current</x:v>
@@ -11576,23 +11572,23 @@
     </x:row>
     <x:row r="186" ht="32" customHeight="1">
       <x:c r="A186" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
       <x:c r="B186" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C186" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D186" s="11" t="n">
-        <x:v>3.5</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E186" s="11" t="n">
-        <x:v>13.06</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F186" s="11" t="n">
         <x:f>SQRT((C186-C185)^2+(D186-D185)^2+(E186-E185)^2)</x:f>
-        <x:v>0.18900000000000006</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G186" s="8" t="str">
         <x:v>Current</x:v>
@@ -11603,20 +11599,20 @@
         <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
       <x:c r="B187" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C187" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D187" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E187" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F187" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C187-C186)^2+(D187-D186)^2+(E187-E186)^2)</x:f>
+        <x:v>1.0279999999999996</x:v>
       </x:c>
       <x:c r="G187" s="8" t="str">
         <x:v>Current</x:v>
@@ -11627,20 +11623,20 @@
         <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
       <x:c r="B188" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C188" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>14.475000000000001</x:v>
       </x:c>
       <x:c r="D188" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E188" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F188" s="11" t="n">
         <x:f>SQRT((C188-C187)^2+(D188-D187)^2+(E188-E187)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
+        <x:v>22.5</x:v>
       </x:c>
       <x:c r="G188" s="8" t="str">
         <x:v>Current</x:v>
@@ -11648,23 +11644,23 @@
     </x:row>
     <x:row r="189" ht="32" customHeight="1">
       <x:c r="A189" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F244</x:v>
       </x:c>
       <x:c r="B189" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C189" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>14.475000000000001</x:v>
       </x:c>
       <x:c r="D189" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E189" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F189" s="11" t="n">
-        <x:f>SQRT((C189-C188)^2+(D189-D188)^2+(E189-E188)^2)</x:f>
-        <x:v>2.64</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G189" s="8" t="str">
         <x:v>Current</x:v>
@@ -11672,23 +11668,23 @@
     </x:row>
     <x:row r="190" ht="32" customHeight="1">
       <x:c r="A190" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F244</x:v>
       </x:c>
       <x:c r="B190" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C190" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>14.475000000000001</x:v>
       </x:c>
       <x:c r="D190" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E190" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F190" s="11" t="n">
         <x:f>SQRT((C190-C189)^2+(D190-D189)^2+(E190-E189)^2)</x:f>
-        <x:v>2.38</x:v>
+        <x:v>0.46200000000000063</x:v>
       </x:c>
       <x:c r="G190" s="8" t="str">
         <x:v>Current</x:v>
@@ -11696,23 +11692,23 @@
     </x:row>
     <x:row r="191" ht="32" customHeight="1">
       <x:c r="A191" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F244</x:v>
       </x:c>
       <x:c r="B191" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C191" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>14.475</x:v>
       </x:c>
       <x:c r="D191" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E191" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-7.07</x:v>
       </x:c>
       <x:c r="F191" s="11" t="n">
         <x:f>SQRT((C191-C190)^2+(D191-D190)^2+(E191-E190)^2)</x:f>
-        <x:v>1.0599999999999996</x:v>
+        <x:v>0.29000000000000004</x:v>
       </x:c>
       <x:c r="G191" s="8" t="str">
         <x:v>Current</x:v>
@@ -11720,23 +11716,23 @@
     </x:row>
     <x:row r="192" ht="32" customHeight="1">
       <x:c r="A192" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F246</x:v>
       </x:c>
       <x:c r="B192" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C192" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>23.475</x:v>
       </x:c>
       <x:c r="D192" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E192" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F192" s="11" t="n">
-        <x:f>SQRT((C192-C191)^2+(D192-D191)^2+(E192-E191)^2)</x:f>
-        <x:v>4.280999999999999</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G192" s="8" t="str">
         <x:v>Current</x:v>
@@ -11744,23 +11740,23 @@
     </x:row>
     <x:row r="193" ht="32" customHeight="1">
       <x:c r="A193" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F246</x:v>
       </x:c>
       <x:c r="B193" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C193" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>23.475</x:v>
       </x:c>
       <x:c r="D193" s="11" t="n">
-        <x:v>6.0120000000000005</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E193" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F193" s="11" t="n">
         <x:f>SQRT((C193-C192)^2+(D193-D192)^2+(E193-E192)^2)</x:f>
-        <x:v>1.6820000000000004</x:v>
+        <x:v>0.46200000000000063</x:v>
       </x:c>
       <x:c r="G193" s="8" t="str">
         <x:v>Current</x:v>
@@ -11768,23 +11764,23 @@
     </x:row>
     <x:row r="194" ht="32" customHeight="1">
       <x:c r="A194" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F246</x:v>
       </x:c>
       <x:c r="B194" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C194" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>23.475</x:v>
       </x:c>
       <x:c r="D194" s="11" t="n">
-        <x:v>6.0120000000000005</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E194" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-7.07</x:v>
       </x:c>
       <x:c r="F194" s="11" t="n">
         <x:f>SQRT((C194-C193)^2+(D194-D193)^2+(E194-E193)^2)</x:f>
-        <x:v>4.0600000000000005</x:v>
+        <x:v>0.29000000000000004</x:v>
       </x:c>
       <x:c r="G194" s="8" t="str">
         <x:v>Current</x:v>
@@ -11792,13 +11788,13 @@
     </x:row>
     <x:row r="195" ht="32" customHeight="1">
       <x:c r="A195" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F248</x:v>
       </x:c>
       <x:c r="B195" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C195" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>32.475</x:v>
       </x:c>
       <x:c r="D195" s="11" t="n">
         <x:v>6.0120000000000005</x:v>
@@ -11807,8 +11803,8 @@
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F195" s="11" t="n">
-        <x:f>SQRT((C195-C194)^2+(D195-D194)^2+(E195-E194)^2)</x:f>
-        <x:v>8.841000000000001</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G195" s="8" t="str">
         <x:v>Current</x:v>
@@ -11816,23 +11812,23 @@
     </x:row>
     <x:row r="196" ht="32" customHeight="1">
       <x:c r="A196" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F248</x:v>
       </x:c>
       <x:c r="B196" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C196" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>32.475</x:v>
       </x:c>
       <x:c r="D196" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E196" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F196" s="11" t="n">
         <x:f>SQRT((C196-C195)^2+(D196-D195)^2+(E196-E195)^2)</x:f>
-        <x:v>1.0279999999999996</x:v>
+        <x:v>0.46200000000000063</x:v>
       </x:c>
       <x:c r="G196" s="8" t="str">
         <x:v>Current</x:v>
@@ -11840,23 +11836,23 @@
     </x:row>
     <x:row r="197" ht="32" customHeight="1">
       <x:c r="A197" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F248</x:v>
       </x:c>
       <x:c r="B197" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C197" s="11" t="n">
-        <x:v>43.535</x:v>
+        <x:v>32.475</x:v>
       </x:c>
       <x:c r="D197" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E197" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-7.07</x:v>
       </x:c>
       <x:c r="F197" s="11" t="n">
         <x:f>SQRT((C197-C196)^2+(D197-D196)^2+(E197-E196)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>0.29000000000000004</x:v>
       </x:c>
       <x:c r="G197" s="8" t="str">
         <x:v>Current</x:v>
@@ -11864,23 +11860,23 @@
     </x:row>
     <x:row r="198" ht="32" customHeight="1">
       <x:c r="A198" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B198" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C198" s="11" t="n">
-        <x:v>43.455</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D198" s="11" t="n">
-        <x:v>6.950412371134024</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E198" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F198" s="11" t="n">
-        <x:f>SQRT((C198-C197)^2+(D198-D197)^2+(E198-E197)^2)</x:f>
-        <x:v>0.12010804821421249</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G198" s="8" t="str">
         <x:v>Current</x:v>
@@ -11888,23 +11884,23 @@
     </x:row>
     <x:row r="199" ht="32" customHeight="1">
       <x:c r="A199" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B199" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C199" s="11" t="n">
-        <x:v>40.574999999999996</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D199" s="11" t="n">
-        <x:v>9.269999999999994</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E199" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F199" s="11" t="n">
         <x:f>SQRT((C199-C198)^2+(D199-D198)^2+(E199-E198)^2)</x:f>
-        <x:v>3.6979571073753776</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G199" s="8" t="str">
         <x:v>Current</x:v>
@@ -11912,23 +11908,23 @@
     </x:row>
     <x:row r="200" ht="32" customHeight="1">
       <x:c r="A200" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B200" s="8" t="n">
-        <x:v>14</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C200" s="11" t="n">
-        <x:v>37.695</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D200" s="11" t="n">
-        <x:v>6.950412371134018</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E200" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F200" s="11" t="n">
         <x:f>SQRT((C200-C199)^2+(D200-D199)^2+(E200-E199)^2)</x:f>
-        <x:v>3.697957107375376</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="G200" s="8" t="str">
         <x:v>Current</x:v>
@@ -11936,23 +11932,23 @@
     </x:row>
     <x:row r="201" ht="32" customHeight="1">
       <x:c r="A201" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B201" s="8" t="n">
-        <x:v>15</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C201" s="11" t="n">
-        <x:v>37.615</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D201" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E201" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F201" s="11" t="n">
         <x:f>SQRT((C201-C200)^2+(D201-D200)^2+(E201-E200)^2)</x:f>
-        <x:v>0.12010804821421713</x:v>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="G201" s="8" t="str">
         <x:v>Current</x:v>
@@ -11960,23 +11956,23 @@
     </x:row>
     <x:row r="202" ht="32" customHeight="1">
       <x:c r="A202" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B202" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C202" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D202" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E202" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F202" s="11" t="n">
         <x:f>SQRT((C202-C201)^2+(D202-D201)^2+(E202-E201)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G202" s="8" t="str">
         <x:v>Current</x:v>
@@ -11984,23 +11980,23 @@
     </x:row>
     <x:row r="203" ht="32" customHeight="1">
       <x:c r="A203" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B203" s="8" t="n">
-        <x:v>17</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C203" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D203" s="11" t="n">
-        <x:v>6.0120000000000005</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E203" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F203" s="11" t="n">
         <x:f>SQRT((C203-C202)^2+(D203-D202)^2+(E203-E202)^2)</x:f>
-        <x:v>1.0279999999999996</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G203" s="8" t="str">
         <x:v>Current</x:v>
@@ -12008,23 +12004,23 @@
     </x:row>
     <x:row r="204" ht="32" customHeight="1">
       <x:c r="A204" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B204" s="8" t="n">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C204" s="11" t="n">
-        <x:v>14.475000000000001</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D204" s="11" t="n">
         <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E204" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F204" s="11" t="n">
         <x:f>SQRT((C204-C203)^2+(D204-D203)^2+(E204-E203)^2)</x:f>
-        <x:v>22.5</x:v>
+        <x:v>1.6820000000000004</x:v>
       </x:c>
       <x:c r="G204" s="8" t="str">
         <x:v>Current</x:v>
@@ -12032,23 +12028,23 @@
     </x:row>
     <x:row r="205" ht="32" customHeight="1">
       <x:c r="A205" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:-1:F244</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B205" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C205" s="11" t="n">
-        <x:v>14.475000000000001</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D205" s="11" t="n">
         <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E205" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F205" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C205-C204)^2+(D205-D204)^2+(E205-E204)^2)</x:f>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G205" s="8" t="str">
         <x:v>Current</x:v>
@@ -12056,23 +12052,23 @@
     </x:row>
     <x:row r="206" ht="32" customHeight="1">
       <x:c r="A206" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:-1:F244</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B206" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C206" s="11" t="n">
-        <x:v>14.475000000000001</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D206" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E206" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F206" s="11" t="n">
         <x:f>SQRT((C206-C205)^2+(D206-D205)^2+(E206-E205)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G206" s="8" t="str">
         <x:v>Current</x:v>
@@ -12080,23 +12076,23 @@
     </x:row>
     <x:row r="207" ht="32" customHeight="1">
       <x:c r="A207" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:-1:F244</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B207" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C207" s="11" t="n">
-        <x:v>14.475</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D207" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E207" s="11" t="n">
-        <x:v>-7.07</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F207" s="11" t="n">
         <x:f>SQRT((C207-C206)^2+(D207-D206)^2+(E207-E206)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
+        <x:v>1.0279999999999996</x:v>
       </x:c>
       <x:c r="G207" s="8" t="str">
         <x:v>Current</x:v>
@@ -12104,23 +12100,23 @@
     </x:row>
     <x:row r="208" ht="32" customHeight="1">
       <x:c r="A208" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:-1:F246</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B208" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C208" s="11" t="n">
-        <x:v>23.475</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D208" s="11" t="n">
-        <x:v>6.0120000000000005</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E208" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F208" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C208-C207)^2+(D208-D207)^2+(E208-E207)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G208" s="8" t="str">
         <x:v>Current</x:v>
@@ -12128,23 +12124,23 @@
     </x:row>
     <x:row r="209" ht="32" customHeight="1">
       <x:c r="A209" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:-1:F246</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B209" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C209" s="11" t="n">
-        <x:v>23.475</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D209" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E209" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F209" s="11" t="n">
         <x:f>SQRT((C209-C208)^2+(D209-D208)^2+(E209-E208)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G209" s="8" t="str">
         <x:v>Current</x:v>
@@ -12152,23 +12148,23 @@
     </x:row>
     <x:row r="210" ht="32" customHeight="1">
       <x:c r="A210" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:-1:F246</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B210" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C210" s="11" t="n">
-        <x:v>23.475</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D210" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E210" s="11" t="n">
-        <x:v>-7.07</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F210" s="11" t="n">
         <x:f>SQRT((C210-C209)^2+(D210-D209)^2+(E210-E209)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G210" s="8" t="str">
         <x:v>Current</x:v>
@@ -12176,23 +12172,23 @@
     </x:row>
     <x:row r="211" ht="32" customHeight="1">
       <x:c r="A211" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:-1:F248</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B211" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C211" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>37.695</x:v>
       </x:c>
       <x:c r="D211" s="11" t="n">
-        <x:v>6.0120000000000005</x:v>
+        <x:v>6.950412371134018</x:v>
       </x:c>
       <x:c r="E211" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F211" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C211-C210)^2+(D211-D210)^2+(E211-E210)^2)</x:f>
+        <x:v>3.697957107375376</x:v>
       </x:c>
       <x:c r="G211" s="8" t="str">
         <x:v>Current</x:v>
@@ -12200,23 +12196,23 @@
     </x:row>
     <x:row r="212" ht="32" customHeight="1">
       <x:c r="A212" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:-1:F248</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B212" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C212" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>37.615</x:v>
       </x:c>
       <x:c r="D212" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E212" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F212" s="11" t="n">
         <x:f>SQRT((C212-C211)^2+(D212-D211)^2+(E212-E211)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>0.12010804821421713</x:v>
       </x:c>
       <x:c r="G212" s="8" t="str">
         <x:v>Current</x:v>
@@ -12224,23 +12220,23 @@
     </x:row>
     <x:row r="213" ht="32" customHeight="1">
       <x:c r="A213" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:-1:F248</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B213" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C213" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D213" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E213" s="11" t="n">
-        <x:v>-7.07</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F213" s="11" t="n">
         <x:f>SQRT((C213-C212)^2+(D213-D212)^2+(E213-E212)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G213" s="8" t="str">
         <x:v>Current</x:v>
@@ -12251,20 +12247,20 @@
         <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B214" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C214" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D214" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E214" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F214" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C214-C213)^2+(D214-D213)^2+(E214-E213)^2)</x:f>
+        <x:v>1.0279999999999996</x:v>
       </x:c>
       <x:c r="G214" s="8" t="str">
         <x:v>Current</x:v>
@@ -12275,20 +12271,20 @@
         <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B215" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C215" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>14.475000000000001</x:v>
       </x:c>
       <x:c r="D215" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E215" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F215" s="11" t="n">
         <x:f>SQRT((C215-C214)^2+(D215-D214)^2+(E215-E214)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
+        <x:v>22.5</x:v>
       </x:c>
       <x:c r="G215" s="8" t="str">
         <x:v>Current</x:v>
@@ -12296,23 +12292,23 @@
     </x:row>
     <x:row r="216" ht="32" customHeight="1">
       <x:c r="A216" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F245</x:v>
       </x:c>
       <x:c r="B216" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C216" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>14.475000000000001</x:v>
       </x:c>
       <x:c r="D216" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E216" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F216" s="11" t="n">
-        <x:f>SQRT((C216-C215)^2+(D216-D215)^2+(E216-E215)^2)</x:f>
-        <x:v>2.64</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G216" s="8" t="str">
         <x:v>Current</x:v>
@@ -12320,23 +12316,23 @@
     </x:row>
     <x:row r="217" ht="32" customHeight="1">
       <x:c r="A217" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F245</x:v>
       </x:c>
       <x:c r="B217" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C217" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>14.475000000000001</x:v>
       </x:c>
       <x:c r="D217" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E217" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F217" s="11" t="n">
         <x:f>SQRT((C217-C216)^2+(D217-D216)^2+(E217-E216)^2)</x:f>
-        <x:v>2.38</x:v>
+        <x:v>0.46200000000000063</x:v>
       </x:c>
       <x:c r="G217" s="8" t="str">
         <x:v>Current</x:v>
@@ -12344,23 +12340,23 @@
     </x:row>
     <x:row r="218" ht="32" customHeight="1">
       <x:c r="A218" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F245</x:v>
       </x:c>
       <x:c r="B218" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C218" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>14.475</x:v>
       </x:c>
       <x:c r="D218" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E218" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>7.07</x:v>
       </x:c>
       <x:c r="F218" s="11" t="n">
         <x:f>SQRT((C218-C217)^2+(D218-D217)^2+(E218-E217)^2)</x:f>
-        <x:v>1.0599999999999996</x:v>
+        <x:v>0.29000000000000004</x:v>
       </x:c>
       <x:c r="G218" s="8" t="str">
         <x:v>Current</x:v>
@@ -12368,23 +12364,23 @@
     </x:row>
     <x:row r="219" ht="32" customHeight="1">
       <x:c r="A219" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F247</x:v>
       </x:c>
       <x:c r="B219" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C219" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>23.475</x:v>
       </x:c>
       <x:c r="D219" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E219" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F219" s="11" t="n">
-        <x:f>SQRT((C219-C218)^2+(D219-D218)^2+(E219-E218)^2)</x:f>
-        <x:v>4.280999999999999</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G219" s="8" t="str">
         <x:v>Current</x:v>
@@ -12392,23 +12388,23 @@
     </x:row>
     <x:row r="220" ht="32" customHeight="1">
       <x:c r="A220" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F247</x:v>
       </x:c>
       <x:c r="B220" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C220" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>23.475</x:v>
       </x:c>
       <x:c r="D220" s="11" t="n">
-        <x:v>6.0120000000000005</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E220" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F220" s="11" t="n">
         <x:f>SQRT((C220-C219)^2+(D220-D219)^2+(E220-E219)^2)</x:f>
-        <x:v>1.6820000000000004</x:v>
+        <x:v>0.46200000000000063</x:v>
       </x:c>
       <x:c r="G220" s="8" t="str">
         <x:v>Current</x:v>
@@ -12416,23 +12412,23 @@
     </x:row>
     <x:row r="221" ht="32" customHeight="1">
       <x:c r="A221" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F247</x:v>
       </x:c>
       <x:c r="B221" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C221" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>23.475</x:v>
       </x:c>
       <x:c r="D221" s="11" t="n">
-        <x:v>6.0120000000000005</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E221" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>7.07</x:v>
       </x:c>
       <x:c r="F221" s="11" t="n">
         <x:f>SQRT((C221-C220)^2+(D221-D220)^2+(E221-E220)^2)</x:f>
-        <x:v>10.66</x:v>
+        <x:v>0.29000000000000004</x:v>
       </x:c>
       <x:c r="G221" s="8" t="str">
         <x:v>Current</x:v>
@@ -12440,13 +12436,13 @@
     </x:row>
     <x:row r="222" ht="32" customHeight="1">
       <x:c r="A222" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F249</x:v>
       </x:c>
       <x:c r="B222" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C222" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>32.475</x:v>
       </x:c>
       <x:c r="D222" s="11" t="n">
         <x:v>6.0120000000000005</x:v>
@@ -12455,8 +12451,8 @@
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F222" s="11" t="n">
-        <x:f>SQRT((C222-C221)^2+(D222-D221)^2+(E222-E221)^2)</x:f>
-        <x:v>8.841000000000001</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G222" s="8" t="str">
         <x:v>Current</x:v>
@@ -12464,23 +12460,23 @@
     </x:row>
     <x:row r="223" ht="32" customHeight="1">
       <x:c r="A223" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F249</x:v>
       </x:c>
       <x:c r="B223" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C223" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>32.475</x:v>
       </x:c>
       <x:c r="D223" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E223" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F223" s="11" t="n">
         <x:f>SQRT((C223-C222)^2+(D223-D222)^2+(E223-E222)^2)</x:f>
-        <x:v>1.0279999999999996</x:v>
+        <x:v>0.46200000000000063</x:v>
       </x:c>
       <x:c r="G223" s="8" t="str">
         <x:v>Current</x:v>
@@ -12488,23 +12484,23 @@
     </x:row>
     <x:row r="224" ht="32" customHeight="1">
       <x:c r="A224" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F249</x:v>
       </x:c>
       <x:c r="B224" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C224" s="11" t="n">
-        <x:v>43.535</x:v>
+        <x:v>32.475</x:v>
       </x:c>
       <x:c r="D224" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E224" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>7.07</x:v>
       </x:c>
       <x:c r="F224" s="11" t="n">
         <x:f>SQRT((C224-C223)^2+(D224-D223)^2+(E224-E223)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>0.29000000000000004</x:v>
       </x:c>
       <x:c r="G224" s="8" t="str">
         <x:v>Current</x:v>
@@ -12512,23 +12508,23 @@
     </x:row>
     <x:row r="225" ht="32" customHeight="1">
       <x:c r="A225" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B225" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C225" s="11" t="n">
-        <x:v>43.455</x:v>
+        <x:v>2.73</x:v>
       </x:c>
       <x:c r="D225" s="11" t="n">
-        <x:v>6.950412371134024</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="E225" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F225" s="11" t="n">
-        <x:f>SQRT((C225-C224)^2+(D225-D224)^2+(E225-E224)^2)</x:f>
-        <x:v>0.12010804821421249</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G225" s="8" t="str">
         <x:v>Current</x:v>
@@ -12536,23 +12532,23 @@
     </x:row>
     <x:row r="226" ht="32" customHeight="1">
       <x:c r="A226" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B226" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C226" s="11" t="n">
-        <x:v>40.574999999999996</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D226" s="11" t="n">
-        <x:v>9.269999999999994</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="E226" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F226" s="11" t="n">
         <x:f>SQRT((C226-C225)^2+(D226-D225)^2+(E226-E225)^2)</x:f>
-        <x:v>3.6979571073753776</x:v>
+        <x:v>0.3799999999999999</x:v>
       </x:c>
       <x:c r="G226" s="8" t="str">
         <x:v>Current</x:v>
@@ -12560,23 +12556,23 @@
     </x:row>
     <x:row r="227" ht="32" customHeight="1">
       <x:c r="A227" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B227" s="8" t="n">
-        <x:v>14</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C227" s="11" t="n">
-        <x:v>37.695</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D227" s="11" t="n">
-        <x:v>6.950412371134018</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E227" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F227" s="11" t="n">
         <x:f>SQRT((C227-C226)^2+(D227-D226)^2+(E227-E226)^2)</x:f>
-        <x:v>3.697957107375376</x:v>
+        <x:v>6.15</x:v>
       </x:c>
       <x:c r="G227" s="8" t="str">
         <x:v>Current</x:v>
@@ -12584,23 +12580,23 @@
     </x:row>
     <x:row r="228" ht="32" customHeight="1">
       <x:c r="A228" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B228" s="8" t="n">
-        <x:v>15</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C228" s="11" t="n">
-        <x:v>37.615</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D228" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E228" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F228" s="11" t="n">
         <x:f>SQRT((C228-C227)^2+(D228-D227)^2+(E228-E227)^2)</x:f>
-        <x:v>0.12010804821421713</x:v>
+        <x:v>4.0600000000000005</x:v>
       </x:c>
       <x:c r="G228" s="8" t="str">
         <x:v>Current</x:v>
@@ -12608,23 +12604,23 @@
     </x:row>
     <x:row r="229" ht="32" customHeight="1">
       <x:c r="A229" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B229" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C229" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D229" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>6.0280000000000005</x:v>
       </x:c>
       <x:c r="E229" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F229" s="11" t="n">
         <x:f>SQRT((C229-C228)^2+(D229-D228)^2+(E229-E228)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>1.6219999999999999</x:v>
       </x:c>
       <x:c r="G229" s="8" t="str">
         <x:v>Current</x:v>
@@ -12632,23 +12628,23 @@
     </x:row>
     <x:row r="230" ht="32" customHeight="1">
       <x:c r="A230" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B230" s="8" t="n">
-        <x:v>17</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C230" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>2.655</x:v>
       </x:c>
       <x:c r="D230" s="11" t="n">
-        <x:v>6.0120000000000005</x:v>
+        <x:v>6.0280000000000005</x:v>
       </x:c>
       <x:c r="E230" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F230" s="11" t="n">
         <x:f>SQRT((C230-C229)^2+(D230-D229)^2+(E230-E229)^2)</x:f>
-        <x:v>1.0279999999999996</x:v>
+        <x:v>0.3049999999999997</x:v>
       </x:c>
       <x:c r="G230" s="8" t="str">
         <x:v>Current</x:v>
@@ -12656,23 +12652,23 @@
     </x:row>
     <x:row r="231" ht="32" customHeight="1">
       <x:c r="A231" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
       </x:c>
       <x:c r="B231" s="8" t="n">
-        <x:v>18</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C231" s="11" t="n">
-        <x:v>14.475000000000001</x:v>
+        <x:v>2.655</x:v>
       </x:c>
       <x:c r="D231" s="11" t="n">
-        <x:v>6.0120000000000005</x:v>
+        <x:v>6.0280000000000005</x:v>
       </x:c>
       <x:c r="E231" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F231" s="11" t="n">
-        <x:f>SQRT((C231-C230)^2+(D231-D230)^2+(E231-E230)^2)</x:f>
-        <x:v>22.5</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G231" s="8" t="str">
         <x:v>Current</x:v>
@@ -12680,274 +12676,274 @@
     </x:row>
     <x:row r="232" ht="32" customHeight="1">
       <x:c r="A232" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F245</x:v>
+        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
       </x:c>
       <x:c r="B232" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C232" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D232" s="11" t="n">
+        <x:v>7.65</x:v>
+      </x:c>
+      <x:c r="E232" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F232" s="11" t="n">
+        <x:f>SQRT((C232-C231)^2+(D232-D231)^2+(E232-E231)^2)</x:f>
+        <x:v>1.6504269144678898</x:v>
+      </x:c>
+      <x:c r="G232" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" ht="32" customHeight="1">
+      <x:c r="A233" s="8" t="str">
+        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+      </x:c>
+      <x:c r="B233" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C233" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D233" s="11" t="n">
+        <x:v>7.65</x:v>
+      </x:c>
+      <x:c r="E233" s="11" t="n">
+        <x:v>-3.05</x:v>
+      </x:c>
+      <x:c r="F233" s="11" t="n">
+        <x:f>SQRT((C233-C232)^2+(D233-D232)^2+(E233-E232)^2)</x:f>
+        <x:v>4.3100000000000005</x:v>
+      </x:c>
+      <x:c r="G233" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" ht="32" customHeight="1">
+      <x:c r="A234" s="8" t="str">
+        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+      </x:c>
+      <x:c r="B234" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C234" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D234" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E234" s="11" t="n">
+        <x:v>-3.05</x:v>
+      </x:c>
+      <x:c r="F234" s="11" t="n">
+        <x:f>SQRT((C234-C233)^2+(D234-D233)^2+(E234-E233)^2)</x:f>
+        <x:v>1.6500000000000004</x:v>
+      </x:c>
+      <x:c r="G234" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" ht="32" customHeight="1">
+      <x:c r="A235" s="8" t="str">
+        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+      </x:c>
+      <x:c r="B235" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C235" s="11" t="n">
+        <x:v>2.655</x:v>
+      </x:c>
+      <x:c r="D235" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E235" s="11" t="n">
+        <x:v>-3.05</x:v>
+      </x:c>
+      <x:c r="F235" s="11" t="n">
+        <x:f>SQRT((C235-C234)^2+(D235-D234)^2+(E235-E234)^2)</x:f>
+        <x:v>0.3049999999999997</x:v>
+      </x:c>
+      <x:c r="G235" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" ht="32" customHeight="1">
+      <x:c r="A236" s="8" t="str">
+        <x:v>trunk:DB2:F4:fan:1</x:v>
+      </x:c>
+      <x:c r="B236" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C232" s="11" t="n">
-        <x:v>14.475000000000001</x:v>
-      </x:c>
-      <x:c r="D232" s="11" t="n">
-        <x:v>6.0120000000000005</x:v>
-      </x:c>
-      <x:c r="E232" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F232" s="11" t="n">
+      <x:c r="C236" s="11" t="n">
+        <x:v>2.73</x:v>
+      </x:c>
+      <x:c r="D236" s="11" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E236" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F236" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G232" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="233" ht="32" customHeight="1">
-      <x:c r="A233" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F245</x:v>
-      </x:c>
-      <x:c r="B233" s="8" t="n">
+      <x:c r="G236" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" ht="32" customHeight="1">
+      <x:c r="A237" s="8" t="str">
+        <x:v>trunk:DB2:F4:fan:1</x:v>
+      </x:c>
+      <x:c r="B237" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C233" s="11" t="n">
-        <x:v>14.475000000000001</x:v>
-      </x:c>
-      <x:c r="D233" s="11" t="n">
-        <x:v>5.55</x:v>
-      </x:c>
-      <x:c r="E233" s="11" t="n">
+      <x:c r="C237" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D237" s="11" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E237" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F237" s="11" t="n">
+        <x:f>SQRT((C237-C236)^2+(D237-D236)^2+(E237-E236)^2)</x:f>
+        <x:v>0.3799999999999999</x:v>
+      </x:c>
+      <x:c r="G237" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" ht="32" customHeight="1">
+      <x:c r="A238" s="8" t="str">
+        <x:v>trunk:DB2:F4:fan:1</x:v>
+      </x:c>
+      <x:c r="B238" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C238" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D238" s="11" t="n">
+        <x:v>7.65</x:v>
+      </x:c>
+      <x:c r="E238" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F238" s="11" t="n">
+        <x:f>SQRT((C238-C237)^2+(D238-D237)^2+(E238-E237)^2)</x:f>
+        <x:v>6.15</x:v>
+      </x:c>
+      <x:c r="G238" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" ht="32" customHeight="1">
+      <x:c r="A239" s="8" t="str">
+        <x:v>trunk:DB2:F4:fan:1</x:v>
+      </x:c>
+      <x:c r="B239" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C239" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D239" s="11" t="n">
+        <x:v>7.65</x:v>
+      </x:c>
+      <x:c r="E239" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
-      <x:c r="F233" s="11" t="n">
-        <x:f>SQRT((C233-C232)^2+(D233-D232)^2+(E233-E232)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
-      </x:c>
-      <x:c r="G233" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="234" ht="32" customHeight="1">
-      <x:c r="A234" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F245</x:v>
-      </x:c>
-      <x:c r="B234" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C234" s="11" t="n">
-        <x:v>14.475</x:v>
-      </x:c>
-      <x:c r="D234" s="11" t="n">
-        <x:v>5.55</x:v>
-      </x:c>
-      <x:c r="E234" s="11" t="n">
-        <x:v>7.07</x:v>
-      </x:c>
-      <x:c r="F234" s="11" t="n">
-        <x:f>SQRT((C234-C233)^2+(D234-D233)^2+(E234-E233)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
-      </x:c>
-      <x:c r="G234" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="235" ht="32" customHeight="1">
-      <x:c r="A235" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F247</x:v>
-      </x:c>
-      <x:c r="B235" s="8" t="n">
+      <x:c r="F239" s="11" t="n">
+        <x:f>SQRT((C239-C238)^2+(D239-D238)^2+(E239-E238)^2)</x:f>
+        <x:v>10.66</x:v>
+      </x:c>
+      <x:c r="G239" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" ht="32" customHeight="1">
+      <x:c r="A240" s="8" t="str">
+        <x:v>trunk:DB2:F4:fan:1</x:v>
+      </x:c>
+      <x:c r="B240" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C240" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D240" s="11" t="n">
+        <x:v>6.0280000000000005</x:v>
+      </x:c>
+      <x:c r="E240" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F240" s="11" t="n">
+        <x:f>SQRT((C240-C239)^2+(D240-D239)^2+(E240-E239)^2)</x:f>
+        <x:v>1.6219999999999999</x:v>
+      </x:c>
+      <x:c r="G240" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" ht="32" customHeight="1">
+      <x:c r="A241" s="8" t="str">
+        <x:v>trunk:DB2:F4:fan:1</x:v>
+      </x:c>
+      <x:c r="B241" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C241" s="11" t="n">
+        <x:v>2.655</x:v>
+      </x:c>
+      <x:c r="D241" s="11" t="n">
+        <x:v>6.0280000000000005</x:v>
+      </x:c>
+      <x:c r="E241" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F241" s="11" t="n">
+        <x:f>SQRT((C241-C240)^2+(D241-D240)^2+(E241-E240)^2)</x:f>
+        <x:v>0.3049999999999997</x:v>
+      </x:c>
+      <x:c r="G241" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" ht="32" customHeight="1">
+      <x:c r="A242" s="8" t="str">
+        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+      </x:c>
+      <x:c r="B242" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C235" s="11" t="n">
-        <x:v>23.475</x:v>
-      </x:c>
-      <x:c r="D235" s="11" t="n">
-        <x:v>6.0120000000000005</x:v>
-      </x:c>
-      <x:c r="E235" s="11" t="n">
+      <x:c r="C242" s="11" t="n">
+        <x:v>2.655</x:v>
+      </x:c>
+      <x:c r="D242" s="11" t="n">
+        <x:v>6.0280000000000005</x:v>
+      </x:c>
+      <x:c r="E242" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
-      <x:c r="F235" s="11" t="n">
+      <x:c r="F242" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G235" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="236" ht="32" customHeight="1">
-      <x:c r="A236" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F247</x:v>
-      </x:c>
-      <x:c r="B236" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C236" s="11" t="n">
-        <x:v>23.475</x:v>
-      </x:c>
-      <x:c r="D236" s="11" t="n">
-        <x:v>5.55</x:v>
-      </x:c>
-      <x:c r="E236" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F236" s="11" t="n">
-        <x:f>SQRT((C236-C235)^2+(D236-D235)^2+(E236-E235)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
-      </x:c>
-      <x:c r="G236" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="237" ht="32" customHeight="1">
-      <x:c r="A237" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F247</x:v>
-      </x:c>
-      <x:c r="B237" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C237" s="11" t="n">
-        <x:v>23.475</x:v>
-      </x:c>
-      <x:c r="D237" s="11" t="n">
-        <x:v>5.55</x:v>
-      </x:c>
-      <x:c r="E237" s="11" t="n">
-        <x:v>7.07</x:v>
-      </x:c>
-      <x:c r="F237" s="11" t="n">
-        <x:f>SQRT((C237-C236)^2+(D237-D236)^2+(E237-E236)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
-      </x:c>
-      <x:c r="G237" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="238" ht="32" customHeight="1">
-      <x:c r="A238" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F249</x:v>
-      </x:c>
-      <x:c r="B238" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C238" s="11" t="n">
-        <x:v>32.475</x:v>
-      </x:c>
-      <x:c r="D238" s="11" t="n">
-        <x:v>6.0120000000000005</x:v>
-      </x:c>
-      <x:c r="E238" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F238" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G238" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="239" ht="32" customHeight="1">
-      <x:c r="A239" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F249</x:v>
-      </x:c>
-      <x:c r="B239" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C239" s="11" t="n">
-        <x:v>32.475</x:v>
-      </x:c>
-      <x:c r="D239" s="11" t="n">
-        <x:v>5.55</x:v>
-      </x:c>
-      <x:c r="E239" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F239" s="11" t="n">
-        <x:f>SQRT((C239-C238)^2+(D239-D238)^2+(E239-E238)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
-      </x:c>
-      <x:c r="G239" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="240" ht="32" customHeight="1">
-      <x:c r="A240" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F249</x:v>
-      </x:c>
-      <x:c r="B240" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C240" s="11" t="n">
-        <x:v>32.475</x:v>
-      </x:c>
-      <x:c r="D240" s="11" t="n">
-        <x:v>5.55</x:v>
-      </x:c>
-      <x:c r="E240" s="11" t="n">
-        <x:v>7.07</x:v>
-      </x:c>
-      <x:c r="F240" s="11" t="n">
-        <x:f>SQRT((C240-C239)^2+(D240-D239)^2+(E240-E239)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
-      </x:c>
-      <x:c r="G240" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="241" ht="32" customHeight="1">
-      <x:c r="A241" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
-      </x:c>
-      <x:c r="B241" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C241" s="11" t="n">
-        <x:v>2.73</x:v>
-      </x:c>
-      <x:c r="D241" s="11" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="E241" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F241" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G241" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="242" ht="32" customHeight="1">
-      <x:c r="A242" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
-      </x:c>
-      <x:c r="B242" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C242" s="11" t="n">
-        <x:v>2.35</x:v>
-      </x:c>
-      <x:c r="D242" s="11" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="E242" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F242" s="11" t="n">
-        <x:f>SQRT((C242-C241)^2+(D242-D241)^2+(E242-E241)^2)</x:f>
-        <x:v>0.3799999999999999</x:v>
-      </x:c>
       <x:c r="G242" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="243" ht="32" customHeight="1">
       <x:c r="A243" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
+        <x:v>drop:DB2:F4:fan:1:F251</x:v>
       </x:c>
       <x:c r="B243" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C243" s="11" t="n">
         <x:v>2.35</x:v>
@@ -12956,11 +12952,11 @@
         <x:v>7.65</x:v>
       </x:c>
       <x:c r="E243" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F243" s="11" t="n">
         <x:f>SQRT((C243-C242)^2+(D243-D242)^2+(E243-E242)^2)</x:f>
-        <x:v>6.15</x:v>
+        <x:v>1.6504269144678898</x:v>
       </x:c>
       <x:c r="G243" s="8" t="str">
         <x:v>Current</x:v>
@@ -12968,10 +12964,10 @@
     </x:row>
     <x:row r="244" ht="32" customHeight="1">
       <x:c r="A244" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
+        <x:v>drop:DB2:F4:fan:1:F251</x:v>
       </x:c>
       <x:c r="B244" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C244" s="11" t="n">
         <x:v>2.35</x:v>
@@ -12980,11 +12976,11 @@
         <x:v>7.65</x:v>
       </x:c>
       <x:c r="E244" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>3.05</x:v>
       </x:c>
       <x:c r="F244" s="11" t="n">
         <x:f>SQRT((C244-C243)^2+(D244-D243)^2+(E244-E243)^2)</x:f>
-        <x:v>4.0600000000000005</x:v>
+        <x:v>4.3100000000000005</x:v>
       </x:c>
       <x:c r="G244" s="8" t="str">
         <x:v>Current</x:v>
@@ -12992,23 +12988,23 @@
     </x:row>
     <x:row r="245" ht="32" customHeight="1">
       <x:c r="A245" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
+        <x:v>drop:DB2:F4:fan:1:F251</x:v>
       </x:c>
       <x:c r="B245" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C245" s="11" t="n">
         <x:v>2.35</x:v>
       </x:c>
       <x:c r="D245" s="11" t="n">
-        <x:v>6.0280000000000005</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E245" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>3.05</x:v>
       </x:c>
       <x:c r="F245" s="11" t="n">
         <x:f>SQRT((C245-C244)^2+(D245-D244)^2+(E245-E244)^2)</x:f>
-        <x:v>1.6219999999999999</x:v>
+        <x:v>1.6500000000000004</x:v>
       </x:c>
       <x:c r="G245" s="8" t="str">
         <x:v>Current</x:v>
@@ -13016,19 +13012,19 @@
     </x:row>
     <x:row r="246" ht="32" customHeight="1">
       <x:c r="A246" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
+        <x:v>drop:DB2:F4:fan:1:F251</x:v>
       </x:c>
       <x:c r="B246" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C246" s="11" t="n">
         <x:v>2.655</x:v>
       </x:c>
       <x:c r="D246" s="11" t="n">
-        <x:v>6.0280000000000005</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E246" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>3.05</x:v>
       </x:c>
       <x:c r="F246" s="11" t="n">
         <x:f>SQRT((C246-C245)^2+(D246-D245)^2+(E246-E245)^2)</x:f>
@@ -13040,19 +13036,19 @@
     </x:row>
     <x:row r="247" ht="32" customHeight="1">
       <x:c r="A247" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B247" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C247" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D247" s="11" t="n">
-        <x:v>6.0280000000000005</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E247" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F247" s="11" t="n">
         <x:f>0</x:f>
@@ -13064,23 +13060,23 @@
     </x:row>
     <x:row r="248" ht="32" customHeight="1">
       <x:c r="A248" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B248" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C248" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D248" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E248" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F248" s="11" t="n">
         <x:f>SQRT((C248-C247)^2+(D248-D247)^2+(E248-E247)^2)</x:f>
-        <x:v>1.6504269144678898</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G248" s="8" t="str">
         <x:v>Current</x:v>
@@ -13088,23 +13084,23 @@
     </x:row>
     <x:row r="249" ht="32" customHeight="1">
       <x:c r="A249" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B249" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C249" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D249" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E249" s="11" t="n">
-        <x:v>-3.05</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F249" s="11" t="n">
         <x:f>SQRT((C249-C248)^2+(D249-D248)^2+(E249-E248)^2)</x:f>
-        <x:v>4.3100000000000005</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="G249" s="8" t="str">
         <x:v>Current</x:v>
@@ -13112,23 +13108,23 @@
     </x:row>
     <x:row r="250" ht="32" customHeight="1">
       <x:c r="A250" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B250" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C250" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D250" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E250" s="11" t="n">
-        <x:v>-3.05</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F250" s="11" t="n">
         <x:f>SQRT((C250-C249)^2+(D250-D249)^2+(E250-E249)^2)</x:f>
-        <x:v>1.6500000000000004</x:v>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="G250" s="8" t="str">
         <x:v>Current</x:v>
@@ -13136,23 +13132,23 @@
     </x:row>
     <x:row r="251" ht="32" customHeight="1">
       <x:c r="A251" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B251" s="8" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C251" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D251" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E251" s="11" t="n">
-        <x:v>-3.05</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F251" s="11" t="n">
         <x:f>SQRT((C251-C250)^2+(D251-D250)^2+(E251-E250)^2)</x:f>
-        <x:v>0.3049999999999997</x:v>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G251" s="8" t="str">
         <x:v>Current</x:v>
@@ -13160,23 +13156,23 @@
     </x:row>
     <x:row r="252" ht="32" customHeight="1">
       <x:c r="A252" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B252" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C252" s="11" t="n">
-        <x:v>2.73</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D252" s="11" t="n">
-        <x:v>1.5</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E252" s="11" t="n">
         <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F252" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C252-C251)^2+(D252-D251)^2+(E252-E251)^2)</x:f>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G252" s="8" t="str">
         <x:v>Current</x:v>
@@ -13184,23 +13180,23 @@
     </x:row>
     <x:row r="253" ht="32" customHeight="1">
       <x:c r="A253" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B253" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C253" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D253" s="11" t="n">
-        <x:v>1.5</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E253" s="11" t="n">
         <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F253" s="11" t="n">
         <x:f>SQRT((C253-C252)^2+(D253-D252)^2+(E253-E252)^2)</x:f>
-        <x:v>0.3799999999999999</x:v>
+        <x:v>1.7060000000000004</x:v>
       </x:c>
       <x:c r="G253" s="8" t="str">
         <x:v>Current</x:v>
@@ -13208,23 +13204,23 @@
     </x:row>
     <x:row r="254" ht="32" customHeight="1">
       <x:c r="A254" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B254" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C254" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D254" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E254" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F254" s="11" t="n">
         <x:f>SQRT((C254-C253)^2+(D254-D253)^2+(E254-E253)^2)</x:f>
-        <x:v>6.15</x:v>
+        <x:v>4.0600000000000005</x:v>
       </x:c>
       <x:c r="G254" s="8" t="str">
         <x:v>Current</x:v>
@@ -13232,23 +13228,23 @@
     </x:row>
     <x:row r="255" ht="32" customHeight="1">
       <x:c r="A255" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B255" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C255" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D255" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E255" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F255" s="11" t="n">
         <x:f>SQRT((C255-C254)^2+(D255-D254)^2+(E255-E254)^2)</x:f>
-        <x:v>10.66</x:v>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G255" s="8" t="str">
         <x:v>Current</x:v>
@@ -13256,23 +13252,23 @@
     </x:row>
     <x:row r="256" ht="32" customHeight="1">
       <x:c r="A256" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B256" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C256" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D256" s="11" t="n">
-        <x:v>6.0280000000000005</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E256" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F256" s="11" t="n">
         <x:f>SQRT((C256-C255)^2+(D256-D255)^2+(E256-E255)^2)</x:f>
-        <x:v>1.6219999999999999</x:v>
+        <x:v>1.0039999999999996</x:v>
       </x:c>
       <x:c r="G256" s="8" t="str">
         <x:v>Current</x:v>
@@ -13280,23 +13276,23 @@
     </x:row>
     <x:row r="257" ht="32" customHeight="1">
       <x:c r="A257" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B257" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C257" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D257" s="11" t="n">
-        <x:v>6.0280000000000005</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E257" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F257" s="11" t="n">
         <x:f>SQRT((C257-C256)^2+(D257-D256)^2+(E257-E256)^2)</x:f>
-        <x:v>0.3049999999999997</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G257" s="8" t="str">
         <x:v>Current</x:v>
@@ -13304,23 +13300,23 @@
     </x:row>
     <x:row r="258" ht="32" customHeight="1">
       <x:c r="A258" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B258" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C258" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D258" s="11" t="n">
-        <x:v>6.0280000000000005</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E258" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F258" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C258-C257)^2+(D258-D257)^2+(E258-E257)^2)</x:f>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G258" s="8" t="str">
         <x:v>Current</x:v>
@@ -13328,23 +13324,23 @@
     </x:row>
     <x:row r="259" ht="32" customHeight="1">
       <x:c r="A259" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B259" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C259" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D259" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E259" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F259" s="11" t="n">
         <x:f>SQRT((C259-C258)^2+(D259-D258)^2+(E259-E258)^2)</x:f>
-        <x:v>1.6504269144678898</x:v>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G259" s="8" t="str">
         <x:v>Current</x:v>
@@ -13352,23 +13348,23 @@
     </x:row>
     <x:row r="260" ht="32" customHeight="1">
       <x:c r="A260" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B260" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C260" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>37.695</x:v>
       </x:c>
       <x:c r="D260" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>6.950412371134018</x:v>
       </x:c>
       <x:c r="E260" s="11" t="n">
-        <x:v>3.05</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F260" s="11" t="n">
         <x:f>SQRT((C260-C259)^2+(D260-D259)^2+(E260-E259)^2)</x:f>
-        <x:v>4.3100000000000005</x:v>
+        <x:v>3.697957107375376</x:v>
       </x:c>
       <x:c r="G260" s="8" t="str">
         <x:v>Current</x:v>
@@ -13376,23 +13372,23 @@
     </x:row>
     <x:row r="261" ht="32" customHeight="1">
       <x:c r="A261" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B261" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C261" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>37.615</x:v>
       </x:c>
       <x:c r="D261" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E261" s="11" t="n">
-        <x:v>3.05</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F261" s="11" t="n">
         <x:f>SQRT((C261-C260)^2+(D261-D260)^2+(E261-E260)^2)</x:f>
-        <x:v>1.6500000000000004</x:v>
+        <x:v>0.12010804821421713</x:v>
       </x:c>
       <x:c r="G261" s="8" t="str">
         <x:v>Current</x:v>
@@ -13400,23 +13396,23 @@
     </x:row>
     <x:row r="262" ht="32" customHeight="1">
       <x:c r="A262" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B262" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C262" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D262" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E262" s="11" t="n">
-        <x:v>3.05</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F262" s="11" t="n">
         <x:f>SQRT((C262-C261)^2+(D262-D261)^2+(E262-E261)^2)</x:f>
-        <x:v>0.3049999999999997</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G262" s="8" t="str">
         <x:v>Current</x:v>
@@ -13427,20 +13423,20 @@
         <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B263" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C263" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D263" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E263" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F263" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C263-C262)^2+(D263-D262)^2+(E263-E262)^2)</x:f>
+        <x:v>1.0039999999999996</x:v>
       </x:c>
       <x:c r="G263" s="8" t="str">
         <x:v>Current</x:v>
@@ -13451,20 +13447,20 @@
         <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B264" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C264" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D264" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E264" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F264" s="11" t="n">
         <x:f>SQRT((C264-C263)^2+(D264-D263)^2+(E264-E263)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
+        <x:v>31.495</x:v>
       </x:c>
       <x:c r="G264" s="8" t="str">
         <x:v>Current</x:v>
@@ -13472,23 +13468,23 @@
     </x:row>
     <x:row r="265" ht="32" customHeight="1">
       <x:c r="A265" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
       </x:c>
       <x:c r="B265" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C265" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D265" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E265" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F265" s="11" t="n">
-        <x:f>SQRT((C265-C264)^2+(D265-D264)^2+(E265-E264)^2)</x:f>
-        <x:v>2.64</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G265" s="8" t="str">
         <x:v>Current</x:v>
@@ -13496,23 +13492,23 @@
     </x:row>
     <x:row r="266" ht="32" customHeight="1">
       <x:c r="A266" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
       </x:c>
       <x:c r="B266" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C266" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D266" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E266" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F266" s="11" t="n">
         <x:f>SQRT((C266-C265)^2+(D266-D265)^2+(E266-E265)^2)</x:f>
-        <x:v>2.38</x:v>
+        <x:v>1.0039999999999996</x:v>
       </x:c>
       <x:c r="G266" s="8" t="str">
         <x:v>Current</x:v>
@@ -13520,23 +13516,23 @@
     </x:row>
     <x:row r="267" ht="32" customHeight="1">
       <x:c r="A267" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
       </x:c>
       <x:c r="B267" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C267" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D267" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E267" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F267" s="11" t="n">
         <x:f>SQRT((C267-C266)^2+(D267-D266)^2+(E267-E266)^2)</x:f>
-        <x:v>1.0599999999999996</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G267" s="8" t="str">
         <x:v>Current</x:v>
@@ -13544,23 +13540,23 @@
     </x:row>
     <x:row r="268" ht="32" customHeight="1">
       <x:c r="A268" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
       </x:c>
       <x:c r="B268" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C268" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D268" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>10.64004347826087</x:v>
       </x:c>
       <x:c r="E268" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-2.3999999999999995</x:v>
       </x:c>
       <x:c r="F268" s="11" t="n">
         <x:f>SQRT((C268-C267)^2+(D268-D267)^2+(E268-E267)^2)</x:f>
-        <x:v>4.280999999999999</x:v>
+        <x:v>6.128777451120952</x:v>
       </x:c>
       <x:c r="G268" s="8" t="str">
         <x:v>Current</x:v>
@@ -13568,23 +13564,23 @@
     </x:row>
     <x:row r="269" ht="32" customHeight="1">
       <x:c r="A269" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
       </x:c>
       <x:c r="B269" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C269" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D269" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E269" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-2.4</x:v>
       </x:c>
       <x:c r="F269" s="11" t="n">
         <x:f>SQRT((C269-C268)^2+(D269-D268)^2+(E269-E268)^2)</x:f>
-        <x:v>1.7060000000000004</x:v>
+        <x:v>1.2400434782608691</x:v>
       </x:c>
       <x:c r="G269" s="8" t="str">
         <x:v>Current</x:v>
@@ -13592,23 +13588,23 @@
     </x:row>
     <x:row r="270" ht="32" customHeight="1">
       <x:c r="A270" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
       </x:c>
       <x:c r="B270" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C270" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D270" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E270" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-2.4</x:v>
       </x:c>
       <x:c r="F270" s="11" t="n">
         <x:f>SQRT((C270-C269)^2+(D270-D269)^2+(E270-E269)^2)</x:f>
-        <x:v>4.0600000000000005</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G270" s="8" t="str">
         <x:v>Current</x:v>
@@ -13616,13 +13612,13 @@
     </x:row>
     <x:row r="271" ht="32" customHeight="1">
       <x:c r="A271" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
       </x:c>
       <x:c r="B271" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C271" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D271" s="11" t="n">
         <x:v>6.0360000000000005</x:v>
@@ -13631,8 +13627,8 @@
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F271" s="11" t="n">
-        <x:f>SQRT((C271-C270)^2+(D271-D270)^2+(E271-E270)^2)</x:f>
-        <x:v>8.841000000000001</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G271" s="8" t="str">
         <x:v>Current</x:v>
@@ -13640,13 +13636,13 @@
     </x:row>
     <x:row r="272" ht="32" customHeight="1">
       <x:c r="A272" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
       </x:c>
       <x:c r="B272" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C272" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D272" s="11" t="n">
         <x:v>7.04</x:v>
@@ -13664,13 +13660,13 @@
     </x:row>
     <x:row r="273" ht="32" customHeight="1">
       <x:c r="A273" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
       </x:c>
       <x:c r="B273" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C273" s="11" t="n">
-        <x:v>43.535</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D273" s="11" t="n">
         <x:v>7.04</x:v>
@@ -13680,7 +13676,7 @@
       </x:c>
       <x:c r="F273" s="11" t="n">
         <x:f>SQRT((C273-C272)^2+(D273-D272)^2+(E273-E272)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G273" s="8" t="str">
         <x:v>Current</x:v>
@@ -13688,23 +13684,23 @@
     </x:row>
     <x:row r="274" ht="32" customHeight="1">
       <x:c r="A274" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
       </x:c>
       <x:c r="B274" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C274" s="11" t="n">
-        <x:v>43.455</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D274" s="11" t="n">
-        <x:v>6.950412371134024</x:v>
+        <x:v>11.801347826086957</x:v>
       </x:c>
       <x:c r="E274" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-0.7999999999999998</x:v>
       </x:c>
       <x:c r="F274" s="11" t="n">
         <x:f>SQRT((C274-C273)^2+(D274-D273)^2+(E274-E273)^2)</x:f>
-        <x:v>0.12010804821421249</x:v>
+        <x:v>8.105802435353516</x:v>
       </x:c>
       <x:c r="G274" s="8" t="str">
         <x:v>Current</x:v>
@@ -13712,23 +13708,23 @@
     </x:row>
     <x:row r="275" ht="32" customHeight="1">
       <x:c r="A275" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
       </x:c>
       <x:c r="B275" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C275" s="11" t="n">
-        <x:v>40.574999999999996</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D275" s="11" t="n">
-        <x:v>9.269999999999994</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E275" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="F275" s="11" t="n">
         <x:f>SQRT((C275-C274)^2+(D275-D274)^2+(E275-E274)^2)</x:f>
-        <x:v>3.6979571073753776</x:v>
+        <x:v>2.4013478260869565</x:v>
       </x:c>
       <x:c r="G275" s="8" t="str">
         <x:v>Current</x:v>
@@ -13736,23 +13732,23 @@
     </x:row>
     <x:row r="276" ht="32" customHeight="1">
       <x:c r="A276" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
       </x:c>
       <x:c r="B276" s="8" t="n">
-        <x:v>14</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C276" s="11" t="n">
-        <x:v>37.695</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D276" s="11" t="n">
-        <x:v>6.950412371134018</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E276" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="F276" s="11" t="n">
         <x:f>SQRT((C276-C275)^2+(D276-D275)^2+(E276-E275)^2)</x:f>
-        <x:v>3.697957107375376</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G276" s="8" t="str">
         <x:v>Current</x:v>
@@ -13760,23 +13756,23 @@
     </x:row>
     <x:row r="277" ht="32" customHeight="1">
       <x:c r="A277" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
       </x:c>
       <x:c r="B277" s="8" t="n">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C277" s="11" t="n">
-        <x:v>37.615</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D277" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>8.565264175257731</x:v>
       </x:c>
       <x:c r="E277" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F277" s="11" t="n">
-        <x:f>SQRT((C277-C276)^2+(D277-D276)^2+(E277-E276)^2)</x:f>
-        <x:v>0.12010804821421713</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G277" s="8" t="str">
         <x:v>Current</x:v>
@@ -13784,23 +13780,23 @@
     </x:row>
     <x:row r="278" ht="32" customHeight="1">
       <x:c r="A278" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
       </x:c>
       <x:c r="B278" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C278" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D278" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>8.565264175257731</x:v>
       </x:c>
       <x:c r="E278" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-13.249</x:v>
       </x:c>
       <x:c r="F278" s="11" t="n">
         <x:f>SQRT((C278-C277)^2+(D278-D277)^2+(E278-E277)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>5.889</x:v>
       </x:c>
       <x:c r="G278" s="8" t="str">
         <x:v>Current</x:v>
@@ -13808,23 +13804,23 @@
     </x:row>
     <x:row r="279" ht="32" customHeight="1">
       <x:c r="A279" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
       </x:c>
       <x:c r="B279" s="8" t="n">
-        <x:v>17</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C279" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D279" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="E279" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-13.249</x:v>
       </x:c>
       <x:c r="F279" s="11" t="n">
         <x:f>SQRT((C279-C278)^2+(D279-D278)^2+(E279-E278)^2)</x:f>
-        <x:v>1.0039999999999996</x:v>
+        <x:v>0.9652641752577313</x:v>
       </x:c>
       <x:c r="G279" s="8" t="str">
         <x:v>Current</x:v>
@@ -13832,23 +13828,23 @@
     </x:row>
     <x:row r="280" ht="32" customHeight="1">
       <x:c r="A280" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
       </x:c>
       <x:c r="B280" s="8" t="n">
-        <x:v>18</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C280" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D280" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="E280" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-13.13</x:v>
       </x:c>
       <x:c r="F280" s="11" t="n">
         <x:f>SQRT((C280-C279)^2+(D280-D279)^2+(E280-E279)^2)</x:f>
-        <x:v>31.495</x:v>
+        <x:v>0.11899999999999977</x:v>
       </x:c>
       <x:c r="G280" s="8" t="str">
         <x:v>Current</x:v>
@@ -13856,16 +13852,16 @@
     </x:row>
     <x:row r="281" ht="32" customHeight="1">
       <x:c r="A281" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
       </x:c>
       <x:c r="B281" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C281" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>41.45</x:v>
       </x:c>
       <x:c r="D281" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>8.565264175257724</x:v>
       </x:c>
       <x:c r="E281" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -13880,23 +13876,23 @@
     </x:row>
     <x:row r="282" ht="32" customHeight="1">
       <x:c r="A282" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
       </x:c>
       <x:c r="B282" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C282" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>41.45</x:v>
       </x:c>
       <x:c r="D282" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>8.565264175257731</x:v>
       </x:c>
       <x:c r="E282" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-13.249</x:v>
       </x:c>
       <x:c r="F282" s="11" t="n">
         <x:f>SQRT((C282-C281)^2+(D282-D281)^2+(E282-E281)^2)</x:f>
-        <x:v>1.0039999999999996</x:v>
+        <x:v>5.889</x:v>
       </x:c>
       <x:c r="G282" s="8" t="str">
         <x:v>Current</x:v>
@@ -13904,23 +13900,23 @@
     </x:row>
     <x:row r="283" ht="32" customHeight="1">
       <x:c r="A283" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
       </x:c>
       <x:c r="B283" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C283" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>41.45</x:v>
       </x:c>
       <x:c r="D283" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="E283" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-13.249</x:v>
       </x:c>
       <x:c r="F283" s="11" t="n">
         <x:f>SQRT((C283-C282)^2+(D283-D282)^2+(E283-E282)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
+        <x:v>0.9652641752577313</x:v>
       </x:c>
       <x:c r="G283" s="8" t="str">
         <x:v>Current</x:v>
@@ -13928,23 +13924,23 @@
     </x:row>
     <x:row r="284" ht="32" customHeight="1">
       <x:c r="A284" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
       </x:c>
       <x:c r="B284" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C284" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>41.45</x:v>
       </x:c>
       <x:c r="D284" s="11" t="n">
-        <x:v>10.64004347826087</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="E284" s="11" t="n">
-        <x:v>-2.3999999999999995</x:v>
+        <x:v>-13.13</x:v>
       </x:c>
       <x:c r="F284" s="11" t="n">
         <x:f>SQRT((C284-C283)^2+(D284-D283)^2+(E284-E283)^2)</x:f>
-        <x:v>6.128777451120952</x:v>
+        <x:v>0.11899999999999977</x:v>
       </x:c>
       <x:c r="G284" s="8" t="str">
         <x:v>Current</x:v>
@@ -13952,23 +13948,23 @@
     </x:row>
     <x:row r="285" ht="32" customHeight="1">
       <x:c r="A285" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
       </x:c>
       <x:c r="B285" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C285" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D285" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E285" s="11" t="n">
-        <x:v>-2.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F285" s="11" t="n">
-        <x:f>SQRT((C285-C284)^2+(D285-D284)^2+(E285-E284)^2)</x:f>
-        <x:v>1.2400434782608691</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G285" s="8" t="str">
         <x:v>Current</x:v>
@@ -13976,23 +13972,23 @@
     </x:row>
     <x:row r="286" ht="32" customHeight="1">
       <x:c r="A286" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
       </x:c>
       <x:c r="B286" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C286" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D286" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E286" s="11" t="n">
-        <x:v>-2.4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F286" s="11" t="n">
         <x:f>SQRT((C286-C285)^2+(D286-D285)^2+(E286-E285)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="G286" s="8" t="str">
         <x:v>Current</x:v>
@@ -14000,95 +13996,95 @@
     </x:row>
     <x:row r="287" ht="32" customHeight="1">
       <x:c r="A287" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
       </x:c>
       <x:c r="B287" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C287" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D287" s="11" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="E287" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F287" s="11" t="n">
+        <x:f>SQRT((C287-C286)^2+(D287-D286)^2+(E287-E286)^2)</x:f>
+        <x:v>2.7360000000000007</x:v>
+      </x:c>
+      <x:c r="G287" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288" ht="32" customHeight="1">
+      <x:c r="A288" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
+      </x:c>
+      <x:c r="B288" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C288" s="11" t="n">
+        <x:v>53.12</x:v>
+      </x:c>
+      <x:c r="D288" s="11" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="E288" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F288" s="11" t="n">
+        <x:f>SQRT((C288-C287)^2+(D288-D287)^2+(E288-E287)^2)</x:f>
+        <x:v>0.1039999999999992</x:v>
+      </x:c>
+      <x:c r="G288" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289" ht="32" customHeight="1">
+      <x:c r="A289" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+      <x:c r="B289" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C287" s="11" t="n">
-        <x:v>5.48</x:v>
-      </x:c>
-      <x:c r="D287" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
-      </x:c>
-      <x:c r="E287" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F287" s="11" t="n">
+      <x:c r="C289" s="11" t="n">
+        <x:v>48.895</x:v>
+      </x:c>
+      <x:c r="D289" s="11" t="n">
+        <x:v>1.95</x:v>
+      </x:c>
+      <x:c r="E289" s="11" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="F289" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G287" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="288" ht="32" customHeight="1">
-      <x:c r="A288" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
-      </x:c>
-      <x:c r="B288" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C288" s="11" t="n">
-        <x:v>5.48</x:v>
-      </x:c>
-      <x:c r="D288" s="11" t="n">
-        <x:v>7.04</x:v>
-      </x:c>
-      <x:c r="E288" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F288" s="11" t="n">
-        <x:f>SQRT((C288-C287)^2+(D288-D287)^2+(E288-E287)^2)</x:f>
-        <x:v>1.0039999999999996</x:v>
-      </x:c>
-      <x:c r="G288" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="289" ht="32" customHeight="1">
-      <x:c r="A289" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
-      </x:c>
-      <x:c r="B289" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C289" s="11" t="n">
-        <x:v>5.32</x:v>
-      </x:c>
-      <x:c r="D289" s="11" t="n">
-        <x:v>7.04</x:v>
-      </x:c>
-      <x:c r="E289" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F289" s="11" t="n">
-        <x:f>SQRT((C289-C288)^2+(D289-D288)^2+(E289-E288)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
-      </x:c>
       <x:c r="G289" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="290" ht="32" customHeight="1">
       <x:c r="A290" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B290" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C290" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D290" s="11" t="n">
-        <x:v>11.801347826086957</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E290" s="11" t="n">
-        <x:v>-0.7999999999999998</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F290" s="11" t="n">
         <x:f>SQRT((C290-C289)^2+(D290-D289)^2+(E290-E289)^2)</x:f>
-        <x:v>8.105802435353516</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G290" s="8" t="str">
         <x:v>Current</x:v>
@@ -14096,23 +14092,23 @@
     </x:row>
     <x:row r="291" ht="32" customHeight="1">
       <x:c r="A291" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B291" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C291" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D291" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E291" s="11" t="n">
-        <x:v>-0.8</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F291" s="11" t="n">
         <x:f>SQRT((C291-C290)^2+(D291-D290)^2+(E291-E290)^2)</x:f>
-        <x:v>2.4013478260869565</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="G291" s="8" t="str">
         <x:v>Current</x:v>
@@ -14120,23 +14116,23 @@
     </x:row>
     <x:row r="292" ht="32" customHeight="1">
       <x:c r="A292" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B292" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C292" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D292" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E292" s="11" t="n">
-        <x:v>-0.8</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F292" s="11" t="n">
         <x:f>SQRT((C292-C291)^2+(D292-D291)^2+(E292-E291)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="G292" s="8" t="str">
         <x:v>Current</x:v>
@@ -14144,23 +14140,23 @@
     </x:row>
     <x:row r="293" ht="32" customHeight="1">
       <x:c r="A293" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B293" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C293" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D293" s="11" t="n">
-        <x:v>8.565264175257731</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E293" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F293" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C293-C292)^2+(D293-D292)^2+(E293-E292)^2)</x:f>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G293" s="8" t="str">
         <x:v>Current</x:v>
@@ -14168,23 +14164,23 @@
     </x:row>
     <x:row r="294" ht="32" customHeight="1">
       <x:c r="A294" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B294" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C294" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D294" s="11" t="n">
-        <x:v>8.565264175257731</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E294" s="11" t="n">
-        <x:v>-13.249</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F294" s="11" t="n">
         <x:f>SQRT((C294-C293)^2+(D294-D293)^2+(E294-E293)^2)</x:f>
-        <x:v>5.889</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G294" s="8" t="str">
         <x:v>Current</x:v>
@@ -14192,23 +14188,23 @@
     </x:row>
     <x:row r="295" ht="32" customHeight="1">
       <x:c r="A295" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B295" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C295" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D295" s="11" t="n">
-        <x:v>7.6</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E295" s="11" t="n">
-        <x:v>-13.249</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F295" s="11" t="n">
         <x:f>SQRT((C295-C294)^2+(D295-D294)^2+(E295-E294)^2)</x:f>
-        <x:v>0.9652641752577313</x:v>
+        <x:v>1.7060000000000004</x:v>
       </x:c>
       <x:c r="G295" s="8" t="str">
         <x:v>Current</x:v>
@@ -14216,23 +14212,23 @@
     </x:row>
     <x:row r="296" ht="32" customHeight="1">
       <x:c r="A296" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B296" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C296" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D296" s="11" t="n">
-        <x:v>7.6</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E296" s="11" t="n">
-        <x:v>-13.13</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F296" s="11" t="n">
         <x:f>SQRT((C296-C295)^2+(D296-D295)^2+(E296-E295)^2)</x:f>
-        <x:v>0.11899999999999977</x:v>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G296" s="8" t="str">
         <x:v>Current</x:v>
@@ -14240,23 +14236,23 @@
     </x:row>
     <x:row r="297" ht="32" customHeight="1">
       <x:c r="A297" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B297" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C297" s="11" t="n">
-        <x:v>41.45</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D297" s="11" t="n">
-        <x:v>8.565264175257724</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E297" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F297" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C297-C296)^2+(D297-D296)^2+(E297-E296)^2)</x:f>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G297" s="8" t="str">
         <x:v>Current</x:v>
@@ -14264,23 +14260,23 @@
     </x:row>
     <x:row r="298" ht="32" customHeight="1">
       <x:c r="A298" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B298" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C298" s="11" t="n">
-        <x:v>41.45</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D298" s="11" t="n">
-        <x:v>8.565264175257731</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E298" s="11" t="n">
-        <x:v>-13.249</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F298" s="11" t="n">
         <x:f>SQRT((C298-C297)^2+(D298-D297)^2+(E298-E297)^2)</x:f>
-        <x:v>5.889</x:v>
+        <x:v>1.0039999999999996</x:v>
       </x:c>
       <x:c r="G298" s="8" t="str">
         <x:v>Current</x:v>
@@ -14288,23 +14284,23 @@
     </x:row>
     <x:row r="299" ht="32" customHeight="1">
       <x:c r="A299" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B299" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C299" s="11" t="n">
-        <x:v>41.45</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D299" s="11" t="n">
-        <x:v>7.6</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E299" s="11" t="n">
-        <x:v>-13.249</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F299" s="11" t="n">
         <x:f>SQRT((C299-C298)^2+(D299-D298)^2+(E299-E298)^2)</x:f>
-        <x:v>0.9652641752577313</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G299" s="8" t="str">
         <x:v>Current</x:v>
@@ -14312,23 +14308,23 @@
     </x:row>
     <x:row r="300" ht="32" customHeight="1">
       <x:c r="A300" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B300" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C300" s="11" t="n">
-        <x:v>41.45</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D300" s="11" t="n">
-        <x:v>7.6</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E300" s="11" t="n">
-        <x:v>-13.13</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F300" s="11" t="n">
         <x:f>SQRT((C300-C299)^2+(D300-D299)^2+(E300-E299)^2)</x:f>
-        <x:v>0.11899999999999977</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G300" s="8" t="str">
         <x:v>Current</x:v>
@@ -14336,23 +14332,23 @@
     </x:row>
     <x:row r="301" ht="32" customHeight="1">
       <x:c r="A301" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B301" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C301" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D301" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E301" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F301" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C301-C300)^2+(D301-D300)^2+(E301-E300)^2)</x:f>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G301" s="8" t="str">
         <x:v>Current</x:v>
@@ -14360,23 +14356,23 @@
     </x:row>
     <x:row r="302" ht="32" customHeight="1">
       <x:c r="A302" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B302" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C302" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>37.695</x:v>
       </x:c>
       <x:c r="D302" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>6.950412371134018</x:v>
       </x:c>
       <x:c r="E302" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F302" s="11" t="n">
         <x:f>SQRT((C302-C301)^2+(D302-D301)^2+(E302-E301)^2)</x:f>
-        <x:v>7.36</x:v>
+        <x:v>3.697957107375376</x:v>
       </x:c>
       <x:c r="G302" s="8" t="str">
         <x:v>Current</x:v>
@@ -14384,23 +14380,23 @@
     </x:row>
     <x:row r="303" ht="32" customHeight="1">
       <x:c r="A303" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B303" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C303" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>37.615</x:v>
       </x:c>
       <x:c r="D303" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E303" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F303" s="11" t="n">
         <x:f>SQRT((C303-C302)^2+(D303-D302)^2+(E303-E302)^2)</x:f>
-        <x:v>2.7360000000000007</x:v>
+        <x:v>0.12010804821421713</x:v>
       </x:c>
       <x:c r="G303" s="8" t="str">
         <x:v>Current</x:v>
@@ -14408,23 +14404,23 @@
     </x:row>
     <x:row r="304" ht="32" customHeight="1">
       <x:c r="A304" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B304" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C304" s="11" t="n">
-        <x:v>53.12</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D304" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E304" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F304" s="11" t="n">
         <x:f>SQRT((C304-C303)^2+(D304-D303)^2+(E304-E303)^2)</x:f>
-        <x:v>0.1039999999999992</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G304" s="8" t="str">
         <x:v>Current</x:v>
@@ -14435,20 +14431,20 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B305" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C305" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D305" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E305" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F305" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C305-C304)^2+(D305-D304)^2+(E305-E304)^2)</x:f>
+        <x:v>1.0039999999999996</x:v>
       </x:c>
       <x:c r="G305" s="8" t="str">
         <x:v>Current</x:v>
@@ -14459,20 +14455,20 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B306" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C306" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D306" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E306" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F306" s="11" t="n">
         <x:f>SQRT((C306-C305)^2+(D306-D305)^2+(E306-E305)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
+        <x:v>31.495</x:v>
       </x:c>
       <x:c r="G306" s="8" t="str">
         <x:v>Current</x:v>
@@ -14480,23 +14476,23 @@
     </x:row>
     <x:row r="307" ht="32" customHeight="1">
       <x:c r="A307" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B307" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C307" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D307" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E307" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F307" s="11" t="n">
-        <x:f>SQRT((C307-C306)^2+(D307-D306)^2+(E307-E306)^2)</x:f>
-        <x:v>2.64</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G307" s="8" t="str">
         <x:v>Current</x:v>
@@ -14504,23 +14500,23 @@
     </x:row>
     <x:row r="308" ht="32" customHeight="1">
       <x:c r="A308" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B308" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C308" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D308" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E308" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F308" s="11" t="n">
         <x:f>SQRT((C308-C307)^2+(D308-D307)^2+(E308-E307)^2)</x:f>
-        <x:v>2.38</x:v>
+        <x:v>1.0039999999999996</x:v>
       </x:c>
       <x:c r="G308" s="8" t="str">
         <x:v>Current</x:v>
@@ -14528,23 +14524,23 @@
     </x:row>
     <x:row r="309" ht="32" customHeight="1">
       <x:c r="A309" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B309" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C309" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D309" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E309" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F309" s="11" t="n">
         <x:f>SQRT((C309-C308)^2+(D309-D308)^2+(E309-E308)^2)</x:f>
-        <x:v>1.0599999999999996</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G309" s="8" t="str">
         <x:v>Current</x:v>
@@ -14552,23 +14548,23 @@
     </x:row>
     <x:row r="310" ht="32" customHeight="1">
       <x:c r="A310" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B310" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C310" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D310" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>11.801347826086957</x:v>
       </x:c>
       <x:c r="E310" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>0.7999999999999998</x:v>
       </x:c>
       <x:c r="F310" s="11" t="n">
         <x:f>SQRT((C310-C309)^2+(D310-D309)^2+(E310-E309)^2)</x:f>
-        <x:v>4.280999999999999</x:v>
+        <x:v>8.105802435353516</x:v>
       </x:c>
       <x:c r="G310" s="8" t="str">
         <x:v>Current</x:v>
@@ -14576,23 +14572,23 @@
     </x:row>
     <x:row r="311" ht="32" customHeight="1">
       <x:c r="A311" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B311" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C311" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D311" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E311" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="F311" s="11" t="n">
         <x:f>SQRT((C311-C310)^2+(D311-D310)^2+(E311-E310)^2)</x:f>
-        <x:v>1.7060000000000004</x:v>
+        <x:v>2.4013478260869565</x:v>
       </x:c>
       <x:c r="G311" s="8" t="str">
         <x:v>Current</x:v>
@@ -14600,23 +14596,23 @@
     </x:row>
     <x:row r="312" ht="32" customHeight="1">
       <x:c r="A312" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B312" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C312" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D312" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E312" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="F312" s="11" t="n">
         <x:f>SQRT((C312-C311)^2+(D312-D311)^2+(E312-E311)^2)</x:f>
-        <x:v>10.66</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G312" s="8" t="str">
         <x:v>Current</x:v>
@@ -14624,13 +14620,13 @@
     </x:row>
     <x:row r="313" ht="32" customHeight="1">
       <x:c r="A313" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B313" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C313" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D313" s="11" t="n">
         <x:v>6.0360000000000005</x:v>
@@ -14639,8 +14635,8 @@
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F313" s="11" t="n">
-        <x:f>SQRT((C313-C312)^2+(D313-D312)^2+(E313-E312)^2)</x:f>
-        <x:v>8.841000000000001</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G313" s="8" t="str">
         <x:v>Current</x:v>
@@ -14648,13 +14644,13 @@
     </x:row>
     <x:row r="314" ht="32" customHeight="1">
       <x:c r="A314" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B314" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C314" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D314" s="11" t="n">
         <x:v>7.04</x:v>
@@ -14672,13 +14668,13 @@
     </x:row>
     <x:row r="315" ht="32" customHeight="1">
       <x:c r="A315" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B315" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C315" s="11" t="n">
-        <x:v>43.535</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D315" s="11" t="n">
         <x:v>7.04</x:v>
@@ -14688,7 +14684,7 @@
       </x:c>
       <x:c r="F315" s="11" t="n">
         <x:f>SQRT((C315-C314)^2+(D315-D314)^2+(E315-E314)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G315" s="8" t="str">
         <x:v>Current</x:v>
@@ -14696,23 +14692,23 @@
     </x:row>
     <x:row r="316" ht="32" customHeight="1">
       <x:c r="A316" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B316" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C316" s="11" t="n">
-        <x:v>43.455</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D316" s="11" t="n">
-        <x:v>6.950412371134024</x:v>
+        <x:v>10.64004347826087</x:v>
       </x:c>
       <x:c r="E316" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>2.3999999999999995</x:v>
       </x:c>
       <x:c r="F316" s="11" t="n">
         <x:f>SQRT((C316-C315)^2+(D316-D315)^2+(E316-E315)^2)</x:f>
-        <x:v>0.12010804821421249</x:v>
+        <x:v>6.128777451120952</x:v>
       </x:c>
       <x:c r="G316" s="8" t="str">
         <x:v>Current</x:v>
@@ -14720,23 +14716,23 @@
     </x:row>
     <x:row r="317" ht="32" customHeight="1">
       <x:c r="A317" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B317" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C317" s="11" t="n">
-        <x:v>40.574999999999996</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D317" s="11" t="n">
-        <x:v>9.269999999999994</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E317" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="F317" s="11" t="n">
         <x:f>SQRT((C317-C316)^2+(D317-D316)^2+(E317-E316)^2)</x:f>
-        <x:v>3.6979571073753776</x:v>
+        <x:v>1.2400434782608691</x:v>
       </x:c>
       <x:c r="G317" s="8" t="str">
         <x:v>Current</x:v>
@@ -14744,23 +14740,23 @@
     </x:row>
     <x:row r="318" ht="32" customHeight="1">
       <x:c r="A318" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B318" s="8" t="n">
-        <x:v>14</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C318" s="11" t="n">
-        <x:v>37.695</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D318" s="11" t="n">
-        <x:v>6.950412371134018</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E318" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="F318" s="11" t="n">
         <x:f>SQRT((C318-C317)^2+(D318-D317)^2+(E318-E317)^2)</x:f>
-        <x:v>3.697957107375376</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G318" s="8" t="str">
         <x:v>Current</x:v>
@@ -14768,23 +14764,23 @@
     </x:row>
     <x:row r="319" ht="32" customHeight="1">
       <x:c r="A319" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F258</x:v>
       </x:c>
       <x:c r="B319" s="8" t="n">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C319" s="11" t="n">
-        <x:v>37.615</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D319" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>8.565264175257731</x:v>
       </x:c>
       <x:c r="E319" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F319" s="11" t="n">
-        <x:f>SQRT((C319-C318)^2+(D319-D318)^2+(E319-E318)^2)</x:f>
-        <x:v>0.12010804821421713</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G319" s="8" t="str">
         <x:v>Current</x:v>
@@ -14792,23 +14788,23 @@
     </x:row>
     <x:row r="320" ht="32" customHeight="1">
       <x:c r="A320" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F258</x:v>
       </x:c>
       <x:c r="B320" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C320" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D320" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>8.565264175257731</x:v>
       </x:c>
       <x:c r="E320" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>13.249</x:v>
       </x:c>
       <x:c r="F320" s="11" t="n">
         <x:f>SQRT((C320-C319)^2+(D320-D319)^2+(E320-E319)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>5.889</x:v>
       </x:c>
       <x:c r="G320" s="8" t="str">
         <x:v>Current</x:v>
@@ -14816,23 +14812,23 @@
     </x:row>
     <x:row r="321" ht="32" customHeight="1">
       <x:c r="A321" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F258</x:v>
       </x:c>
       <x:c r="B321" s="8" t="n">
-        <x:v>17</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C321" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D321" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="E321" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>13.249</x:v>
       </x:c>
       <x:c r="F321" s="11" t="n">
         <x:f>SQRT((C321-C320)^2+(D321-D320)^2+(E321-E320)^2)</x:f>
-        <x:v>1.0039999999999996</x:v>
+        <x:v>0.9652641752577313</x:v>
       </x:c>
       <x:c r="G321" s="8" t="str">
         <x:v>Current</x:v>
@@ -14840,23 +14836,23 @@
     </x:row>
     <x:row r="322" ht="32" customHeight="1">
       <x:c r="A322" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F258</x:v>
       </x:c>
       <x:c r="B322" s="8" t="n">
-        <x:v>18</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C322" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D322" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="E322" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>13.13</x:v>
       </x:c>
       <x:c r="F322" s="11" t="n">
         <x:f>SQRT((C322-C321)^2+(D322-D321)^2+(E322-E321)^2)</x:f>
-        <x:v>31.495</x:v>
+        <x:v>0.11899999999999977</x:v>
       </x:c>
       <x:c r="G322" s="8" t="str">
         <x:v>Current</x:v>
@@ -14864,16 +14860,16 @@
     </x:row>
     <x:row r="323" ht="32" customHeight="1">
       <x:c r="A323" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>drop:FC1:V1:fan:1:F259</x:v>
       </x:c>
       <x:c r="B323" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C323" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>41.45</x:v>
       </x:c>
       <x:c r="D323" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>8.565264175257724</x:v>
       </x:c>
       <x:c r="E323" s="11" t="n">
         <x:v>7.36</x:v>
@@ -14888,23 +14884,23 @@
     </x:row>
     <x:row r="324" ht="32" customHeight="1">
       <x:c r="A324" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>drop:FC1:V1:fan:1:F259</x:v>
       </x:c>
       <x:c r="B324" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C324" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>41.45</x:v>
       </x:c>
       <x:c r="D324" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>8.565264175257731</x:v>
       </x:c>
       <x:c r="E324" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>13.249</x:v>
       </x:c>
       <x:c r="F324" s="11" t="n">
         <x:f>SQRT((C324-C323)^2+(D324-D323)^2+(E324-E323)^2)</x:f>
-        <x:v>1.0039999999999996</x:v>
+        <x:v>5.889</x:v>
       </x:c>
       <x:c r="G324" s="8" t="str">
         <x:v>Current</x:v>
@@ -14912,23 +14908,23 @@
     </x:row>
     <x:row r="325" ht="32" customHeight="1">
       <x:c r="A325" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>drop:FC1:V1:fan:1:F259</x:v>
       </x:c>
       <x:c r="B325" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C325" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>41.45</x:v>
       </x:c>
       <x:c r="D325" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="E325" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>13.249</x:v>
       </x:c>
       <x:c r="F325" s="11" t="n">
         <x:f>SQRT((C325-C324)^2+(D325-D324)^2+(E325-E324)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
+        <x:v>0.9652641752577313</x:v>
       </x:c>
       <x:c r="G325" s="8" t="str">
         <x:v>Current</x:v>
@@ -14936,23 +14932,23 @@
     </x:row>
     <x:row r="326" ht="32" customHeight="1">
       <x:c r="A326" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>drop:FC1:V1:fan:1:F259</x:v>
       </x:c>
       <x:c r="B326" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C326" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>41.45</x:v>
       </x:c>
       <x:c r="D326" s="11" t="n">
-        <x:v>11.801347826086957</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="E326" s="11" t="n">
-        <x:v>0.7999999999999998</x:v>
+        <x:v>13.13</x:v>
       </x:c>
       <x:c r="F326" s="11" t="n">
         <x:f>SQRT((C326-C325)^2+(D326-D325)^2+(E326-E325)^2)</x:f>
-        <x:v>8.105802435353516</x:v>
+        <x:v>0.11899999999999977</x:v>
       </x:c>
       <x:c r="G326" s="8" t="str">
         <x:v>Current</x:v>
@@ -14960,208 +14956,208 @@
     </x:row>
     <x:row r="327" ht="32" customHeight="1">
       <x:c r="A327" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
       </x:c>
       <x:c r="B327" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C327" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>41.2</x:v>
       </x:c>
       <x:c r="D327" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>8.766617268041228</x:v>
       </x:c>
       <x:c r="E327" s="11" t="n">
-        <x:v>0.8</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F327" s="11" t="n">
-        <x:f>SQRT((C327-C326)^2+(D327-D326)^2+(E327-E326)^2)</x:f>
-        <x:v>2.4013478260869565</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G327" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
     </x:row>
     <x:row r="328" ht="32" customHeight="1">
       <x:c r="A328" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
       </x:c>
       <x:c r="B328" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C328" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>41.2</x:v>
       </x:c>
       <x:c r="D328" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>8.766617268041237</x:v>
       </x:c>
       <x:c r="E328" s="11" t="n">
-        <x:v>0.8</x:v>
+        <x:v>-13.249</x:v>
       </x:c>
       <x:c r="F328" s="11" t="n">
         <x:f>SQRT((C328-C327)^2+(D328-D327)^2+(E328-E327)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
+        <x:v>5.889</x:v>
       </x:c>
       <x:c r="G328" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
     </x:row>
     <x:row r="329" ht="32" customHeight="1">
       <x:c r="A329" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
       </x:c>
       <x:c r="B329" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C329" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="D329" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E329" s="11" t="n">
+        <x:v>-13.249</x:v>
+      </x:c>
+      <x:c r="F329" s="11" t="n">
+        <x:f>SQRT((C329-C328)^2+(D329-D328)^2+(E329-E328)^2)</x:f>
+        <x:v>6.066617268041237</x:v>
+      </x:c>
+      <x:c r="G329" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330" ht="32" customHeight="1">
+      <x:c r="A330" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+      </x:c>
+      <x:c r="B330" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C330" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="D330" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E330" s="11" t="n">
+        <x:v>-13.06</x:v>
+      </x:c>
+      <x:c r="F330" s="11" t="n">
+        <x:f>SQRT((C330-C329)^2+(D330-D329)^2+(E330-E329)^2)</x:f>
+        <x:v>0.18900000000000006</x:v>
+      </x:c>
+      <x:c r="G330" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331" ht="32" customHeight="1">
+      <x:c r="A331" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+      </x:c>
+      <x:c r="B331" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C329" s="11" t="n">
-        <x:v>5.48</x:v>
-      </x:c>
-      <x:c r="D329" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
-      </x:c>
-      <x:c r="E329" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F329" s="11" t="n">
+      <x:c r="C331" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D331" s="11" t="n">
+        <x:v>8.122287371134018</x:v>
+      </x:c>
+      <x:c r="E331" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F331" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G329" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="330" ht="32" customHeight="1">
-      <x:c r="A330" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
-      </x:c>
-      <x:c r="B330" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C330" s="11" t="n">
-        <x:v>5.48</x:v>
-      </x:c>
-      <x:c r="D330" s="11" t="n">
-        <x:v>7.04</x:v>
-      </x:c>
-      <x:c r="E330" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F330" s="11" t="n">
-        <x:f>SQRT((C330-C329)^2+(D330-D329)^2+(E330-E329)^2)</x:f>
-        <x:v>1.0039999999999996</x:v>
-      </x:c>
-      <x:c r="G330" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="331" ht="32" customHeight="1">
-      <x:c r="A331" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
-      </x:c>
-      <x:c r="B331" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C331" s="11" t="n">
-        <x:v>5.32</x:v>
-      </x:c>
-      <x:c r="D331" s="11" t="n">
-        <x:v>7.04</x:v>
-      </x:c>
-      <x:c r="E331" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F331" s="11" t="n">
-        <x:f>SQRT((C331-C330)^2+(D331-D330)^2+(E331-E330)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
-      </x:c>
       <x:c r="G331" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
     </x:row>
     <x:row r="332" ht="32" customHeight="1">
       <x:c r="A332" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
       </x:c>
       <x:c r="B332" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C332" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D332" s="11" t="n">
-        <x:v>10.64004347826087</x:v>
+        <x:v>8.122287371134023</x:v>
       </x:c>
       <x:c r="E332" s="11" t="n">
-        <x:v>2.3999999999999995</x:v>
+        <x:v>-13.249</x:v>
       </x:c>
       <x:c r="F332" s="11" t="n">
         <x:f>SQRT((C332-C331)^2+(D332-D331)^2+(E332-E331)^2)</x:f>
-        <x:v>6.128777451120952</x:v>
+        <x:v>5.889</x:v>
       </x:c>
       <x:c r="G332" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
     </x:row>
     <x:row r="333" ht="32" customHeight="1">
       <x:c r="A333" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
       </x:c>
       <x:c r="B333" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C333" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D333" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="E333" s="11" t="n">
-        <x:v>2.4</x:v>
+        <x:v>-13.249</x:v>
       </x:c>
       <x:c r="F333" s="11" t="n">
         <x:f>SQRT((C333-C332)^2+(D333-D332)^2+(E333-E332)^2)</x:f>
-        <x:v>1.2400434782608691</x:v>
+        <x:v>4.622287371134023</x:v>
       </x:c>
       <x:c r="G333" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
     </x:row>
     <x:row r="334" ht="32" customHeight="1">
       <x:c r="A334" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
       </x:c>
       <x:c r="B334" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C334" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D334" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="E334" s="11" t="n">
-        <x:v>2.4</x:v>
+        <x:v>-13.06</x:v>
       </x:c>
       <x:c r="F334" s="11" t="n">
         <x:f>SQRT((C334-C333)^2+(D334-D333)^2+(E334-E333)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
+        <x:v>0.18900000000000006</x:v>
       </x:c>
       <x:c r="G334" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
     </x:row>
     <x:row r="335" ht="32" customHeight="1">
       <x:c r="A335" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F258</x:v>
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
       </x:c>
       <x:c r="B335" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C335" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>41.2</x:v>
       </x:c>
       <x:c r="D335" s="11" t="n">
-        <x:v>8.565264175257731</x:v>
+        <x:v>8.766617268041228</x:v>
       </x:c>
       <x:c r="E335" s="11" t="n">
         <x:v>7.36</x:v>
@@ -15171,21 +15167,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G335" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
     </x:row>
     <x:row r="336" ht="32" customHeight="1">
       <x:c r="A336" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F258</x:v>
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
       </x:c>
       <x:c r="B336" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C336" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>41.2</x:v>
       </x:c>
       <x:c r="D336" s="11" t="n">
-        <x:v>8.565264175257731</x:v>
+        <x:v>8.766617268041237</x:v>
       </x:c>
       <x:c r="E336" s="11" t="n">
         <x:v>13.249</x:v>
@@ -15195,69 +15191,69 @@
         <x:v>5.889</x:v>
       </x:c>
       <x:c r="G336" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
     </x:row>
     <x:row r="337" ht="32" customHeight="1">
       <x:c r="A337" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F258</x:v>
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
       </x:c>
       <x:c r="B337" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C337" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>41.2</x:v>
       </x:c>
       <x:c r="D337" s="11" t="n">
-        <x:v>7.6</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E337" s="11" t="n">
         <x:v>13.249</x:v>
       </x:c>
       <x:c r="F337" s="11" t="n">
         <x:f>SQRT((C337-C336)^2+(D337-D336)^2+(E337-E336)^2)</x:f>
-        <x:v>0.9652641752577313</x:v>
+        <x:v>6.066617268041237</x:v>
       </x:c>
       <x:c r="G337" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
     </x:row>
     <x:row r="338" ht="32" customHeight="1">
       <x:c r="A338" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F258</x:v>
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
       </x:c>
       <x:c r="B338" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C338" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>41.2</x:v>
       </x:c>
       <x:c r="D338" s="11" t="n">
-        <x:v>7.6</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E338" s="11" t="n">
-        <x:v>13.13</x:v>
+        <x:v>13.06</x:v>
       </x:c>
       <x:c r="F338" s="11" t="n">
         <x:f>SQRT((C338-C337)^2+(D338-D337)^2+(E338-E337)^2)</x:f>
-        <x:v>0.11899999999999977</x:v>
+        <x:v>0.18900000000000006</x:v>
       </x:c>
       <x:c r="G338" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
     </x:row>
     <x:row r="339" ht="32" customHeight="1">
       <x:c r="A339" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F259</x:v>
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
       </x:c>
       <x:c r="B339" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C339" s="11" t="n">
-        <x:v>41.45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D339" s="11" t="n">
-        <x:v>8.565264175257724</x:v>
+        <x:v>8.122287371134018</x:v>
       </x:c>
       <x:c r="E339" s="11" t="n">
         <x:v>7.36</x:v>
@@ -15267,21 +15263,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G339" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
     </x:row>
     <x:row r="340" ht="32" customHeight="1">
       <x:c r="A340" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F259</x:v>
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
       </x:c>
       <x:c r="B340" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C340" s="11" t="n">
-        <x:v>41.45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D340" s="11" t="n">
-        <x:v>8.565264175257731</x:v>
+        <x:v>8.122287371134023</x:v>
       </x:c>
       <x:c r="E340" s="11" t="n">
         <x:v>13.249</x:v>
@@ -15291,55 +15287,55 @@
         <x:v>5.889</x:v>
       </x:c>
       <x:c r="G340" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
     </x:row>
     <x:row r="341" ht="32" customHeight="1">
       <x:c r="A341" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F259</x:v>
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
       </x:c>
       <x:c r="B341" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C341" s="11" t="n">
-        <x:v>41.45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D341" s="11" t="n">
-        <x:v>7.6</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="E341" s="11" t="n">
         <x:v>13.249</x:v>
       </x:c>
       <x:c r="F341" s="11" t="n">
         <x:f>SQRT((C341-C340)^2+(D341-D340)^2+(E341-E340)^2)</x:f>
-        <x:v>0.9652641752577313</x:v>
+        <x:v>4.622287371134023</x:v>
       </x:c>
       <x:c r="G341" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
     </x:row>
     <x:row r="342" ht="32" customHeight="1">
       <x:c r="A342" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F259</x:v>
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
       </x:c>
       <x:c r="B342" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C342" s="11" t="n">
-        <x:v>41.45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D342" s="11" t="n">
-        <x:v>7.6</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="E342" s="11" t="n">
-        <x:v>13.13</x:v>
+        <x:v>13.06</x:v>
       </x:c>
       <x:c r="F342" s="11" t="n">
         <x:f>SQRT((C342-C341)^2+(D342-D341)^2+(E342-E341)^2)</x:f>
-        <x:v>0.11899999999999977</x:v>
+        <x:v>0.18900000000000006</x:v>
       </x:c>
       <x:c r="G342" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
     </x:row>
     <x:row r="343" ht="32" customHeight="1">
@@ -15636,7 +15632,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R681372329658430c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdac1135357bd4fb8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rb3b0736505764436"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rf70ceaec0af64720"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R9bb0772940044295"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rad4721993fb548c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rfbc9bc68e00b49fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rac9e91e1872c411c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R2e1c4f2163ce436c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rb4470f6b0ae94062"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EquipmentRegister" displayName="EquipmentRegister" ref="A6:AC45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EquipmentRegister" displayName="EquipmentRegister" ref="A6:AC55" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="29">
     <x:tableColumn id="1" name="Equipment ID"/>
     <x:tableColumn id="2" name="Name"/>
@@ -217,7 +217,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ElectricalLineRegister" displayName="ElectricalLineRegister" ref="A6:Z59" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ElectricalLineRegister" displayName="ElectricalLineRegister" ref="A6:Z69" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="26">
     <x:tableColumn id="1" name="Route ID"/>
     <x:tableColumn id="2" name="Name"/>
@@ -251,7 +251,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G354" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G384" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Route ID"/>
     <x:tableColumn id="2" name="Vertex"/>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-09T01:06:21.478Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-09T01:31:17.233Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -495,8 +495,8 @@
         <x:v>Current equipment</x:v>
       </x:c>
       <x:c r="B5" s="16" t="n">
-        <x:f>COUNTIFS(Equipment!$AA$7:$AA$45,"Current")</x:f>
-        <x:v>35</x:v>
+        <x:f>COUNTIFS(Equipment!$AA$7:$AA$55,"Current")</x:f>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
@@ -504,8 +504,8 @@
         <x:v>Current routes</x:v>
       </x:c>
       <x:c r="B6" s="16" t="n">
-        <x:f>COUNTIFS('Electrical Lines'!$Y$7:$Y$59,"Current")</x:f>
-        <x:v>45</x:v>
+        <x:f>COUNTIFS('Electrical Lines'!$Y$7:$Y$69,"Current")</x:f>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
@@ -513,7 +513,7 @@
         <x:v>Retired equipment / routes</x:v>
       </x:c>
       <x:c r="B7" s="16" t="n">
-        <x:f>COUNTIFS(Equipment!$AA$7:$AA$45,"Retired")+COUNTIFS('Electrical Lines'!$Y$7:$Y$59,"Retired")</x:f>
+        <x:f>COUNTIFS(Equipment!$AA$7:$AA$55,"Retired")+COUNTIFS('Electrical Lines'!$Y$7:$Y$69,"Retired")</x:f>
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>d4067e8bb027f3bb435cc6fee67c0fc1d0e462a2d8802a6ada0bb37df793ab52</x:v>
+        <x:v>80b0da7d5afe7ebc6ad40230d4100ad0f2b4b395a8a63b44da5d741ccd64e05d</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>e2130aeffb518d934149fa35c32d858856db06e804d9cb98aac4f1896cd3b761</x:v>
+        <x:v>78a1f21a5458fc451b1fadb227a547feb6afa62226cd02a3db53eaacd4fe65ce</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -2226,7 +2226,7 @@
         <x:v>Off</x:v>
       </x:c>
       <x:c r="L25" s="8" t="str">
-        <x:v>460 × 490 × 490</x:v>
+        <x:v>665 × 490 × 490</x:v>
       </x:c>
       <x:c r="M25" s="8" t="str">
         <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
@@ -2295,7 +2295,7 @@
         <x:v>Off</x:v>
       </x:c>
       <x:c r="L26" s="8" t="str">
-        <x:v>460 × 490 × 490</x:v>
+        <x:v>665 × 490 × 490</x:v>
       </x:c>
       <x:c r="M26" s="8" t="str">
         <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
@@ -2364,7 +2364,7 @@
         <x:v>Off</x:v>
       </x:c>
       <x:c r="L27" s="8" t="str">
-        <x:v>460 × 490 × 490</x:v>
+        <x:v>665 × 490 × 490</x:v>
       </x:c>
       <x:c r="M27" s="8" t="str">
         <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
@@ -2433,7 +2433,7 @@
         <x:v>Off</x:v>
       </x:c>
       <x:c r="L28" s="8" t="str">
-        <x:v>460 × 490 × 490</x:v>
+        <x:v>665 × 490 × 490</x:v>
       </x:c>
       <x:c r="M28" s="8" t="str">
         <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
@@ -2502,7 +2502,7 @@
         <x:v>Off</x:v>
       </x:c>
       <x:c r="L29" s="8" t="str">
-        <x:v>460 × 490 × 490</x:v>
+        <x:v>665 × 490 × 490</x:v>
       </x:c>
       <x:c r="M29" s="8" t="str">
         <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
@@ -2571,7 +2571,7 @@
         <x:v>Off</x:v>
       </x:c>
       <x:c r="L30" s="8" t="str">
-        <x:v>460 × 490 × 490</x:v>
+        <x:v>665 × 490 × 490</x:v>
       </x:c>
       <x:c r="M30" s="8" t="str">
         <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
@@ -3366,10 +3366,10 @@
     </x:row>
     <x:row r="42" ht="96" customHeight="1">
       <x:c r="A42" s="8" t="str">
-        <x:v>F-WING-B-3</x:v>
+        <x:v>F-NAVE-B-2P</x:v>
       </x:c>
       <x:c r="B42" s="8" t="str">
-        <x:v>Wall fan · wing B · 3 · held review</x:v>
+        <x:v>Wall fan · axis 2′ · B</x:v>
       </x:c>
       <x:c r="C42" s="8" t="str">
         <x:v>fan</x:v>
@@ -3378,16 +3378,16 @@
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="E42" s="8" t="str">
-        <x:v>F5</x:v>
+        <x:v>F2</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
-        <x:v>41.2</x:v>
+        <x:v>5.475</x:v>
       </x:c>
       <x:c r="G42" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="H42" s="11" t="n">
-        <x:v>-13.06</x:v>
+        <x:v>-7.07</x:v>
       </x:c>
       <x:c r="I42" s="8" t="str">
         <x:v>wall</x:v>
@@ -3396,10 +3396,10 @@
         <x:v>Shown</x:v>
       </x:c>
       <x:c r="K42" s="8" t="str">
-        <x:v>On</x:v>
+        <x:v>Off</x:v>
       </x:c>
       <x:c r="L42" s="8" t="str">
-        <x:v>460 × 490 × 490</x:v>
+        <x:v>665 × 490 × 490</x:v>
       </x:c>
       <x:c r="M42" s="8" t="str">
         <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
@@ -3408,10 +3408,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O42" s="11" t="n">
-        <x:v>75.89736516026656</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="P42" s="11" t="n">
-        <x:v>-30.031965296126412</x:v>
+        <x:v>-38</x:v>
       </x:c>
       <x:c r="Q42" s="9"/>
       <x:c r="R42" s="9"/>
@@ -3424,21 +3424,21 @@
       <x:c r="Y42" s="13"/>
       <x:c r="Z42" s="9"/>
       <x:c r="AA42" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
       <x:c r="AB42" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-2P</x:v>
       </x:c>
       <x:c r="AC42" s="8" t="str">
-        <x:v>{"dim":1,"speed":1,"note":"ENGINEERING HOLD: 4 per wing at low speed cover 68/80 seats; noise and speech criteria fail. Gable anchors, concealment, sweep clearance and maintenance unapproved."}</x:v>
+        <x:v>{"dim":1,"speed":1}</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="96" customHeight="1">
       <x:c r="A43" s="8" t="str">
-        <x:v>F-WING-B-4</x:v>
+        <x:v>F-NAVE-H-2P</x:v>
       </x:c>
       <x:c r="B43" s="8" t="str">
-        <x:v>Wall fan · wing B · 4 · held review</x:v>
+        <x:v>Wall fan · axis 2′ · H</x:v>
       </x:c>
       <x:c r="C43" s="8" t="str">
         <x:v>fan</x:v>
@@ -3447,16 +3447,16 @@
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="E43" s="8" t="str">
-        <x:v>F5</x:v>
+        <x:v>F2</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>5.475</x:v>
       </x:c>
       <x:c r="G43" s="11" t="n">
-        <x:v>3.5</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="H43" s="11" t="n">
-        <x:v>-13.06</x:v>
+        <x:v>7.07</x:v>
       </x:c>
       <x:c r="I43" s="8" t="str">
         <x:v>wall</x:v>
@@ -3465,10 +3465,10 @@
         <x:v>Shown</x:v>
       </x:c>
       <x:c r="K43" s="8" t="str">
-        <x:v>On</x:v>
+        <x:v>Off</x:v>
       </x:c>
       <x:c r="L43" s="8" t="str">
-        <x:v>460 × 490 × 490</x:v>
+        <x:v>665 × 490 × 490</x:v>
       </x:c>
       <x:c r="M43" s="8" t="str">
         <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
@@ -3477,10 +3477,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O43" s="11" t="n">
-        <x:v>81.9727624895681</x:v>
+        <x:v>-90</x:v>
       </x:c>
       <x:c r="P43" s="11" t="n">
-        <x:v>-63.92906953677533</x:v>
+        <x:v>-38</x:v>
       </x:c>
       <x:c r="Q43" s="9"/>
       <x:c r="R43" s="9"/>
@@ -3493,21 +3493,21 @@
       <x:c r="Y43" s="13"/>
       <x:c r="Z43" s="9"/>
       <x:c r="AA43" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
       <x:c r="AB43" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-2P</x:v>
       </x:c>
       <x:c r="AC43" s="8" t="str">
-        <x:v>{"dim":1,"speed":1,"note":"ENGINEERING HOLD: 4 per wing at low speed cover 68/80 seats; noise and speech criteria fail. Gable anchors, concealment, sweep clearance and maintenance unapproved."}</x:v>
+        <x:v>{"dim":1,"speed":1}</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="96" customHeight="1">
       <x:c r="A44" s="8" t="str">
-        <x:v>F-WING-H-3</x:v>
+        <x:v>F-NAVE-B-3</x:v>
       </x:c>
       <x:c r="B44" s="8" t="str">
-        <x:v>Wall fan · wing H · 3 · held review</x:v>
+        <x:v>Wall fan · axis 3 · B</x:v>
       </x:c>
       <x:c r="C44" s="8" t="str">
         <x:v>fan</x:v>
@@ -3516,16 +3516,16 @@
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="E44" s="8" t="str">
-        <x:v>F5</x:v>
+        <x:v>F2</x:v>
       </x:c>
       <x:c r="F44" s="11" t="n">
-        <x:v>41.2</x:v>
+        <x:v>9.975</x:v>
       </x:c>
       <x:c r="G44" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="H44" s="11" t="n">
-        <x:v>13.06</x:v>
+        <x:v>-7.07</x:v>
       </x:c>
       <x:c r="I44" s="8" t="str">
         <x:v>wall</x:v>
@@ -3534,10 +3534,10 @@
         <x:v>Shown</x:v>
       </x:c>
       <x:c r="K44" s="8" t="str">
-        <x:v>On</x:v>
+        <x:v>Off</x:v>
       </x:c>
       <x:c r="L44" s="8" t="str">
-        <x:v>460 × 490 × 490</x:v>
+        <x:v>665 × 490 × 490</x:v>
       </x:c>
       <x:c r="M44" s="8" t="str">
         <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
@@ -3546,10 +3546,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O44" s="11" t="n">
-        <x:v>-75.89736516026656</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="P44" s="11" t="n">
-        <x:v>-30.031965296126412</x:v>
+        <x:v>-38</x:v>
       </x:c>
       <x:c r="Q44" s="9"/>
       <x:c r="R44" s="9"/>
@@ -3562,21 +3562,21 @@
       <x:c r="Y44" s="13"/>
       <x:c r="Z44" s="9"/>
       <x:c r="AA44" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
       <x:c r="AB44" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-3</x:v>
       </x:c>
       <x:c r="AC44" s="8" t="str">
-        <x:v>{"dim":1,"speed":1,"note":"ENGINEERING HOLD: 4 per wing at low speed cover 68/80 seats; noise and speech criteria fail. Gable anchors, concealment, sweep clearance and maintenance unapproved."}</x:v>
+        <x:v>{"dim":1,"speed":1}</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="96" customHeight="1">
       <x:c r="A45" s="8" t="str">
-        <x:v>F-WING-H-4</x:v>
+        <x:v>F-NAVE-H-3</x:v>
       </x:c>
       <x:c r="B45" s="8" t="str">
-        <x:v>Wall fan · wing H · 4 · held review</x:v>
+        <x:v>Wall fan · axis 3 · H</x:v>
       </x:c>
       <x:c r="C45" s="8" t="str">
         <x:v>fan</x:v>
@@ -3585,16 +3585,16 @@
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="E45" s="8" t="str">
-        <x:v>F5</x:v>
+        <x:v>F2</x:v>
       </x:c>
       <x:c r="F45" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>9.975</x:v>
       </x:c>
       <x:c r="G45" s="11" t="n">
-        <x:v>3.5</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="H45" s="11" t="n">
-        <x:v>13.06</x:v>
+        <x:v>7.07</x:v>
       </x:c>
       <x:c r="I45" s="8" t="str">
         <x:v>wall</x:v>
@@ -3603,10 +3603,10 @@
         <x:v>Shown</x:v>
       </x:c>
       <x:c r="K45" s="8" t="str">
-        <x:v>On</x:v>
+        <x:v>Off</x:v>
       </x:c>
       <x:c r="L45" s="8" t="str">
-        <x:v>460 × 490 × 490</x:v>
+        <x:v>665 × 490 × 490</x:v>
       </x:c>
       <x:c r="M45" s="8" t="str">
         <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
@@ -3615,10 +3615,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="O45" s="11" t="n">
-        <x:v>-81.9727624895681</x:v>
+        <x:v>-90</x:v>
       </x:c>
       <x:c r="P45" s="11" t="n">
-        <x:v>-63.92906953677533</x:v>
+        <x:v>-38</x:v>
       </x:c>
       <x:c r="Q45" s="9"/>
       <x:c r="R45" s="9"/>
@@ -3631,36 +3631,726 @@
       <x:c r="Y45" s="13"/>
       <x:c r="Z45" s="9"/>
       <x:c r="AA45" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB45" s="8" t="str">
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-3</x:v>
+      </x:c>
+      <x:c r="AC45" s="8" t="str">
+        <x:v>{"dim":1,"speed":1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="96" customHeight="1">
+      <x:c r="A46" s="8" t="str">
+        <x:v>F-NAVE-B-5</x:v>
+      </x:c>
+      <x:c r="B46" s="8" t="str">
+        <x:v>Wall fan · axis 5 · B</x:v>
+      </x:c>
+      <x:c r="C46" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="D46" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="E46" s="8" t="str">
+        <x:v>F2</x:v>
+      </x:c>
+      <x:c r="F46" s="11" t="n">
+        <x:v>18.975</x:v>
+      </x:c>
+      <x:c r="G46" s="11" t="n">
+        <x:v>5.55</x:v>
+      </x:c>
+      <x:c r="H46" s="11" t="n">
+        <x:v>-7.07</x:v>
+      </x:c>
+      <x:c r="I46" s="8" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="J46" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K46" s="8" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="L46" s="8" t="str">
+        <x:v>665 × 490 × 490</x:v>
+      </x:c>
+      <x:c r="M46" s="8" t="str">
+        <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
+      </x:c>
+      <x:c r="N46" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="O46" s="11" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="P46" s="11" t="n">
+        <x:v>-38</x:v>
+      </x:c>
+      <x:c r="Q46" s="9"/>
+      <x:c r="R46" s="9"/>
+      <x:c r="S46" s="9"/>
+      <x:c r="T46" s="9"/>
+      <x:c r="U46" s="9"/>
+      <x:c r="V46" s="9"/>
+      <x:c r="W46" s="13"/>
+      <x:c r="X46" s="13"/>
+      <x:c r="Y46" s="13"/>
+      <x:c r="Z46" s="9"/>
+      <x:c r="AA46" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB46" s="8" t="str">
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-5</x:v>
+      </x:c>
+      <x:c r="AC46" s="8" t="str">
+        <x:v>{"dim":1,"speed":1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="96" customHeight="1">
+      <x:c r="A47" s="8" t="str">
+        <x:v>F-NAVE-H-5</x:v>
+      </x:c>
+      <x:c r="B47" s="8" t="str">
+        <x:v>Wall fan · axis 5 · H</x:v>
+      </x:c>
+      <x:c r="C47" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="D47" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="E47" s="8" t="str">
+        <x:v>F2</x:v>
+      </x:c>
+      <x:c r="F47" s="11" t="n">
+        <x:v>18.975</x:v>
+      </x:c>
+      <x:c r="G47" s="11" t="n">
+        <x:v>5.55</x:v>
+      </x:c>
+      <x:c r="H47" s="11" t="n">
+        <x:v>7.07</x:v>
+      </x:c>
+      <x:c r="I47" s="8" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="J47" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K47" s="8" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="L47" s="8" t="str">
+        <x:v>665 × 490 × 490</x:v>
+      </x:c>
+      <x:c r="M47" s="8" t="str">
+        <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
+      </x:c>
+      <x:c r="N47" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="O47" s="11" t="n">
+        <x:v>-90</x:v>
+      </x:c>
+      <x:c r="P47" s="11" t="n">
+        <x:v>-38</x:v>
+      </x:c>
+      <x:c r="Q47" s="9"/>
+      <x:c r="R47" s="9"/>
+      <x:c r="S47" s="9"/>
+      <x:c r="T47" s="9"/>
+      <x:c r="U47" s="9"/>
+      <x:c r="V47" s="9"/>
+      <x:c r="W47" s="13"/>
+      <x:c r="X47" s="13"/>
+      <x:c r="Y47" s="13"/>
+      <x:c r="Z47" s="9"/>
+      <x:c r="AA47" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB47" s="8" t="str">
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-5</x:v>
+      </x:c>
+      <x:c r="AC47" s="8" t="str">
+        <x:v>{"dim":1,"speed":1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="96" customHeight="1">
+      <x:c r="A48" s="8" t="str">
+        <x:v>F-NAVE-B-7</x:v>
+      </x:c>
+      <x:c r="B48" s="8" t="str">
+        <x:v>Wall fan · axis 7 · B</x:v>
+      </x:c>
+      <x:c r="C48" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="D48" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="E48" s="8" t="str">
+        <x:v>F2</x:v>
+      </x:c>
+      <x:c r="F48" s="11" t="n">
+        <x:v>27.975</x:v>
+      </x:c>
+      <x:c r="G48" s="11" t="n">
+        <x:v>5.55</x:v>
+      </x:c>
+      <x:c r="H48" s="11" t="n">
+        <x:v>-7.07</x:v>
+      </x:c>
+      <x:c r="I48" s="8" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="J48" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K48" s="8" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="L48" s="8" t="str">
+        <x:v>665 × 490 × 490</x:v>
+      </x:c>
+      <x:c r="M48" s="8" t="str">
+        <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
+      </x:c>
+      <x:c r="N48" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="O48" s="11" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="P48" s="11" t="n">
+        <x:v>-38</x:v>
+      </x:c>
+      <x:c r="Q48" s="9"/>
+      <x:c r="R48" s="9"/>
+      <x:c r="S48" s="9"/>
+      <x:c r="T48" s="9"/>
+      <x:c r="U48" s="9"/>
+      <x:c r="V48" s="9"/>
+      <x:c r="W48" s="13"/>
+      <x:c r="X48" s="13"/>
+      <x:c r="Y48" s="13"/>
+      <x:c r="Z48" s="9"/>
+      <x:c r="AA48" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB48" s="8" t="str">
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-7</x:v>
+      </x:c>
+      <x:c r="AC48" s="8" t="str">
+        <x:v>{"dim":1,"speed":1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="96" customHeight="1">
+      <x:c r="A49" s="8" t="str">
+        <x:v>F-NAVE-H-7</x:v>
+      </x:c>
+      <x:c r="B49" s="8" t="str">
+        <x:v>Wall fan · axis 7 · H</x:v>
+      </x:c>
+      <x:c r="C49" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="D49" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="E49" s="8" t="str">
+        <x:v>F2</x:v>
+      </x:c>
+      <x:c r="F49" s="11" t="n">
+        <x:v>27.975</x:v>
+      </x:c>
+      <x:c r="G49" s="11" t="n">
+        <x:v>5.55</x:v>
+      </x:c>
+      <x:c r="H49" s="11" t="n">
+        <x:v>7.07</x:v>
+      </x:c>
+      <x:c r="I49" s="8" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="J49" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K49" s="8" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="L49" s="8" t="str">
+        <x:v>665 × 490 × 490</x:v>
+      </x:c>
+      <x:c r="M49" s="8" t="str">
+        <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
+      </x:c>
+      <x:c r="N49" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="O49" s="11" t="n">
+        <x:v>-90</x:v>
+      </x:c>
+      <x:c r="P49" s="11" t="n">
+        <x:v>-38</x:v>
+      </x:c>
+      <x:c r="Q49" s="9"/>
+      <x:c r="R49" s="9"/>
+      <x:c r="S49" s="9"/>
+      <x:c r="T49" s="9"/>
+      <x:c r="U49" s="9"/>
+      <x:c r="V49" s="9"/>
+      <x:c r="W49" s="13"/>
+      <x:c r="X49" s="13"/>
+      <x:c r="Y49" s="13"/>
+      <x:c r="Z49" s="9"/>
+      <x:c r="AA49" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB49" s="8" t="str">
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-7</x:v>
+      </x:c>
+      <x:c r="AC49" s="8" t="str">
+        <x:v>{"dim":1,"speed":1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="96" customHeight="1">
+      <x:c r="A50" s="8" t="str">
+        <x:v>F-NAVE-B-9</x:v>
+      </x:c>
+      <x:c r="B50" s="8" t="str">
+        <x:v>Wall fan · axis 9 · B</x:v>
+      </x:c>
+      <x:c r="C50" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="D50" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="E50" s="8" t="str">
+        <x:v>F2</x:v>
+      </x:c>
+      <x:c r="F50" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="G50" s="11" t="n">
+        <x:v>5.55</x:v>
+      </x:c>
+      <x:c r="H50" s="11" t="n">
+        <x:v>-7.07</x:v>
+      </x:c>
+      <x:c r="I50" s="8" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="J50" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K50" s="8" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="L50" s="8" t="str">
+        <x:v>665 × 490 × 490</x:v>
+      </x:c>
+      <x:c r="M50" s="8" t="str">
+        <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
+      </x:c>
+      <x:c r="N50" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="O50" s="11" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="P50" s="11" t="n">
+        <x:v>-38</x:v>
+      </x:c>
+      <x:c r="Q50" s="9"/>
+      <x:c r="R50" s="9"/>
+      <x:c r="S50" s="9"/>
+      <x:c r="T50" s="9"/>
+      <x:c r="U50" s="9"/>
+      <x:c r="V50" s="9"/>
+      <x:c r="W50" s="13"/>
+      <x:c r="X50" s="13"/>
+      <x:c r="Y50" s="13"/>
+      <x:c r="Z50" s="9"/>
+      <x:c r="AA50" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB50" s="8" t="str">
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-9</x:v>
+      </x:c>
+      <x:c r="AC50" s="8" t="str">
+        <x:v>{"dim":1,"speed":1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="96" customHeight="1">
+      <x:c r="A51" s="8" t="str">
+        <x:v>F-NAVE-H-9</x:v>
+      </x:c>
+      <x:c r="B51" s="8" t="str">
+        <x:v>Wall fan · axis 9 · H</x:v>
+      </x:c>
+      <x:c r="C51" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="D51" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="E51" s="8" t="str">
+        <x:v>F2</x:v>
+      </x:c>
+      <x:c r="F51" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="G51" s="11" t="n">
+        <x:v>5.55</x:v>
+      </x:c>
+      <x:c r="H51" s="11" t="n">
+        <x:v>7.07</x:v>
+      </x:c>
+      <x:c r="I51" s="8" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="J51" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K51" s="8" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="L51" s="8" t="str">
+        <x:v>665 × 490 × 490</x:v>
+      </x:c>
+      <x:c r="M51" s="8" t="str">
+        <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
+      </x:c>
+      <x:c r="N51" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="O51" s="11" t="n">
+        <x:v>-90</x:v>
+      </x:c>
+      <x:c r="P51" s="11" t="n">
+        <x:v>-38</x:v>
+      </x:c>
+      <x:c r="Q51" s="9"/>
+      <x:c r="R51" s="9"/>
+      <x:c r="S51" s="9"/>
+      <x:c r="T51" s="9"/>
+      <x:c r="U51" s="9"/>
+      <x:c r="V51" s="9"/>
+      <x:c r="W51" s="13"/>
+      <x:c r="X51" s="13"/>
+      <x:c r="Y51" s="13"/>
+      <x:c r="Z51" s="9"/>
+      <x:c r="AA51" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB51" s="8" t="str">
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-9</x:v>
+      </x:c>
+      <x:c r="AC51" s="8" t="str">
+        <x:v>{"dim":1,"speed":1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="96" customHeight="1">
+      <x:c r="A52" s="8" t="str">
+        <x:v>F-WING-B-3</x:v>
+      </x:c>
+      <x:c r="B52" s="8" t="str">
+        <x:v>Wall fan · wing B · 3 · held review</x:v>
+      </x:c>
+      <x:c r="C52" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="D52" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="E52" s="8" t="str">
+        <x:v>F5</x:v>
+      </x:c>
+      <x:c r="F52" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="G52" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="H52" s="11" t="n">
+        <x:v>-13.06</x:v>
+      </x:c>
+      <x:c r="I52" s="8" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="J52" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K52" s="8" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="L52" s="8" t="str">
+        <x:v>460 × 490 × 490</x:v>
+      </x:c>
+      <x:c r="M52" s="8" t="str">
+        <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
+      </x:c>
+      <x:c r="N52" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="O52" s="11" t="n">
+        <x:v>75.89736516026656</x:v>
+      </x:c>
+      <x:c r="P52" s="11" t="n">
+        <x:v>-30.031965296126412</x:v>
+      </x:c>
+      <x:c r="Q52" s="9"/>
+      <x:c r="R52" s="9"/>
+      <x:c r="S52" s="9"/>
+      <x:c r="T52" s="9"/>
+      <x:c r="U52" s="9"/>
+      <x:c r="V52" s="9"/>
+      <x:c r="W52" s="13"/>
+      <x:c r="X52" s="13"/>
+      <x:c r="Y52" s="13"/>
+      <x:c r="Z52" s="9"/>
+      <x:c r="AA52" s="8" t="str">
         <x:v>Retired</x:v>
       </x:c>
-      <x:c r="AB45" s="8" t="str">
+      <x:c r="AB52" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+      </x:c>
+      <x:c r="AC52" s="8" t="str">
+        <x:v>{"dim":1,"speed":1,"note":"ENGINEERING HOLD: 4 per wing at low speed cover 68/80 seats; noise and speech criteria fail. Gable anchors, concealment, sweep clearance and maintenance unapproved."}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="96" customHeight="1">
+      <x:c r="A53" s="8" t="str">
+        <x:v>F-WING-B-4</x:v>
+      </x:c>
+      <x:c r="B53" s="8" t="str">
+        <x:v>Wall fan · wing B · 4 · held review</x:v>
+      </x:c>
+      <x:c r="C53" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="D53" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="E53" s="8" t="str">
+        <x:v>F5</x:v>
+      </x:c>
+      <x:c r="F53" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G53" s="11" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="H53" s="11" t="n">
+        <x:v>-13.06</x:v>
+      </x:c>
+      <x:c r="I53" s="8" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="J53" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K53" s="8" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="L53" s="8" t="str">
+        <x:v>460 × 490 × 490</x:v>
+      </x:c>
+      <x:c r="M53" s="8" t="str">
+        <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
+      </x:c>
+      <x:c r="N53" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="O53" s="11" t="n">
+        <x:v>81.9727624895681</x:v>
+      </x:c>
+      <x:c r="P53" s="11" t="n">
+        <x:v>-63.92906953677533</x:v>
+      </x:c>
+      <x:c r="Q53" s="9"/>
+      <x:c r="R53" s="9"/>
+      <x:c r="S53" s="9"/>
+      <x:c r="T53" s="9"/>
+      <x:c r="U53" s="9"/>
+      <x:c r="V53" s="9"/>
+      <x:c r="W53" s="13"/>
+      <x:c r="X53" s="13"/>
+      <x:c r="Y53" s="13"/>
+      <x:c r="Z53" s="9"/>
+      <x:c r="AA53" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="AB53" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+      </x:c>
+      <x:c r="AC53" s="8" t="str">
+        <x:v>{"dim":1,"speed":1,"note":"ENGINEERING HOLD: 4 per wing at low speed cover 68/80 seats; noise and speech criteria fail. Gable anchors, concealment, sweep clearance and maintenance unapproved."}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="96" customHeight="1">
+      <x:c r="A54" s="8" t="str">
+        <x:v>F-WING-H-3</x:v>
+      </x:c>
+      <x:c r="B54" s="8" t="str">
+        <x:v>Wall fan · wing H · 3 · held review</x:v>
+      </x:c>
+      <x:c r="C54" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="D54" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="E54" s="8" t="str">
+        <x:v>F5</x:v>
+      </x:c>
+      <x:c r="F54" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="G54" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="H54" s="11" t="n">
+        <x:v>13.06</x:v>
+      </x:c>
+      <x:c r="I54" s="8" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="J54" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K54" s="8" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="L54" s="8" t="str">
+        <x:v>460 × 490 × 490</x:v>
+      </x:c>
+      <x:c r="M54" s="8" t="str">
+        <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
+      </x:c>
+      <x:c r="N54" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="O54" s="11" t="n">
+        <x:v>-75.89736516026656</x:v>
+      </x:c>
+      <x:c r="P54" s="11" t="n">
+        <x:v>-30.031965296126412</x:v>
+      </x:c>
+      <x:c r="Q54" s="9"/>
+      <x:c r="R54" s="9"/>
+      <x:c r="S54" s="9"/>
+      <x:c r="T54" s="9"/>
+      <x:c r="U54" s="9"/>
+      <x:c r="V54" s="9"/>
+      <x:c r="W54" s="13"/>
+      <x:c r="X54" s="13"/>
+      <x:c r="Y54" s="13"/>
+      <x:c r="Z54" s="9"/>
+      <x:c r="AA54" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="AB54" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+      </x:c>
+      <x:c r="AC54" s="8" t="str">
+        <x:v>{"dim":1,"speed":1,"note":"ENGINEERING HOLD: 4 per wing at low speed cover 68/80 seats; noise and speech criteria fail. Gable anchors, concealment, sweep clearance and maintenance unapproved."}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="96" customHeight="1">
+      <x:c r="A55" s="8" t="str">
+        <x:v>F-WING-H-4</x:v>
+      </x:c>
+      <x:c r="B55" s="8" t="str">
+        <x:v>Wall fan · wing H · 4 · held review</x:v>
+      </x:c>
+      <x:c r="C55" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="D55" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="E55" s="8" t="str">
+        <x:v>F5</x:v>
+      </x:c>
+      <x:c r="F55" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G55" s="11" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="H55" s="11" t="n">
+        <x:v>13.06</x:v>
+      </x:c>
+      <x:c r="I55" s="8" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="J55" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K55" s="8" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="L55" s="8" t="str">
+        <x:v>460 × 490 × 490</x:v>
+      </x:c>
+      <x:c r="M55" s="8" t="str">
+        <x:v>0.45 m diameter · 55 W at maximum speed. Speed steps: 1: 0.45 m3/s, 35 W, 47 dBA, 900 rpm; 2: 0.6 m3/s, 45 W, 52 dBA, 1100 rpm; 3: 0.75 m3/s, 55 W, 57 dBA, 1300 rpm</x:v>
+      </x:c>
+      <x:c r="N55" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="O55" s="11" t="n">
+        <x:v>-81.9727624895681</x:v>
+      </x:c>
+      <x:c r="P55" s="11" t="n">
+        <x:v>-63.92906953677533</x:v>
+      </x:c>
+      <x:c r="Q55" s="9"/>
+      <x:c r="R55" s="9"/>
+      <x:c r="S55" s="9"/>
+      <x:c r="T55" s="9"/>
+      <x:c r="U55" s="9"/>
+      <x:c r="V55" s="9"/>
+      <x:c r="W55" s="13"/>
+      <x:c r="X55" s="13"/>
+      <x:c r="Y55" s="13"/>
+      <x:c r="Z55" s="9"/>
+      <x:c r="AA55" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="AB55" s="8" t="str">
         <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
       </x:c>
-      <x:c r="AC45" s="8" t="str">
+      <x:c r="AC55" s="8" t="str">
         <x:v>{"dim":1,"speed":1,"note":"ENGINEERING HOLD: 4 per wing at low speed cover 68/80 seats; noise and speech criteria fail. Gable anchors, concealment, sweep clearance and maintenance unapproved."}</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="AA7:AA45">
+  <x:conditionalFormatting sqref="AA7:AA55">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
-    <x:dataValidation type="decimal" operator="between" sqref="W7:W45">
+    <x:dataValidation type="decimal" operator="between" sqref="W7:W55">
       <x:formula1>-1000</x:formula1>
       <x:formula2>1000</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="between" sqref="X7:X45">
+    <x:dataValidation type="decimal" operator="between" sqref="X7:X55">
       <x:formula1>-1000</x:formula1>
       <x:formula2>1000</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="between" sqref="Y7:Y45">
+    <x:dataValidation type="decimal" operator="between" sqref="Y7:Y55">
       <x:formula1>-1000</x:formula1>
       <x:formula2>1000</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21ba3d8c79e149df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra74925802338430d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3957,7 +4647,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I7" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A7,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A7,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>64.02913031117919</x:v>
       </x:c>
       <x:c r="J7" s="11"/>
@@ -4016,7 +4706,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A8,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A8,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>11.286909264308505</x:v>
       </x:c>
       <x:c r="J8" s="11"/>
@@ -4077,7 +4767,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A9,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A9,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>11.286909264308505</x:v>
       </x:c>
       <x:c r="J9" s="11"/>
@@ -4138,7 +4828,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A10,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A10,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>11.276909264308502</x:v>
       </x:c>
       <x:c r="J10" s="11"/>
@@ -4199,7 +4889,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A11,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A11,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>11.286909264308504</x:v>
       </x:c>
       <x:c r="J11" s="11"/>
@@ -4260,7 +4950,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A12,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A12,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>11.286909264308504</x:v>
       </x:c>
       <x:c r="J12" s="11"/>
@@ -4321,7 +5011,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I13" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A13,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A13,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>11.286909264308504</x:v>
       </x:c>
       <x:c r="J13" s="11"/>
@@ -4382,7 +5072,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I14" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A14,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A14,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>11.276909264308506</x:v>
       </x:c>
       <x:c r="J14" s="11"/>
@@ -4449,7 +5139,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I15" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A15,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A15,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>70.62913031117918</x:v>
       </x:c>
       <x:c r="J15" s="11"/>
@@ -4508,7 +5198,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I16" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A16,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A16,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>11.286909264308505</x:v>
       </x:c>
       <x:c r="J16" s="11"/>
@@ -4569,7 +5259,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I17" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A17,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A17,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>11.286909264308505</x:v>
       </x:c>
       <x:c r="J17" s="11"/>
@@ -4630,7 +5320,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I18" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A18,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A18,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>11.276909264308502</x:v>
       </x:c>
       <x:c r="J18" s="11"/>
@@ -4691,7 +5381,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I19" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A19,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A19,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>11.286909264308504</x:v>
       </x:c>
       <x:c r="J19" s="11"/>
@@ -4752,7 +5442,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I20" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A20,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A20,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>11.286909264308504</x:v>
       </x:c>
       <x:c r="J20" s="11"/>
@@ -4813,7 +5503,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I21" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A21,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A21,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>11.286909264308504</x:v>
       </x:c>
       <x:c r="J21" s="11"/>
@@ -4874,7 +5564,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I22" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A22,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A22,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>11.276909264308506</x:v>
       </x:c>
       <x:c r="J22" s="11"/>
@@ -4936,7 +5626,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I23" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A23,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A23,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>33.83219768896557</x:v>
       </x:c>
       <x:c r="J23" s="11"/>
@@ -4995,7 +5685,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I24" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A24,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A24,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>9.264333762886594</x:v>
       </x:c>
       <x:c r="J24" s="11"/>
@@ -5056,7 +5746,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I25" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A25,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A25,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>9.264333762886599</x:v>
       </x:c>
       <x:c r="J25" s="11"/>
@@ -5118,7 +5808,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I26" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A26,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A26,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>40.43219768896558</x:v>
       </x:c>
       <x:c r="J26" s="11"/>
@@ -5177,7 +5867,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I27" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A27,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A27,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>9.264333762886594</x:v>
       </x:c>
       <x:c r="J27" s="11"/>
@@ -5238,7 +5928,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I28" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A28,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A28,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>9.264333762886599</x:v>
       </x:c>
       <x:c r="J28" s="11"/>
@@ -5273,7 +5963,7 @@
         <x:v>trunk:FC1:F5:fan:1</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="90" customHeight="1">
+    <x:row r="29" ht="116" customHeight="1">
       <x:c r="A29" s="8" t="str">
         <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
@@ -5286,7 +5976,12 @@
       <x:c r="D29" s="8" t="str">
         <x:v>F244
 F246
-F248</x:v>
+F248
+F-NAVE-B-2P
+F-NAVE-B-3
+F-NAVE-B-5
+F-NAVE-B-7
+F-NAVE-B-9</x:v>
       </x:c>
       <x:c r="E29" s="8" t="str">
         <x:v>DB1</x:v>
@@ -5301,8 +5996,8 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I29" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A29,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>58.576130311179185</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A29,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>67.57613031117918</x:v>
       </x:c>
       <x:c r="J29" s="11"/>
       <x:c r="K29" s="11" t="str">
@@ -5360,7 +6055,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I30" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A30,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A30,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J30" s="11"/>
@@ -5421,7 +6116,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I31" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A31,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A31,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J31" s="11"/>
@@ -5482,7 +6177,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I32" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A32,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A32,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J32" s="11"/>
@@ -5519,18 +6214,16 @@
     </x:row>
     <x:row r="33" ht="90" customHeight="1">
       <x:c r="A33" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-2P</x:v>
       </x:c>
       <x:c r="B33" s="8" t="str">
-        <x:v>F2 · H · circuit trunk</x:v>
+        <x:v>F2 → Wall fan · axis 2′ · B</x:v>
       </x:c>
       <x:c r="C33" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D33" s="8" t="str">
-        <x:v>F245
-F247
-F249</x:v>
+        <x:v>F-NAVE-B-2P</x:v>
       </x:c>
       <x:c r="E33" s="8" t="str">
         <x:v>DB1</x:v>
@@ -5542,11 +6235,11 @@
         <x:v>fan</x:v>
       </x:c>
       <x:c r="H33" s="8" t="str">
-        <x:v>trunk</x:v>
+        <x:v>drop</x:v>
       </x:c>
       <x:c r="I33" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A33,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>65.17613031117918</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A33,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J33" s="11"/>
       <x:c r="K33" s="11" t="str">
@@ -5563,7 +6256,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P33" s="8" t="str">
-        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
       </x:c>
       <x:c r="Q33" s="9"/>
       <x:c r="R33" s="9"/>
@@ -5576,20 +6269,22 @@
       <x:c r="Y33" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z33" s="8"/>
+      <x:c r="Z33" s="8" t="str">
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="90" customHeight="1">
       <x:c r="A34" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F245</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-3</x:v>
       </x:c>
       <x:c r="B34" s="8" t="str">
-        <x:v>F2 → Wall fan · axis 4 · H</x:v>
+        <x:v>F2 → Wall fan · axis 3 · B</x:v>
       </x:c>
       <x:c r="C34" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D34" s="8" t="str">
-        <x:v>F245</x:v>
+        <x:v>F-NAVE-B-3</x:v>
       </x:c>
       <x:c r="E34" s="8" t="str">
         <x:v>DB1</x:v>
@@ -5604,7 +6299,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I34" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A34,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A34,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J34" s="11"/>
@@ -5636,21 +6331,21 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z34" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="90" customHeight="1">
       <x:c r="A35" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F247</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-5</x:v>
       </x:c>
       <x:c r="B35" s="8" t="str">
-        <x:v>F2 → Wall fan · axis 6 · H</x:v>
+        <x:v>F2 → Wall fan · axis 5 · B</x:v>
       </x:c>
       <x:c r="C35" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D35" s="8" t="str">
-        <x:v>F247</x:v>
+        <x:v>F-NAVE-B-5</x:v>
       </x:c>
       <x:c r="E35" s="8" t="str">
         <x:v>DB1</x:v>
@@ -5665,7 +6360,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I35" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A35,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A35,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J35" s="11"/>
@@ -5697,21 +6392,21 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z35" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="90" customHeight="1">
       <x:c r="A36" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F249</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-7</x:v>
       </x:c>
       <x:c r="B36" s="8" t="str">
-        <x:v>F2 → Wall fan · axis 8 · H</x:v>
+        <x:v>F2 → Wall fan · axis 7 · B</x:v>
       </x:c>
       <x:c r="C36" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D36" s="8" t="str">
-        <x:v>F249</x:v>
+        <x:v>F-NAVE-B-7</x:v>
       </x:c>
       <x:c r="E36" s="8" t="str">
         <x:v>DB1</x:v>
@@ -5726,7 +6421,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I36" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A36,'Route Points'!$F$7:$F$354)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A36,'Route Points'!$F$7:$F$384)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J36" s="11"/>
@@ -5758,37 +6453,37 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z36" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="90" customHeight="1">
       <x:c r="A37" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-9</x:v>
       </x:c>
       <x:c r="B37" s="8" t="str">
-        <x:v>F4 · B · circuit trunk</x:v>
+        <x:v>F2 → Wall fan · axis 9 · B</x:v>
       </x:c>
       <x:c r="C37" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>FC1</x:v>
       </x:c>
       <x:c r="D37" s="8" t="str">
-        <x:v>F250</x:v>
+        <x:v>F-NAVE-B-9</x:v>
       </x:c>
       <x:c r="E37" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>DB1</x:v>
       </x:c>
       <x:c r="F37" s="8" t="str">
-        <x:v>F4</x:v>
+        <x:v>F2</x:v>
       </x:c>
       <x:c r="G37" s="8" t="str">
         <x:v>fan</x:v>
       </x:c>
       <x:c r="H37" s="8" t="str">
-        <x:v>trunk</x:v>
+        <x:v>drop</x:v>
       </x:c>
       <x:c r="I37" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A37,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>12.517</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A37,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J37" s="11"/>
       <x:c r="K37" s="11" t="str">
@@ -5805,7 +6500,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P37" s="8" t="str">
-        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
       </x:c>
       <x:c r="Q37" s="9"/>
       <x:c r="R37" s="9"/>
@@ -5818,36 +6513,45 @@
       <x:c r="Y37" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z37" s="8"/>
-    </x:row>
-    <x:row r="38" ht="90" customHeight="1">
+      <x:c r="Z37" s="8" t="str">
+        <x:v>trunk:FC1:F2:fan:-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="116" customHeight="1">
       <x:c r="A38" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B38" s="8" t="str">
-        <x:v>F4 → Entrance circulator · B</x:v>
+        <x:v>F2 · H · circuit trunk</x:v>
       </x:c>
       <x:c r="C38" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>FC1</x:v>
       </x:c>
       <x:c r="D38" s="8" t="str">
-        <x:v>F250</x:v>
+        <x:v>F245
+F247
+F249
+F-NAVE-H-2P
+F-NAVE-H-3
+F-NAVE-H-5
+F-NAVE-H-7
+F-NAVE-H-9</x:v>
       </x:c>
       <x:c r="E38" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>DB1</x:v>
       </x:c>
       <x:c r="F38" s="8" t="str">
-        <x:v>F4</x:v>
+        <x:v>F2</x:v>
       </x:c>
       <x:c r="G38" s="8" t="str">
         <x:v>fan</x:v>
       </x:c>
       <x:c r="H38" s="8" t="str">
-        <x:v>drop</x:v>
+        <x:v>trunk</x:v>
       </x:c>
       <x:c r="I38" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A38,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>7.91542691446789</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A38,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>74.17613031117918</x:v>
       </x:c>
       <x:c r="J38" s="11"/>
       <x:c r="K38" s="11" t="str">
@@ -5864,7 +6568,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P38" s="8" t="str">
-        <x:v>Concealed entrance wall band, solid pier and local termination.</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q38" s="9"/>
       <x:c r="R38" s="9"/>
@@ -5877,38 +6581,36 @@
       <x:c r="Y38" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z38" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
-      </x:c>
+      <x:c r="Z38" s="8"/>
     </x:row>
     <x:row r="39" ht="90" customHeight="1">
       <x:c r="A39" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F245</x:v>
       </x:c>
       <x:c r="B39" s="8" t="str">
-        <x:v>F4 · H · circuit trunk</x:v>
+        <x:v>F2 → Wall fan · axis 4 · H</x:v>
       </x:c>
       <x:c r="C39" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>FC1</x:v>
       </x:c>
       <x:c r="D39" s="8" t="str">
-        <x:v>F251</x:v>
+        <x:v>F245</x:v>
       </x:c>
       <x:c r="E39" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>DB1</x:v>
       </x:c>
       <x:c r="F39" s="8" t="str">
-        <x:v>F4</x:v>
+        <x:v>F2</x:v>
       </x:c>
       <x:c r="G39" s="8" t="str">
         <x:v>fan</x:v>
       </x:c>
       <x:c r="H39" s="8" t="str">
-        <x:v>trunk</x:v>
+        <x:v>drop</x:v>
       </x:c>
       <x:c r="I39" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A39,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>19.117</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A39,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J39" s="11"/>
       <x:c r="K39" s="11" t="str">
@@ -5925,7 +6627,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P39" s="8" t="str">
-        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
       </x:c>
       <x:c r="Q39" s="9"/>
       <x:c r="R39" s="9"/>
@@ -5938,26 +6640,28 @@
       <x:c r="Y39" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z39" s="8"/>
+      <x:c r="Z39" s="8" t="str">
+        <x:v>trunk:FC1:F2:fan:1</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="90" customHeight="1">
       <x:c r="A40" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+        <x:v>drop:FC1:F2:fan:1:F247</x:v>
       </x:c>
       <x:c r="B40" s="8" t="str">
-        <x:v>F4 → Entrance circulator · H</x:v>
+        <x:v>F2 → Wall fan · axis 6 · H</x:v>
       </x:c>
       <x:c r="C40" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>FC1</x:v>
       </x:c>
       <x:c r="D40" s="8" t="str">
-        <x:v>F251</x:v>
+        <x:v>F247</x:v>
       </x:c>
       <x:c r="E40" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>DB1</x:v>
       </x:c>
       <x:c r="F40" s="8" t="str">
-        <x:v>F4</x:v>
+        <x:v>F2</x:v>
       </x:c>
       <x:c r="G40" s="8" t="str">
         <x:v>fan</x:v>
@@ -5966,8 +6670,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I40" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A40,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>7.91542691446789</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A40,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J40" s="11"/>
       <x:c r="K40" s="11" t="str">
@@ -5984,7 +6688,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P40" s="8" t="str">
-        <x:v>Concealed entrance wall band, solid pier and local termination.</x:v>
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
       </x:c>
       <x:c r="Q40" s="9"/>
       <x:c r="R40" s="9"/>
@@ -5998,41 +6702,37 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z40" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="90" customHeight="1">
       <x:c r="A41" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F249</x:v>
       </x:c>
       <x:c r="B41" s="8" t="str">
-        <x:v>V1 · B · circuit trunk</x:v>
+        <x:v>F2 → Wall fan · axis 8 · H</x:v>
       </x:c>
       <x:c r="C41" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D41" s="8" t="str">
-        <x:v>F252
-F253
-F256
-F257
-F260</x:v>
+        <x:v>F249</x:v>
       </x:c>
       <x:c r="E41" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F41" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>F2</x:v>
       </x:c>
       <x:c r="G41" s="8" t="str">
         <x:v>fan</x:v>
       </x:c>
       <x:c r="H41" s="8" t="str">
-        <x:v>trunk</x:v>
+        <x:v>drop</x:v>
       </x:c>
       <x:c r="I41" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A41,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>67.54713031117919</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A41,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J41" s="11"/>
       <x:c r="K41" s="11" t="str">
@@ -6049,7 +6749,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P41" s="8" t="str">
-        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
       </x:c>
       <x:c r="Q41" s="9"/>
       <x:c r="R41" s="9"/>
@@ -6062,26 +6762,28 @@
       <x:c r="Y41" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z41" s="8"/>
+      <x:c r="Z41" s="8" t="str">
+        <x:v>trunk:FC1:F2:fan:1</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="90" customHeight="1">
       <x:c r="A42" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-2P</x:v>
       </x:c>
       <x:c r="B42" s="8" t="str">
-        <x:v>V1 → Exhaust fan · front gable · B outer</x:v>
+        <x:v>F2 → Wall fan · axis 2′ · H</x:v>
       </x:c>
       <x:c r="C42" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D42" s="8" t="str">
-        <x:v>F252</x:v>
+        <x:v>F-NAVE-H-2P</x:v>
       </x:c>
       <x:c r="E42" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F42" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>F2</x:v>
       </x:c>
       <x:c r="G42" s="8" t="str">
         <x:v>fan</x:v>
@@ -6090,8 +6792,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I42" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A42,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>8.69282092938182</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A42,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J42" s="11"/>
       <x:c r="K42" s="11" t="str">
@@ -6108,7 +6810,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P42" s="8" t="str">
-        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
       </x:c>
       <x:c r="Q42" s="9"/>
       <x:c r="R42" s="9"/>
@@ -6122,27 +6824,27 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z42" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="90" customHeight="1">
       <x:c r="A43" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-3</x:v>
       </x:c>
       <x:c r="B43" s="8" t="str">
-        <x:v>V1 → Exhaust fan · front gable · B inner</x:v>
+        <x:v>F2 → Wall fan · axis 3 · H</x:v>
       </x:c>
       <x:c r="C43" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D43" s="8" t="str">
-        <x:v>F253</x:v>
+        <x:v>F-NAVE-H-3</x:v>
       </x:c>
       <x:c r="E43" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F43" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>F2</x:v>
       </x:c>
       <x:c r="G43" s="8" t="str">
         <x:v>fan</x:v>
@@ -6151,8 +6853,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I43" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A43,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>11.831150261440472</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A43,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J43" s="11"/>
       <x:c r="K43" s="11" t="str">
@@ -6169,7 +6871,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P43" s="8" t="str">
-        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
       </x:c>
       <x:c r="Q43" s="9"/>
       <x:c r="R43" s="9"/>
@@ -6183,27 +6885,27 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z43" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="90" customHeight="1">
       <x:c r="A44" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-5</x:v>
       </x:c>
       <x:c r="B44" s="8" t="str">
-        <x:v>V1 → Exhaust fan · wing gable B · front</x:v>
+        <x:v>F2 → Wall fan · axis 5 · H</x:v>
       </x:c>
       <x:c r="C44" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D44" s="8" t="str">
-        <x:v>F256</x:v>
+        <x:v>F-NAVE-H-5</x:v>
       </x:c>
       <x:c r="E44" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F44" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>F2</x:v>
       </x:c>
       <x:c r="G44" s="8" t="str">
         <x:v>fan</x:v>
@@ -6212,8 +6914,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I44" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A44,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>6.973264175257731</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A44,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J44" s="11"/>
       <x:c r="K44" s="11" t="str">
@@ -6230,7 +6932,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P44" s="8" t="str">
-        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
       </x:c>
       <x:c r="Q44" s="9"/>
       <x:c r="R44" s="9"/>
@@ -6244,27 +6946,27 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z44" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="90" customHeight="1">
       <x:c r="A45" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-7</x:v>
       </x:c>
       <x:c r="B45" s="8" t="str">
-        <x:v>V1 → Exhaust fan · wing gable B · rear</x:v>
+        <x:v>F2 → Wall fan · axis 7 · H</x:v>
       </x:c>
       <x:c r="C45" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D45" s="8" t="str">
-        <x:v>F257</x:v>
+        <x:v>F-NAVE-H-7</x:v>
       </x:c>
       <x:c r="E45" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F45" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>F2</x:v>
       </x:c>
       <x:c r="G45" s="8" t="str">
         <x:v>fan</x:v>
@@ -6273,8 +6975,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I45" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A45,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>6.973264175257731</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A45,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J45" s="11"/>
       <x:c r="K45" s="11" t="str">
@@ -6291,7 +6993,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P45" s="8" t="str">
-        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
       </x:c>
       <x:c r="Q45" s="9"/>
       <x:c r="R45" s="9"/>
@@ -6305,27 +7007,27 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z45" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="90" customHeight="1">
       <x:c r="A46" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-9</x:v>
       </x:c>
       <x:c r="B46" s="8" t="str">
-        <x:v>V1 → Exhaust fan · service room</x:v>
+        <x:v>F2 → Wall fan · axis 9 · H</x:v>
       </x:c>
       <x:c r="C46" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D46" s="8" t="str">
-        <x:v>F260</x:v>
+        <x:v>F-NAVE-H-9</x:v>
       </x:c>
       <x:c r="E46" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F46" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>F2</x:v>
       </x:c>
       <x:c r="G46" s="8" t="str">
         <x:v>fan</x:v>
@@ -6334,8 +7036,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I46" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A46,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>10.2</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A46,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J46" s="11"/>
       <x:c r="K46" s="11" t="str">
@@ -6352,7 +7054,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P46" s="8" t="str">
-        <x:v>Rear-wall band and local termination; gable / weatherproof entry details pending.</x:v>
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
       </x:c>
       <x:c r="Q46" s="9"/>
       <x:c r="R46" s="9"/>
@@ -6366,30 +7068,27 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z46" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="90" customHeight="1">
       <x:c r="A47" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B47" s="8" t="str">
-        <x:v>V1 · H · circuit trunk</x:v>
+        <x:v>F4 · B · circuit trunk</x:v>
       </x:c>
       <x:c r="C47" s="8" t="str">
-        <x:v>FC1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="D47" s="8" t="str">
-        <x:v>F254
-F255
-F258
-F259</x:v>
+        <x:v>F250</x:v>
       </x:c>
       <x:c r="E47" s="8" t="str">
-        <x:v>DB1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="F47" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>F4</x:v>
       </x:c>
       <x:c r="G47" s="8" t="str">
         <x:v>fan</x:v>
@@ -6398,8 +7097,8 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I47" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A47,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>74.14713031117918</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A47,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>12.517</x:v>
       </x:c>
       <x:c r="J47" s="11"/>
       <x:c r="K47" s="11" t="str">
@@ -6433,22 +7132,22 @@
     </x:row>
     <x:row r="48" ht="90" customHeight="1">
       <x:c r="A48" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
       </x:c>
       <x:c r="B48" s="8" t="str">
-        <x:v>V1 → Exhaust fan · front gable · H inner</x:v>
+        <x:v>F4 → Entrance circulator · B</x:v>
       </x:c>
       <x:c r="C48" s="8" t="str">
-        <x:v>FC1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="D48" s="8" t="str">
-        <x:v>F254</x:v>
+        <x:v>F250</x:v>
       </x:c>
       <x:c r="E48" s="8" t="str">
-        <x:v>DB1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="F48" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>F4</x:v>
       </x:c>
       <x:c r="G48" s="8" t="str">
         <x:v>fan</x:v>
@@ -6457,8 +7156,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I48" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A48,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>11.831150261440472</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A48,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>7.91542691446789</x:v>
       </x:c>
       <x:c r="J48" s="11"/>
       <x:c r="K48" s="11" t="str">
@@ -6475,7 +7174,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P48" s="8" t="str">
-        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
+        <x:v>Concealed entrance wall band, solid pier and local termination.</x:v>
       </x:c>
       <x:c r="Q48" s="9"/>
       <x:c r="R48" s="9"/>
@@ -6489,37 +7188,37 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z48" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="90" customHeight="1">
       <x:c r="A49" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
+        <x:v>trunk:DB2:F4:fan:1</x:v>
       </x:c>
       <x:c r="B49" s="8" t="str">
-        <x:v>V1 → Exhaust fan · front gable · H outer</x:v>
+        <x:v>F4 · H · circuit trunk</x:v>
       </x:c>
       <x:c r="C49" s="8" t="str">
-        <x:v>FC1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="D49" s="8" t="str">
-        <x:v>F255</x:v>
+        <x:v>F251</x:v>
       </x:c>
       <x:c r="E49" s="8" t="str">
-        <x:v>DB1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="F49" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>F4</x:v>
       </x:c>
       <x:c r="G49" s="8" t="str">
         <x:v>fan</x:v>
       </x:c>
       <x:c r="H49" s="8" t="str">
-        <x:v>drop</x:v>
+        <x:v>trunk</x:v>
       </x:c>
       <x:c r="I49" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A49,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>8.69282092938182</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A49,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>19.117</x:v>
       </x:c>
       <x:c r="J49" s="11"/>
       <x:c r="K49" s="11" t="str">
@@ -6536,7 +7235,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P49" s="8" t="str">
-        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q49" s="9"/>
       <x:c r="R49" s="9"/>
@@ -6549,28 +7248,26 @@
       <x:c r="Y49" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z49" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
-      </x:c>
+      <x:c r="Z49" s="8"/>
     </x:row>
     <x:row r="50" ht="90" customHeight="1">
       <x:c r="A50" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F258</x:v>
+        <x:v>drop:DB2:F4:fan:1:F251</x:v>
       </x:c>
       <x:c r="B50" s="8" t="str">
-        <x:v>V1 → Exhaust fan · wing gable H · front</x:v>
+        <x:v>F4 → Entrance circulator · H</x:v>
       </x:c>
       <x:c r="C50" s="8" t="str">
-        <x:v>FC1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="D50" s="8" t="str">
-        <x:v>F258</x:v>
+        <x:v>F251</x:v>
       </x:c>
       <x:c r="E50" s="8" t="str">
-        <x:v>DB1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="F50" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>F4</x:v>
       </x:c>
       <x:c r="G50" s="8" t="str">
         <x:v>fan</x:v>
@@ -6579,8 +7276,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I50" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A50,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>6.973264175257731</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A50,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>7.91542691446789</x:v>
       </x:c>
       <x:c r="J50" s="11"/>
       <x:c r="K50" s="11" t="str">
@@ -6597,7 +7294,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P50" s="8" t="str">
-        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+        <x:v>Concealed entrance wall band, solid pier and local termination.</x:v>
       </x:c>
       <x:c r="Q50" s="9"/>
       <x:c r="R50" s="9"/>
@@ -6611,21 +7308,25 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z50" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>trunk:DB2:F4:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="90" customHeight="1">
       <x:c r="A51" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F259</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B51" s="8" t="str">
-        <x:v>V1 → Exhaust fan · wing gable H · rear</x:v>
+        <x:v>V1 · B · circuit trunk</x:v>
       </x:c>
       <x:c r="C51" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D51" s="8" t="str">
-        <x:v>F259</x:v>
+        <x:v>F252
+F253
+F256
+F257
+F260</x:v>
       </x:c>
       <x:c r="E51" s="8" t="str">
         <x:v>DB1</x:v>
@@ -6637,11 +7338,11 @@
         <x:v>fan</x:v>
       </x:c>
       <x:c r="H51" s="8" t="str">
-        <x:v>drop</x:v>
+        <x:v>trunk</x:v>
       </x:c>
       <x:c r="I51" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A51,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>6.973264175257731</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A51,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>67.54713031117919</x:v>
       </x:c>
       <x:c r="J51" s="11"/>
       <x:c r="K51" s="11" t="str">
@@ -6658,7 +7359,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P51" s="8" t="str">
-        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q51" s="9"/>
       <x:c r="R51" s="9"/>
@@ -6671,28 +7372,26 @@
       <x:c r="Y51" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z51" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
-      </x:c>
+      <x:c r="Z51" s="8"/>
     </x:row>
     <x:row r="52" ht="90" customHeight="1">
       <x:c r="A52" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
       </x:c>
       <x:c r="B52" s="8" t="str">
-        <x:v>F5 → Wall fan · wing B · 3 · held review</x:v>
+        <x:v>V1 → Exhaust fan · front gable · B outer</x:v>
       </x:c>
       <x:c r="C52" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D52" s="8" t="str">
-        <x:v>F-WING-B-3</x:v>
+        <x:v>F252</x:v>
       </x:c>
       <x:c r="E52" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F52" s="8" t="str">
-        <x:v>F5</x:v>
+        <x:v>V1</x:v>
       </x:c>
       <x:c r="G52" s="8" t="str">
         <x:v>fan</x:v>
@@ -6701,8 +7400,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I52" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A52,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>12.144617268041237</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A52,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>8.69282092938182</x:v>
       </x:c>
       <x:c r="J52" s="11"/>
       <x:c r="K52" s="11" t="str">
@@ -6719,7 +7418,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P52" s="8" t="str">
-        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
       </x:c>
       <x:c r="Q52" s="9"/>
       <x:c r="R52" s="9"/>
@@ -6730,30 +7429,30 @@
       <x:c r="W52" s="9"/>
       <x:c r="X52" s="9"/>
       <x:c r="Y52" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
       <x:c r="Z52" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:-1</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="90" customHeight="1">
       <x:c r="A53" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
       </x:c>
       <x:c r="B53" s="8" t="str">
-        <x:v>F5 → Wall fan · wing B · 4 · held review</x:v>
+        <x:v>V1 → Exhaust fan · front gable · B inner</x:v>
       </x:c>
       <x:c r="C53" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D53" s="8" t="str">
-        <x:v>F-WING-B-4</x:v>
+        <x:v>F253</x:v>
       </x:c>
       <x:c r="E53" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F53" s="8" t="str">
-        <x:v>F5</x:v>
+        <x:v>V1</x:v>
       </x:c>
       <x:c r="G53" s="8" t="str">
         <x:v>fan</x:v>
@@ -6762,8 +7461,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I53" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A53,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>10.700287371134024</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A53,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>11.831150261440472</x:v>
       </x:c>
       <x:c r="J53" s="11"/>
       <x:c r="K53" s="11" t="str">
@@ -6780,7 +7479,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P53" s="8" t="str">
-        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
       </x:c>
       <x:c r="Q53" s="9"/>
       <x:c r="R53" s="9"/>
@@ -6791,30 +7490,30 @@
       <x:c r="W53" s="9"/>
       <x:c r="X53" s="9"/>
       <x:c r="Y53" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
       <x:c r="Z53" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:-1</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="90" customHeight="1">
       <x:c r="A54" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
       </x:c>
       <x:c r="B54" s="8" t="str">
-        <x:v>F5 → Wall fan · wing H · 3 · held review</x:v>
+        <x:v>V1 → Exhaust fan · wing gable B · front</x:v>
       </x:c>
       <x:c r="C54" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D54" s="8" t="str">
-        <x:v>F-WING-H-3</x:v>
+        <x:v>F256</x:v>
       </x:c>
       <x:c r="E54" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F54" s="8" t="str">
-        <x:v>F5</x:v>
+        <x:v>V1</x:v>
       </x:c>
       <x:c r="G54" s="8" t="str">
         <x:v>fan</x:v>
@@ -6823,8 +7522,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I54" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A54,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>12.144617268041237</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A54,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>6.973264175257731</x:v>
       </x:c>
       <x:c r="J54" s="11"/>
       <x:c r="K54" s="11" t="str">
@@ -6852,30 +7551,30 @@
       <x:c r="W54" s="9"/>
       <x:c r="X54" s="9"/>
       <x:c r="Y54" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
       <x:c r="Z54" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:1</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="90" customHeight="1">
       <x:c r="A55" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
       </x:c>
       <x:c r="B55" s="8" t="str">
-        <x:v>F5 → Wall fan · wing H · 4 · held review</x:v>
+        <x:v>V1 → Exhaust fan · wing gable B · rear</x:v>
       </x:c>
       <x:c r="C55" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D55" s="8" t="str">
-        <x:v>F-WING-H-4</x:v>
+        <x:v>F257</x:v>
       </x:c>
       <x:c r="E55" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F55" s="8" t="str">
-        <x:v>F5</x:v>
+        <x:v>V1</x:v>
       </x:c>
       <x:c r="G55" s="8" t="str">
         <x:v>fan</x:v>
@@ -6884,8 +7583,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I55" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A55,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>10.700287371134024</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A55,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>6.973264175257731</x:v>
       </x:c>
       <x:c r="J55" s="11"/>
       <x:c r="K55" s="11" t="str">
@@ -6913,30 +7612,30 @@
       <x:c r="W55" s="9"/>
       <x:c r="X55" s="9"/>
       <x:c r="Y55" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
       <x:c r="Z55" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:1</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="90" customHeight="1">
       <x:c r="A56" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
       </x:c>
       <x:c r="B56" s="8" t="str">
-        <x:v>F1 → Ceiling fan · wing B · front</x:v>
+        <x:v>V1 → Exhaust fan · service room</x:v>
       </x:c>
       <x:c r="C56" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D56" s="8" t="str">
-        <x:v>F240</x:v>
+        <x:v>F260</x:v>
       </x:c>
       <x:c r="E56" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F56" s="8" t="str">
-        <x:v>F1</x:v>
+        <x:v>V1</x:v>
       </x:c>
       <x:c r="G56" s="8" t="str">
         <x:v>fan</x:v>
@@ -6945,8 +7644,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I56" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A56,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>7.73309922680412</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A56,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="J56" s="11"/>
       <x:c r="K56" s="11" t="str">
@@ -6963,7 +7662,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P56" s="8" t="str">
-        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
+        <x:v>Rear-wall band and local termination; gable / weatherproof entry details pending.</x:v>
       </x:c>
       <x:c r="Q56" s="9"/>
       <x:c r="R56" s="9"/>
@@ -6974,40 +7673,43 @@
       <x:c r="W56" s="9"/>
       <x:c r="X56" s="9"/>
       <x:c r="Y56" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
       <x:c r="Z56" s="8" t="str">
-        <x:v>trunk:FC1:F1:fan:-1</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="90" customHeight="1">
       <x:c r="A57" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B57" s="8" t="str">
-        <x:v>F1 → Ceiling fan · wing B · rear</x:v>
+        <x:v>V1 · H · circuit trunk</x:v>
       </x:c>
       <x:c r="C57" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D57" s="8" t="str">
-        <x:v>F241</x:v>
+        <x:v>F254
+F255
+F258
+F259</x:v>
       </x:c>
       <x:c r="E57" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F57" s="8" t="str">
-        <x:v>F1</x:v>
+        <x:v>V1</x:v>
       </x:c>
       <x:c r="G57" s="8" t="str">
         <x:v>fan</x:v>
       </x:c>
       <x:c r="H57" s="8" t="str">
-        <x:v>drop</x:v>
+        <x:v>trunk</x:v>
       </x:c>
       <x:c r="I57" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A57,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>7.733099226804125</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A57,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>74.14713031117918</x:v>
       </x:c>
       <x:c r="J57" s="11"/>
       <x:c r="K57" s="11" t="str">
@@ -7024,7 +7726,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P57" s="8" t="str">
-        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q57" s="9"/>
       <x:c r="R57" s="9"/>
@@ -7035,30 +7737,28 @@
       <x:c r="W57" s="9"/>
       <x:c r="X57" s="9"/>
       <x:c r="Y57" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-      <x:c r="Z57" s="8" t="str">
-        <x:v>trunk:FC1:F1:fan:-1</x:v>
-      </x:c>
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="Z57" s="8"/>
     </x:row>
     <x:row r="58" ht="90" customHeight="1">
       <x:c r="A58" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F242</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B58" s="8" t="str">
-        <x:v>F1 → Ceiling fan · wing H · front</x:v>
+        <x:v>V1 → Exhaust fan · front gable · H inner</x:v>
       </x:c>
       <x:c r="C58" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D58" s="8" t="str">
-        <x:v>F242</x:v>
+        <x:v>F254</x:v>
       </x:c>
       <x:c r="E58" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F58" s="8" t="str">
-        <x:v>F1</x:v>
+        <x:v>V1</x:v>
       </x:c>
       <x:c r="G58" s="8" t="str">
         <x:v>fan</x:v>
@@ -7067,8 +7767,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I58" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A58,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>7.73309922680412</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A58,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>11.831150261440472</x:v>
       </x:c>
       <x:c r="J58" s="11"/>
       <x:c r="K58" s="11" t="str">
@@ -7085,7 +7785,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P58" s="8" t="str">
-        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
+        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
       </x:c>
       <x:c r="Q58" s="9"/>
       <x:c r="R58" s="9"/>
@@ -7096,30 +7796,30 @@
       <x:c r="W58" s="9"/>
       <x:c r="X58" s="9"/>
       <x:c r="Y58" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
       <x:c r="Z58" s="8" t="str">
-        <x:v>trunk:FC1:F1:fan:1</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="90" customHeight="1">
       <x:c r="A59" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F243</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B59" s="8" t="str">
-        <x:v>F1 → Ceiling fan · wing H · rear</x:v>
+        <x:v>V1 → Exhaust fan · front gable · H outer</x:v>
       </x:c>
       <x:c r="C59" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D59" s="8" t="str">
-        <x:v>F243</x:v>
+        <x:v>F255</x:v>
       </x:c>
       <x:c r="E59" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F59" s="8" t="str">
-        <x:v>F1</x:v>
+        <x:v>V1</x:v>
       </x:c>
       <x:c r="G59" s="8" t="str">
         <x:v>fan</x:v>
@@ -7128,8 +7828,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I59" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$354,A59,'Route Points'!$F$7:$F$354)</x:f>
-        <x:v>7.733099226804125</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A59,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>8.69282092938182</x:v>
       </x:c>
       <x:c r="J59" s="11"/>
       <x:c r="K59" s="11" t="str">
@@ -7146,7 +7846,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P59" s="8" t="str">
-        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
+        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
       </x:c>
       <x:c r="Q59" s="9"/>
       <x:c r="R59" s="9"/>
@@ -7157,30 +7857,640 @@
       <x:c r="W59" s="9"/>
       <x:c r="X59" s="9"/>
       <x:c r="Y59" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="Z59" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="90" customHeight="1">
+      <x:c r="A60" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F258</x:v>
+      </x:c>
+      <x:c r="B60" s="8" t="str">
+        <x:v>V1 → Exhaust fan · wing gable H · front</x:v>
+      </x:c>
+      <x:c r="C60" s="8" t="str">
+        <x:v>FC1</x:v>
+      </x:c>
+      <x:c r="D60" s="8" t="str">
+        <x:v>F258</x:v>
+      </x:c>
+      <x:c r="E60" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F60" s="8" t="str">
+        <x:v>V1</x:v>
+      </x:c>
+      <x:c r="G60" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="H60" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I60" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A60,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>6.973264175257731</x:v>
+      </x:c>
+      <x:c r="J60" s="11"/>
+      <x:c r="K60" s="11" t="str">
+        <x:f>IF(L60="Full home run",I60+J60,"")</x:f>
+      </x:c>
+      <x:c r="L60" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M60" s="13"/>
+      <x:c r="N60" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M60),L60&lt;&gt;"Shared bundle"),IF(L60="Full home run",K60,I60)+M60,"")</x:f>
+      </x:c>
+      <x:c r="O60" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P60" s="8" t="str">
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+      </x:c>
+      <x:c r="Q60" s="9"/>
+      <x:c r="R60" s="9"/>
+      <x:c r="S60" s="13"/>
+      <x:c r="T60" s="9"/>
+      <x:c r="U60" s="9"/>
+      <x:c r="V60" s="9"/>
+      <x:c r="W60" s="9"/>
+      <x:c r="X60" s="9"/>
+      <x:c r="Y60" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="Z60" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="90" customHeight="1">
+      <x:c r="A61" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F259</x:v>
+      </x:c>
+      <x:c r="B61" s="8" t="str">
+        <x:v>V1 → Exhaust fan · wing gable H · rear</x:v>
+      </x:c>
+      <x:c r="C61" s="8" t="str">
+        <x:v>FC1</x:v>
+      </x:c>
+      <x:c r="D61" s="8" t="str">
+        <x:v>F259</x:v>
+      </x:c>
+      <x:c r="E61" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F61" s="8" t="str">
+        <x:v>V1</x:v>
+      </x:c>
+      <x:c r="G61" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="H61" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I61" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A61,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>6.973264175257731</x:v>
+      </x:c>
+      <x:c r="J61" s="11"/>
+      <x:c r="K61" s="11" t="str">
+        <x:f>IF(L61="Full home run",I61+J61,"")</x:f>
+      </x:c>
+      <x:c r="L61" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M61" s="13"/>
+      <x:c r="N61" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M61),L61&lt;&gt;"Shared bundle"),IF(L61="Full home run",K61,I61)+M61,"")</x:f>
+      </x:c>
+      <x:c r="O61" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P61" s="8" t="str">
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+      </x:c>
+      <x:c r="Q61" s="9"/>
+      <x:c r="R61" s="9"/>
+      <x:c r="S61" s="13"/>
+      <x:c r="T61" s="9"/>
+      <x:c r="U61" s="9"/>
+      <x:c r="V61" s="9"/>
+      <x:c r="W61" s="9"/>
+      <x:c r="X61" s="9"/>
+      <x:c r="Y61" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="Z61" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="90" customHeight="1">
+      <x:c r="A62" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+      </x:c>
+      <x:c r="B62" s="8" t="str">
+        <x:v>F5 → Wall fan · wing B · 3 · held review</x:v>
+      </x:c>
+      <x:c r="C62" s="8" t="str">
+        <x:v>FC1</x:v>
+      </x:c>
+      <x:c r="D62" s="8" t="str">
+        <x:v>F-WING-B-3</x:v>
+      </x:c>
+      <x:c r="E62" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F62" s="8" t="str">
+        <x:v>F5</x:v>
+      </x:c>
+      <x:c r="G62" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="H62" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I62" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A62,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>12.144617268041237</x:v>
+      </x:c>
+      <x:c r="J62" s="11"/>
+      <x:c r="K62" s="11" t="str">
+        <x:f>IF(L62="Full home run",I62+J62,"")</x:f>
+      </x:c>
+      <x:c r="L62" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M62" s="13"/>
+      <x:c r="N62" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M62),L62&lt;&gt;"Shared bundle"),IF(L62="Full home run",K62,I62)+M62,"")</x:f>
+      </x:c>
+      <x:c r="O62" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P62" s="8" t="str">
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+      </x:c>
+      <x:c r="Q62" s="9"/>
+      <x:c r="R62" s="9"/>
+      <x:c r="S62" s="13"/>
+      <x:c r="T62" s="9"/>
+      <x:c r="U62" s="9"/>
+      <x:c r="V62" s="9"/>
+      <x:c r="W62" s="9"/>
+      <x:c r="X62" s="9"/>
+      <x:c r="Y62" s="8" t="str">
         <x:v>Retired</x:v>
       </x:c>
-      <x:c r="Z59" s="8" t="str">
+      <x:c r="Z62" s="8" t="str">
+        <x:v>trunk:FC1:F5:fan:-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="90" customHeight="1">
+      <x:c r="A63" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+      </x:c>
+      <x:c r="B63" s="8" t="str">
+        <x:v>F5 → Wall fan · wing B · 4 · held review</x:v>
+      </x:c>
+      <x:c r="C63" s="8" t="str">
+        <x:v>FC1</x:v>
+      </x:c>
+      <x:c r="D63" s="8" t="str">
+        <x:v>F-WING-B-4</x:v>
+      </x:c>
+      <x:c r="E63" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F63" s="8" t="str">
+        <x:v>F5</x:v>
+      </x:c>
+      <x:c r="G63" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="H63" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I63" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A63,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>10.700287371134024</x:v>
+      </x:c>
+      <x:c r="J63" s="11"/>
+      <x:c r="K63" s="11" t="str">
+        <x:f>IF(L63="Full home run",I63+J63,"")</x:f>
+      </x:c>
+      <x:c r="L63" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M63" s="13"/>
+      <x:c r="N63" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M63),L63&lt;&gt;"Shared bundle"),IF(L63="Full home run",K63,I63)+M63,"")</x:f>
+      </x:c>
+      <x:c r="O63" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P63" s="8" t="str">
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+      </x:c>
+      <x:c r="Q63" s="9"/>
+      <x:c r="R63" s="9"/>
+      <x:c r="S63" s="13"/>
+      <x:c r="T63" s="9"/>
+      <x:c r="U63" s="9"/>
+      <x:c r="V63" s="9"/>
+      <x:c r="W63" s="9"/>
+      <x:c r="X63" s="9"/>
+      <x:c r="Y63" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z63" s="8" t="str">
+        <x:v>trunk:FC1:F5:fan:-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="90" customHeight="1">
+      <x:c r="A64" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+      </x:c>
+      <x:c r="B64" s="8" t="str">
+        <x:v>F5 → Wall fan · wing H · 3 · held review</x:v>
+      </x:c>
+      <x:c r="C64" s="8" t="str">
+        <x:v>FC1</x:v>
+      </x:c>
+      <x:c r="D64" s="8" t="str">
+        <x:v>F-WING-H-3</x:v>
+      </x:c>
+      <x:c r="E64" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F64" s="8" t="str">
+        <x:v>F5</x:v>
+      </x:c>
+      <x:c r="G64" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="H64" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I64" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A64,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>12.144617268041237</x:v>
+      </x:c>
+      <x:c r="J64" s="11"/>
+      <x:c r="K64" s="11" t="str">
+        <x:f>IF(L64="Full home run",I64+J64,"")</x:f>
+      </x:c>
+      <x:c r="L64" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M64" s="13"/>
+      <x:c r="N64" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M64),L64&lt;&gt;"Shared bundle"),IF(L64="Full home run",K64,I64)+M64,"")</x:f>
+      </x:c>
+      <x:c r="O64" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P64" s="8" t="str">
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+      </x:c>
+      <x:c r="Q64" s="9"/>
+      <x:c r="R64" s="9"/>
+      <x:c r="S64" s="13"/>
+      <x:c r="T64" s="9"/>
+      <x:c r="U64" s="9"/>
+      <x:c r="V64" s="9"/>
+      <x:c r="W64" s="9"/>
+      <x:c r="X64" s="9"/>
+      <x:c r="Y64" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z64" s="8" t="str">
+        <x:v>trunk:FC1:F5:fan:1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="90" customHeight="1">
+      <x:c r="A65" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+      </x:c>
+      <x:c r="B65" s="8" t="str">
+        <x:v>F5 → Wall fan · wing H · 4 · held review</x:v>
+      </x:c>
+      <x:c r="C65" s="8" t="str">
+        <x:v>FC1</x:v>
+      </x:c>
+      <x:c r="D65" s="8" t="str">
+        <x:v>F-WING-H-4</x:v>
+      </x:c>
+      <x:c r="E65" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F65" s="8" t="str">
+        <x:v>F5</x:v>
+      </x:c>
+      <x:c r="G65" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="H65" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I65" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A65,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>10.700287371134024</x:v>
+      </x:c>
+      <x:c r="J65" s="11"/>
+      <x:c r="K65" s="11" t="str">
+        <x:f>IF(L65="Full home run",I65+J65,"")</x:f>
+      </x:c>
+      <x:c r="L65" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M65" s="13"/>
+      <x:c r="N65" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M65),L65&lt;&gt;"Shared bundle"),IF(L65="Full home run",K65,I65)+M65,"")</x:f>
+      </x:c>
+      <x:c r="O65" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P65" s="8" t="str">
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+      </x:c>
+      <x:c r="Q65" s="9"/>
+      <x:c r="R65" s="9"/>
+      <x:c r="S65" s="13"/>
+      <x:c r="T65" s="9"/>
+      <x:c r="U65" s="9"/>
+      <x:c r="V65" s="9"/>
+      <x:c r="W65" s="9"/>
+      <x:c r="X65" s="9"/>
+      <x:c r="Y65" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z65" s="8" t="str">
+        <x:v>trunk:FC1:F5:fan:1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="90" customHeight="1">
+      <x:c r="A66" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
+      </x:c>
+      <x:c r="B66" s="8" t="str">
+        <x:v>F1 → Ceiling fan · wing B · front</x:v>
+      </x:c>
+      <x:c r="C66" s="8" t="str">
+        <x:v>FC1</x:v>
+      </x:c>
+      <x:c r="D66" s="8" t="str">
+        <x:v>F240</x:v>
+      </x:c>
+      <x:c r="E66" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F66" s="8" t="str">
+        <x:v>F1</x:v>
+      </x:c>
+      <x:c r="G66" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="H66" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I66" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A66,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>7.73309922680412</x:v>
+      </x:c>
+      <x:c r="J66" s="11"/>
+      <x:c r="K66" s="11" t="str">
+        <x:f>IF(L66="Full home run",I66+J66,"")</x:f>
+      </x:c>
+      <x:c r="L66" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M66" s="13"/>
+      <x:c r="N66" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M66),L66&lt;&gt;"Shared bundle"),IF(L66="Full home run",K66,I66)+M66,"")</x:f>
+      </x:c>
+      <x:c r="O66" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P66" s="8" t="str">
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
+      </x:c>
+      <x:c r="Q66" s="9"/>
+      <x:c r="R66" s="9"/>
+      <x:c r="S66" s="13"/>
+      <x:c r="T66" s="9"/>
+      <x:c r="U66" s="9"/>
+      <x:c r="V66" s="9"/>
+      <x:c r="W66" s="9"/>
+      <x:c r="X66" s="9"/>
+      <x:c r="Y66" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z66" s="8" t="str">
+        <x:v>trunk:FC1:F1:fan:-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="90" customHeight="1">
+      <x:c r="A67" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+      </x:c>
+      <x:c r="B67" s="8" t="str">
+        <x:v>F1 → Ceiling fan · wing B · rear</x:v>
+      </x:c>
+      <x:c r="C67" s="8" t="str">
+        <x:v>FC1</x:v>
+      </x:c>
+      <x:c r="D67" s="8" t="str">
+        <x:v>F241</x:v>
+      </x:c>
+      <x:c r="E67" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F67" s="8" t="str">
+        <x:v>F1</x:v>
+      </x:c>
+      <x:c r="G67" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="H67" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I67" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A67,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>7.733099226804125</x:v>
+      </x:c>
+      <x:c r="J67" s="11"/>
+      <x:c r="K67" s="11" t="str">
+        <x:f>IF(L67="Full home run",I67+J67,"")</x:f>
+      </x:c>
+      <x:c r="L67" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M67" s="13"/>
+      <x:c r="N67" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M67),L67&lt;&gt;"Shared bundle"),IF(L67="Full home run",K67,I67)+M67,"")</x:f>
+      </x:c>
+      <x:c r="O67" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P67" s="8" t="str">
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
+      </x:c>
+      <x:c r="Q67" s="9"/>
+      <x:c r="R67" s="9"/>
+      <x:c r="S67" s="13"/>
+      <x:c r="T67" s="9"/>
+      <x:c r="U67" s="9"/>
+      <x:c r="V67" s="9"/>
+      <x:c r="W67" s="9"/>
+      <x:c r="X67" s="9"/>
+      <x:c r="Y67" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z67" s="8" t="str">
+        <x:v>trunk:FC1:F1:fan:-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="90" customHeight="1">
+      <x:c r="A68" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:1:F242</x:v>
+      </x:c>
+      <x:c r="B68" s="8" t="str">
+        <x:v>F1 → Ceiling fan · wing H · front</x:v>
+      </x:c>
+      <x:c r="C68" s="8" t="str">
+        <x:v>FC1</x:v>
+      </x:c>
+      <x:c r="D68" s="8" t="str">
+        <x:v>F242</x:v>
+      </x:c>
+      <x:c r="E68" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F68" s="8" t="str">
+        <x:v>F1</x:v>
+      </x:c>
+      <x:c r="G68" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="H68" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I68" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A68,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>7.73309922680412</x:v>
+      </x:c>
+      <x:c r="J68" s="11"/>
+      <x:c r="K68" s="11" t="str">
+        <x:f>IF(L68="Full home run",I68+J68,"")</x:f>
+      </x:c>
+      <x:c r="L68" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M68" s="13"/>
+      <x:c r="N68" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M68),L68&lt;&gt;"Shared bundle"),IF(L68="Full home run",K68,I68)+M68,"")</x:f>
+      </x:c>
+      <x:c r="O68" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P68" s="8" t="str">
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
+      </x:c>
+      <x:c r="Q68" s="9"/>
+      <x:c r="R68" s="9"/>
+      <x:c r="S68" s="13"/>
+      <x:c r="T68" s="9"/>
+      <x:c r="U68" s="9"/>
+      <x:c r="V68" s="9"/>
+      <x:c r="W68" s="9"/>
+      <x:c r="X68" s="9"/>
+      <x:c r="Y68" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z68" s="8" t="str">
         <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
     </x:row>
+    <x:row r="69" ht="90" customHeight="1">
+      <x:c r="A69" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:1:F243</x:v>
+      </x:c>
+      <x:c r="B69" s="8" t="str">
+        <x:v>F1 → Ceiling fan · wing H · rear</x:v>
+      </x:c>
+      <x:c r="C69" s="8" t="str">
+        <x:v>FC1</x:v>
+      </x:c>
+      <x:c r="D69" s="8" t="str">
+        <x:v>F243</x:v>
+      </x:c>
+      <x:c r="E69" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F69" s="8" t="str">
+        <x:v>F1</x:v>
+      </x:c>
+      <x:c r="G69" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="H69" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I69" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$384,A69,'Route Points'!$F$7:$F$384)</x:f>
+        <x:v>7.733099226804125</x:v>
+      </x:c>
+      <x:c r="J69" s="11"/>
+      <x:c r="K69" s="11" t="str">
+        <x:f>IF(L69="Full home run",I69+J69,"")</x:f>
+      </x:c>
+      <x:c r="L69" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M69" s="13"/>
+      <x:c r="N69" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M69),L69&lt;&gt;"Shared bundle"),IF(L69="Full home run",K69,I69)+M69,"")</x:f>
+      </x:c>
+      <x:c r="O69" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P69" s="8" t="str">
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
+      </x:c>
+      <x:c r="Q69" s="9"/>
+      <x:c r="R69" s="9"/>
+      <x:c r="S69" s="13"/>
+      <x:c r="T69" s="9"/>
+      <x:c r="U69" s="9"/>
+      <x:c r="V69" s="9"/>
+      <x:c r="W69" s="9"/>
+      <x:c r="X69" s="9"/>
+      <x:c r="Y69" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z69" s="8" t="str">
+        <x:v>trunk:FC1:F1:fan:1</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="Y7:Y59">
+  <x:conditionalFormatting sqref="Y7:Y69">
     <x:cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="M7:M59">
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="M7:M69">
       <x:formula1>0</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="R7:R59">
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="R7:R69">
       <x:formula1>0</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="S7:S59">
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="S7:S69">
       <x:formula1>0</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb28d14df9954578"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf94e654f0bee427f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11626,7 +12936,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C188" s="11" t="n">
-        <x:v>14.475000000000001</x:v>
+        <x:v>5.475000000000001</x:v>
       </x:c>
       <x:c r="D188" s="11" t="n">
         <x:v>6.0120000000000005</x:v>
@@ -11636,7 +12946,7 @@
       </x:c>
       <x:c r="F188" s="11" t="n">
         <x:f>SQRT((C188-C187)^2+(D188-D187)^2+(E188-E187)^2)</x:f>
-        <x:v>22.5</x:v>
+        <x:v>31.5</x:v>
       </x:c>
       <x:c r="G188" s="8" t="str">
         <x:v>Current</x:v>
@@ -11860,19 +13170,19 @@
     </x:row>
     <x:row r="198" ht="32" customHeight="1">
       <x:c r="A198" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-2P</x:v>
       </x:c>
       <x:c r="B198" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C198" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>5.475000000000001</x:v>
       </x:c>
       <x:c r="D198" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E198" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F198" s="11" t="n">
         <x:f>0</x:f>
@@ -11884,23 +13194,23 @@
     </x:row>
     <x:row r="199" ht="32" customHeight="1">
       <x:c r="A199" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-2P</x:v>
       </x:c>
       <x:c r="B199" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C199" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>5.475000000000001</x:v>
       </x:c>
       <x:c r="D199" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E199" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F199" s="11" t="n">
         <x:f>SQRT((C199-C198)^2+(D199-D198)^2+(E199-E198)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
+        <x:v>0.46200000000000063</x:v>
       </x:c>
       <x:c r="G199" s="8" t="str">
         <x:v>Current</x:v>
@@ -11908,23 +13218,23 @@
     </x:row>
     <x:row r="200" ht="32" customHeight="1">
       <x:c r="A200" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-2P</x:v>
       </x:c>
       <x:c r="B200" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C200" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>5.475</x:v>
       </x:c>
       <x:c r="D200" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E200" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>-7.07</x:v>
       </x:c>
       <x:c r="F200" s="11" t="n">
         <x:f>SQRT((C200-C199)^2+(D200-D199)^2+(E200-E199)^2)</x:f>
-        <x:v>2.64</x:v>
+        <x:v>0.29000000000000004</x:v>
       </x:c>
       <x:c r="G200" s="8" t="str">
         <x:v>Current</x:v>
@@ -11932,23 +13242,23 @@
     </x:row>
     <x:row r="201" ht="32" customHeight="1">
       <x:c r="A201" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-3</x:v>
       </x:c>
       <x:c r="B201" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C201" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>9.975000000000001</x:v>
       </x:c>
       <x:c r="D201" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E201" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F201" s="11" t="n">
-        <x:f>SQRT((C201-C200)^2+(D201-D200)^2+(E201-E200)^2)</x:f>
-        <x:v>2.38</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G201" s="8" t="str">
         <x:v>Current</x:v>
@@ -11956,23 +13266,23 @@
     </x:row>
     <x:row r="202" ht="32" customHeight="1">
       <x:c r="A202" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-3</x:v>
       </x:c>
       <x:c r="B202" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C202" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>9.975000000000001</x:v>
       </x:c>
       <x:c r="D202" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E202" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F202" s="11" t="n">
         <x:f>SQRT((C202-C201)^2+(D202-D201)^2+(E202-E201)^2)</x:f>
-        <x:v>1.0599999999999996</x:v>
+        <x:v>0.46200000000000063</x:v>
       </x:c>
       <x:c r="G202" s="8" t="str">
         <x:v>Current</x:v>
@@ -11980,23 +13290,23 @@
     </x:row>
     <x:row r="203" ht="32" customHeight="1">
       <x:c r="A203" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-3</x:v>
       </x:c>
       <x:c r="B203" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C203" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>9.975</x:v>
       </x:c>
       <x:c r="D203" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E203" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-7.07</x:v>
       </x:c>
       <x:c r="F203" s="11" t="n">
         <x:f>SQRT((C203-C202)^2+(D203-D202)^2+(E203-E202)^2)</x:f>
-        <x:v>4.280999999999999</x:v>
+        <x:v>0.29000000000000004</x:v>
       </x:c>
       <x:c r="G203" s="8" t="str">
         <x:v>Current</x:v>
@@ -12004,23 +13314,23 @@
     </x:row>
     <x:row r="204" ht="32" customHeight="1">
       <x:c r="A204" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-5</x:v>
       </x:c>
       <x:c r="B204" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C204" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>18.975</x:v>
       </x:c>
       <x:c r="D204" s="11" t="n">
         <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E204" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F204" s="11" t="n">
-        <x:f>SQRT((C204-C203)^2+(D204-D203)^2+(E204-E203)^2)</x:f>
-        <x:v>1.6820000000000004</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G204" s="8" t="str">
         <x:v>Current</x:v>
@@ -12028,23 +13338,23 @@
     </x:row>
     <x:row r="205" ht="32" customHeight="1">
       <x:c r="A205" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-5</x:v>
       </x:c>
       <x:c r="B205" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C205" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>18.975</x:v>
       </x:c>
       <x:c r="D205" s="11" t="n">
-        <x:v>6.0120000000000005</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E205" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F205" s="11" t="n">
         <x:f>SQRT((C205-C204)^2+(D205-D204)^2+(E205-E204)^2)</x:f>
-        <x:v>10.66</x:v>
+        <x:v>0.46200000000000063</x:v>
       </x:c>
       <x:c r="G205" s="8" t="str">
         <x:v>Current</x:v>
@@ -12052,23 +13362,23 @@
     </x:row>
     <x:row r="206" ht="32" customHeight="1">
       <x:c r="A206" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-5</x:v>
       </x:c>
       <x:c r="B206" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C206" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>18.975</x:v>
       </x:c>
       <x:c r="D206" s="11" t="n">
-        <x:v>6.0120000000000005</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E206" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.07</x:v>
       </x:c>
       <x:c r="F206" s="11" t="n">
         <x:f>SQRT((C206-C205)^2+(D206-D205)^2+(E206-E205)^2)</x:f>
-        <x:v>8.841000000000001</x:v>
+        <x:v>0.29000000000000004</x:v>
       </x:c>
       <x:c r="G206" s="8" t="str">
         <x:v>Current</x:v>
@@ -12076,23 +13386,23 @@
     </x:row>
     <x:row r="207" ht="32" customHeight="1">
       <x:c r="A207" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-7</x:v>
       </x:c>
       <x:c r="B207" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C207" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>27.975</x:v>
       </x:c>
       <x:c r="D207" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E207" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F207" s="11" t="n">
-        <x:f>SQRT((C207-C206)^2+(D207-D206)^2+(E207-E206)^2)</x:f>
-        <x:v>1.0279999999999996</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G207" s="8" t="str">
         <x:v>Current</x:v>
@@ -12100,23 +13410,23 @@
     </x:row>
     <x:row r="208" ht="32" customHeight="1">
       <x:c r="A208" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-7</x:v>
       </x:c>
       <x:c r="B208" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C208" s="11" t="n">
-        <x:v>43.535</x:v>
+        <x:v>27.975</x:v>
       </x:c>
       <x:c r="D208" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E208" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F208" s="11" t="n">
         <x:f>SQRT((C208-C207)^2+(D208-D207)^2+(E208-E207)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>0.46200000000000063</x:v>
       </x:c>
       <x:c r="G208" s="8" t="str">
         <x:v>Current</x:v>
@@ -12124,23 +13434,23 @@
     </x:row>
     <x:row r="209" ht="32" customHeight="1">
       <x:c r="A209" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-7</x:v>
       </x:c>
       <x:c r="B209" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C209" s="11" t="n">
-        <x:v>43.455</x:v>
+        <x:v>27.975</x:v>
       </x:c>
       <x:c r="D209" s="11" t="n">
-        <x:v>6.950412371134024</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E209" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.07</x:v>
       </x:c>
       <x:c r="F209" s="11" t="n">
         <x:f>SQRT((C209-C208)^2+(D209-D208)^2+(E209-E208)^2)</x:f>
-        <x:v>0.12010804821421249</x:v>
+        <x:v>0.29000000000000004</x:v>
       </x:c>
       <x:c r="G209" s="8" t="str">
         <x:v>Current</x:v>
@@ -12148,23 +13458,23 @@
     </x:row>
     <x:row r="210" ht="32" customHeight="1">
       <x:c r="A210" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-9</x:v>
       </x:c>
       <x:c r="B210" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C210" s="11" t="n">
-        <x:v>40.574999999999996</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D210" s="11" t="n">
-        <x:v>9.269999999999994</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E210" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F210" s="11" t="n">
-        <x:f>SQRT((C210-C209)^2+(D210-D209)^2+(E210-E209)^2)</x:f>
-        <x:v>3.6979571073753776</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G210" s="8" t="str">
         <x:v>Current</x:v>
@@ -12172,23 +13482,23 @@
     </x:row>
     <x:row r="211" ht="32" customHeight="1">
       <x:c r="A211" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-9</x:v>
       </x:c>
       <x:c r="B211" s="8" t="n">
-        <x:v>14</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C211" s="11" t="n">
-        <x:v>37.695</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D211" s="11" t="n">
-        <x:v>6.950412371134018</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E211" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F211" s="11" t="n">
         <x:f>SQRT((C211-C210)^2+(D211-D210)^2+(E211-E210)^2)</x:f>
-        <x:v>3.697957107375376</x:v>
+        <x:v>0.46200000000000063</x:v>
       </x:c>
       <x:c r="G211" s="8" t="str">
         <x:v>Current</x:v>
@@ -12196,23 +13506,23 @@
     </x:row>
     <x:row r="212" ht="32" customHeight="1">
       <x:c r="A212" s="8" t="str">
-        <x:v>trunk:FC1:F2:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:-1:F-NAVE-B-9</x:v>
       </x:c>
       <x:c r="B212" s="8" t="n">
-        <x:v>15</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C212" s="11" t="n">
-        <x:v>37.615</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D212" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E212" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.07</x:v>
       </x:c>
       <x:c r="F212" s="11" t="n">
         <x:f>SQRT((C212-C211)^2+(D212-D211)^2+(E212-E211)^2)</x:f>
-        <x:v>0.12010804821421713</x:v>
+        <x:v>0.29000000000000004</x:v>
       </x:c>
       <x:c r="G212" s="8" t="str">
         <x:v>Current</x:v>
@@ -12223,20 +13533,20 @@
         <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B213" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C213" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D213" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E213" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F213" s="11" t="n">
-        <x:f>SQRT((C213-C212)^2+(D213-D212)^2+(E213-E212)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G213" s="8" t="str">
         <x:v>Current</x:v>
@@ -12247,20 +13557,20 @@
         <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B214" s="8" t="n">
-        <x:v>17</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C214" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D214" s="11" t="n">
-        <x:v>6.0120000000000005</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E214" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F214" s="11" t="n">
         <x:f>SQRT((C214-C213)^2+(D214-D213)^2+(E214-E213)^2)</x:f>
-        <x:v>1.0279999999999996</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G214" s="8" t="str">
         <x:v>Current</x:v>
@@ -12271,20 +13581,20 @@
         <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B215" s="8" t="n">
-        <x:v>18</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C215" s="11" t="n">
-        <x:v>14.475000000000001</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D215" s="11" t="n">
-        <x:v>6.0120000000000005</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E215" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F215" s="11" t="n">
         <x:f>SQRT((C215-C214)^2+(D215-D214)^2+(E215-E214)^2)</x:f>
-        <x:v>22.5</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="G215" s="8" t="str">
         <x:v>Current</x:v>
@@ -12292,23 +13602,23 @@
     </x:row>
     <x:row r="216" ht="32" customHeight="1">
       <x:c r="A216" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F245</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B216" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C216" s="11" t="n">
-        <x:v>14.475000000000001</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D216" s="11" t="n">
-        <x:v>6.0120000000000005</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E216" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F216" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C216-C215)^2+(D216-D215)^2+(E216-E215)^2)</x:f>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="G216" s="8" t="str">
         <x:v>Current</x:v>
@@ -12316,23 +13626,23 @@
     </x:row>
     <x:row r="217" ht="32" customHeight="1">
       <x:c r="A217" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F245</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B217" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C217" s="11" t="n">
-        <x:v>14.475000000000001</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D217" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E217" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F217" s="11" t="n">
         <x:f>SQRT((C217-C216)^2+(D217-D216)^2+(E217-E216)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G217" s="8" t="str">
         <x:v>Current</x:v>
@@ -12340,23 +13650,23 @@
     </x:row>
     <x:row r="218" ht="32" customHeight="1">
       <x:c r="A218" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F245</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B218" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C218" s="11" t="n">
-        <x:v>14.475</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D218" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E218" s="11" t="n">
-        <x:v>7.07</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F218" s="11" t="n">
         <x:f>SQRT((C218-C217)^2+(D218-D217)^2+(E218-E217)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G218" s="8" t="str">
         <x:v>Current</x:v>
@@ -12364,23 +13674,23 @@
     </x:row>
     <x:row r="219" ht="32" customHeight="1">
       <x:c r="A219" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F247</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B219" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C219" s="11" t="n">
-        <x:v>23.475</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D219" s="11" t="n">
         <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E219" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F219" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C219-C218)^2+(D219-D218)^2+(E219-E218)^2)</x:f>
+        <x:v>1.6820000000000004</x:v>
       </x:c>
       <x:c r="G219" s="8" t="str">
         <x:v>Current</x:v>
@@ -12388,23 +13698,23 @@
     </x:row>
     <x:row r="220" ht="32" customHeight="1">
       <x:c r="A220" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F247</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B220" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C220" s="11" t="n">
-        <x:v>23.475</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D220" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E220" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F220" s="11" t="n">
         <x:f>SQRT((C220-C219)^2+(D220-D219)^2+(E220-E219)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G220" s="8" t="str">
         <x:v>Current</x:v>
@@ -12412,23 +13722,23 @@
     </x:row>
     <x:row r="221" ht="32" customHeight="1">
       <x:c r="A221" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F247</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B221" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C221" s="11" t="n">
-        <x:v>23.475</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D221" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E221" s="11" t="n">
-        <x:v>7.07</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F221" s="11" t="n">
         <x:f>SQRT((C221-C220)^2+(D221-D220)^2+(E221-E220)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G221" s="8" t="str">
         <x:v>Current</x:v>
@@ -12436,23 +13746,23 @@
     </x:row>
     <x:row r="222" ht="32" customHeight="1">
       <x:c r="A222" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F249</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B222" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C222" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D222" s="11" t="n">
-        <x:v>6.0120000000000005</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E222" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F222" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C222-C221)^2+(D222-D221)^2+(E222-E221)^2)</x:f>
+        <x:v>1.0279999999999996</x:v>
       </x:c>
       <x:c r="G222" s="8" t="str">
         <x:v>Current</x:v>
@@ -12460,23 +13770,23 @@
     </x:row>
     <x:row r="223" ht="32" customHeight="1">
       <x:c r="A223" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F249</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B223" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C223" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D223" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E223" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F223" s="11" t="n">
         <x:f>SQRT((C223-C222)^2+(D223-D222)^2+(E223-E222)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G223" s="8" t="str">
         <x:v>Current</x:v>
@@ -12484,23 +13794,23 @@
     </x:row>
     <x:row r="224" ht="32" customHeight="1">
       <x:c r="A224" s="8" t="str">
-        <x:v>drop:FC1:F2:fan:1:F249</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B224" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C224" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D224" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E224" s="11" t="n">
-        <x:v>7.07</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F224" s="11" t="n">
         <x:f>SQRT((C224-C223)^2+(D224-D223)^2+(E224-E223)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G224" s="8" t="str">
         <x:v>Current</x:v>
@@ -12508,23 +13818,23 @@
     </x:row>
     <x:row r="225" ht="32" customHeight="1">
       <x:c r="A225" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B225" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C225" s="11" t="n">
-        <x:v>2.73</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D225" s="11" t="n">
-        <x:v>1.5</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E225" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F225" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C225-C224)^2+(D225-D224)^2+(E225-E224)^2)</x:f>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G225" s="8" t="str">
         <x:v>Current</x:v>
@@ -12532,23 +13842,23 @@
     </x:row>
     <x:row r="226" ht="32" customHeight="1">
       <x:c r="A226" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B226" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C226" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>37.695</x:v>
       </x:c>
       <x:c r="D226" s="11" t="n">
-        <x:v>1.5</x:v>
+        <x:v>6.950412371134018</x:v>
       </x:c>
       <x:c r="E226" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F226" s="11" t="n">
         <x:f>SQRT((C226-C225)^2+(D226-D225)^2+(E226-E225)^2)</x:f>
-        <x:v>0.3799999999999999</x:v>
+        <x:v>3.697957107375376</x:v>
       </x:c>
       <x:c r="G226" s="8" t="str">
         <x:v>Current</x:v>
@@ -12556,23 +13866,23 @@
     </x:row>
     <x:row r="227" ht="32" customHeight="1">
       <x:c r="A227" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B227" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C227" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>37.615</x:v>
       </x:c>
       <x:c r="D227" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E227" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F227" s="11" t="n">
         <x:f>SQRT((C227-C226)^2+(D227-D226)^2+(E227-E226)^2)</x:f>
-        <x:v>6.15</x:v>
+        <x:v>0.12010804821421713</x:v>
       </x:c>
       <x:c r="G227" s="8" t="str">
         <x:v>Current</x:v>
@@ -12580,23 +13890,23 @@
     </x:row>
     <x:row r="228" ht="32" customHeight="1">
       <x:c r="A228" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B228" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C228" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D228" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E228" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F228" s="11" t="n">
         <x:f>SQRT((C228-C227)^2+(D228-D227)^2+(E228-E227)^2)</x:f>
-        <x:v>4.0600000000000005</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G228" s="8" t="str">
         <x:v>Current</x:v>
@@ -12604,23 +13914,23 @@
     </x:row>
     <x:row r="229" ht="32" customHeight="1">
       <x:c r="A229" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B229" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C229" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D229" s="11" t="n">
-        <x:v>6.0280000000000005</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E229" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F229" s="11" t="n">
         <x:f>SQRT((C229-C228)^2+(D229-D228)^2+(E229-E228)^2)</x:f>
-        <x:v>1.6219999999999999</x:v>
+        <x:v>1.0279999999999996</x:v>
       </x:c>
       <x:c r="G229" s="8" t="str">
         <x:v>Current</x:v>
@@ -12628,23 +13938,23 @@
     </x:row>
     <x:row r="230" ht="32" customHeight="1">
       <x:c r="A230" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:-1</x:v>
+        <x:v>trunk:FC1:F2:fan:1</x:v>
       </x:c>
       <x:c r="B230" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C230" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>5.475000000000001</x:v>
       </x:c>
       <x:c r="D230" s="11" t="n">
-        <x:v>6.0280000000000005</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E230" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F230" s="11" t="n">
         <x:f>SQRT((C230-C229)^2+(D230-D229)^2+(E230-E229)^2)</x:f>
-        <x:v>0.3049999999999997</x:v>
+        <x:v>31.5</x:v>
       </x:c>
       <x:c r="G230" s="8" t="str">
         <x:v>Current</x:v>
@@ -12652,19 +13962,19 @@
     </x:row>
     <x:row r="231" ht="32" customHeight="1">
       <x:c r="A231" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+        <x:v>drop:FC1:F2:fan:1:F245</x:v>
       </x:c>
       <x:c r="B231" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C231" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>14.475000000000001</x:v>
       </x:c>
       <x:c r="D231" s="11" t="n">
-        <x:v>6.0280000000000005</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E231" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F231" s="11" t="n">
         <x:f>0</x:f>
@@ -12676,23 +13986,23 @@
     </x:row>
     <x:row r="232" ht="32" customHeight="1">
       <x:c r="A232" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+        <x:v>drop:FC1:F2:fan:1:F245</x:v>
       </x:c>
       <x:c r="B232" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C232" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>14.475000000000001</x:v>
       </x:c>
       <x:c r="D232" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E232" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F232" s="11" t="n">
         <x:f>SQRT((C232-C231)^2+(D232-D231)^2+(E232-E231)^2)</x:f>
-        <x:v>1.6504269144678898</x:v>
+        <x:v>0.46200000000000063</x:v>
       </x:c>
       <x:c r="G232" s="8" t="str">
         <x:v>Current</x:v>
@@ -12700,23 +14010,23 @@
     </x:row>
     <x:row r="233" ht="32" customHeight="1">
       <x:c r="A233" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+        <x:v>drop:FC1:F2:fan:1:F245</x:v>
       </x:c>
       <x:c r="B233" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C233" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>14.475</x:v>
       </x:c>
       <x:c r="D233" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E233" s="11" t="n">
-        <x:v>-3.05</x:v>
+        <x:v>7.07</x:v>
       </x:c>
       <x:c r="F233" s="11" t="n">
         <x:f>SQRT((C233-C232)^2+(D233-D232)^2+(E233-E232)^2)</x:f>
-        <x:v>4.3100000000000005</x:v>
+        <x:v>0.29000000000000004</x:v>
       </x:c>
       <x:c r="G233" s="8" t="str">
         <x:v>Current</x:v>
@@ -12724,23 +14034,23 @@
     </x:row>
     <x:row r="234" ht="32" customHeight="1">
       <x:c r="A234" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+        <x:v>drop:FC1:F2:fan:1:F247</x:v>
       </x:c>
       <x:c r="B234" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C234" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>23.475</x:v>
       </x:c>
       <x:c r="D234" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E234" s="11" t="n">
-        <x:v>-3.05</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F234" s="11" t="n">
-        <x:f>SQRT((C234-C233)^2+(D234-D233)^2+(E234-E233)^2)</x:f>
-        <x:v>1.6500000000000004</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G234" s="8" t="str">
         <x:v>Current</x:v>
@@ -12748,23 +14058,23 @@
     </x:row>
     <x:row r="235" ht="32" customHeight="1">
       <x:c r="A235" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+        <x:v>drop:FC1:F2:fan:1:F247</x:v>
       </x:c>
       <x:c r="B235" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C235" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>23.475</x:v>
       </x:c>
       <x:c r="D235" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E235" s="11" t="n">
-        <x:v>-3.05</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F235" s="11" t="n">
         <x:f>SQRT((C235-C234)^2+(D235-D234)^2+(E235-E234)^2)</x:f>
-        <x:v>0.3049999999999997</x:v>
+        <x:v>0.46200000000000063</x:v>
       </x:c>
       <x:c r="G235" s="8" t="str">
         <x:v>Current</x:v>
@@ -12772,71 +14082,71 @@
     </x:row>
     <x:row r="236" ht="32" customHeight="1">
       <x:c r="A236" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F247</x:v>
       </x:c>
       <x:c r="B236" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C236" s="11" t="n">
+        <x:v>23.475</x:v>
+      </x:c>
+      <x:c r="D236" s="11" t="n">
+        <x:v>5.55</x:v>
+      </x:c>
+      <x:c r="E236" s="11" t="n">
+        <x:v>7.07</x:v>
+      </x:c>
+      <x:c r="F236" s="11" t="n">
+        <x:f>SQRT((C236-C235)^2+(D236-D235)^2+(E236-E235)^2)</x:f>
+        <x:v>0.29000000000000004</x:v>
+      </x:c>
+      <x:c r="G236" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" ht="32" customHeight="1">
+      <x:c r="A237" s="8" t="str">
+        <x:v>drop:FC1:F2:fan:1:F249</x:v>
+      </x:c>
+      <x:c r="B237" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C236" s="11" t="n">
-        <x:v>2.73</x:v>
-      </x:c>
-      <x:c r="D236" s="11" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="E236" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F236" s="11" t="n">
+      <x:c r="C237" s="11" t="n">
+        <x:v>32.475</x:v>
+      </x:c>
+      <x:c r="D237" s="11" t="n">
+        <x:v>6.0120000000000005</x:v>
+      </x:c>
+      <x:c r="E237" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F237" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G236" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="237" ht="32" customHeight="1">
-      <x:c r="A237" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
-      </x:c>
-      <x:c r="B237" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C237" s="11" t="n">
-        <x:v>2.35</x:v>
-      </x:c>
-      <x:c r="D237" s="11" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="E237" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F237" s="11" t="n">
-        <x:f>SQRT((C237-C236)^2+(D237-D236)^2+(E237-E236)^2)</x:f>
-        <x:v>0.3799999999999999</x:v>
-      </x:c>
       <x:c r="G237" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="238" ht="32" customHeight="1">
       <x:c r="A238" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F249</x:v>
       </x:c>
       <x:c r="B238" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C238" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>32.475</x:v>
       </x:c>
       <x:c r="D238" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E238" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F238" s="11" t="n">
         <x:f>SQRT((C238-C237)^2+(D238-D237)^2+(E238-E237)^2)</x:f>
-        <x:v>6.15</x:v>
+        <x:v>0.46200000000000063</x:v>
       </x:c>
       <x:c r="G238" s="8" t="str">
         <x:v>Current</x:v>
@@ -12844,23 +14154,23 @@
     </x:row>
     <x:row r="239" ht="32" customHeight="1">
       <x:c r="A239" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F249</x:v>
       </x:c>
       <x:c r="B239" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C239" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>32.475</x:v>
       </x:c>
       <x:c r="D239" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E239" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>7.07</x:v>
       </x:c>
       <x:c r="F239" s="11" t="n">
         <x:f>SQRT((C239-C238)^2+(D239-D238)^2+(E239-E238)^2)</x:f>
-        <x:v>10.66</x:v>
+        <x:v>0.29000000000000004</x:v>
       </x:c>
       <x:c r="G239" s="8" t="str">
         <x:v>Current</x:v>
@@ -12868,23 +14178,23 @@
     </x:row>
     <x:row r="240" ht="32" customHeight="1">
       <x:c r="A240" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-2P</x:v>
       </x:c>
       <x:c r="B240" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C240" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>5.475000000000001</x:v>
       </x:c>
       <x:c r="D240" s="11" t="n">
-        <x:v>6.0280000000000005</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E240" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F240" s="11" t="n">
-        <x:f>SQRT((C240-C239)^2+(D240-D239)^2+(E240-E239)^2)</x:f>
-        <x:v>1.6219999999999999</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G240" s="8" t="str">
         <x:v>Current</x:v>
@@ -12892,23 +14202,23 @@
     </x:row>
     <x:row r="241" ht="32" customHeight="1">
       <x:c r="A241" s="8" t="str">
-        <x:v>trunk:DB2:F4:fan:1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-2P</x:v>
       </x:c>
       <x:c r="B241" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C241" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>5.475000000000001</x:v>
       </x:c>
       <x:c r="D241" s="11" t="n">
-        <x:v>6.0280000000000005</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E241" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F241" s="11" t="n">
         <x:f>SQRT((C241-C240)^2+(D241-D240)^2+(E241-E240)^2)</x:f>
-        <x:v>0.3049999999999997</x:v>
+        <x:v>0.46200000000000063</x:v>
       </x:c>
       <x:c r="G241" s="8" t="str">
         <x:v>Current</x:v>
@@ -12916,71 +14226,71 @@
     </x:row>
     <x:row r="242" ht="32" customHeight="1">
       <x:c r="A242" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-2P</x:v>
       </x:c>
       <x:c r="B242" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C242" s="11" t="n">
+        <x:v>5.475</x:v>
+      </x:c>
+      <x:c r="D242" s="11" t="n">
+        <x:v>5.55</x:v>
+      </x:c>
+      <x:c r="E242" s="11" t="n">
+        <x:v>7.07</x:v>
+      </x:c>
+      <x:c r="F242" s="11" t="n">
+        <x:f>SQRT((C242-C241)^2+(D242-D241)^2+(E242-E241)^2)</x:f>
+        <x:v>0.29000000000000004</x:v>
+      </x:c>
+      <x:c r="G242" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" ht="32" customHeight="1">
+      <x:c r="A243" s="8" t="str">
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-3</x:v>
+      </x:c>
+      <x:c r="B243" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C242" s="11" t="n">
-        <x:v>2.655</x:v>
-      </x:c>
-      <x:c r="D242" s="11" t="n">
-        <x:v>6.0280000000000005</x:v>
-      </x:c>
-      <x:c r="E242" s="11" t="n">
+      <x:c r="C243" s="11" t="n">
+        <x:v>9.975000000000001</x:v>
+      </x:c>
+      <x:c r="D243" s="11" t="n">
+        <x:v>6.0120000000000005</x:v>
+      </x:c>
+      <x:c r="E243" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
-      <x:c r="F242" s="11" t="n">
+      <x:c r="F243" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G242" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="243" ht="32" customHeight="1">
-      <x:c r="A243" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:1:F251</x:v>
-      </x:c>
-      <x:c r="B243" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C243" s="11" t="n">
-        <x:v>2.35</x:v>
-      </x:c>
-      <x:c r="D243" s="11" t="n">
-        <x:v>7.65</x:v>
-      </x:c>
-      <x:c r="E243" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F243" s="11" t="n">
-        <x:f>SQRT((C243-C242)^2+(D243-D242)^2+(E243-E242)^2)</x:f>
-        <x:v>1.6504269144678898</x:v>
-      </x:c>
       <x:c r="G243" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="244" ht="32" customHeight="1">
       <x:c r="A244" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-3</x:v>
       </x:c>
       <x:c r="B244" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C244" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>9.975000000000001</x:v>
       </x:c>
       <x:c r="D244" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E244" s="11" t="n">
-        <x:v>3.05</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F244" s="11" t="n">
         <x:f>SQRT((C244-C243)^2+(D244-D243)^2+(E244-E243)^2)</x:f>
-        <x:v>4.3100000000000005</x:v>
+        <x:v>0.46200000000000063</x:v>
       </x:c>
       <x:c r="G244" s="8" t="str">
         <x:v>Current</x:v>
@@ -12988,23 +14298,23 @@
     </x:row>
     <x:row r="245" ht="32" customHeight="1">
       <x:c r="A245" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-3</x:v>
       </x:c>
       <x:c r="B245" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C245" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>9.975</x:v>
       </x:c>
       <x:c r="D245" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E245" s="11" t="n">
-        <x:v>3.05</x:v>
+        <x:v>7.07</x:v>
       </x:c>
       <x:c r="F245" s="11" t="n">
         <x:f>SQRT((C245-C244)^2+(D245-D244)^2+(E245-E244)^2)</x:f>
-        <x:v>1.6500000000000004</x:v>
+        <x:v>0.29000000000000004</x:v>
       </x:c>
       <x:c r="G245" s="8" t="str">
         <x:v>Current</x:v>
@@ -13012,23 +14322,23 @@
     </x:row>
     <x:row r="246" ht="32" customHeight="1">
       <x:c r="A246" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-5</x:v>
       </x:c>
       <x:c r="B246" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C246" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>18.975</x:v>
       </x:c>
       <x:c r="D246" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E246" s="11" t="n">
-        <x:v>3.05</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F246" s="11" t="n">
-        <x:f>SQRT((C246-C245)^2+(D246-D245)^2+(E246-E245)^2)</x:f>
-        <x:v>0.3049999999999997</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G246" s="8" t="str">
         <x:v>Current</x:v>
@@ -13036,95 +14346,95 @@
     </x:row>
     <x:row r="247" ht="32" customHeight="1">
       <x:c r="A247" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-5</x:v>
       </x:c>
       <x:c r="B247" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C247" s="11" t="n">
+        <x:v>18.975</x:v>
+      </x:c>
+      <x:c r="D247" s="11" t="n">
+        <x:v>5.55</x:v>
+      </x:c>
+      <x:c r="E247" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F247" s="11" t="n">
+        <x:f>SQRT((C247-C246)^2+(D247-D246)^2+(E247-E246)^2)</x:f>
+        <x:v>0.46200000000000063</x:v>
+      </x:c>
+      <x:c r="G247" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" ht="32" customHeight="1">
+      <x:c r="A248" s="8" t="str">
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-5</x:v>
+      </x:c>
+      <x:c r="B248" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C248" s="11" t="n">
+        <x:v>18.975</x:v>
+      </x:c>
+      <x:c r="D248" s="11" t="n">
+        <x:v>5.55</x:v>
+      </x:c>
+      <x:c r="E248" s="11" t="n">
+        <x:v>7.07</x:v>
+      </x:c>
+      <x:c r="F248" s="11" t="n">
+        <x:f>SQRT((C248-C247)^2+(D248-D247)^2+(E248-E247)^2)</x:f>
+        <x:v>0.29000000000000004</x:v>
+      </x:c>
+      <x:c r="G248" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249" ht="32" customHeight="1">
+      <x:c r="A249" s="8" t="str">
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-7</x:v>
+      </x:c>
+      <x:c r="B249" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C247" s="11" t="n">
-        <x:v>48.895</x:v>
-      </x:c>
-      <x:c r="D247" s="11" t="n">
-        <x:v>1.95</x:v>
-      </x:c>
-      <x:c r="E247" s="11" t="n">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="F247" s="11" t="n">
+      <x:c r="C249" s="11" t="n">
+        <x:v>27.975</x:v>
+      </x:c>
+      <x:c r="D249" s="11" t="n">
+        <x:v>6.0120000000000005</x:v>
+      </x:c>
+      <x:c r="E249" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F249" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G247" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="248" ht="32" customHeight="1">
-      <x:c r="A248" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
-      </x:c>
-      <x:c r="B248" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C248" s="11" t="n">
-        <x:v>48.735</x:v>
-      </x:c>
-      <x:c r="D248" s="11" t="n">
-        <x:v>1.95</x:v>
-      </x:c>
-      <x:c r="E248" s="11" t="n">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="F248" s="11" t="n">
-        <x:f>SQRT((C248-C247)^2+(D248-D247)^2+(E248-E247)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
-      </x:c>
-      <x:c r="G248" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="249" ht="32" customHeight="1">
-      <x:c r="A249" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
-      </x:c>
-      <x:c r="B249" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C249" s="11" t="n">
-        <x:v>48.735</x:v>
-      </x:c>
-      <x:c r="D249" s="11" t="n">
-        <x:v>1.95</x:v>
-      </x:c>
-      <x:c r="E249" s="11" t="n">
-        <x:v>-2.24</x:v>
-      </x:c>
-      <x:c r="F249" s="11" t="n">
-        <x:f>SQRT((C249-C248)^2+(D249-D248)^2+(E249-E248)^2)</x:f>
-        <x:v>2.64</x:v>
-      </x:c>
       <x:c r="G249" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="250" ht="32" customHeight="1">
       <x:c r="A250" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-7</x:v>
       </x:c>
       <x:c r="B250" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C250" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>27.975</x:v>
       </x:c>
       <x:c r="D250" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E250" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F250" s="11" t="n">
         <x:f>SQRT((C250-C249)^2+(D250-D249)^2+(E250-E249)^2)</x:f>
-        <x:v>2.38</x:v>
+        <x:v>0.46200000000000063</x:v>
       </x:c>
       <x:c r="G250" s="8" t="str">
         <x:v>Current</x:v>
@@ -13132,23 +14442,23 @@
     </x:row>
     <x:row r="251" ht="32" customHeight="1">
       <x:c r="A251" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-7</x:v>
       </x:c>
       <x:c r="B251" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C251" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>27.975</x:v>
       </x:c>
       <x:c r="D251" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E251" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>7.07</x:v>
       </x:c>
       <x:c r="F251" s="11" t="n">
         <x:f>SQRT((C251-C250)^2+(D251-D250)^2+(E251-E250)^2)</x:f>
-        <x:v>1.0599999999999996</x:v>
+        <x:v>0.29000000000000004</x:v>
       </x:c>
       <x:c r="G251" s="8" t="str">
         <x:v>Current</x:v>
@@ -13156,23 +14466,23 @@
     </x:row>
     <x:row r="252" ht="32" customHeight="1">
       <x:c r="A252" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-9</x:v>
       </x:c>
       <x:c r="B252" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C252" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D252" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>6.0120000000000005</x:v>
       </x:c>
       <x:c r="E252" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F252" s="11" t="n">
-        <x:f>SQRT((C252-C251)^2+(D252-D251)^2+(E252-E251)^2)</x:f>
-        <x:v>4.280999999999999</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G252" s="8" t="str">
         <x:v>Current</x:v>
@@ -13180,23 +14490,23 @@
     </x:row>
     <x:row r="253" ht="32" customHeight="1">
       <x:c r="A253" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-9</x:v>
       </x:c>
       <x:c r="B253" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C253" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D253" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E253" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F253" s="11" t="n">
         <x:f>SQRT((C253-C252)^2+(D253-D252)^2+(E253-E252)^2)</x:f>
-        <x:v>1.7060000000000004</x:v>
+        <x:v>0.46200000000000063</x:v>
       </x:c>
       <x:c r="G253" s="8" t="str">
         <x:v>Current</x:v>
@@ -13204,23 +14514,23 @@
     </x:row>
     <x:row r="254" ht="32" customHeight="1">
       <x:c r="A254" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:FC1:F2:fan:1:F-NAVE-H-9</x:v>
       </x:c>
       <x:c r="B254" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C254" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D254" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E254" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.07</x:v>
       </x:c>
       <x:c r="F254" s="11" t="n">
         <x:f>SQRT((C254-C253)^2+(D254-D253)^2+(E254-E253)^2)</x:f>
-        <x:v>4.0600000000000005</x:v>
+        <x:v>0.29000000000000004</x:v>
       </x:c>
       <x:c r="G254" s="8" t="str">
         <x:v>Current</x:v>
@@ -13228,23 +14538,23 @@
     </x:row>
     <x:row r="255" ht="32" customHeight="1">
       <x:c r="A255" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B255" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C255" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>2.73</x:v>
       </x:c>
       <x:c r="D255" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="E255" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F255" s="11" t="n">
-        <x:f>SQRT((C255-C254)^2+(D255-D254)^2+(E255-E254)^2)</x:f>
-        <x:v>8.841000000000001</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G255" s="8" t="str">
         <x:v>Current</x:v>
@@ -13252,23 +14562,23 @@
     </x:row>
     <x:row r="256" ht="32" customHeight="1">
       <x:c r="A256" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B256" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C256" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D256" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="E256" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F256" s="11" t="n">
         <x:f>SQRT((C256-C255)^2+(D256-D255)^2+(E256-E255)^2)</x:f>
-        <x:v>1.0039999999999996</x:v>
+        <x:v>0.3799999999999999</x:v>
       </x:c>
       <x:c r="G256" s="8" t="str">
         <x:v>Current</x:v>
@@ -13276,23 +14586,23 @@
     </x:row>
     <x:row r="257" ht="32" customHeight="1">
       <x:c r="A257" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B257" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C257" s="11" t="n">
-        <x:v>43.535</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D257" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E257" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F257" s="11" t="n">
         <x:f>SQRT((C257-C256)^2+(D257-D256)^2+(E257-E256)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>6.15</x:v>
       </x:c>
       <x:c r="G257" s="8" t="str">
         <x:v>Current</x:v>
@@ -13300,23 +14610,23 @@
     </x:row>
     <x:row r="258" ht="32" customHeight="1">
       <x:c r="A258" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B258" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C258" s="11" t="n">
-        <x:v>43.455</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D258" s="11" t="n">
-        <x:v>6.950412371134024</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E258" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F258" s="11" t="n">
         <x:f>SQRT((C258-C257)^2+(D258-D257)^2+(E258-E257)^2)</x:f>
-        <x:v>0.12010804821421249</x:v>
+        <x:v>4.0600000000000005</x:v>
       </x:c>
       <x:c r="G258" s="8" t="str">
         <x:v>Current</x:v>
@@ -13324,23 +14634,23 @@
     </x:row>
     <x:row r="259" ht="32" customHeight="1">
       <x:c r="A259" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B259" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C259" s="11" t="n">
-        <x:v>40.574999999999996</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D259" s="11" t="n">
-        <x:v>9.269999999999994</x:v>
+        <x:v>6.0280000000000005</x:v>
       </x:c>
       <x:c r="E259" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F259" s="11" t="n">
         <x:f>SQRT((C259-C258)^2+(D259-D258)^2+(E259-E258)^2)</x:f>
-        <x:v>3.6979571073753776</x:v>
+        <x:v>1.6219999999999999</x:v>
       </x:c>
       <x:c r="G259" s="8" t="str">
         <x:v>Current</x:v>
@@ -13348,23 +14658,23 @@
     </x:row>
     <x:row r="260" ht="32" customHeight="1">
       <x:c r="A260" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B260" s="8" t="n">
-        <x:v>14</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C260" s="11" t="n">
-        <x:v>37.695</x:v>
+        <x:v>2.655</x:v>
       </x:c>
       <x:c r="D260" s="11" t="n">
-        <x:v>6.950412371134018</x:v>
+        <x:v>6.0280000000000005</x:v>
       </x:c>
       <x:c r="E260" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F260" s="11" t="n">
         <x:f>SQRT((C260-C259)^2+(D260-D259)^2+(E260-E259)^2)</x:f>
-        <x:v>3.697957107375376</x:v>
+        <x:v>0.3049999999999997</x:v>
       </x:c>
       <x:c r="G260" s="8" t="str">
         <x:v>Current</x:v>
@@ -13372,23 +14682,23 @@
     </x:row>
     <x:row r="261" ht="32" customHeight="1">
       <x:c r="A261" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
       </x:c>
       <x:c r="B261" s="8" t="n">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C261" s="11" t="n">
-        <x:v>37.615</x:v>
+        <x:v>2.655</x:v>
       </x:c>
       <x:c r="D261" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>6.0280000000000005</x:v>
       </x:c>
       <x:c r="E261" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F261" s="11" t="n">
-        <x:f>SQRT((C261-C260)^2+(D261-D260)^2+(E261-E260)^2)</x:f>
-        <x:v>0.12010804821421713</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G261" s="8" t="str">
         <x:v>Current</x:v>
@@ -13396,23 +14706,23 @@
     </x:row>
     <x:row r="262" ht="32" customHeight="1">
       <x:c r="A262" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
       </x:c>
       <x:c r="B262" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C262" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D262" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E262" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F262" s="11" t="n">
         <x:f>SQRT((C262-C261)^2+(D262-D261)^2+(E262-E261)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>1.6504269144678898</x:v>
       </x:c>
       <x:c r="G262" s="8" t="str">
         <x:v>Current</x:v>
@@ -13420,23 +14730,23 @@
     </x:row>
     <x:row r="263" ht="32" customHeight="1">
       <x:c r="A263" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
       </x:c>
       <x:c r="B263" s="8" t="n">
-        <x:v>17</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C263" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D263" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E263" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-3.05</x:v>
       </x:c>
       <x:c r="F263" s="11" t="n">
         <x:f>SQRT((C263-C262)^2+(D263-D262)^2+(E263-E262)^2)</x:f>
-        <x:v>1.0039999999999996</x:v>
+        <x:v>4.3100000000000005</x:v>
       </x:c>
       <x:c r="G263" s="8" t="str">
         <x:v>Current</x:v>
@@ -13444,23 +14754,23 @@
     </x:row>
     <x:row r="264" ht="32" customHeight="1">
       <x:c r="A264" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
       </x:c>
       <x:c r="B264" s="8" t="n">
-        <x:v>18</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C264" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D264" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E264" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-3.05</x:v>
       </x:c>
       <x:c r="F264" s="11" t="n">
         <x:f>SQRT((C264-C263)^2+(D264-D263)^2+(E264-E263)^2)</x:f>
-        <x:v>31.495</x:v>
+        <x:v>1.6500000000000004</x:v>
       </x:c>
       <x:c r="G264" s="8" t="str">
         <x:v>Current</x:v>
@@ -13468,71 +14778,71 @@
     </x:row>
     <x:row r="265" ht="32" customHeight="1">
       <x:c r="A265" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
       </x:c>
       <x:c r="B265" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C265" s="11" t="n">
+        <x:v>2.655</x:v>
+      </x:c>
+      <x:c r="D265" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E265" s="11" t="n">
+        <x:v>-3.05</x:v>
+      </x:c>
+      <x:c r="F265" s="11" t="n">
+        <x:f>SQRT((C265-C264)^2+(D265-D264)^2+(E265-E264)^2)</x:f>
+        <x:v>0.3049999999999997</x:v>
+      </x:c>
+      <x:c r="G265" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266" ht="32" customHeight="1">
+      <x:c r="A266" s="8" t="str">
+        <x:v>trunk:DB2:F4:fan:1</x:v>
+      </x:c>
+      <x:c r="B266" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C265" s="11" t="n">
-        <x:v>5.48</x:v>
-      </x:c>
-      <x:c r="D265" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
-      </x:c>
-      <x:c r="E265" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F265" s="11" t="n">
+      <x:c r="C266" s="11" t="n">
+        <x:v>2.73</x:v>
+      </x:c>
+      <x:c r="D266" s="11" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E266" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F266" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G265" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="266" ht="32" customHeight="1">
-      <x:c r="A266" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
-      </x:c>
-      <x:c r="B266" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C266" s="11" t="n">
-        <x:v>5.48</x:v>
-      </x:c>
-      <x:c r="D266" s="11" t="n">
-        <x:v>7.04</x:v>
-      </x:c>
-      <x:c r="E266" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F266" s="11" t="n">
-        <x:f>SQRT((C266-C265)^2+(D266-D265)^2+(E266-E265)^2)</x:f>
-        <x:v>1.0039999999999996</x:v>
-      </x:c>
       <x:c r="G266" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="267" ht="32" customHeight="1">
       <x:c r="A267" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+        <x:v>trunk:DB2:F4:fan:1</x:v>
       </x:c>
       <x:c r="B267" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C267" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D267" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="E267" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F267" s="11" t="n">
         <x:f>SQRT((C267-C266)^2+(D267-D266)^2+(E267-E266)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
+        <x:v>0.3799999999999999</x:v>
       </x:c>
       <x:c r="G267" s="8" t="str">
         <x:v>Current</x:v>
@@ -13540,23 +14850,23 @@
     </x:row>
     <x:row r="268" ht="32" customHeight="1">
       <x:c r="A268" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+        <x:v>trunk:DB2:F4:fan:1</x:v>
       </x:c>
       <x:c r="B268" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C268" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D268" s="11" t="n">
-        <x:v>10.64004347826087</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E268" s="11" t="n">
-        <x:v>-2.3999999999999995</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F268" s="11" t="n">
         <x:f>SQRT((C268-C267)^2+(D268-D267)^2+(E268-E267)^2)</x:f>
-        <x:v>6.128777451120952</x:v>
+        <x:v>6.15</x:v>
       </x:c>
       <x:c r="G268" s="8" t="str">
         <x:v>Current</x:v>
@@ -13564,23 +14874,23 @@
     </x:row>
     <x:row r="269" ht="32" customHeight="1">
       <x:c r="A269" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+        <x:v>trunk:DB2:F4:fan:1</x:v>
       </x:c>
       <x:c r="B269" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C269" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D269" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E269" s="11" t="n">
-        <x:v>-2.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F269" s="11" t="n">
         <x:f>SQRT((C269-C268)^2+(D269-D268)^2+(E269-E268)^2)</x:f>
-        <x:v>1.2400434782608691</x:v>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G269" s="8" t="str">
         <x:v>Current</x:v>
@@ -13588,23 +14898,23 @@
     </x:row>
     <x:row r="270" ht="32" customHeight="1">
       <x:c r="A270" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+        <x:v>trunk:DB2:F4:fan:1</x:v>
       </x:c>
       <x:c r="B270" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C270" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D270" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>6.0280000000000005</x:v>
       </x:c>
       <x:c r="E270" s="11" t="n">
-        <x:v>-2.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F270" s="11" t="n">
         <x:f>SQRT((C270-C269)^2+(D270-D269)^2+(E270-E269)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
+        <x:v>1.6219999999999999</x:v>
       </x:c>
       <x:c r="G270" s="8" t="str">
         <x:v>Current</x:v>
@@ -13612,71 +14922,71 @@
     </x:row>
     <x:row r="271" ht="32" customHeight="1">
       <x:c r="A271" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
+        <x:v>trunk:DB2:F4:fan:1</x:v>
       </x:c>
       <x:c r="B271" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C271" s="11" t="n">
+        <x:v>2.655</x:v>
+      </x:c>
+      <x:c r="D271" s="11" t="n">
+        <x:v>6.0280000000000005</x:v>
+      </x:c>
+      <x:c r="E271" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F271" s="11" t="n">
+        <x:f>SQRT((C271-C270)^2+(D271-D270)^2+(E271-E270)^2)</x:f>
+        <x:v>0.3049999999999997</x:v>
+      </x:c>
+      <x:c r="G271" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" ht="32" customHeight="1">
+      <x:c r="A272" s="8" t="str">
+        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+      </x:c>
+      <x:c r="B272" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C271" s="11" t="n">
-        <x:v>5.48</x:v>
-      </x:c>
-      <x:c r="D271" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
-      </x:c>
-      <x:c r="E271" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F271" s="11" t="n">
+      <x:c r="C272" s="11" t="n">
+        <x:v>2.655</x:v>
+      </x:c>
+      <x:c r="D272" s="11" t="n">
+        <x:v>6.0280000000000005</x:v>
+      </x:c>
+      <x:c r="E272" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F272" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G271" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="272" ht="32" customHeight="1">
-      <x:c r="A272" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
-      </x:c>
-      <x:c r="B272" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C272" s="11" t="n">
-        <x:v>5.48</x:v>
-      </x:c>
-      <x:c r="D272" s="11" t="n">
-        <x:v>7.04</x:v>
-      </x:c>
-      <x:c r="E272" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F272" s="11" t="n">
-        <x:f>SQRT((C272-C271)^2+(D272-D271)^2+(E272-E271)^2)</x:f>
-        <x:v>1.0039999999999996</x:v>
-      </x:c>
       <x:c r="G272" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="273" ht="32" customHeight="1">
       <x:c r="A273" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
+        <x:v>drop:DB2:F4:fan:1:F251</x:v>
       </x:c>
       <x:c r="B273" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C273" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D273" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E273" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F273" s="11" t="n">
         <x:f>SQRT((C273-C272)^2+(D273-D272)^2+(E273-E272)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
+        <x:v>1.6504269144678898</x:v>
       </x:c>
       <x:c r="G273" s="8" t="str">
         <x:v>Current</x:v>
@@ -13684,23 +14994,23 @@
     </x:row>
     <x:row r="274" ht="32" customHeight="1">
       <x:c r="A274" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
+        <x:v>drop:DB2:F4:fan:1:F251</x:v>
       </x:c>
       <x:c r="B274" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C274" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D274" s="11" t="n">
-        <x:v>11.801347826086957</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E274" s="11" t="n">
-        <x:v>-0.7999999999999998</x:v>
+        <x:v>3.05</x:v>
       </x:c>
       <x:c r="F274" s="11" t="n">
         <x:f>SQRT((C274-C273)^2+(D274-D273)^2+(E274-E273)^2)</x:f>
-        <x:v>8.105802435353516</x:v>
+        <x:v>4.3100000000000005</x:v>
       </x:c>
       <x:c r="G274" s="8" t="str">
         <x:v>Current</x:v>
@@ -13708,23 +15018,23 @@
     </x:row>
     <x:row r="275" ht="32" customHeight="1">
       <x:c r="A275" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
+        <x:v>drop:DB2:F4:fan:1:F251</x:v>
       </x:c>
       <x:c r="B275" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C275" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D275" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E275" s="11" t="n">
-        <x:v>-0.8</x:v>
+        <x:v>3.05</x:v>
       </x:c>
       <x:c r="F275" s="11" t="n">
         <x:f>SQRT((C275-C274)^2+(D275-D274)^2+(E275-E274)^2)</x:f>
-        <x:v>2.4013478260869565</x:v>
+        <x:v>1.6500000000000004</x:v>
       </x:c>
       <x:c r="G275" s="8" t="str">
         <x:v>Current</x:v>
@@ -13732,23 +15042,23 @@
     </x:row>
     <x:row r="276" ht="32" customHeight="1">
       <x:c r="A276" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
+        <x:v>drop:DB2:F4:fan:1:F251</x:v>
       </x:c>
       <x:c r="B276" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C276" s="11" t="n">
+        <x:v>2.655</x:v>
+      </x:c>
+      <x:c r="D276" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C276" s="11" t="n">
-        <x:v>5.48</x:v>
-      </x:c>
-      <x:c r="D276" s="11" t="n">
-        <x:v>9.4</x:v>
-      </x:c>
       <x:c r="E276" s="11" t="n">
-        <x:v>-0.8</x:v>
+        <x:v>3.05</x:v>
       </x:c>
       <x:c r="F276" s="11" t="n">
         <x:f>SQRT((C276-C275)^2+(D276-D275)^2+(E276-E275)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
+        <x:v>0.3049999999999997</x:v>
       </x:c>
       <x:c r="G276" s="8" t="str">
         <x:v>Current</x:v>
@@ -13756,19 +15066,19 @@
     </x:row>
     <x:row r="277" ht="32" customHeight="1">
       <x:c r="A277" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B277" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C277" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D277" s="11" t="n">
-        <x:v>8.565264175257731</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E277" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F277" s="11" t="n">
         <x:f>0</x:f>
@@ -13780,23 +15090,23 @@
     </x:row>
     <x:row r="278" ht="32" customHeight="1">
       <x:c r="A278" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B278" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C278" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D278" s="11" t="n">
-        <x:v>8.565264175257731</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E278" s="11" t="n">
-        <x:v>-13.249</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F278" s="11" t="n">
         <x:f>SQRT((C278-C277)^2+(D278-D277)^2+(E278-E277)^2)</x:f>
-        <x:v>5.889</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G278" s="8" t="str">
         <x:v>Current</x:v>
@@ -13804,23 +15114,23 @@
     </x:row>
     <x:row r="279" ht="32" customHeight="1">
       <x:c r="A279" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B279" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C279" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D279" s="11" t="n">
-        <x:v>7.6</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E279" s="11" t="n">
-        <x:v>-13.249</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F279" s="11" t="n">
         <x:f>SQRT((C279-C278)^2+(D279-D278)^2+(E279-E278)^2)</x:f>
-        <x:v>0.9652641752577313</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="G279" s="8" t="str">
         <x:v>Current</x:v>
@@ -13828,23 +15138,23 @@
     </x:row>
     <x:row r="280" ht="32" customHeight="1">
       <x:c r="A280" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B280" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C280" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D280" s="11" t="n">
-        <x:v>7.6</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E280" s="11" t="n">
-        <x:v>-13.13</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F280" s="11" t="n">
         <x:f>SQRT((C280-C279)^2+(D280-D279)^2+(E280-E279)^2)</x:f>
-        <x:v>0.11899999999999977</x:v>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="G280" s="8" t="str">
         <x:v>Current</x:v>
@@ -13852,527 +15162,527 @@
     </x:row>
     <x:row r="281" ht="32" customHeight="1">
       <x:c r="A281" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
       <x:c r="B281" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C281" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D281" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E281" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F281" s="11" t="n">
+        <x:f>SQRT((C281-C280)^2+(D281-D280)^2+(E281-E280)^2)</x:f>
+        <x:v>1.0599999999999996</x:v>
+      </x:c>
+      <x:c r="G281" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" ht="32" customHeight="1">
+      <x:c r="A282" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
+      </x:c>
+      <x:c r="B282" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C282" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D282" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E282" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F282" s="11" t="n">
+        <x:f>SQRT((C282-C281)^2+(D282-D281)^2+(E282-E281)^2)</x:f>
+        <x:v>4.280999999999999</x:v>
+      </x:c>
+      <x:c r="G282" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" ht="32" customHeight="1">
+      <x:c r="A283" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
+      </x:c>
+      <x:c r="B283" s="8" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C283" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D283" s="11" t="n">
+        <x:v>6.0360000000000005</x:v>
+      </x:c>
+      <x:c r="E283" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F283" s="11" t="n">
+        <x:f>SQRT((C283-C282)^2+(D283-D282)^2+(E283-E282)^2)</x:f>
+        <x:v>1.7060000000000004</x:v>
+      </x:c>
+      <x:c r="G283" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284" ht="32" customHeight="1">
+      <x:c r="A284" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
+      </x:c>
+      <x:c r="B284" s="8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C284" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D284" s="11" t="n">
+        <x:v>6.0360000000000005</x:v>
+      </x:c>
+      <x:c r="E284" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F284" s="11" t="n">
+        <x:f>SQRT((C284-C283)^2+(D284-D283)^2+(E284-E283)^2)</x:f>
+        <x:v>4.0600000000000005</x:v>
+      </x:c>
+      <x:c r="G284" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285" ht="32" customHeight="1">
+      <x:c r="A285" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
+      </x:c>
+      <x:c r="B285" s="8" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C285" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D285" s="11" t="n">
+        <x:v>6.0360000000000005</x:v>
+      </x:c>
+      <x:c r="E285" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F285" s="11" t="n">
+        <x:f>SQRT((C285-C284)^2+(D285-D284)^2+(E285-E284)^2)</x:f>
+        <x:v>8.841000000000001</x:v>
+      </x:c>
+      <x:c r="G285" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286" ht="32" customHeight="1">
+      <x:c r="A286" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
+      </x:c>
+      <x:c r="B286" s="8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C286" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D286" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E286" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F286" s="11" t="n">
+        <x:f>SQRT((C286-C285)^2+(D286-D285)^2+(E286-E285)^2)</x:f>
+        <x:v>1.0039999999999996</x:v>
+      </x:c>
+      <x:c r="G286" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287" ht="32" customHeight="1">
+      <x:c r="A287" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
+      </x:c>
+      <x:c r="B287" s="8" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C287" s="11" t="n">
+        <x:v>43.535</x:v>
+      </x:c>
+      <x:c r="D287" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E287" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F287" s="11" t="n">
+        <x:f>SQRT((C287-C286)^2+(D287-D286)^2+(E287-E286)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G287" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288" ht="32" customHeight="1">
+      <x:c r="A288" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
+      </x:c>
+      <x:c r="B288" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C288" s="11" t="n">
+        <x:v>43.455</x:v>
+      </x:c>
+      <x:c r="D288" s="11" t="n">
+        <x:v>6.950412371134024</x:v>
+      </x:c>
+      <x:c r="E288" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F288" s="11" t="n">
+        <x:f>SQRT((C288-C287)^2+(D288-D287)^2+(E288-E287)^2)</x:f>
+        <x:v>0.12010804821421249</x:v>
+      </x:c>
+      <x:c r="G288" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289" ht="32" customHeight="1">
+      <x:c r="A289" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
+      </x:c>
+      <x:c r="B289" s="8" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C289" s="11" t="n">
+        <x:v>40.574999999999996</x:v>
+      </x:c>
+      <x:c r="D289" s="11" t="n">
+        <x:v>9.269999999999994</x:v>
+      </x:c>
+      <x:c r="E289" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F289" s="11" t="n">
+        <x:f>SQRT((C289-C288)^2+(D289-D288)^2+(E289-E288)^2)</x:f>
+        <x:v>3.6979571073753776</x:v>
+      </x:c>
+      <x:c r="G289" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290" ht="32" customHeight="1">
+      <x:c r="A290" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
+      </x:c>
+      <x:c r="B290" s="8" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C290" s="11" t="n">
+        <x:v>37.695</x:v>
+      </x:c>
+      <x:c r="D290" s="11" t="n">
+        <x:v>6.950412371134018</x:v>
+      </x:c>
+      <x:c r="E290" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F290" s="11" t="n">
+        <x:f>SQRT((C290-C289)^2+(D290-D289)^2+(E290-E289)^2)</x:f>
+        <x:v>3.697957107375376</x:v>
+      </x:c>
+      <x:c r="G290" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291" ht="32" customHeight="1">
+      <x:c r="A291" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
+      </x:c>
+      <x:c r="B291" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C291" s="11" t="n">
+        <x:v>37.615</x:v>
+      </x:c>
+      <x:c r="D291" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E291" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F291" s="11" t="n">
+        <x:f>SQRT((C291-C290)^2+(D291-D290)^2+(E291-E290)^2)</x:f>
+        <x:v>0.12010804821421713</x:v>
+      </x:c>
+      <x:c r="G291" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292" ht="32" customHeight="1">
+      <x:c r="A292" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
+      </x:c>
+      <x:c r="B292" s="8" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C292" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D292" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E292" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F292" s="11" t="n">
+        <x:f>SQRT((C292-C291)^2+(D292-D291)^2+(E292-E291)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G292" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293" ht="32" customHeight="1">
+      <x:c r="A293" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
+      </x:c>
+      <x:c r="B293" s="8" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C293" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D293" s="11" t="n">
+        <x:v>6.0360000000000005</x:v>
+      </x:c>
+      <x:c r="E293" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F293" s="11" t="n">
+        <x:f>SQRT((C293-C292)^2+(D293-D292)^2+(E293-E292)^2)</x:f>
+        <x:v>1.0039999999999996</x:v>
+      </x:c>
+      <x:c r="G293" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294" ht="32" customHeight="1">
+      <x:c r="A294" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
+      </x:c>
+      <x:c r="B294" s="8" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C294" s="11" t="n">
+        <x:v>5.48</x:v>
+      </x:c>
+      <x:c r="D294" s="11" t="n">
+        <x:v>6.0360000000000005</x:v>
+      </x:c>
+      <x:c r="E294" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F294" s="11" t="n">
+        <x:f>SQRT((C294-C293)^2+(D294-D293)^2+(E294-E293)^2)</x:f>
+        <x:v>31.495</x:v>
+      </x:c>
+      <x:c r="G294" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295" ht="32" customHeight="1">
+      <x:c r="A295" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+      </x:c>
+      <x:c r="B295" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C281" s="11" t="n">
-        <x:v>41.45</x:v>
-      </x:c>
-      <x:c r="D281" s="11" t="n">
-        <x:v>8.565264175257724</x:v>
-      </x:c>
-      <x:c r="E281" s="11" t="n">
+      <x:c r="C295" s="11" t="n">
+        <x:v>5.48</x:v>
+      </x:c>
+      <x:c r="D295" s="11" t="n">
+        <x:v>6.0360000000000005</x:v>
+      </x:c>
+      <x:c r="E295" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
-      <x:c r="F281" s="11" t="n">
+      <x:c r="F295" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G281" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="282" ht="32" customHeight="1">
-      <x:c r="A282" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
-      </x:c>
-      <x:c r="B282" s="8" t="n">
+      <x:c r="G295" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296" ht="32" customHeight="1">
+      <x:c r="A296" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+      </x:c>
+      <x:c r="B296" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C282" s="11" t="n">
-        <x:v>41.45</x:v>
-      </x:c>
-      <x:c r="D282" s="11" t="n">
-        <x:v>8.565264175257731</x:v>
-      </x:c>
-      <x:c r="E282" s="11" t="n">
-        <x:v>-13.249</x:v>
-      </x:c>
-      <x:c r="F282" s="11" t="n">
-        <x:f>SQRT((C282-C281)^2+(D282-D281)^2+(E282-E281)^2)</x:f>
-        <x:v>5.889</x:v>
-      </x:c>
-      <x:c r="G282" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="283" ht="32" customHeight="1">
-      <x:c r="A283" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
-      </x:c>
-      <x:c r="B283" s="8" t="n">
+      <x:c r="C296" s="11" t="n">
+        <x:v>5.48</x:v>
+      </x:c>
+      <x:c r="D296" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E296" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F296" s="11" t="n">
+        <x:f>SQRT((C296-C295)^2+(D296-D295)^2+(E296-E295)^2)</x:f>
+        <x:v>1.0039999999999996</x:v>
+      </x:c>
+      <x:c r="G296" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297" ht="32" customHeight="1">
+      <x:c r="A297" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+      </x:c>
+      <x:c r="B297" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C283" s="11" t="n">
-        <x:v>41.45</x:v>
-      </x:c>
-      <x:c r="D283" s="11" t="n">
-        <x:v>7.6</x:v>
-      </x:c>
-      <x:c r="E283" s="11" t="n">
-        <x:v>-13.249</x:v>
-      </x:c>
-      <x:c r="F283" s="11" t="n">
-        <x:f>SQRT((C283-C282)^2+(D283-D282)^2+(E283-E282)^2)</x:f>
-        <x:v>0.9652641752577313</x:v>
-      </x:c>
-      <x:c r="G283" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="284" ht="32" customHeight="1">
-      <x:c r="A284" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
-      </x:c>
-      <x:c r="B284" s="8" t="n">
+      <x:c r="C297" s="11" t="n">
+        <x:v>5.32</x:v>
+      </x:c>
+      <x:c r="D297" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E297" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F297" s="11" t="n">
+        <x:f>SQRT((C297-C296)^2+(D297-D296)^2+(E297-E296)^2)</x:f>
+        <x:v>0.16000000000000014</x:v>
+      </x:c>
+      <x:c r="G297" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298" ht="32" customHeight="1">
+      <x:c r="A298" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+      </x:c>
+      <x:c r="B298" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C284" s="11" t="n">
-        <x:v>41.45</x:v>
-      </x:c>
-      <x:c r="D284" s="11" t="n">
-        <x:v>7.6</x:v>
-      </x:c>
-      <x:c r="E284" s="11" t="n">
-        <x:v>-13.13</x:v>
-      </x:c>
-      <x:c r="F284" s="11" t="n">
-        <x:f>SQRT((C284-C283)^2+(D284-D283)^2+(E284-E283)^2)</x:f>
-        <x:v>0.11899999999999977</x:v>
-      </x:c>
-      <x:c r="G284" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="285" ht="32" customHeight="1">
-      <x:c r="A285" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
-      </x:c>
-      <x:c r="B285" s="8" t="n">
+      <x:c r="C298" s="11" t="n">
+        <x:v>5.32</x:v>
+      </x:c>
+      <x:c r="D298" s="11" t="n">
+        <x:v>10.64004347826087</x:v>
+      </x:c>
+      <x:c r="E298" s="11" t="n">
+        <x:v>-2.3999999999999995</x:v>
+      </x:c>
+      <x:c r="F298" s="11" t="n">
+        <x:f>SQRT((C298-C297)^2+(D298-D297)^2+(E298-E297)^2)</x:f>
+        <x:v>6.128777451120952</x:v>
+      </x:c>
+      <x:c r="G298" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299" ht="32" customHeight="1">
+      <x:c r="A299" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+      </x:c>
+      <x:c r="B299" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C299" s="11" t="n">
+        <x:v>5.32</x:v>
+      </x:c>
+      <x:c r="D299" s="11" t="n">
+        <x:v>9.4</x:v>
+      </x:c>
+      <x:c r="E299" s="11" t="n">
+        <x:v>-2.4</x:v>
+      </x:c>
+      <x:c r="F299" s="11" t="n">
+        <x:f>SQRT((C299-C298)^2+(D299-D298)^2+(E299-E298)^2)</x:f>
+        <x:v>1.2400434782608691</x:v>
+      </x:c>
+      <x:c r="G299" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300" ht="32" customHeight="1">
+      <x:c r="A300" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F252</x:v>
+      </x:c>
+      <x:c r="B300" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C300" s="11" t="n">
+        <x:v>5.48</x:v>
+      </x:c>
+      <x:c r="D300" s="11" t="n">
+        <x:v>9.4</x:v>
+      </x:c>
+      <x:c r="E300" s="11" t="n">
+        <x:v>-2.4</x:v>
+      </x:c>
+      <x:c r="F300" s="11" t="n">
+        <x:f>SQRT((C300-C299)^2+(D300-D299)^2+(E300-E299)^2)</x:f>
+        <x:v>0.16000000000000014</x:v>
+      </x:c>
+      <x:c r="G300" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301" ht="32" customHeight="1">
+      <x:c r="A301" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
+      </x:c>
+      <x:c r="B301" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C285" s="11" t="n">
-        <x:v>53.016</x:v>
-      </x:c>
-      <x:c r="D285" s="11" t="n">
+      <x:c r="C301" s="11" t="n">
+        <x:v>5.48</x:v>
+      </x:c>
+      <x:c r="D301" s="11" t="n">
         <x:v>6.0360000000000005</x:v>
       </x:c>
-      <x:c r="E285" s="11" t="n">
+      <x:c r="E301" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
-      <x:c r="F285" s="11" t="n">
+      <x:c r="F301" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G285" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="286" ht="32" customHeight="1">
-      <x:c r="A286" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
-      </x:c>
-      <x:c r="B286" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C286" s="11" t="n">
-        <x:v>53.016</x:v>
-      </x:c>
-      <x:c r="D286" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
-      </x:c>
-      <x:c r="E286" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F286" s="11" t="n">
-        <x:f>SQRT((C286-C285)^2+(D286-D285)^2+(E286-E285)^2)</x:f>
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="G286" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="287" ht="32" customHeight="1">
-      <x:c r="A287" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
-      </x:c>
-      <x:c r="B287" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C287" s="11" t="n">
-        <x:v>53.016</x:v>
-      </x:c>
-      <x:c r="D287" s="11" t="n">
-        <x:v>3.3</x:v>
-      </x:c>
-      <x:c r="E287" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F287" s="11" t="n">
-        <x:f>SQRT((C287-C286)^2+(D287-D286)^2+(E287-E286)^2)</x:f>
-        <x:v>2.7360000000000007</x:v>
-      </x:c>
-      <x:c r="G287" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="288" ht="32" customHeight="1">
-      <x:c r="A288" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
-      </x:c>
-      <x:c r="B288" s="8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C288" s="11" t="n">
-        <x:v>53.12</x:v>
-      </x:c>
-      <x:c r="D288" s="11" t="n">
-        <x:v>3.3</x:v>
-      </x:c>
-      <x:c r="E288" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F288" s="11" t="n">
-        <x:f>SQRT((C288-C287)^2+(D288-D287)^2+(E288-E287)^2)</x:f>
-        <x:v>0.1039999999999992</x:v>
-      </x:c>
-      <x:c r="G288" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="289" ht="32" customHeight="1">
-      <x:c r="A289" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
-      </x:c>
-      <x:c r="B289" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C289" s="11" t="n">
-        <x:v>48.895</x:v>
-      </x:c>
-      <x:c r="D289" s="11" t="n">
-        <x:v>1.95</x:v>
-      </x:c>
-      <x:c r="E289" s="11" t="n">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="F289" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G289" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="290" ht="32" customHeight="1">
-      <x:c r="A290" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
-      </x:c>
-      <x:c r="B290" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C290" s="11" t="n">
-        <x:v>48.735</x:v>
-      </x:c>
-      <x:c r="D290" s="11" t="n">
-        <x:v>1.95</x:v>
-      </x:c>
-      <x:c r="E290" s="11" t="n">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="F290" s="11" t="n">
-        <x:f>SQRT((C290-C289)^2+(D290-D289)^2+(E290-E289)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
-      </x:c>
-      <x:c r="G290" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="291" ht="32" customHeight="1">
-      <x:c r="A291" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
-      </x:c>
-      <x:c r="B291" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C291" s="11" t="n">
-        <x:v>48.735</x:v>
-      </x:c>
-      <x:c r="D291" s="11" t="n">
-        <x:v>1.95</x:v>
-      </x:c>
-      <x:c r="E291" s="11" t="n">
-        <x:v>-2.24</x:v>
-      </x:c>
-      <x:c r="F291" s="11" t="n">
-        <x:f>SQRT((C291-C290)^2+(D291-D290)^2+(E291-E290)^2)</x:f>
-        <x:v>2.64</x:v>
-      </x:c>
-      <x:c r="G291" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="292" ht="32" customHeight="1">
-      <x:c r="A292" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
-      </x:c>
-      <x:c r="B292" s="8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C292" s="11" t="n">
-        <x:v>48.735</x:v>
-      </x:c>
-      <x:c r="D292" s="11" t="n">
-        <x:v>4.33</x:v>
-      </x:c>
-      <x:c r="E292" s="11" t="n">
-        <x:v>-2.24</x:v>
-      </x:c>
-      <x:c r="F292" s="11" t="n">
-        <x:f>SQRT((C292-C291)^2+(D292-D291)^2+(E292-E291)^2)</x:f>
-        <x:v>2.38</x:v>
-      </x:c>
-      <x:c r="G292" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="293" ht="32" customHeight="1">
-      <x:c r="A293" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
-      </x:c>
-      <x:c r="B293" s="8" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C293" s="11" t="n">
-        <x:v>48.735</x:v>
-      </x:c>
-      <x:c r="D293" s="11" t="n">
-        <x:v>4.33</x:v>
-      </x:c>
-      <x:c r="E293" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F293" s="11" t="n">
-        <x:f>SQRT((C293-C292)^2+(D293-D292)^2+(E293-E292)^2)</x:f>
-        <x:v>1.0599999999999996</x:v>
-      </x:c>
-      <x:c r="G293" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="294" ht="32" customHeight="1">
-      <x:c r="A294" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
-      </x:c>
-      <x:c r="B294" s="8" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C294" s="11" t="n">
-        <x:v>53.016</x:v>
-      </x:c>
-      <x:c r="D294" s="11" t="n">
-        <x:v>4.33</x:v>
-      </x:c>
-      <x:c r="E294" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F294" s="11" t="n">
-        <x:f>SQRT((C294-C293)^2+(D294-D293)^2+(E294-E293)^2)</x:f>
-        <x:v>4.280999999999999</x:v>
-      </x:c>
-      <x:c r="G294" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="295" ht="32" customHeight="1">
-      <x:c r="A295" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
-      </x:c>
-      <x:c r="B295" s="8" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C295" s="11" t="n">
-        <x:v>53.016</x:v>
-      </x:c>
-      <x:c r="D295" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
-      </x:c>
-      <x:c r="E295" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F295" s="11" t="n">
-        <x:f>SQRT((C295-C294)^2+(D295-D294)^2+(E295-E294)^2)</x:f>
-        <x:v>1.7060000000000004</x:v>
-      </x:c>
-      <x:c r="G295" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="296" ht="32" customHeight="1">
-      <x:c r="A296" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
-      </x:c>
-      <x:c r="B296" s="8" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C296" s="11" t="n">
-        <x:v>53.016</x:v>
-      </x:c>
-      <x:c r="D296" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
-      </x:c>
-      <x:c r="E296" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F296" s="11" t="n">
-        <x:f>SQRT((C296-C295)^2+(D296-D295)^2+(E296-E295)^2)</x:f>
-        <x:v>10.66</x:v>
-      </x:c>
-      <x:c r="G296" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="297" ht="32" customHeight="1">
-      <x:c r="A297" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
-      </x:c>
-      <x:c r="B297" s="8" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C297" s="11" t="n">
-        <x:v>44.175</x:v>
-      </x:c>
-      <x:c r="D297" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
-      </x:c>
-      <x:c r="E297" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F297" s="11" t="n">
-        <x:f>SQRT((C297-C296)^2+(D297-D296)^2+(E297-E296)^2)</x:f>
-        <x:v>8.841000000000001</x:v>
-      </x:c>
-      <x:c r="G297" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="298" ht="32" customHeight="1">
-      <x:c r="A298" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
-      </x:c>
-      <x:c r="B298" s="8" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C298" s="11" t="n">
-        <x:v>44.175</x:v>
-      </x:c>
-      <x:c r="D298" s="11" t="n">
-        <x:v>7.04</x:v>
-      </x:c>
-      <x:c r="E298" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F298" s="11" t="n">
-        <x:f>SQRT((C298-C297)^2+(D298-D297)^2+(E298-E297)^2)</x:f>
-        <x:v>1.0039999999999996</x:v>
-      </x:c>
-      <x:c r="G298" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="299" ht="32" customHeight="1">
-      <x:c r="A299" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
-      </x:c>
-      <x:c r="B299" s="8" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C299" s="11" t="n">
-        <x:v>43.535</x:v>
-      </x:c>
-      <x:c r="D299" s="11" t="n">
-        <x:v>7.04</x:v>
-      </x:c>
-      <x:c r="E299" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F299" s="11" t="n">
-        <x:f>SQRT((C299-C298)^2+(D299-D298)^2+(E299-E298)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
-      </x:c>
-      <x:c r="G299" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="300" ht="32" customHeight="1">
-      <x:c r="A300" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
-      </x:c>
-      <x:c r="B300" s="8" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C300" s="11" t="n">
-        <x:v>43.455</x:v>
-      </x:c>
-      <x:c r="D300" s="11" t="n">
-        <x:v>6.950412371134024</x:v>
-      </x:c>
-      <x:c r="E300" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F300" s="11" t="n">
-        <x:f>SQRT((C300-C299)^2+(D300-D299)^2+(E300-E299)^2)</x:f>
-        <x:v>0.12010804821421249</x:v>
-      </x:c>
-      <x:c r="G300" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="301" ht="32" customHeight="1">
-      <x:c r="A301" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
-      </x:c>
-      <x:c r="B301" s="8" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C301" s="11" t="n">
-        <x:v>40.574999999999996</x:v>
-      </x:c>
-      <x:c r="D301" s="11" t="n">
-        <x:v>9.269999999999994</x:v>
-      </x:c>
-      <x:c r="E301" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F301" s="11" t="n">
-        <x:f>SQRT((C301-C300)^2+(D301-D300)^2+(E301-E300)^2)</x:f>
-        <x:v>3.6979571073753776</x:v>
-      </x:c>
       <x:c r="G301" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="302" ht="32" customHeight="1">
       <x:c r="A302" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
       </x:c>
       <x:c r="B302" s="8" t="n">
-        <x:v>14</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C302" s="11" t="n">
-        <x:v>37.695</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D302" s="11" t="n">
-        <x:v>6.950412371134018</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E302" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F302" s="11" t="n">
         <x:f>SQRT((C302-C301)^2+(D302-D301)^2+(E302-E301)^2)</x:f>
-        <x:v>3.697957107375376</x:v>
+        <x:v>1.0039999999999996</x:v>
       </x:c>
       <x:c r="G302" s="8" t="str">
         <x:v>Current</x:v>
@@ -14380,23 +15690,23 @@
     </x:row>
     <x:row r="303" ht="32" customHeight="1">
       <x:c r="A303" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
       </x:c>
       <x:c r="B303" s="8" t="n">
-        <x:v>15</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C303" s="11" t="n">
-        <x:v>37.615</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D303" s="11" t="n">
         <x:v>7.04</x:v>
       </x:c>
       <x:c r="E303" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F303" s="11" t="n">
         <x:f>SQRT((C303-C302)^2+(D303-D302)^2+(E303-E302)^2)</x:f>
-        <x:v>0.12010804821421713</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G303" s="8" t="str">
         <x:v>Current</x:v>
@@ -14404,23 +15714,23 @@
     </x:row>
     <x:row r="304" ht="32" customHeight="1">
       <x:c r="A304" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
       </x:c>
       <x:c r="B304" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C304" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D304" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>11.801347826086957</x:v>
       </x:c>
       <x:c r="E304" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-0.7999999999999998</x:v>
       </x:c>
       <x:c r="F304" s="11" t="n">
         <x:f>SQRT((C304-C303)^2+(D304-D303)^2+(E304-E303)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>8.105802435353516</x:v>
       </x:c>
       <x:c r="G304" s="8" t="str">
         <x:v>Current</x:v>
@@ -14428,23 +15738,23 @@
     </x:row>
     <x:row r="305" ht="32" customHeight="1">
       <x:c r="A305" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
       </x:c>
       <x:c r="B305" s="8" t="n">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C305" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D305" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E305" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="F305" s="11" t="n">
         <x:f>SQRT((C305-C304)^2+(D305-D304)^2+(E305-E304)^2)</x:f>
-        <x:v>1.0039999999999996</x:v>
+        <x:v>2.4013478260869565</x:v>
       </x:c>
       <x:c r="G305" s="8" t="str">
         <x:v>Current</x:v>
@@ -14452,23 +15762,23 @@
     </x:row>
     <x:row r="306" ht="32" customHeight="1">
       <x:c r="A306" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F253</x:v>
       </x:c>
       <x:c r="B306" s="8" t="n">
-        <x:v>18</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C306" s="11" t="n">
         <x:v>5.48</x:v>
       </x:c>
       <x:c r="D306" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E306" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="F306" s="11" t="n">
         <x:f>SQRT((C306-C305)^2+(D306-D305)^2+(E306-E305)^2)</x:f>
-        <x:v>31.495</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G306" s="8" t="str">
         <x:v>Current</x:v>
@@ -14476,19 +15786,19 @@
     </x:row>
     <x:row r="307" ht="32" customHeight="1">
       <x:c r="A307" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
       </x:c>
       <x:c r="B307" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C307" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D307" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>8.565264175257731</x:v>
       </x:c>
       <x:c r="E307" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F307" s="11" t="n">
         <x:f>0</x:f>
@@ -14500,23 +15810,23 @@
     </x:row>
     <x:row r="308" ht="32" customHeight="1">
       <x:c r="A308" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
       </x:c>
       <x:c r="B308" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C308" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D308" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>8.565264175257731</x:v>
       </x:c>
       <x:c r="E308" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-13.249</x:v>
       </x:c>
       <x:c r="F308" s="11" t="n">
         <x:f>SQRT((C308-C307)^2+(D308-D307)^2+(E308-E307)^2)</x:f>
-        <x:v>1.0039999999999996</x:v>
+        <x:v>5.889</x:v>
       </x:c>
       <x:c r="G308" s="8" t="str">
         <x:v>Current</x:v>
@@ -14524,23 +15834,23 @@
     </x:row>
     <x:row r="309" ht="32" customHeight="1">
       <x:c r="A309" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
       </x:c>
       <x:c r="B309" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C309" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D309" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="E309" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-13.249</x:v>
       </x:c>
       <x:c r="F309" s="11" t="n">
         <x:f>SQRT((C309-C308)^2+(D309-D308)^2+(E309-E308)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
+        <x:v>0.9652641752577313</x:v>
       </x:c>
       <x:c r="G309" s="8" t="str">
         <x:v>Current</x:v>
@@ -14548,23 +15858,23 @@
     </x:row>
     <x:row r="310" ht="32" customHeight="1">
       <x:c r="A310" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
       </x:c>
       <x:c r="B310" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C310" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D310" s="11" t="n">
-        <x:v>11.801347826086957</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="E310" s="11" t="n">
-        <x:v>0.7999999999999998</x:v>
+        <x:v>-13.13</x:v>
       </x:c>
       <x:c r="F310" s="11" t="n">
         <x:f>SQRT((C310-C309)^2+(D310-D309)^2+(E310-E309)^2)</x:f>
-        <x:v>8.105802435353516</x:v>
+        <x:v>0.11899999999999977</x:v>
       </x:c>
       <x:c r="G310" s="8" t="str">
         <x:v>Current</x:v>
@@ -14572,23 +15882,23 @@
     </x:row>
     <x:row r="311" ht="32" customHeight="1">
       <x:c r="A311" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
       </x:c>
       <x:c r="B311" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C311" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>41.45</x:v>
       </x:c>
       <x:c r="D311" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>8.565264175257724</x:v>
       </x:c>
       <x:c r="E311" s="11" t="n">
-        <x:v>0.8</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F311" s="11" t="n">
-        <x:f>SQRT((C311-C310)^2+(D311-D310)^2+(E311-E310)^2)</x:f>
-        <x:v>2.4013478260869565</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G311" s="8" t="str">
         <x:v>Current</x:v>
@@ -14596,23 +15906,23 @@
     </x:row>
     <x:row r="312" ht="32" customHeight="1">
       <x:c r="A312" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
       </x:c>
       <x:c r="B312" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C312" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>41.45</x:v>
       </x:c>
       <x:c r="D312" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>8.565264175257731</x:v>
       </x:c>
       <x:c r="E312" s="11" t="n">
-        <x:v>0.8</x:v>
+        <x:v>-13.249</x:v>
       </x:c>
       <x:c r="F312" s="11" t="n">
         <x:f>SQRT((C312-C311)^2+(D312-D311)^2+(E312-E311)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
+        <x:v>5.889</x:v>
       </x:c>
       <x:c r="G312" s="8" t="str">
         <x:v>Current</x:v>
@@ -14620,95 +15930,95 @@
     </x:row>
     <x:row r="313" ht="32" customHeight="1">
       <x:c r="A313" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
       </x:c>
       <x:c r="B313" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C313" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D313" s="11" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="E313" s="11" t="n">
+        <x:v>-13.249</x:v>
+      </x:c>
+      <x:c r="F313" s="11" t="n">
+        <x:f>SQRT((C313-C312)^2+(D313-D312)^2+(E313-E312)^2)</x:f>
+        <x:v>0.9652641752577313</x:v>
+      </x:c>
+      <x:c r="G313" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314" ht="32" customHeight="1">
+      <x:c r="A314" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
+      </x:c>
+      <x:c r="B314" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C314" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D314" s="11" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="E314" s="11" t="n">
+        <x:v>-13.13</x:v>
+      </x:c>
+      <x:c r="F314" s="11" t="n">
+        <x:f>SQRT((C314-C313)^2+(D314-D313)^2+(E314-E313)^2)</x:f>
+        <x:v>0.11899999999999977</x:v>
+      </x:c>
+      <x:c r="G314" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315" ht="32" customHeight="1">
+      <x:c r="A315" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
+      </x:c>
+      <x:c r="B315" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C313" s="11" t="n">
-        <x:v>5.48</x:v>
-      </x:c>
-      <x:c r="D313" s="11" t="n">
+      <x:c r="C315" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D315" s="11" t="n">
         <x:v>6.0360000000000005</x:v>
       </x:c>
-      <x:c r="E313" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F313" s="11" t="n">
+      <x:c r="E315" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F315" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G313" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="314" ht="32" customHeight="1">
-      <x:c r="A314" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
-      </x:c>
-      <x:c r="B314" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C314" s="11" t="n">
-        <x:v>5.48</x:v>
-      </x:c>
-      <x:c r="D314" s="11" t="n">
-        <x:v>7.04</x:v>
-      </x:c>
-      <x:c r="E314" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F314" s="11" t="n">
-        <x:f>SQRT((C314-C313)^2+(D314-D313)^2+(E314-E313)^2)</x:f>
-        <x:v>1.0039999999999996</x:v>
-      </x:c>
-      <x:c r="G314" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="315" ht="32" customHeight="1">
-      <x:c r="A315" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
-      </x:c>
-      <x:c r="B315" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C315" s="11" t="n">
-        <x:v>5.32</x:v>
-      </x:c>
-      <x:c r="D315" s="11" t="n">
-        <x:v>7.04</x:v>
-      </x:c>
-      <x:c r="E315" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F315" s="11" t="n">
-        <x:f>SQRT((C315-C314)^2+(D315-D314)^2+(E315-E314)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
-      </x:c>
       <x:c r="G315" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="316" ht="32" customHeight="1">
       <x:c r="A316" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
       </x:c>
       <x:c r="B316" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C316" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D316" s="11" t="n">
-        <x:v>10.64004347826087</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E316" s="11" t="n">
-        <x:v>2.3999999999999995</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F316" s="11" t="n">
         <x:f>SQRT((C316-C315)^2+(D316-D315)^2+(E316-E315)^2)</x:f>
-        <x:v>6.128777451120952</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="G316" s="8" t="str">
         <x:v>Current</x:v>
@@ -14716,23 +16026,23 @@
     </x:row>
     <x:row r="317" ht="32" customHeight="1">
       <x:c r="A317" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
       </x:c>
       <x:c r="B317" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C317" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D317" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="E317" s="11" t="n">
-        <x:v>2.4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F317" s="11" t="n">
         <x:f>SQRT((C317-C316)^2+(D317-D316)^2+(E317-E316)^2)</x:f>
-        <x:v>1.2400434782608691</x:v>
+        <x:v>2.7360000000000007</x:v>
       </x:c>
       <x:c r="G317" s="8" t="str">
         <x:v>Current</x:v>
@@ -14740,23 +16050,23 @@
     </x:row>
     <x:row r="318" ht="32" customHeight="1">
       <x:c r="A318" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
       </x:c>
       <x:c r="B318" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C318" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>53.12</x:v>
       </x:c>
       <x:c r="D318" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="E318" s="11" t="n">
-        <x:v>2.4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F318" s="11" t="n">
         <x:f>SQRT((C318-C317)^2+(D318-D317)^2+(E318-E317)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
+        <x:v>0.1039999999999992</x:v>
       </x:c>
       <x:c r="G318" s="8" t="str">
         <x:v>Current</x:v>
@@ -14764,19 +16074,19 @@
     </x:row>
     <x:row r="319" ht="32" customHeight="1">
       <x:c r="A319" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F258</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B319" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C319" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D319" s="11" t="n">
-        <x:v>8.565264175257731</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E319" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F319" s="11" t="n">
         <x:f>0</x:f>
@@ -14788,23 +16098,23 @@
     </x:row>
     <x:row r="320" ht="32" customHeight="1">
       <x:c r="A320" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F258</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B320" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C320" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D320" s="11" t="n">
-        <x:v>8.565264175257731</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E320" s="11" t="n">
-        <x:v>13.249</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F320" s="11" t="n">
         <x:f>SQRT((C320-C319)^2+(D320-D319)^2+(E320-E319)^2)</x:f>
-        <x:v>5.889</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G320" s="8" t="str">
         <x:v>Current</x:v>
@@ -14812,23 +16122,23 @@
     </x:row>
     <x:row r="321" ht="32" customHeight="1">
       <x:c r="A321" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F258</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B321" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C321" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D321" s="11" t="n">
-        <x:v>7.6</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E321" s="11" t="n">
-        <x:v>13.249</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F321" s="11" t="n">
         <x:f>SQRT((C321-C320)^2+(D321-D320)^2+(E321-E320)^2)</x:f>
-        <x:v>0.9652641752577313</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="G321" s="8" t="str">
         <x:v>Current</x:v>
@@ -14836,23 +16146,23 @@
     </x:row>
     <x:row r="322" ht="32" customHeight="1">
       <x:c r="A322" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F258</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B322" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C322" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D322" s="11" t="n">
-        <x:v>7.6</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E322" s="11" t="n">
-        <x:v>13.13</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F322" s="11" t="n">
         <x:f>SQRT((C322-C321)^2+(D322-D321)^2+(E322-E321)^2)</x:f>
-        <x:v>0.11899999999999977</x:v>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="G322" s="8" t="str">
         <x:v>Current</x:v>
@@ -14860,640 +16170,640 @@
     </x:row>
     <x:row r="323" ht="32" customHeight="1">
       <x:c r="A323" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F259</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B323" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C323" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D323" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E323" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F323" s="11" t="n">
+        <x:f>SQRT((C323-C322)^2+(D323-D322)^2+(E323-E322)^2)</x:f>
+        <x:v>1.0599999999999996</x:v>
+      </x:c>
+      <x:c r="G323" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324" ht="32" customHeight="1">
+      <x:c r="A324" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+      <x:c r="B324" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C324" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D324" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E324" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F324" s="11" t="n">
+        <x:f>SQRT((C324-C323)^2+(D324-D323)^2+(E324-E323)^2)</x:f>
+        <x:v>4.280999999999999</x:v>
+      </x:c>
+      <x:c r="G324" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325" ht="32" customHeight="1">
+      <x:c r="A325" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+      <x:c r="B325" s="8" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C325" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D325" s="11" t="n">
+        <x:v>6.0360000000000005</x:v>
+      </x:c>
+      <x:c r="E325" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F325" s="11" t="n">
+        <x:f>SQRT((C325-C324)^2+(D325-D324)^2+(E325-E324)^2)</x:f>
+        <x:v>1.7060000000000004</x:v>
+      </x:c>
+      <x:c r="G325" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326" ht="32" customHeight="1">
+      <x:c r="A326" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+      <x:c r="B326" s="8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C326" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D326" s="11" t="n">
+        <x:v>6.0360000000000005</x:v>
+      </x:c>
+      <x:c r="E326" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F326" s="11" t="n">
+        <x:f>SQRT((C326-C325)^2+(D326-D325)^2+(E326-E325)^2)</x:f>
+        <x:v>10.66</x:v>
+      </x:c>
+      <x:c r="G326" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327" ht="32" customHeight="1">
+      <x:c r="A327" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+      <x:c r="B327" s="8" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C327" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D327" s="11" t="n">
+        <x:v>6.0360000000000005</x:v>
+      </x:c>
+      <x:c r="E327" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F327" s="11" t="n">
+        <x:f>SQRT((C327-C326)^2+(D327-D326)^2+(E327-E326)^2)</x:f>
+        <x:v>8.841000000000001</x:v>
+      </x:c>
+      <x:c r="G327" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328" ht="32" customHeight="1">
+      <x:c r="A328" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+      <x:c r="B328" s="8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C328" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D328" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E328" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F328" s="11" t="n">
+        <x:f>SQRT((C328-C327)^2+(D328-D327)^2+(E328-E327)^2)</x:f>
+        <x:v>1.0039999999999996</x:v>
+      </x:c>
+      <x:c r="G328" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329" ht="32" customHeight="1">
+      <x:c r="A329" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+      <x:c r="B329" s="8" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C329" s="11" t="n">
+        <x:v>43.535</x:v>
+      </x:c>
+      <x:c r="D329" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E329" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F329" s="11" t="n">
+        <x:f>SQRT((C329-C328)^2+(D329-D328)^2+(E329-E328)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G329" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330" ht="32" customHeight="1">
+      <x:c r="A330" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+      <x:c r="B330" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C330" s="11" t="n">
+        <x:v>43.455</x:v>
+      </x:c>
+      <x:c r="D330" s="11" t="n">
+        <x:v>6.950412371134024</x:v>
+      </x:c>
+      <x:c r="E330" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F330" s="11" t="n">
+        <x:f>SQRT((C330-C329)^2+(D330-D329)^2+(E330-E329)^2)</x:f>
+        <x:v>0.12010804821421249</x:v>
+      </x:c>
+      <x:c r="G330" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331" ht="32" customHeight="1">
+      <x:c r="A331" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+      <x:c r="B331" s="8" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C331" s="11" t="n">
+        <x:v>40.574999999999996</x:v>
+      </x:c>
+      <x:c r="D331" s="11" t="n">
+        <x:v>9.269999999999994</x:v>
+      </x:c>
+      <x:c r="E331" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F331" s="11" t="n">
+        <x:f>SQRT((C331-C330)^2+(D331-D330)^2+(E331-E330)^2)</x:f>
+        <x:v>3.6979571073753776</x:v>
+      </x:c>
+      <x:c r="G331" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332" ht="32" customHeight="1">
+      <x:c r="A332" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+      <x:c r="B332" s="8" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C332" s="11" t="n">
+        <x:v>37.695</x:v>
+      </x:c>
+      <x:c r="D332" s="11" t="n">
+        <x:v>6.950412371134018</x:v>
+      </x:c>
+      <x:c r="E332" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F332" s="11" t="n">
+        <x:f>SQRT((C332-C331)^2+(D332-D331)^2+(E332-E331)^2)</x:f>
+        <x:v>3.697957107375376</x:v>
+      </x:c>
+      <x:c r="G332" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333" ht="32" customHeight="1">
+      <x:c r="A333" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+      <x:c r="B333" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C333" s="11" t="n">
+        <x:v>37.615</x:v>
+      </x:c>
+      <x:c r="D333" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E333" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F333" s="11" t="n">
+        <x:f>SQRT((C333-C332)^2+(D333-D332)^2+(E333-E332)^2)</x:f>
+        <x:v>0.12010804821421713</x:v>
+      </x:c>
+      <x:c r="G333" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334" ht="32" customHeight="1">
+      <x:c r="A334" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+      <x:c r="B334" s="8" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C334" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D334" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E334" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F334" s="11" t="n">
+        <x:f>SQRT((C334-C333)^2+(D334-D333)^2+(E334-E333)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G334" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335" ht="32" customHeight="1">
+      <x:c r="A335" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+      <x:c r="B335" s="8" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C335" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D335" s="11" t="n">
+        <x:v>6.0360000000000005</x:v>
+      </x:c>
+      <x:c r="E335" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F335" s="11" t="n">
+        <x:f>SQRT((C335-C334)^2+(D335-D334)^2+(E335-E334)^2)</x:f>
+        <x:v>1.0039999999999996</x:v>
+      </x:c>
+      <x:c r="G335" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336" ht="32" customHeight="1">
+      <x:c r="A336" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+      <x:c r="B336" s="8" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C336" s="11" t="n">
+        <x:v>5.48</x:v>
+      </x:c>
+      <x:c r="D336" s="11" t="n">
+        <x:v>6.0360000000000005</x:v>
+      </x:c>
+      <x:c r="E336" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F336" s="11" t="n">
+        <x:f>SQRT((C336-C335)^2+(D336-D335)^2+(E336-E335)^2)</x:f>
+        <x:v>31.495</x:v>
+      </x:c>
+      <x:c r="G336" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337" ht="32" customHeight="1">
+      <x:c r="A337" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+      </x:c>
+      <x:c r="B337" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C323" s="11" t="n">
-        <x:v>41.45</x:v>
-      </x:c>
-      <x:c r="D323" s="11" t="n">
-        <x:v>8.565264175257724</x:v>
-      </x:c>
-      <x:c r="E323" s="11" t="n">
+      <x:c r="C337" s="11" t="n">
+        <x:v>5.48</x:v>
+      </x:c>
+      <x:c r="D337" s="11" t="n">
+        <x:v>6.0360000000000005</x:v>
+      </x:c>
+      <x:c r="E337" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
-      <x:c r="F323" s="11" t="n">
+      <x:c r="F337" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G323" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="324" ht="32" customHeight="1">
-      <x:c r="A324" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F259</x:v>
-      </x:c>
-      <x:c r="B324" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C324" s="11" t="n">
-        <x:v>41.45</x:v>
-      </x:c>
-      <x:c r="D324" s="11" t="n">
-        <x:v>8.565264175257731</x:v>
-      </x:c>
-      <x:c r="E324" s="11" t="n">
-        <x:v>13.249</x:v>
-      </x:c>
-      <x:c r="F324" s="11" t="n">
-        <x:f>SQRT((C324-C323)^2+(D324-D323)^2+(E324-E323)^2)</x:f>
-        <x:v>5.889</x:v>
-      </x:c>
-      <x:c r="G324" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="325" ht="32" customHeight="1">
-      <x:c r="A325" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F259</x:v>
-      </x:c>
-      <x:c r="B325" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C325" s="11" t="n">
-        <x:v>41.45</x:v>
-      </x:c>
-      <x:c r="D325" s="11" t="n">
-        <x:v>7.6</x:v>
-      </x:c>
-      <x:c r="E325" s="11" t="n">
-        <x:v>13.249</x:v>
-      </x:c>
-      <x:c r="F325" s="11" t="n">
-        <x:f>SQRT((C325-C324)^2+(D325-D324)^2+(E325-E324)^2)</x:f>
-        <x:v>0.9652641752577313</x:v>
-      </x:c>
-      <x:c r="G325" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="326" ht="32" customHeight="1">
-      <x:c r="A326" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F259</x:v>
-      </x:c>
-      <x:c r="B326" s="8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C326" s="11" t="n">
-        <x:v>41.45</x:v>
-      </x:c>
-      <x:c r="D326" s="11" t="n">
-        <x:v>7.6</x:v>
-      </x:c>
-      <x:c r="E326" s="11" t="n">
-        <x:v>13.13</x:v>
-      </x:c>
-      <x:c r="F326" s="11" t="n">
-        <x:f>SQRT((C326-C325)^2+(D326-D325)^2+(E326-E325)^2)</x:f>
-        <x:v>0.11899999999999977</x:v>
-      </x:c>
-      <x:c r="G326" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="327" ht="32" customHeight="1">
-      <x:c r="A327" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
-      </x:c>
-      <x:c r="B327" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C327" s="11" t="n">
-        <x:v>41.2</x:v>
-      </x:c>
-      <x:c r="D327" s="11" t="n">
-        <x:v>8.766617268041228</x:v>
-      </x:c>
-      <x:c r="E327" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F327" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G327" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="328" ht="32" customHeight="1">
-      <x:c r="A328" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
-      </x:c>
-      <x:c r="B328" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C328" s="11" t="n">
-        <x:v>41.2</x:v>
-      </x:c>
-      <x:c r="D328" s="11" t="n">
-        <x:v>8.766617268041237</x:v>
-      </x:c>
-      <x:c r="E328" s="11" t="n">
-        <x:v>-13.249</x:v>
-      </x:c>
-      <x:c r="F328" s="11" t="n">
-        <x:f>SQRT((C328-C327)^2+(D328-D327)^2+(E328-E327)^2)</x:f>
-        <x:v>5.889</x:v>
-      </x:c>
-      <x:c r="G328" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="329" ht="32" customHeight="1">
-      <x:c r="A329" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
-      </x:c>
-      <x:c r="B329" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C329" s="11" t="n">
-        <x:v>41.2</x:v>
-      </x:c>
-      <x:c r="D329" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E329" s="11" t="n">
-        <x:v>-13.249</x:v>
-      </x:c>
-      <x:c r="F329" s="11" t="n">
-        <x:f>SQRT((C329-C328)^2+(D329-D328)^2+(E329-E328)^2)</x:f>
-        <x:v>6.066617268041237</x:v>
-      </x:c>
-      <x:c r="G329" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="330" ht="32" customHeight="1">
-      <x:c r="A330" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
-      </x:c>
-      <x:c r="B330" s="8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C330" s="11" t="n">
-        <x:v>41.2</x:v>
-      </x:c>
-      <x:c r="D330" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E330" s="11" t="n">
-        <x:v>-13.06</x:v>
-      </x:c>
-      <x:c r="F330" s="11" t="n">
-        <x:f>SQRT((C330-C329)^2+(D330-D329)^2+(E330-E329)^2)</x:f>
-        <x:v>0.18900000000000006</x:v>
-      </x:c>
-      <x:c r="G330" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="331" ht="32" customHeight="1">
-      <x:c r="A331" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
-      </x:c>
-      <x:c r="B331" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C331" s="11" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D331" s="11" t="n">
-        <x:v>8.122287371134018</x:v>
-      </x:c>
-      <x:c r="E331" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F331" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G331" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="332" ht="32" customHeight="1">
-      <x:c r="A332" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
-      </x:c>
-      <x:c r="B332" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C332" s="11" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D332" s="11" t="n">
-        <x:v>8.122287371134023</x:v>
-      </x:c>
-      <x:c r="E332" s="11" t="n">
-        <x:v>-13.249</x:v>
-      </x:c>
-      <x:c r="F332" s="11" t="n">
-        <x:f>SQRT((C332-C331)^2+(D332-D331)^2+(E332-E331)^2)</x:f>
-        <x:v>5.889</x:v>
-      </x:c>
-      <x:c r="G332" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="333" ht="32" customHeight="1">
-      <x:c r="A333" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
-      </x:c>
-      <x:c r="B333" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C333" s="11" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D333" s="11" t="n">
-        <x:v>3.5</x:v>
-      </x:c>
-      <x:c r="E333" s="11" t="n">
-        <x:v>-13.249</x:v>
-      </x:c>
-      <x:c r="F333" s="11" t="n">
-        <x:f>SQRT((C333-C332)^2+(D333-D332)^2+(E333-E332)^2)</x:f>
-        <x:v>4.622287371134023</x:v>
-      </x:c>
-      <x:c r="G333" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="334" ht="32" customHeight="1">
-      <x:c r="A334" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
-      </x:c>
-      <x:c r="B334" s="8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C334" s="11" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D334" s="11" t="n">
-        <x:v>3.5</x:v>
-      </x:c>
-      <x:c r="E334" s="11" t="n">
-        <x:v>-13.06</x:v>
-      </x:c>
-      <x:c r="F334" s="11" t="n">
-        <x:f>SQRT((C334-C333)^2+(D334-D333)^2+(E334-E333)^2)</x:f>
-        <x:v>0.18900000000000006</x:v>
-      </x:c>
-      <x:c r="G334" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="335" ht="32" customHeight="1">
-      <x:c r="A335" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
-      </x:c>
-      <x:c r="B335" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C335" s="11" t="n">
-        <x:v>41.2</x:v>
-      </x:c>
-      <x:c r="D335" s="11" t="n">
-        <x:v>8.766617268041228</x:v>
-      </x:c>
-      <x:c r="E335" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F335" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G335" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="336" ht="32" customHeight="1">
-      <x:c r="A336" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
-      </x:c>
-      <x:c r="B336" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C336" s="11" t="n">
-        <x:v>41.2</x:v>
-      </x:c>
-      <x:c r="D336" s="11" t="n">
-        <x:v>8.766617268041237</x:v>
-      </x:c>
-      <x:c r="E336" s="11" t="n">
-        <x:v>13.249</x:v>
-      </x:c>
-      <x:c r="F336" s="11" t="n">
-        <x:f>SQRT((C336-C335)^2+(D336-D335)^2+(E336-E335)^2)</x:f>
-        <x:v>5.889</x:v>
-      </x:c>
-      <x:c r="G336" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="337" ht="32" customHeight="1">
-      <x:c r="A337" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
-      </x:c>
-      <x:c r="B337" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C337" s="11" t="n">
-        <x:v>41.2</x:v>
-      </x:c>
-      <x:c r="D337" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E337" s="11" t="n">
-        <x:v>13.249</x:v>
-      </x:c>
-      <x:c r="F337" s="11" t="n">
-        <x:f>SQRT((C337-C336)^2+(D337-D336)^2+(E337-E336)^2)</x:f>
-        <x:v>6.066617268041237</x:v>
-      </x:c>
       <x:c r="G337" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="338" ht="32" customHeight="1">
       <x:c r="A338" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B338" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C338" s="11" t="n">
-        <x:v>41.2</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D338" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E338" s="11" t="n">
-        <x:v>13.06</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F338" s="11" t="n">
         <x:f>SQRT((C338-C337)^2+(D338-D337)^2+(E338-E337)^2)</x:f>
-        <x:v>0.18900000000000006</x:v>
+        <x:v>1.0039999999999996</x:v>
       </x:c>
       <x:c r="G338" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="339" ht="32" customHeight="1">
       <x:c r="A339" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B339" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C339" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D339" s="11" t="n">
-        <x:v>8.122287371134018</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E339" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F339" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C339-C338)^2+(D339-D338)^2+(E339-E338)^2)</x:f>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G339" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="340" ht="32" customHeight="1">
       <x:c r="A340" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B340" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C340" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D340" s="11" t="n">
-        <x:v>8.122287371134023</x:v>
+        <x:v>11.801347826086957</x:v>
       </x:c>
       <x:c r="E340" s="11" t="n">
-        <x:v>13.249</x:v>
+        <x:v>0.7999999999999998</x:v>
       </x:c>
       <x:c r="F340" s="11" t="n">
         <x:f>SQRT((C340-C339)^2+(D340-D339)^2+(E340-E339)^2)</x:f>
-        <x:v>5.889</x:v>
+        <x:v>8.105802435353516</x:v>
       </x:c>
       <x:c r="G340" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="341" ht="32" customHeight="1">
       <x:c r="A341" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B341" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C341" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D341" s="11" t="n">
-        <x:v>3.5</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E341" s="11" t="n">
-        <x:v>13.249</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="F341" s="11" t="n">
         <x:f>SQRT((C341-C340)^2+(D341-D340)^2+(E341-E340)^2)</x:f>
-        <x:v>4.622287371134023</x:v>
+        <x:v>2.4013478260869565</x:v>
       </x:c>
       <x:c r="G341" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="342" ht="32" customHeight="1">
       <x:c r="A342" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B342" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C342" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D342" s="11" t="n">
-        <x:v>3.5</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E342" s="11" t="n">
-        <x:v>13.06</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="F342" s="11" t="n">
         <x:f>SQRT((C342-C341)^2+(D342-D341)^2+(E342-E341)^2)</x:f>
-        <x:v>0.18900000000000006</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G342" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="343" ht="32" customHeight="1">
       <x:c r="A343" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B343" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C343" s="11" t="n">
-        <x:v>39.3</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D343" s="11" t="n">
-        <x:v>8.24309922680412</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E343" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F343" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G343" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="344" ht="32" customHeight="1">
       <x:c r="A344" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B344" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C344" s="11" t="n">
-        <x:v>39.3</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D344" s="11" t="n">
-        <x:v>8.24309922680412</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E344" s="11" t="n">
-        <x:v>-10.15</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F344" s="11" t="n">
         <x:f>SQRT((C344-C343)^2+(D344-D343)^2+(E344-E343)^2)</x:f>
-        <x:v>2.79</x:v>
+        <x:v>1.0039999999999996</x:v>
       </x:c>
       <x:c r="G344" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="345" ht="32" customHeight="1">
       <x:c r="A345" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B345" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C345" s="11" t="n">
-        <x:v>39.3</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D345" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E345" s="11" t="n">
-        <x:v>-10.15</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F345" s="11" t="n">
         <x:f>SQRT((C345-C344)^2+(D345-D344)^2+(E345-E344)^2)</x:f>
-        <x:v>4.94309922680412</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G345" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="346" ht="32" customHeight="1">
       <x:c r="A346" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B346" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C346" s="11" t="n">
-        <x:v>41.85</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D346" s="11" t="n">
-        <x:v>8.243099226804118</x:v>
+        <x:v>10.64004347826087</x:v>
       </x:c>
       <x:c r="E346" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>2.3999999999999995</x:v>
       </x:c>
       <x:c r="F346" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C346-C345)^2+(D346-D345)^2+(E346-E345)^2)</x:f>
+        <x:v>6.128777451120952</x:v>
       </x:c>
       <x:c r="G346" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="347" ht="32" customHeight="1">
       <x:c r="A347" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B347" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C347" s="11" t="n">
-        <x:v>41.85</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D347" s="11" t="n">
-        <x:v>8.243099226804125</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E347" s="11" t="n">
-        <x:v>-10.15</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="F347" s="11" t="n">
         <x:f>SQRT((C347-C346)^2+(D347-D346)^2+(E347-E346)^2)</x:f>
-        <x:v>2.79</x:v>
+        <x:v>1.2400434782608691</x:v>
       </x:c>
       <x:c r="G347" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="348" ht="32" customHeight="1">
       <x:c r="A348" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B348" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C348" s="11" t="n">
-        <x:v>41.85</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D348" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E348" s="11" t="n">
-        <x:v>-10.15</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="F348" s="11" t="n">
         <x:f>SQRT((C348-C347)^2+(D348-D347)^2+(E348-E347)^2)</x:f>
-        <x:v>4.943099226804125</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G348" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="349" ht="32" customHeight="1">
       <x:c r="A349" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F242</x:v>
+        <x:v>drop:FC1:V1:fan:1:F258</x:v>
       </x:c>
       <x:c r="B349" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C349" s="11" t="n">
-        <x:v>39.3</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D349" s="11" t="n">
-        <x:v>8.24309922680412</x:v>
+        <x:v>8.565264175257731</x:v>
       </x:c>
       <x:c r="E349" s="11" t="n">
         <x:v>7.36</x:v>
@@ -15503,136 +16813,856 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G349" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="350" ht="32" customHeight="1">
       <x:c r="A350" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F242</x:v>
+        <x:v>drop:FC1:V1:fan:1:F258</x:v>
       </x:c>
       <x:c r="B350" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C350" s="11" t="n">
-        <x:v>39.3</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D350" s="11" t="n">
-        <x:v>8.24309922680412</x:v>
+        <x:v>8.565264175257731</x:v>
       </x:c>
       <x:c r="E350" s="11" t="n">
-        <x:v>10.15</x:v>
+        <x:v>13.249</x:v>
       </x:c>
       <x:c r="F350" s="11" t="n">
         <x:f>SQRT((C350-C349)^2+(D350-D349)^2+(E350-E349)^2)</x:f>
-        <x:v>2.79</x:v>
+        <x:v>5.889</x:v>
       </x:c>
       <x:c r="G350" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="351" ht="32" customHeight="1">
       <x:c r="A351" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F242</x:v>
+        <x:v>drop:FC1:V1:fan:1:F258</x:v>
       </x:c>
       <x:c r="B351" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C351" s="11" t="n">
-        <x:v>39.3</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D351" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="E351" s="11" t="n">
-        <x:v>10.15</x:v>
+        <x:v>13.249</x:v>
       </x:c>
       <x:c r="F351" s="11" t="n">
         <x:f>SQRT((C351-C350)^2+(D351-D350)^2+(E351-E350)^2)</x:f>
-        <x:v>4.94309922680412</x:v>
+        <x:v>0.9652641752577313</x:v>
       </x:c>
       <x:c r="G351" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="352" ht="32" customHeight="1">
       <x:c r="A352" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F243</x:v>
+        <x:v>drop:FC1:V1:fan:1:F258</x:v>
       </x:c>
       <x:c r="B352" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C352" s="11" t="n">
+        <x:v>39.7</x:v>
+      </x:c>
+      <x:c r="D352" s="11" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="E352" s="11" t="n">
+        <x:v>13.13</x:v>
+      </x:c>
+      <x:c r="F352" s="11" t="n">
+        <x:f>SQRT((C352-C351)^2+(D352-D351)^2+(E352-E351)^2)</x:f>
+        <x:v>0.11899999999999977</x:v>
+      </x:c>
+      <x:c r="G352" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353" ht="32" customHeight="1">
+      <x:c r="A353" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F259</x:v>
+      </x:c>
+      <x:c r="B353" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C352" s="11" t="n">
-        <x:v>41.85</x:v>
-      </x:c>
-      <x:c r="D352" s="11" t="n">
-        <x:v>8.243099226804118</x:v>
-      </x:c>
-      <x:c r="E352" s="11" t="n">
+      <x:c r="C353" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D353" s="11" t="n">
+        <x:v>8.565264175257724</x:v>
+      </x:c>
+      <x:c r="E353" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
-      <x:c r="F352" s="11" t="n">
+      <x:c r="F353" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G352" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="353" ht="32" customHeight="1">
-      <x:c r="A353" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F243</x:v>
-      </x:c>
-      <x:c r="B353" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C353" s="11" t="n">
-        <x:v>41.85</x:v>
-      </x:c>
-      <x:c r="D353" s="11" t="n">
-        <x:v>8.243099226804125</x:v>
-      </x:c>
-      <x:c r="E353" s="11" t="n">
-        <x:v>10.15</x:v>
-      </x:c>
-      <x:c r="F353" s="11" t="n">
-        <x:f>SQRT((C353-C352)^2+(D353-D352)^2+(E353-E352)^2)</x:f>
-        <x:v>2.79</x:v>
-      </x:c>
       <x:c r="G353" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="354" ht="32" customHeight="1">
       <x:c r="A354" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F243</x:v>
+        <x:v>drop:FC1:V1:fan:1:F259</x:v>
       </x:c>
       <x:c r="B354" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C354" s="11" t="n">
-        <x:v>41.85</x:v>
+        <x:v>41.45</x:v>
       </x:c>
       <x:c r="D354" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>8.565264175257731</x:v>
       </x:c>
       <x:c r="E354" s="11" t="n">
-        <x:v>10.15</x:v>
+        <x:v>13.249</x:v>
       </x:c>
       <x:c r="F354" s="11" t="n">
         <x:f>SQRT((C354-C353)^2+(D354-D353)^2+(E354-E353)^2)</x:f>
+        <x:v>5.889</x:v>
+      </x:c>
+      <x:c r="G354" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355" ht="32" customHeight="1">
+      <x:c r="A355" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F259</x:v>
+      </x:c>
+      <x:c r="B355" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C355" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D355" s="11" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="E355" s="11" t="n">
+        <x:v>13.249</x:v>
+      </x:c>
+      <x:c r="F355" s="11" t="n">
+        <x:f>SQRT((C355-C354)^2+(D355-D354)^2+(E355-E354)^2)</x:f>
+        <x:v>0.9652641752577313</x:v>
+      </x:c>
+      <x:c r="G355" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356" ht="32" customHeight="1">
+      <x:c r="A356" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F259</x:v>
+      </x:c>
+      <x:c r="B356" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C356" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D356" s="11" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="E356" s="11" t="n">
+        <x:v>13.13</x:v>
+      </x:c>
+      <x:c r="F356" s="11" t="n">
+        <x:f>SQRT((C356-C355)^2+(D356-D355)^2+(E356-E355)^2)</x:f>
+        <x:v>0.11899999999999977</x:v>
+      </x:c>
+      <x:c r="G356" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357" ht="32" customHeight="1">
+      <x:c r="A357" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+      </x:c>
+      <x:c r="B357" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C357" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="D357" s="11" t="n">
+        <x:v>8.766617268041228</x:v>
+      </x:c>
+      <x:c r="E357" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F357" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G357" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358" ht="32" customHeight="1">
+      <x:c r="A358" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+      </x:c>
+      <x:c r="B358" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C358" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="D358" s="11" t="n">
+        <x:v>8.766617268041237</x:v>
+      </x:c>
+      <x:c r="E358" s="11" t="n">
+        <x:v>-13.249</x:v>
+      </x:c>
+      <x:c r="F358" s="11" t="n">
+        <x:f>SQRT((C358-C357)^2+(D358-D357)^2+(E358-E357)^2)</x:f>
+        <x:v>5.889</x:v>
+      </x:c>
+      <x:c r="G358" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359" ht="32" customHeight="1">
+      <x:c r="A359" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+      </x:c>
+      <x:c r="B359" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C359" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="D359" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E359" s="11" t="n">
+        <x:v>-13.249</x:v>
+      </x:c>
+      <x:c r="F359" s="11" t="n">
+        <x:f>SQRT((C359-C358)^2+(D359-D358)^2+(E359-E358)^2)</x:f>
+        <x:v>6.066617268041237</x:v>
+      </x:c>
+      <x:c r="G359" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360" ht="32" customHeight="1">
+      <x:c r="A360" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+      </x:c>
+      <x:c r="B360" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C360" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="D360" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E360" s="11" t="n">
+        <x:v>-13.06</x:v>
+      </x:c>
+      <x:c r="F360" s="11" t="n">
+        <x:f>SQRT((C360-C359)^2+(D360-D359)^2+(E360-E359)^2)</x:f>
+        <x:v>0.18900000000000006</x:v>
+      </x:c>
+      <x:c r="G360" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361" ht="32" customHeight="1">
+      <x:c r="A361" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+      </x:c>
+      <x:c r="B361" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C361" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D361" s="11" t="n">
+        <x:v>8.122287371134018</x:v>
+      </x:c>
+      <x:c r="E361" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F361" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G361" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362" ht="32" customHeight="1">
+      <x:c r="A362" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+      </x:c>
+      <x:c r="B362" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C362" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D362" s="11" t="n">
+        <x:v>8.122287371134023</x:v>
+      </x:c>
+      <x:c r="E362" s="11" t="n">
+        <x:v>-13.249</x:v>
+      </x:c>
+      <x:c r="F362" s="11" t="n">
+        <x:f>SQRT((C362-C361)^2+(D362-D361)^2+(E362-E361)^2)</x:f>
+        <x:v>5.889</x:v>
+      </x:c>
+      <x:c r="G362" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363" ht="32" customHeight="1">
+      <x:c r="A363" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+      </x:c>
+      <x:c r="B363" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C363" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D363" s="11" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="E363" s="11" t="n">
+        <x:v>-13.249</x:v>
+      </x:c>
+      <x:c r="F363" s="11" t="n">
+        <x:f>SQRT((C363-C362)^2+(D363-D362)^2+(E363-E362)^2)</x:f>
+        <x:v>4.622287371134023</x:v>
+      </x:c>
+      <x:c r="G363" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="364" ht="32" customHeight="1">
+      <x:c r="A364" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+      </x:c>
+      <x:c r="B364" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C364" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D364" s="11" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="E364" s="11" t="n">
+        <x:v>-13.06</x:v>
+      </x:c>
+      <x:c r="F364" s="11" t="n">
+        <x:f>SQRT((C364-C363)^2+(D364-D363)^2+(E364-E363)^2)</x:f>
+        <x:v>0.18900000000000006</x:v>
+      </x:c>
+      <x:c r="G364" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="365" ht="32" customHeight="1">
+      <x:c r="A365" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+      </x:c>
+      <x:c r="B365" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C365" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="D365" s="11" t="n">
+        <x:v>8.766617268041228</x:v>
+      </x:c>
+      <x:c r="E365" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F365" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G365" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="366" ht="32" customHeight="1">
+      <x:c r="A366" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+      </x:c>
+      <x:c r="B366" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C366" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="D366" s="11" t="n">
+        <x:v>8.766617268041237</x:v>
+      </x:c>
+      <x:c r="E366" s="11" t="n">
+        <x:v>13.249</x:v>
+      </x:c>
+      <x:c r="F366" s="11" t="n">
+        <x:f>SQRT((C366-C365)^2+(D366-D365)^2+(E366-E365)^2)</x:f>
+        <x:v>5.889</x:v>
+      </x:c>
+      <x:c r="G366" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="367" ht="32" customHeight="1">
+      <x:c r="A367" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+      </x:c>
+      <x:c r="B367" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C367" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="D367" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E367" s="11" t="n">
+        <x:v>13.249</x:v>
+      </x:c>
+      <x:c r="F367" s="11" t="n">
+        <x:f>SQRT((C367-C366)^2+(D367-D366)^2+(E367-E366)^2)</x:f>
+        <x:v>6.066617268041237</x:v>
+      </x:c>
+      <x:c r="G367" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="368" ht="32" customHeight="1">
+      <x:c r="A368" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+      </x:c>
+      <x:c r="B368" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C368" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="D368" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E368" s="11" t="n">
+        <x:v>13.06</x:v>
+      </x:c>
+      <x:c r="F368" s="11" t="n">
+        <x:f>SQRT((C368-C367)^2+(D368-D367)^2+(E368-E367)^2)</x:f>
+        <x:v>0.18900000000000006</x:v>
+      </x:c>
+      <x:c r="G368" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="369" ht="32" customHeight="1">
+      <x:c r="A369" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+      </x:c>
+      <x:c r="B369" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C369" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D369" s="11" t="n">
+        <x:v>8.122287371134018</x:v>
+      </x:c>
+      <x:c r="E369" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F369" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G369" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="370" ht="32" customHeight="1">
+      <x:c r="A370" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+      </x:c>
+      <x:c r="B370" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C370" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D370" s="11" t="n">
+        <x:v>8.122287371134023</x:v>
+      </x:c>
+      <x:c r="E370" s="11" t="n">
+        <x:v>13.249</x:v>
+      </x:c>
+      <x:c r="F370" s="11" t="n">
+        <x:f>SQRT((C370-C369)^2+(D370-D369)^2+(E370-E369)^2)</x:f>
+        <x:v>5.889</x:v>
+      </x:c>
+      <x:c r="G370" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="371" ht="32" customHeight="1">
+      <x:c r="A371" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+      </x:c>
+      <x:c r="B371" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C371" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D371" s="11" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="E371" s="11" t="n">
+        <x:v>13.249</x:v>
+      </x:c>
+      <x:c r="F371" s="11" t="n">
+        <x:f>SQRT((C371-C370)^2+(D371-D370)^2+(E371-E370)^2)</x:f>
+        <x:v>4.622287371134023</x:v>
+      </x:c>
+      <x:c r="G371" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="372" ht="32" customHeight="1">
+      <x:c r="A372" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+      </x:c>
+      <x:c r="B372" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C372" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D372" s="11" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="E372" s="11" t="n">
+        <x:v>13.06</x:v>
+      </x:c>
+      <x:c r="F372" s="11" t="n">
+        <x:f>SQRT((C372-C371)^2+(D372-D371)^2+(E372-E371)^2)</x:f>
+        <x:v>0.18900000000000006</x:v>
+      </x:c>
+      <x:c r="G372" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="373" ht="32" customHeight="1">
+      <x:c r="A373" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
+      </x:c>
+      <x:c r="B373" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C373" s="11" t="n">
+        <x:v>39.3</x:v>
+      </x:c>
+      <x:c r="D373" s="11" t="n">
+        <x:v>8.24309922680412</x:v>
+      </x:c>
+      <x:c r="E373" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F373" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G373" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="374" ht="32" customHeight="1">
+      <x:c r="A374" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
+      </x:c>
+      <x:c r="B374" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C374" s="11" t="n">
+        <x:v>39.3</x:v>
+      </x:c>
+      <x:c r="D374" s="11" t="n">
+        <x:v>8.24309922680412</x:v>
+      </x:c>
+      <x:c r="E374" s="11" t="n">
+        <x:v>-10.15</x:v>
+      </x:c>
+      <x:c r="F374" s="11" t="n">
+        <x:f>SQRT((C374-C373)^2+(D374-D373)^2+(E374-E373)^2)</x:f>
+        <x:v>2.79</x:v>
+      </x:c>
+      <x:c r="G374" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="375" ht="32" customHeight="1">
+      <x:c r="A375" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
+      </x:c>
+      <x:c r="B375" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C375" s="11" t="n">
+        <x:v>39.3</x:v>
+      </x:c>
+      <x:c r="D375" s="11" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="E375" s="11" t="n">
+        <x:v>-10.15</x:v>
+      </x:c>
+      <x:c r="F375" s="11" t="n">
+        <x:f>SQRT((C375-C374)^2+(D375-D374)^2+(E375-E374)^2)</x:f>
+        <x:v>4.94309922680412</x:v>
+      </x:c>
+      <x:c r="G375" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="376" ht="32" customHeight="1">
+      <x:c r="A376" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+      </x:c>
+      <x:c r="B376" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C376" s="11" t="n">
+        <x:v>41.85</x:v>
+      </x:c>
+      <x:c r="D376" s="11" t="n">
+        <x:v>8.243099226804118</x:v>
+      </x:c>
+      <x:c r="E376" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F376" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G376" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377" ht="32" customHeight="1">
+      <x:c r="A377" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+      </x:c>
+      <x:c r="B377" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C377" s="11" t="n">
+        <x:v>41.85</x:v>
+      </x:c>
+      <x:c r="D377" s="11" t="n">
+        <x:v>8.243099226804125</x:v>
+      </x:c>
+      <x:c r="E377" s="11" t="n">
+        <x:v>-10.15</x:v>
+      </x:c>
+      <x:c r="F377" s="11" t="n">
+        <x:f>SQRT((C377-C376)^2+(D377-D376)^2+(E377-E376)^2)</x:f>
+        <x:v>2.79</x:v>
+      </x:c>
+      <x:c r="G377" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="378" ht="32" customHeight="1">
+      <x:c r="A378" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+      </x:c>
+      <x:c r="B378" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C378" s="11" t="n">
+        <x:v>41.85</x:v>
+      </x:c>
+      <x:c r="D378" s="11" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="E378" s="11" t="n">
+        <x:v>-10.15</x:v>
+      </x:c>
+      <x:c r="F378" s="11" t="n">
+        <x:f>SQRT((C378-C377)^2+(D378-D377)^2+(E378-E377)^2)</x:f>
         <x:v>4.943099226804125</x:v>
       </x:c>
-      <x:c r="G354" s="8" t="str">
+      <x:c r="G378" s="8" t="str">
         <x:v>Retired</x:v>
       </x:c>
     </x:row>
+    <x:row r="379" ht="32" customHeight="1">
+      <x:c r="A379" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:1:F242</x:v>
+      </x:c>
+      <x:c r="B379" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C379" s="11" t="n">
+        <x:v>39.3</x:v>
+      </x:c>
+      <x:c r="D379" s="11" t="n">
+        <x:v>8.24309922680412</x:v>
+      </x:c>
+      <x:c r="E379" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F379" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G379" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="380" ht="32" customHeight="1">
+      <x:c r="A380" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:1:F242</x:v>
+      </x:c>
+      <x:c r="B380" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C380" s="11" t="n">
+        <x:v>39.3</x:v>
+      </x:c>
+      <x:c r="D380" s="11" t="n">
+        <x:v>8.24309922680412</x:v>
+      </x:c>
+      <x:c r="E380" s="11" t="n">
+        <x:v>10.15</x:v>
+      </x:c>
+      <x:c r="F380" s="11" t="n">
+        <x:f>SQRT((C380-C379)^2+(D380-D379)^2+(E380-E379)^2)</x:f>
+        <x:v>2.79</x:v>
+      </x:c>
+      <x:c r="G380" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381" ht="32" customHeight="1">
+      <x:c r="A381" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:1:F242</x:v>
+      </x:c>
+      <x:c r="B381" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C381" s="11" t="n">
+        <x:v>39.3</x:v>
+      </x:c>
+      <x:c r="D381" s="11" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="E381" s="11" t="n">
+        <x:v>10.15</x:v>
+      </x:c>
+      <x:c r="F381" s="11" t="n">
+        <x:f>SQRT((C381-C380)^2+(D381-D380)^2+(E381-E380)^2)</x:f>
+        <x:v>4.94309922680412</x:v>
+      </x:c>
+      <x:c r="G381" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382" ht="32" customHeight="1">
+      <x:c r="A382" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:1:F243</x:v>
+      </x:c>
+      <x:c r="B382" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C382" s="11" t="n">
+        <x:v>41.85</x:v>
+      </x:c>
+      <x:c r="D382" s="11" t="n">
+        <x:v>8.243099226804118</x:v>
+      </x:c>
+      <x:c r="E382" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F382" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G382" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="383" ht="32" customHeight="1">
+      <x:c r="A383" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:1:F243</x:v>
+      </x:c>
+      <x:c r="B383" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C383" s="11" t="n">
+        <x:v>41.85</x:v>
+      </x:c>
+      <x:c r="D383" s="11" t="n">
+        <x:v>8.243099226804125</x:v>
+      </x:c>
+      <x:c r="E383" s="11" t="n">
+        <x:v>10.15</x:v>
+      </x:c>
+      <x:c r="F383" s="11" t="n">
+        <x:f>SQRT((C383-C382)^2+(D383-D382)^2+(E383-E382)^2)</x:f>
+        <x:v>2.79</x:v>
+      </x:c>
+      <x:c r="G383" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384" ht="32" customHeight="1">
+      <x:c r="A384" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:1:F243</x:v>
+      </x:c>
+      <x:c r="B384" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C384" s="11" t="n">
+        <x:v>41.85</x:v>
+      </x:c>
+      <x:c r="D384" s="11" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="E384" s="11" t="n">
+        <x:v>10.15</x:v>
+      </x:c>
+      <x:c r="F384" s="11" t="n">
+        <x:f>SQRT((C384-C383)^2+(D384-D383)^2+(E384-E383)^2)</x:f>
+        <x:v>4.943099226804125</x:v>
+      </x:c>
+      <x:c r="G384" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G7:G354">
+  <x:conditionalFormatting sqref="G7:G384">
     <x:cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdac1135357bd4fb8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8550444a76f4909"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rfbc9bc68e00b49fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rac9e91e1872c411c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R2e1c4f2163ce436c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rb4470f6b0ae94062"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Raf61b3448834429b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R0fe162bbbc2e4524"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R2e8d650c5c004be2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R7412326e0e974738"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-09T01:31:17.233Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-09T03:17:36.119Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>80b0da7d5afe7ebc6ad40230d4100ad0f2b4b395a8a63b44da5d741ccd64e05d</x:v>
+        <x:v>f58ecb8c7e66db5f5a9c359a0501f9a7ff3253b9cb9664b76918bdc2f036e05a</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>78a1f21a5458fc451b1fadb227a547feb6afa62226cd02a3db53eaacd4fe65ce</x:v>
+        <x:v>1646f19d4f8b80070625f5fb407f54d11abbea5d7ecb7c88a4a2534f18542306</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4350,7 +4350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra74925802338430d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R342b3964590c4e63"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8490,7 +8490,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf94e654f0bee427f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b36d42326234c6b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17662,7 +17662,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8550444a76f4909"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbf46bcb5dfa48b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Raf61b3448834429b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R0fe162bbbc2e4524"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R2e8d650c5c004be2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R7412326e0e974738"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R82341faf6e1c447c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R6a9abf41229a4ba9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R77a441654d9d441a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R1e437700d619441f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-09T03:17:36.119Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-09T04:54:03.663Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>f58ecb8c7e66db5f5a9c359a0501f9a7ff3253b9cb9664b76918bdc2f036e05a</x:v>
+        <x:v>e8b0d45e0c5518ca0cc64c1fa511adc8ba03ba31bef6d46426ff3c0c3e699bab</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>1646f19d4f8b80070625f5fb407f54d11abbea5d7ecb7c88a4a2534f18542306</x:v>
+        <x:v>e25c59374b1948a67cdb0ee5bed0beb9884da65931cb92b8dc2af738d4ae1e28</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4350,7 +4350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R342b3964590c4e63"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R174f297dfdd241ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8490,7 +8490,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b36d42326234c6b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a7ebb92f27b41f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17662,7 +17662,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbf46bcb5dfa48b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb77bba74550a4e0d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R82341faf6e1c447c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R6a9abf41229a4ba9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R77a441654d9d441a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R1e437700d619441f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R6238eb5354784933"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R55e3df2aeda345d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R69bbd2ec56c7405b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R9501f7c26e6b4c54"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-09T04:54:03.663Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-09T06:49:14.923Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>e8b0d45e0c5518ca0cc64c1fa511adc8ba03ba31bef6d46426ff3c0c3e699bab</x:v>
+        <x:v>0a6cf2aa5294b46ad1ca267ef78dada74d793fdb4a83f39e392746594b74ba7c</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -4350,7 +4350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R174f297dfdd241ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05a70c0d308446e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8490,7 +8490,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a7ebb92f27b41f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd62a54801cb945df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17662,7 +17662,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb77bba74550a4e0d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a85c319bfa04880"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R6238eb5354784933"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R55e3df2aeda345d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R69bbd2ec56c7405b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R9501f7c26e6b4c54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R88e3411d252c4327"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R9a9cb735fc3548b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rf8d10cf5ead84f4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Re95d001b40304d82"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -77,7 +77,13 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -487,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-09T06:49:14.923Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-17T21:08:50.163Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>0a6cf2aa5294b46ad1ca267ef78dada74d793fdb4a83f39e392746594b74ba7c</x:v>
+        <x:v>37e3acfbe7b2353ccb6bf951d166ae573b85d990a0e3cb06b573b995c64fefa8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>e25c59374b1948a67cdb0ee5bed0beb9884da65931cb92b8dc2af738d4ae1e28</x:v>
+        <x:v>dbabc0c9ddcd7207edad13de9e8b20f5da0865700167c5f9fe7c34d6d03b22b4</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4350,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05a70c0d308446e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17c2ff27c8654787"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8490,7 +8496,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd62a54801cb945df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3cfb6a9ed3f44ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17662,7 +17668,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a85c319bfa04880"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R864a6eb57cc040ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R88e3411d252c4327"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R9a9cb735fc3548b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rf8d10cf5ead84f4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Re95d001b40304d82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R7dc70ed54dae453a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re5a02f525b014727"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R5e2a2d9156f54ec9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rdebbbf2f02314341"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -223,7 +223,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ElectricalLineRegister" displayName="ElectricalLineRegister" ref="A6:Z69" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ElectricalLineRegister" displayName="ElectricalLineRegister" ref="A6:Z77" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="26">
     <x:tableColumn id="1" name="Route ID"/>
     <x:tableColumn id="2" name="Name"/>
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G384" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G440" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Route ID"/>
     <x:tableColumn id="2" name="Vertex"/>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-17T21:08:50.163Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-17T21:33:54.811Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -510,8 +510,8 @@
         <x:v>Current routes</x:v>
       </x:c>
       <x:c r="B6" s="16" t="n">
-        <x:f>COUNTIFS('Electrical Lines'!$Y$7:$Y$69,"Current")</x:f>
-        <x:v>55</x:v>
+        <x:f>COUNTIFS('Electrical Lines'!$Y$7:$Y$77,"Current")</x:f>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
@@ -519,8 +519,8 @@
         <x:v>Retired equipment / routes</x:v>
       </x:c>
       <x:c r="B7" s="16" t="n">
-        <x:f>COUNTIFS(Equipment!$AA$7:$AA$55,"Retired")+COUNTIFS('Electrical Lines'!$Y$7:$Y$69,"Retired")</x:f>
-        <x:v>12</x:v>
+        <x:f>COUNTIFS(Equipment!$AA$7:$AA$55,"Retired")+COUNTIFS('Electrical Lines'!$Y$7:$Y$77,"Retired")</x:f>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>37e3acfbe7b2353ccb6bf951d166ae573b85d990a0e3cb06b573b995c64fefa8</x:v>
+        <x:v>40c0fb48adb616822d2737a378024e64d46f211fcc43ca75ea298cd2570965f8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>dbabc0c9ddcd7207edad13de9e8b20f5da0865700167c5f9fe7c34d6d03b22b4</x:v>
+        <x:v>e8507810679907dc3354f9387ce0b6d5f3b3e307d5939a52680f19a914a4cd86</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3039,7 +3039,7 @@
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="E37" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>V2</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
         <x:v>39.7</x:v>
@@ -3088,7 +3088,7 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="AB37" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+        <x:v>drop:FC1:V2:fan:-1:F256</x:v>
       </x:c>
       <x:c r="AC37" s="8" t="str">
         <x:v>{"dim":1,"speed":1}</x:v>
@@ -3108,7 +3108,7 @@
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="E38" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>V2</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
         <x:v>41.45</x:v>
@@ -3157,7 +3157,7 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="AB38" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
+        <x:v>drop:FC1:V2:fan:-1:F257</x:v>
       </x:c>
       <x:c r="AC38" s="8" t="str">
         <x:v>{"dim":1,"speed":1}</x:v>
@@ -3177,7 +3177,7 @@
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="E39" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>V2</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
         <x:v>39.7</x:v>
@@ -3226,7 +3226,7 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="AB39" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F258</x:v>
+        <x:v>drop:FC1:V2:fan:1:F258</x:v>
       </x:c>
       <x:c r="AC39" s="8" t="str">
         <x:v>{"dim":1,"speed":1}</x:v>
@@ -3246,7 +3246,7 @@
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="E40" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>V2</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
         <x:v>41.45</x:v>
@@ -3295,7 +3295,7 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="AB40" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F259</x:v>
+        <x:v>drop:FC1:V2:fan:1:F259</x:v>
       </x:c>
       <x:c r="AC40" s="8" t="str">
         <x:v>{"dim":1,"speed":1}</x:v>
@@ -3315,7 +3315,7 @@
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="E41" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>V3</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
         <x:v>53.12</x:v>
@@ -3364,7 +3364,7 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="AB41" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
+        <x:v>drop:FC1:V3:fan:-1:F260</x:v>
       </x:c>
       <x:c r="AC41" s="8" t="str">
         <x:v>{"dim":1,"speed":1}</x:v>
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17c2ff27c8654787"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5895ed09e7004630"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4653,7 +4653,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I7" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A7,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A7,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>64.02913031117919</x:v>
       </x:c>
       <x:c r="J7" s="11"/>
@@ -4712,7 +4712,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A8,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A8,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>11.286909264308505</x:v>
       </x:c>
       <x:c r="J8" s="11"/>
@@ -4773,7 +4773,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A9,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A9,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>11.286909264308505</x:v>
       </x:c>
       <x:c r="J9" s="11"/>
@@ -4834,7 +4834,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A10,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A10,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>11.276909264308502</x:v>
       </x:c>
       <x:c r="J10" s="11"/>
@@ -4895,7 +4895,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A11,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A11,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>11.286909264308504</x:v>
       </x:c>
       <x:c r="J11" s="11"/>
@@ -4956,7 +4956,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A12,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A12,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>11.286909264308504</x:v>
       </x:c>
       <x:c r="J12" s="11"/>
@@ -5017,7 +5017,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I13" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A13,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A13,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>11.286909264308504</x:v>
       </x:c>
       <x:c r="J13" s="11"/>
@@ -5078,7 +5078,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I14" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A14,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A14,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>11.276909264308506</x:v>
       </x:c>
       <x:c r="J14" s="11"/>
@@ -5145,7 +5145,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I15" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A15,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A15,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>70.62913031117918</x:v>
       </x:c>
       <x:c r="J15" s="11"/>
@@ -5204,7 +5204,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I16" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A16,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A16,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>11.286909264308505</x:v>
       </x:c>
       <x:c r="J16" s="11"/>
@@ -5265,7 +5265,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I17" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A17,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A17,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>11.286909264308505</x:v>
       </x:c>
       <x:c r="J17" s="11"/>
@@ -5326,7 +5326,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I18" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A18,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A18,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>11.276909264308502</x:v>
       </x:c>
       <x:c r="J18" s="11"/>
@@ -5387,7 +5387,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I19" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A19,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A19,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>11.286909264308504</x:v>
       </x:c>
       <x:c r="J19" s="11"/>
@@ -5448,7 +5448,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I20" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A20,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A20,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>11.286909264308504</x:v>
       </x:c>
       <x:c r="J20" s="11"/>
@@ -5509,7 +5509,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I21" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A21,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A21,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>11.286909264308504</x:v>
       </x:c>
       <x:c r="J21" s="11"/>
@@ -5570,7 +5570,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I22" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A22,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A22,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>11.276909264308506</x:v>
       </x:c>
       <x:c r="J22" s="11"/>
@@ -5632,7 +5632,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I23" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A23,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A23,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>33.83219768896557</x:v>
       </x:c>
       <x:c r="J23" s="11"/>
@@ -5691,7 +5691,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I24" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A24,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A24,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>9.264333762886594</x:v>
       </x:c>
       <x:c r="J24" s="11"/>
@@ -5752,7 +5752,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I25" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A25,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A25,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>9.264333762886599</x:v>
       </x:c>
       <x:c r="J25" s="11"/>
@@ -5814,7 +5814,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I26" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A26,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A26,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>40.43219768896558</x:v>
       </x:c>
       <x:c r="J26" s="11"/>
@@ -5873,7 +5873,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I27" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A27,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A27,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>9.264333762886594</x:v>
       </x:c>
       <x:c r="J27" s="11"/>
@@ -5934,7 +5934,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I28" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A28,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A28,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>9.264333762886599</x:v>
       </x:c>
       <x:c r="J28" s="11"/>
@@ -6002,7 +6002,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I29" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A29,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A29,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>67.57613031117918</x:v>
       </x:c>
       <x:c r="J29" s="11"/>
@@ -6061,7 +6061,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I30" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A30,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A30,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J30" s="11"/>
@@ -6122,7 +6122,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I31" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A31,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A31,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J31" s="11"/>
@@ -6183,7 +6183,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I32" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A32,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A32,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J32" s="11"/>
@@ -6244,7 +6244,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I33" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A33,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A33,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J33" s="11"/>
@@ -6305,7 +6305,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I34" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A34,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A34,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J34" s="11"/>
@@ -6366,7 +6366,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I35" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A35,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A35,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J35" s="11"/>
@@ -6427,7 +6427,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I36" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A36,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A36,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J36" s="11"/>
@@ -6488,7 +6488,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I37" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A37,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A37,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J37" s="11"/>
@@ -6556,7 +6556,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I38" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A38,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A38,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>74.17613031117918</x:v>
       </x:c>
       <x:c r="J38" s="11"/>
@@ -6615,7 +6615,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I39" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A39,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A39,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J39" s="11"/>
@@ -6676,7 +6676,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I40" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A40,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A40,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J40" s="11"/>
@@ -6737,7 +6737,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I41" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A41,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A41,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J41" s="11"/>
@@ -6798,7 +6798,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I42" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A42,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A42,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J42" s="11"/>
@@ -6859,7 +6859,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I43" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A43,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A43,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J43" s="11"/>
@@ -6920,7 +6920,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I44" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A44,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A44,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J44" s="11"/>
@@ -6981,7 +6981,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I45" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A45,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A45,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J45" s="11"/>
@@ -7042,7 +7042,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I46" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A46,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A46,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>0.7520000000000007</x:v>
       </x:c>
       <x:c r="J46" s="11"/>
@@ -7103,7 +7103,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I47" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A47,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A47,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>12.517</x:v>
       </x:c>
       <x:c r="J47" s="11"/>
@@ -7162,7 +7162,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I48" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A48,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A48,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>7.91542691446789</x:v>
       </x:c>
       <x:c r="J48" s="11"/>
@@ -7223,7 +7223,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I49" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A49,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A49,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>19.117</x:v>
       </x:c>
       <x:c r="J49" s="11"/>
@@ -7282,7 +7282,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I50" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A50,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A50,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>7.91542691446789</x:v>
       </x:c>
       <x:c r="J50" s="11"/>
@@ -7329,10 +7329,7 @@
       </x:c>
       <x:c r="D51" s="8" t="str">
         <x:v>F252
-F253
-F256
-F257
-F260</x:v>
+F253</x:v>
       </x:c>
       <x:c r="E51" s="8" t="str">
         <x:v>DB1</x:v>
@@ -7347,7 +7344,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I51" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A51,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A51,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>67.54713031117919</x:v>
       </x:c>
       <x:c r="J51" s="11"/>
@@ -7406,7 +7403,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I52" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A52,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A52,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>8.69282092938182</x:v>
       </x:c>
       <x:c r="J52" s="11"/>
@@ -7467,7 +7464,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I53" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A53,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A53,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>11.831150261440472</x:v>
       </x:c>
       <x:c r="J53" s="11"/>
@@ -7504,16 +7501,17 @@
     </x:row>
     <x:row r="54" ht="90" customHeight="1">
       <x:c r="A54" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B54" s="8" t="str">
-        <x:v>V1 → Exhaust fan · wing gable B · front</x:v>
+        <x:v>V1 · H · circuit trunk</x:v>
       </x:c>
       <x:c r="C54" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D54" s="8" t="str">
-        <x:v>F256</x:v>
+        <x:v>F254
+F255</x:v>
       </x:c>
       <x:c r="E54" s="8" t="str">
         <x:v>DB1</x:v>
@@ -7525,11 +7523,11 @@
         <x:v>fan</x:v>
       </x:c>
       <x:c r="H54" s="8" t="str">
-        <x:v>drop</x:v>
+        <x:v>trunk</x:v>
       </x:c>
       <x:c r="I54" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A54,'Route Points'!$F$7:$F$384)</x:f>
-        <x:v>6.973264175257731</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A54,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>74.14713031117918</x:v>
       </x:c>
       <x:c r="J54" s="11"/>
       <x:c r="K54" s="11" t="str">
@@ -7546,7 +7544,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P54" s="8" t="str">
-        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q54" s="9"/>
       <x:c r="R54" s="9"/>
@@ -7559,22 +7557,20 @@
       <x:c r="Y54" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z54" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
-      </x:c>
+      <x:c r="Z54" s="8"/>
     </x:row>
     <x:row r="55" ht="90" customHeight="1">
       <x:c r="A55" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B55" s="8" t="str">
-        <x:v>V1 → Exhaust fan · wing gable B · rear</x:v>
+        <x:v>V1 → Exhaust fan · front gable · H inner</x:v>
       </x:c>
       <x:c r="C55" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D55" s="8" t="str">
-        <x:v>F257</x:v>
+        <x:v>F254</x:v>
       </x:c>
       <x:c r="E55" s="8" t="str">
         <x:v>DB1</x:v>
@@ -7589,8 +7585,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I55" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A55,'Route Points'!$F$7:$F$384)</x:f>
-        <x:v>6.973264175257731</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A55,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>11.831150261440472</x:v>
       </x:c>
       <x:c r="J55" s="11"/>
       <x:c r="K55" s="11" t="str">
@@ -7607,7 +7603,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P55" s="8" t="str">
-        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
       </x:c>
       <x:c r="Q55" s="9"/>
       <x:c r="R55" s="9"/>
@@ -7621,21 +7617,21 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z55" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="90" customHeight="1">
       <x:c r="A56" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B56" s="8" t="str">
-        <x:v>V1 → Exhaust fan · service room</x:v>
+        <x:v>V1 → Exhaust fan · front gable · H outer</x:v>
       </x:c>
       <x:c r="C56" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D56" s="8" t="str">
-        <x:v>F260</x:v>
+        <x:v>F255</x:v>
       </x:c>
       <x:c r="E56" s="8" t="str">
         <x:v>DB1</x:v>
@@ -7650,8 +7646,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I56" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A56,'Route Points'!$F$7:$F$384)</x:f>
-        <x:v>10.2</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A56,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>8.69282092938182</x:v>
       </x:c>
       <x:c r="J56" s="11"/>
       <x:c r="K56" s="11" t="str">
@@ -7668,7 +7664,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P56" s="8" t="str">
-        <x:v>Rear-wall band and local termination; gable / weatherproof entry details pending.</x:v>
+        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
       </x:c>
       <x:c r="Q56" s="9"/>
       <x:c r="R56" s="9"/>
@@ -7682,30 +7678,28 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z56" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:-1</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="90" customHeight="1">
       <x:c r="A57" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>trunk:FC1:V2:fan:-1</x:v>
       </x:c>
       <x:c r="B57" s="8" t="str">
-        <x:v>V1 · H · circuit trunk</x:v>
+        <x:v>V2 · B · circuit trunk</x:v>
       </x:c>
       <x:c r="C57" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D57" s="8" t="str">
-        <x:v>F254
-F255
-F258
-F259</x:v>
+        <x:v>F256
+F257</x:v>
       </x:c>
       <x:c r="E57" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F57" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>V2</x:v>
       </x:c>
       <x:c r="G57" s="8" t="str">
         <x:v>fan</x:v>
@@ -7714,8 +7708,8 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I57" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A57,'Route Points'!$F$7:$F$384)</x:f>
-        <x:v>74.14713031117918</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A57,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>31.713576429531756</x:v>
       </x:c>
       <x:c r="J57" s="11"/>
       <x:c r="K57" s="11" t="str">
@@ -7749,22 +7743,22 @@
     </x:row>
     <x:row r="58" ht="90" customHeight="1">
       <x:c r="A58" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>drop:FC1:V2:fan:-1:F256</x:v>
       </x:c>
       <x:c r="B58" s="8" t="str">
-        <x:v>V1 → Exhaust fan · front gable · H inner</x:v>
+        <x:v>V2 → Exhaust fan · wing gable B · front</x:v>
       </x:c>
       <x:c r="C58" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D58" s="8" t="str">
-        <x:v>F254</x:v>
+        <x:v>F256</x:v>
       </x:c>
       <x:c r="E58" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F58" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>V2</x:v>
       </x:c>
       <x:c r="G58" s="8" t="str">
         <x:v>fan</x:v>
@@ -7773,8 +7767,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I58" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A58,'Route Points'!$F$7:$F$384)</x:f>
-        <x:v>11.831150261440472</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A58,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>6.973264175257731</x:v>
       </x:c>
       <x:c r="J58" s="11"/>
       <x:c r="K58" s="11" t="str">
@@ -7791,7 +7785,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P58" s="8" t="str">
-        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
       </x:c>
       <x:c r="Q58" s="9"/>
       <x:c r="R58" s="9"/>
@@ -7805,27 +7799,27 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z58" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>trunk:FC1:V2:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="90" customHeight="1">
       <x:c r="A59" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
+        <x:v>drop:FC1:V2:fan:-1:F257</x:v>
       </x:c>
       <x:c r="B59" s="8" t="str">
-        <x:v>V1 → Exhaust fan · front gable · H outer</x:v>
+        <x:v>V2 → Exhaust fan · wing gable B · rear</x:v>
       </x:c>
       <x:c r="C59" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D59" s="8" t="str">
-        <x:v>F255</x:v>
+        <x:v>F257</x:v>
       </x:c>
       <x:c r="E59" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F59" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>V2</x:v>
       </x:c>
       <x:c r="G59" s="8" t="str">
         <x:v>fan</x:v>
@@ -7834,8 +7828,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I59" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A59,'Route Points'!$F$7:$F$384)</x:f>
-        <x:v>8.69282092938182</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A59,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>6.973264175257731</x:v>
       </x:c>
       <x:c r="J59" s="11"/>
       <x:c r="K59" s="11" t="str">
@@ -7852,7 +7846,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P59" s="8" t="str">
-        <x:v>Above roof lining to solid front gable above terrace; local fan connection.</x:v>
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
       </x:c>
       <x:c r="Q59" s="9"/>
       <x:c r="R59" s="9"/>
@@ -7866,37 +7860,38 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z59" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>trunk:FC1:V2:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="90" customHeight="1">
       <x:c r="A60" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F258</x:v>
+        <x:v>trunk:FC1:V2:fan:1</x:v>
       </x:c>
       <x:c r="B60" s="8" t="str">
-        <x:v>V1 → Exhaust fan · wing gable H · front</x:v>
+        <x:v>V2 · H · circuit trunk</x:v>
       </x:c>
       <x:c r="C60" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D60" s="8" t="str">
-        <x:v>F258</x:v>
+        <x:v>F258
+F259</x:v>
       </x:c>
       <x:c r="E60" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F60" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>V2</x:v>
       </x:c>
       <x:c r="G60" s="8" t="str">
         <x:v>fan</x:v>
       </x:c>
       <x:c r="H60" s="8" t="str">
-        <x:v>drop</x:v>
+        <x:v>trunk</x:v>
       </x:c>
       <x:c r="I60" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A60,'Route Points'!$F$7:$F$384)</x:f>
-        <x:v>6.973264175257731</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A60,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>38.31357642953176</x:v>
       </x:c>
       <x:c r="J60" s="11"/>
       <x:c r="K60" s="11" t="str">
@@ -7913,7 +7908,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P60" s="8" t="str">
-        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q60" s="9"/>
       <x:c r="R60" s="9"/>
@@ -7926,28 +7921,26 @@
       <x:c r="Y60" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z60" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
-      </x:c>
+      <x:c r="Z60" s="8"/>
     </x:row>
     <x:row r="61" ht="90" customHeight="1">
       <x:c r="A61" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F259</x:v>
+        <x:v>drop:FC1:V2:fan:1:F258</x:v>
       </x:c>
       <x:c r="B61" s="8" t="str">
-        <x:v>V1 → Exhaust fan · wing gable H · rear</x:v>
+        <x:v>V2 → Exhaust fan · wing gable H · front</x:v>
       </x:c>
       <x:c r="C61" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D61" s="8" t="str">
-        <x:v>F259</x:v>
+        <x:v>F258</x:v>
       </x:c>
       <x:c r="E61" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F61" s="8" t="str">
-        <x:v>V1</x:v>
+        <x:v>V2</x:v>
       </x:c>
       <x:c r="G61" s="8" t="str">
         <x:v>fan</x:v>
@@ -7956,7 +7949,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I61" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A61,'Route Points'!$F$7:$F$384)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A61,'Route Points'!$F$7:$F$440)</x:f>
         <x:v>6.973264175257731</x:v>
       </x:c>
       <x:c r="J61" s="11"/>
@@ -7988,27 +7981,27 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z61" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>trunk:FC1:V2:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="90" customHeight="1">
       <x:c r="A62" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+        <x:v>drop:FC1:V2:fan:1:F259</x:v>
       </x:c>
       <x:c r="B62" s="8" t="str">
-        <x:v>F5 → Wall fan · wing B · 3 · held review</x:v>
+        <x:v>V2 → Exhaust fan · wing gable H · rear</x:v>
       </x:c>
       <x:c r="C62" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D62" s="8" t="str">
-        <x:v>F-WING-B-3</x:v>
+        <x:v>F259</x:v>
       </x:c>
       <x:c r="E62" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F62" s="8" t="str">
-        <x:v>F5</x:v>
+        <x:v>V2</x:v>
       </x:c>
       <x:c r="G62" s="8" t="str">
         <x:v>fan</x:v>
@@ -8017,8 +8010,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I62" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A62,'Route Points'!$F$7:$F$384)</x:f>
-        <x:v>12.144617268041237</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A62,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>6.973264175257731</x:v>
       </x:c>
       <x:c r="J62" s="11"/>
       <x:c r="K62" s="11" t="str">
@@ -8046,40 +8039,40 @@
       <x:c r="W62" s="9"/>
       <x:c r="X62" s="9"/>
       <x:c r="Y62" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
       <x:c r="Z62" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:-1</x:v>
+        <x:v>trunk:FC1:V2:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="90" customHeight="1">
       <x:c r="A63" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+        <x:v>trunk:FC1:V3:fan:-1</x:v>
       </x:c>
       <x:c r="B63" s="8" t="str">
-        <x:v>F5 → Wall fan · wing B · 4 · held review</x:v>
+        <x:v>V3 · B · circuit trunk</x:v>
       </x:c>
       <x:c r="C63" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D63" s="8" t="str">
-        <x:v>F-WING-B-4</x:v>
+        <x:v>F260</x:v>
       </x:c>
       <x:c r="E63" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F63" s="8" t="str">
-        <x:v>F5</x:v>
+        <x:v>V3</x:v>
       </x:c>
       <x:c r="G63" s="8" t="str">
         <x:v>fan</x:v>
       </x:c>
       <x:c r="H63" s="8" t="str">
-        <x:v>drop</x:v>
+        <x:v>trunk</x:v>
       </x:c>
       <x:c r="I63" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A63,'Route Points'!$F$7:$F$384)</x:f>
-        <x:v>10.700287371134024</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A63,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>16.407000000000004</x:v>
       </x:c>
       <x:c r="J63" s="11"/>
       <x:c r="K63" s="11" t="str">
@@ -8096,7 +8089,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P63" s="8" t="str">
-        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q63" s="9"/>
       <x:c r="R63" s="9"/>
@@ -8107,30 +8100,28 @@
       <x:c r="W63" s="9"/>
       <x:c r="X63" s="9"/>
       <x:c r="Y63" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-      <x:c r="Z63" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:-1</x:v>
-      </x:c>
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="Z63" s="8"/>
     </x:row>
     <x:row r="64" ht="90" customHeight="1">
       <x:c r="A64" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+        <x:v>drop:FC1:V3:fan:-1:F260</x:v>
       </x:c>
       <x:c r="B64" s="8" t="str">
-        <x:v>F5 → Wall fan · wing H · 3 · held review</x:v>
+        <x:v>V3 → Exhaust fan · service room</x:v>
       </x:c>
       <x:c r="C64" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D64" s="8" t="str">
-        <x:v>F-WING-H-3</x:v>
+        <x:v>F260</x:v>
       </x:c>
       <x:c r="E64" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F64" s="8" t="str">
-        <x:v>F5</x:v>
+        <x:v>V3</x:v>
       </x:c>
       <x:c r="G64" s="8" t="str">
         <x:v>fan</x:v>
@@ -8139,8 +8130,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I64" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A64,'Route Points'!$F$7:$F$384)</x:f>
-        <x:v>12.144617268041237</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A64,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>10.32</x:v>
       </x:c>
       <x:c r="J64" s="11"/>
       <x:c r="K64" s="11" t="str">
@@ -8157,7 +8148,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P64" s="8" t="str">
-        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+        <x:v>Rear-wall band and local termination; gable / weatherproof entry details pending.</x:v>
       </x:c>
       <x:c r="Q64" s="9"/>
       <x:c r="R64" s="9"/>
@@ -8168,30 +8159,30 @@
       <x:c r="W64" s="9"/>
       <x:c r="X64" s="9"/>
       <x:c r="Y64" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
       <x:c r="Z64" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:1</x:v>
+        <x:v>trunk:FC1:V3:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="90" customHeight="1">
       <x:c r="A65" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
       </x:c>
       <x:c r="B65" s="8" t="str">
-        <x:v>F5 → Wall fan · wing H · 4 · held review</x:v>
+        <x:v>V1 → Exhaust fan · wing gable B · front</x:v>
       </x:c>
       <x:c r="C65" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D65" s="8" t="str">
-        <x:v>F-WING-H-4</x:v>
+        <x:v>F256</x:v>
       </x:c>
       <x:c r="E65" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F65" s="8" t="str">
-        <x:v>F5</x:v>
+        <x:v>V1</x:v>
       </x:c>
       <x:c r="G65" s="8" t="str">
         <x:v>fan</x:v>
@@ -8200,8 +8191,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I65" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A65,'Route Points'!$F$7:$F$384)</x:f>
-        <x:v>10.700287371134024</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A65,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>6.973264175257731</x:v>
       </x:c>
       <x:c r="J65" s="11"/>
       <x:c r="K65" s="11" t="str">
@@ -8232,27 +8223,27 @@
         <x:v>Retired</x:v>
       </x:c>
       <x:c r="Z65" s="8" t="str">
-        <x:v>trunk:FC1:F5:fan:1</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="90" customHeight="1">
       <x:c r="A66" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
       </x:c>
       <x:c r="B66" s="8" t="str">
-        <x:v>F1 → Ceiling fan · wing B · front</x:v>
+        <x:v>V1 → Exhaust fan · wing gable B · rear</x:v>
       </x:c>
       <x:c r="C66" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D66" s="8" t="str">
-        <x:v>F240</x:v>
+        <x:v>F257</x:v>
       </x:c>
       <x:c r="E66" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F66" s="8" t="str">
-        <x:v>F1</x:v>
+        <x:v>V1</x:v>
       </x:c>
       <x:c r="G66" s="8" t="str">
         <x:v>fan</x:v>
@@ -8261,8 +8252,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I66" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A66,'Route Points'!$F$7:$F$384)</x:f>
-        <x:v>7.73309922680412</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A66,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>6.973264175257731</x:v>
       </x:c>
       <x:c r="J66" s="11"/>
       <x:c r="K66" s="11" t="str">
@@ -8279,7 +8270,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P66" s="8" t="str">
-        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
       </x:c>
       <x:c r="Q66" s="9"/>
       <x:c r="R66" s="9"/>
@@ -8293,27 +8284,27 @@
         <x:v>Retired</x:v>
       </x:c>
       <x:c r="Z66" s="8" t="str">
-        <x:v>trunk:FC1:F1:fan:-1</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="90" customHeight="1">
       <x:c r="A67" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
       </x:c>
       <x:c r="B67" s="8" t="str">
-        <x:v>F1 → Ceiling fan · wing B · rear</x:v>
+        <x:v>V1 → Exhaust fan · service room</x:v>
       </x:c>
       <x:c r="C67" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D67" s="8" t="str">
-        <x:v>F241</x:v>
+        <x:v>F260</x:v>
       </x:c>
       <x:c r="E67" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F67" s="8" t="str">
-        <x:v>F1</x:v>
+        <x:v>V1</x:v>
       </x:c>
       <x:c r="G67" s="8" t="str">
         <x:v>fan</x:v>
@@ -8322,8 +8313,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I67" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A67,'Route Points'!$F$7:$F$384)</x:f>
-        <x:v>7.733099226804125</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A67,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="J67" s="11"/>
       <x:c r="K67" s="11" t="str">
@@ -8340,7 +8331,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P67" s="8" t="str">
-        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
+        <x:v>Rear-wall band and local termination; gable / weatherproof entry details pending.</x:v>
       </x:c>
       <x:c r="Q67" s="9"/>
       <x:c r="R67" s="9"/>
@@ -8354,27 +8345,27 @@
         <x:v>Retired</x:v>
       </x:c>
       <x:c r="Z67" s="8" t="str">
-        <x:v>trunk:FC1:F1:fan:-1</x:v>
+        <x:v>trunk:FC1:V1:fan:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="90" customHeight="1">
       <x:c r="A68" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F242</x:v>
+        <x:v>drop:FC1:V1:fan:1:F258</x:v>
       </x:c>
       <x:c r="B68" s="8" t="str">
-        <x:v>F1 → Ceiling fan · wing H · front</x:v>
+        <x:v>V1 → Exhaust fan · wing gable H · front</x:v>
       </x:c>
       <x:c r="C68" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D68" s="8" t="str">
-        <x:v>F242</x:v>
+        <x:v>F258</x:v>
       </x:c>
       <x:c r="E68" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F68" s="8" t="str">
-        <x:v>F1</x:v>
+        <x:v>V1</x:v>
       </x:c>
       <x:c r="G68" s="8" t="str">
         <x:v>fan</x:v>
@@ -8383,8 +8374,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I68" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A68,'Route Points'!$F$7:$F$384)</x:f>
-        <x:v>7.73309922680412</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A68,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>6.973264175257731</x:v>
       </x:c>
       <x:c r="J68" s="11"/>
       <x:c r="K68" s="11" t="str">
@@ -8401,7 +8392,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P68" s="8" t="str">
-        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
       </x:c>
       <x:c r="Q68" s="9"/>
       <x:c r="R68" s="9"/>
@@ -8415,27 +8406,27 @@
         <x:v>Retired</x:v>
       </x:c>
       <x:c r="Z68" s="8" t="str">
-        <x:v>trunk:FC1:F1:fan:1</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="90" customHeight="1">
       <x:c r="A69" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F243</x:v>
+        <x:v>drop:FC1:V1:fan:1:F259</x:v>
       </x:c>
       <x:c r="B69" s="8" t="str">
-        <x:v>F1 → Ceiling fan · wing H · rear</x:v>
+        <x:v>V1 → Exhaust fan · wing gable H · rear</x:v>
       </x:c>
       <x:c r="C69" s="8" t="str">
         <x:v>FC1</x:v>
       </x:c>
       <x:c r="D69" s="8" t="str">
-        <x:v>F243</x:v>
+        <x:v>F259</x:v>
       </x:c>
       <x:c r="E69" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F69" s="8" t="str">
-        <x:v>F1</x:v>
+        <x:v>V1</x:v>
       </x:c>
       <x:c r="G69" s="8" t="str">
         <x:v>fan</x:v>
@@ -8444,8 +8435,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I69" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$384,A69,'Route Points'!$F$7:$F$384)</x:f>
-        <x:v>7.733099226804125</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A69,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>6.973264175257731</x:v>
       </x:c>
       <x:c r="J69" s="11"/>
       <x:c r="K69" s="11" t="str">
@@ -8462,7 +8453,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P69" s="8" t="str">
-        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
       </x:c>
       <x:c r="Q69" s="9"/>
       <x:c r="R69" s="9"/>
@@ -8476,27 +8467,515 @@
         <x:v>Retired</x:v>
       </x:c>
       <x:c r="Z69" s="8" t="str">
+        <x:v>trunk:FC1:V1:fan:1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="90" customHeight="1">
+      <x:c r="A70" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+      </x:c>
+      <x:c r="B70" s="8" t="str">
+        <x:v>F5 → Wall fan · wing B · 3 · held review</x:v>
+      </x:c>
+      <x:c r="C70" s="8" t="str">
+        <x:v>FC1</x:v>
+      </x:c>
+      <x:c r="D70" s="8" t="str">
+        <x:v>F-WING-B-3</x:v>
+      </x:c>
+      <x:c r="E70" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F70" s="8" t="str">
+        <x:v>F5</x:v>
+      </x:c>
+      <x:c r="G70" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="H70" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I70" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A70,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>12.144617268041237</x:v>
+      </x:c>
+      <x:c r="J70" s="11"/>
+      <x:c r="K70" s="11" t="str">
+        <x:f>IF(L70="Full home run",I70+J70,"")</x:f>
+      </x:c>
+      <x:c r="L70" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M70" s="13"/>
+      <x:c r="N70" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M70),L70&lt;&gt;"Shared bundle"),IF(L70="Full home run",K70,I70)+M70,"")</x:f>
+      </x:c>
+      <x:c r="O70" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P70" s="8" t="str">
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+      </x:c>
+      <x:c r="Q70" s="9"/>
+      <x:c r="R70" s="9"/>
+      <x:c r="S70" s="13"/>
+      <x:c r="T70" s="9"/>
+      <x:c r="U70" s="9"/>
+      <x:c r="V70" s="9"/>
+      <x:c r="W70" s="9"/>
+      <x:c r="X70" s="9"/>
+      <x:c r="Y70" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z70" s="8" t="str">
+        <x:v>trunk:FC1:F5:fan:-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="90" customHeight="1">
+      <x:c r="A71" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+      </x:c>
+      <x:c r="B71" s="8" t="str">
+        <x:v>F5 → Wall fan · wing B · 4 · held review</x:v>
+      </x:c>
+      <x:c r="C71" s="8" t="str">
+        <x:v>FC1</x:v>
+      </x:c>
+      <x:c r="D71" s="8" t="str">
+        <x:v>F-WING-B-4</x:v>
+      </x:c>
+      <x:c r="E71" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F71" s="8" t="str">
+        <x:v>F5</x:v>
+      </x:c>
+      <x:c r="G71" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="H71" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I71" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A71,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>10.700287371134024</x:v>
+      </x:c>
+      <x:c r="J71" s="11"/>
+      <x:c r="K71" s="11" t="str">
+        <x:f>IF(L71="Full home run",I71+J71,"")</x:f>
+      </x:c>
+      <x:c r="L71" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M71" s="13"/>
+      <x:c r="N71" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M71),L71&lt;&gt;"Shared bundle"),IF(L71="Full home run",K71,I71)+M71,"")</x:f>
+      </x:c>
+      <x:c r="O71" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P71" s="8" t="str">
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+      </x:c>
+      <x:c r="Q71" s="9"/>
+      <x:c r="R71" s="9"/>
+      <x:c r="S71" s="13"/>
+      <x:c r="T71" s="9"/>
+      <x:c r="U71" s="9"/>
+      <x:c r="V71" s="9"/>
+      <x:c r="W71" s="9"/>
+      <x:c r="X71" s="9"/>
+      <x:c r="Y71" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z71" s="8" t="str">
+        <x:v>trunk:FC1:F5:fan:-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="90" customHeight="1">
+      <x:c r="A72" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+      </x:c>
+      <x:c r="B72" s="8" t="str">
+        <x:v>F5 → Wall fan · wing H · 3 · held review</x:v>
+      </x:c>
+      <x:c r="C72" s="8" t="str">
+        <x:v>FC1</x:v>
+      </x:c>
+      <x:c r="D72" s="8" t="str">
+        <x:v>F-WING-H-3</x:v>
+      </x:c>
+      <x:c r="E72" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F72" s="8" t="str">
+        <x:v>F5</x:v>
+      </x:c>
+      <x:c r="G72" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="H72" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I72" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A72,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>12.144617268041237</x:v>
+      </x:c>
+      <x:c r="J72" s="11"/>
+      <x:c r="K72" s="11" t="str">
+        <x:f>IF(L72="Full home run",I72+J72,"")</x:f>
+      </x:c>
+      <x:c r="L72" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M72" s="13"/>
+      <x:c r="N72" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M72),L72&lt;&gt;"Shared bundle"),IF(L72="Full home run",K72,I72)+M72,"")</x:f>
+      </x:c>
+      <x:c r="O72" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P72" s="8" t="str">
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+      </x:c>
+      <x:c r="Q72" s="9"/>
+      <x:c r="R72" s="9"/>
+      <x:c r="S72" s="13"/>
+      <x:c r="T72" s="9"/>
+      <x:c r="U72" s="9"/>
+      <x:c r="V72" s="9"/>
+      <x:c r="W72" s="9"/>
+      <x:c r="X72" s="9"/>
+      <x:c r="Y72" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z72" s="8" t="str">
+        <x:v>trunk:FC1:F5:fan:1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="90" customHeight="1">
+      <x:c r="A73" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+      </x:c>
+      <x:c r="B73" s="8" t="str">
+        <x:v>F5 → Wall fan · wing H · 4 · held review</x:v>
+      </x:c>
+      <x:c r="C73" s="8" t="str">
+        <x:v>FC1</x:v>
+      </x:c>
+      <x:c r="D73" s="8" t="str">
+        <x:v>F-WING-H-4</x:v>
+      </x:c>
+      <x:c r="E73" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F73" s="8" t="str">
+        <x:v>F5</x:v>
+      </x:c>
+      <x:c r="G73" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="H73" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I73" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A73,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>10.700287371134024</x:v>
+      </x:c>
+      <x:c r="J73" s="11"/>
+      <x:c r="K73" s="11" t="str">
+        <x:f>IF(L73="Full home run",I73+J73,"")</x:f>
+      </x:c>
+      <x:c r="L73" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M73" s="13"/>
+      <x:c r="N73" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M73),L73&lt;&gt;"Shared bundle"),IF(L73="Full home run",K73,I73)+M73,"")</x:f>
+      </x:c>
+      <x:c r="O73" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P73" s="8" t="str">
+        <x:v>Covered roof-soffit crossing into outer arcade / wing-gable wall, then concealed pier drop. No exposed crossing at equipment height.</x:v>
+      </x:c>
+      <x:c r="Q73" s="9"/>
+      <x:c r="R73" s="9"/>
+      <x:c r="S73" s="13"/>
+      <x:c r="T73" s="9"/>
+      <x:c r="U73" s="9"/>
+      <x:c r="V73" s="9"/>
+      <x:c r="W73" s="9"/>
+      <x:c r="X73" s="9"/>
+      <x:c r="Y73" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z73" s="8" t="str">
+        <x:v>trunk:FC1:F5:fan:1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="90" customHeight="1">
+      <x:c r="A74" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
+      </x:c>
+      <x:c r="B74" s="8" t="str">
+        <x:v>F1 → Ceiling fan · wing B · front</x:v>
+      </x:c>
+      <x:c r="C74" s="8" t="str">
+        <x:v>FC1</x:v>
+      </x:c>
+      <x:c r="D74" s="8" t="str">
+        <x:v>F240</x:v>
+      </x:c>
+      <x:c r="E74" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F74" s="8" t="str">
+        <x:v>F1</x:v>
+      </x:c>
+      <x:c r="G74" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="H74" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I74" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A74,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>7.73309922680412</x:v>
+      </x:c>
+      <x:c r="J74" s="11"/>
+      <x:c r="K74" s="11" t="str">
+        <x:f>IF(L74="Full home run",I74+J74,"")</x:f>
+      </x:c>
+      <x:c r="L74" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M74" s="13"/>
+      <x:c r="N74" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M74),L74&lt;&gt;"Shared bundle"),IF(L74="Full home run",K74,I74)+M74,"")</x:f>
+      </x:c>
+      <x:c r="O74" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P74" s="8" t="str">
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
+      </x:c>
+      <x:c r="Q74" s="9"/>
+      <x:c r="R74" s="9"/>
+      <x:c r="S74" s="13"/>
+      <x:c r="T74" s="9"/>
+      <x:c r="U74" s="9"/>
+      <x:c r="V74" s="9"/>
+      <x:c r="W74" s="9"/>
+      <x:c r="X74" s="9"/>
+      <x:c r="Y74" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z74" s="8" t="str">
+        <x:v>trunk:FC1:F1:fan:-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="90" customHeight="1">
+      <x:c r="A75" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+      </x:c>
+      <x:c r="B75" s="8" t="str">
+        <x:v>F1 → Ceiling fan · wing B · rear</x:v>
+      </x:c>
+      <x:c r="C75" s="8" t="str">
+        <x:v>FC1</x:v>
+      </x:c>
+      <x:c r="D75" s="8" t="str">
+        <x:v>F241</x:v>
+      </x:c>
+      <x:c r="E75" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F75" s="8" t="str">
+        <x:v>F1</x:v>
+      </x:c>
+      <x:c r="G75" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="H75" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I75" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A75,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>7.733099226804125</x:v>
+      </x:c>
+      <x:c r="J75" s="11"/>
+      <x:c r="K75" s="11" t="str">
+        <x:f>IF(L75="Full home run",I75+J75,"")</x:f>
+      </x:c>
+      <x:c r="L75" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M75" s="13"/>
+      <x:c r="N75" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M75),L75&lt;&gt;"Shared bundle"),IF(L75="Full home run",K75,I75)+M75,"")</x:f>
+      </x:c>
+      <x:c r="O75" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P75" s="8" t="str">
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
+      </x:c>
+      <x:c r="Q75" s="9"/>
+      <x:c r="R75" s="9"/>
+      <x:c r="S75" s="13"/>
+      <x:c r="T75" s="9"/>
+      <x:c r="U75" s="9"/>
+      <x:c r="V75" s="9"/>
+      <x:c r="W75" s="9"/>
+      <x:c r="X75" s="9"/>
+      <x:c r="Y75" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z75" s="8" t="str">
+        <x:v>trunk:FC1:F1:fan:-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="90" customHeight="1">
+      <x:c r="A76" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:1:F242</x:v>
+      </x:c>
+      <x:c r="B76" s="8" t="str">
+        <x:v>F1 → Ceiling fan · wing H · front</x:v>
+      </x:c>
+      <x:c r="C76" s="8" t="str">
+        <x:v>FC1</x:v>
+      </x:c>
+      <x:c r="D76" s="8" t="str">
+        <x:v>F242</x:v>
+      </x:c>
+      <x:c r="E76" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F76" s="8" t="str">
+        <x:v>F1</x:v>
+      </x:c>
+      <x:c r="G76" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="H76" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I76" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A76,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>7.73309922680412</x:v>
+      </x:c>
+      <x:c r="J76" s="11"/>
+      <x:c r="K76" s="11" t="str">
+        <x:f>IF(L76="Full home run",I76+J76,"")</x:f>
+      </x:c>
+      <x:c r="L76" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M76" s="13"/>
+      <x:c r="N76" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M76),L76&lt;&gt;"Shared bundle"),IF(L76="Full home run",K76,I76)+M76,"")</x:f>
+      </x:c>
+      <x:c r="O76" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P76" s="8" t="str">
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
+      </x:c>
+      <x:c r="Q76" s="9"/>
+      <x:c r="R76" s="9"/>
+      <x:c r="S76" s="13"/>
+      <x:c r="T76" s="9"/>
+      <x:c r="U76" s="9"/>
+      <x:c r="V76" s="9"/>
+      <x:c r="W76" s="9"/>
+      <x:c r="X76" s="9"/>
+      <x:c r="Y76" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z76" s="8" t="str">
         <x:v>trunk:FC1:F1:fan:1</x:v>
       </x:c>
     </x:row>
+    <x:row r="77" ht="90" customHeight="1">
+      <x:c r="A77" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:1:F243</x:v>
+      </x:c>
+      <x:c r="B77" s="8" t="str">
+        <x:v>F1 → Ceiling fan · wing H · rear</x:v>
+      </x:c>
+      <x:c r="C77" s="8" t="str">
+        <x:v>FC1</x:v>
+      </x:c>
+      <x:c r="D77" s="8" t="str">
+        <x:v>F243</x:v>
+      </x:c>
+      <x:c r="E77" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F77" s="8" t="str">
+        <x:v>F1</x:v>
+      </x:c>
+      <x:c r="G77" s="8" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="H77" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I77" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$440,A77,'Route Points'!$F$7:$F$440)</x:f>
+        <x:v>7.733099226804125</x:v>
+      </x:c>
+      <x:c r="J77" s="11"/>
+      <x:c r="K77" s="11" t="str">
+        <x:f>IF(L77="Full home run",I77+J77,"")</x:f>
+      </x:c>
+      <x:c r="L77" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M77" s="13"/>
+      <x:c r="N77" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M77),L77&lt;&gt;"Shared bundle"),IF(L77="Full home run",K77,I77)+M77,"")</x:f>
+      </x:c>
+      <x:c r="O77" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P77" s="8" t="str">
+        <x:v>Above nave lining / covered soffit route at wings and verandas; cable continues inside the existing pendant stem. Roof build-up, supports and access pending.</x:v>
+      </x:c>
+      <x:c r="Q77" s="9"/>
+      <x:c r="R77" s="9"/>
+      <x:c r="S77" s="13"/>
+      <x:c r="T77" s="9"/>
+      <x:c r="U77" s="9"/>
+      <x:c r="V77" s="9"/>
+      <x:c r="W77" s="9"/>
+      <x:c r="X77" s="9"/>
+      <x:c r="Y77" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z77" s="8" t="str">
+        <x:v>trunk:FC1:F1:fan:1</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="Y7:Y69">
+  <x:conditionalFormatting sqref="Y7:Y77">
     <x:cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="M7:M69">
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="M7:M77">
       <x:formula1>0</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="R7:R69">
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="R7:R77">
       <x:formula1>0</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="S7:S69">
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="S7:S77">
       <x:formula1>0</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3cfb6a9ed3f44ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde232074433d482e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15792,19 +16271,19 @@
     </x:row>
     <x:row r="307" ht="32" customHeight="1">
       <x:c r="A307" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B307" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C307" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D307" s="11" t="n">
-        <x:v>8.565264175257731</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E307" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F307" s="11" t="n">
         <x:f>0</x:f>
@@ -15816,23 +16295,23 @@
     </x:row>
     <x:row r="308" ht="32" customHeight="1">
       <x:c r="A308" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B308" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C308" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D308" s="11" t="n">
-        <x:v>8.565264175257731</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E308" s="11" t="n">
-        <x:v>-13.249</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F308" s="11" t="n">
         <x:f>SQRT((C308-C307)^2+(D308-D307)^2+(E308-E307)^2)</x:f>
-        <x:v>5.889</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G308" s="8" t="str">
         <x:v>Current</x:v>
@@ -15840,23 +16319,23 @@
     </x:row>
     <x:row r="309" ht="32" customHeight="1">
       <x:c r="A309" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B309" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C309" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D309" s="11" t="n">
-        <x:v>7.6</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E309" s="11" t="n">
-        <x:v>-13.249</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F309" s="11" t="n">
         <x:f>SQRT((C309-C308)^2+(D309-D308)^2+(E309-E308)^2)</x:f>
-        <x:v>0.9652641752577313</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="G309" s="8" t="str">
         <x:v>Current</x:v>
@@ -15864,23 +16343,23 @@
     </x:row>
     <x:row r="310" ht="32" customHeight="1">
       <x:c r="A310" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B310" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C310" s="11" t="n">
-        <x:v>39.7</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D310" s="11" t="n">
-        <x:v>7.6</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E310" s="11" t="n">
-        <x:v>-13.13</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F310" s="11" t="n">
         <x:f>SQRT((C310-C309)^2+(D310-D309)^2+(E310-E309)^2)</x:f>
-        <x:v>0.11899999999999977</x:v>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="G310" s="8" t="str">
         <x:v>Current</x:v>
@@ -15888,23 +16367,23 @@
     </x:row>
     <x:row r="311" ht="32" customHeight="1">
       <x:c r="A311" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B311" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C311" s="11" t="n">
-        <x:v>41.45</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D311" s="11" t="n">
-        <x:v>8.565264175257724</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E311" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F311" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C311-C310)^2+(D311-D310)^2+(E311-E310)^2)</x:f>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G311" s="8" t="str">
         <x:v>Current</x:v>
@@ -15912,23 +16391,23 @@
     </x:row>
     <x:row r="312" ht="32" customHeight="1">
       <x:c r="A312" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B312" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C312" s="11" t="n">
-        <x:v>41.45</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D312" s="11" t="n">
-        <x:v>8.565264175257731</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E312" s="11" t="n">
-        <x:v>-13.249</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F312" s="11" t="n">
         <x:f>SQRT((C312-C311)^2+(D312-D311)^2+(E312-E311)^2)</x:f>
-        <x:v>5.889</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G312" s="8" t="str">
         <x:v>Current</x:v>
@@ -15936,23 +16415,23 @@
     </x:row>
     <x:row r="313" ht="32" customHeight="1">
       <x:c r="A313" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B313" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C313" s="11" t="n">
-        <x:v>41.45</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D313" s="11" t="n">
-        <x:v>7.6</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E313" s="11" t="n">
-        <x:v>-13.249</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F313" s="11" t="n">
         <x:f>SQRT((C313-C312)^2+(D313-D312)^2+(E313-E312)^2)</x:f>
-        <x:v>0.9652641752577313</x:v>
+        <x:v>1.7060000000000004</x:v>
       </x:c>
       <x:c r="G313" s="8" t="str">
         <x:v>Current</x:v>
@@ -15960,23 +16439,23 @@
     </x:row>
     <x:row r="314" ht="32" customHeight="1">
       <x:c r="A314" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B314" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C314" s="11" t="n">
-        <x:v>41.45</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D314" s="11" t="n">
-        <x:v>7.6</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E314" s="11" t="n">
-        <x:v>-13.13</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F314" s="11" t="n">
         <x:f>SQRT((C314-C313)^2+(D314-D313)^2+(E314-E313)^2)</x:f>
-        <x:v>0.11899999999999977</x:v>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G314" s="8" t="str">
         <x:v>Current</x:v>
@@ -15984,23 +16463,23 @@
     </x:row>
     <x:row r="315" ht="32" customHeight="1">
       <x:c r="A315" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B315" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C315" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D315" s="11" t="n">
         <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E315" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F315" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C315-C314)^2+(D315-D314)^2+(E315-E314)^2)</x:f>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G315" s="8" t="str">
         <x:v>Current</x:v>
@@ -16008,23 +16487,23 @@
     </x:row>
     <x:row r="316" ht="32" customHeight="1">
       <x:c r="A316" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B316" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C316" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D316" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E316" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F316" s="11" t="n">
         <x:f>SQRT((C316-C315)^2+(D316-D315)^2+(E316-E315)^2)</x:f>
-        <x:v>7.36</x:v>
+        <x:v>1.0039999999999996</x:v>
       </x:c>
       <x:c r="G316" s="8" t="str">
         <x:v>Current</x:v>
@@ -16032,23 +16511,23 @@
     </x:row>
     <x:row r="317" ht="32" customHeight="1">
       <x:c r="A317" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B317" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C317" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D317" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E317" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F317" s="11" t="n">
         <x:f>SQRT((C317-C316)^2+(D317-D316)^2+(E317-E316)^2)</x:f>
-        <x:v>2.7360000000000007</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G317" s="8" t="str">
         <x:v>Current</x:v>
@@ -16056,23 +16535,23 @@
     </x:row>
     <x:row r="318" ht="32" customHeight="1">
       <x:c r="A318" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
+        <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B318" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C318" s="11" t="n">
-        <x:v>53.12</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D318" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E318" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F318" s="11" t="n">
         <x:f>SQRT((C318-C317)^2+(D318-D317)^2+(E318-E317)^2)</x:f>
-        <x:v>0.1039999999999992</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G318" s="8" t="str">
         <x:v>Current</x:v>
@@ -16083,20 +16562,20 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B319" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C319" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D319" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E319" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F319" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C319-C318)^2+(D319-D318)^2+(E319-E318)^2)</x:f>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G319" s="8" t="str">
         <x:v>Current</x:v>
@@ -16107,20 +16586,20 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B320" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C320" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>37.695</x:v>
       </x:c>
       <x:c r="D320" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>6.950412371134018</x:v>
       </x:c>
       <x:c r="E320" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F320" s="11" t="n">
         <x:f>SQRT((C320-C319)^2+(D320-D319)^2+(E320-E319)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
+        <x:v>3.697957107375376</x:v>
       </x:c>
       <x:c r="G320" s="8" t="str">
         <x:v>Current</x:v>
@@ -16131,20 +16610,20 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B321" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C321" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>37.615</x:v>
       </x:c>
       <x:c r="D321" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E321" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F321" s="11" t="n">
         <x:f>SQRT((C321-C320)^2+(D321-D320)^2+(E321-E320)^2)</x:f>
-        <x:v>2.64</x:v>
+        <x:v>0.12010804821421713</x:v>
       </x:c>
       <x:c r="G321" s="8" t="str">
         <x:v>Current</x:v>
@@ -16155,20 +16634,20 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B322" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C322" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D322" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E322" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F322" s="11" t="n">
         <x:f>SQRT((C322-C321)^2+(D322-D321)^2+(E322-E321)^2)</x:f>
-        <x:v>2.38</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G322" s="8" t="str">
         <x:v>Current</x:v>
@@ -16179,20 +16658,20 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B323" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C323" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D323" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E323" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F323" s="11" t="n">
         <x:f>SQRT((C323-C322)^2+(D323-D322)^2+(E323-E322)^2)</x:f>
-        <x:v>1.0599999999999996</x:v>
+        <x:v>1.0039999999999996</x:v>
       </x:c>
       <x:c r="G323" s="8" t="str">
         <x:v>Current</x:v>
@@ -16203,20 +16682,20 @@
         <x:v>trunk:FC1:V1:fan:1</x:v>
       </x:c>
       <x:c r="B324" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C324" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D324" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E324" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F324" s="11" t="n">
         <x:f>SQRT((C324-C323)^2+(D324-D323)^2+(E324-E323)^2)</x:f>
-        <x:v>4.280999999999999</x:v>
+        <x:v>31.495</x:v>
       </x:c>
       <x:c r="G324" s="8" t="str">
         <x:v>Current</x:v>
@@ -16224,23 +16703,23 @@
     </x:row>
     <x:row r="325" ht="32" customHeight="1">
       <x:c r="A325" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B325" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C325" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D325" s="11" t="n">
         <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E325" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F325" s="11" t="n">
-        <x:f>SQRT((C325-C324)^2+(D325-D324)^2+(E325-E324)^2)</x:f>
-        <x:v>1.7060000000000004</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G325" s="8" t="str">
         <x:v>Current</x:v>
@@ -16248,23 +16727,23 @@
     </x:row>
     <x:row r="326" ht="32" customHeight="1">
       <x:c r="A326" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B326" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C326" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D326" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E326" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F326" s="11" t="n">
         <x:f>SQRT((C326-C325)^2+(D326-D325)^2+(E326-E325)^2)</x:f>
-        <x:v>10.66</x:v>
+        <x:v>1.0039999999999996</x:v>
       </x:c>
       <x:c r="G326" s="8" t="str">
         <x:v>Current</x:v>
@@ -16272,23 +16751,23 @@
     </x:row>
     <x:row r="327" ht="32" customHeight="1">
       <x:c r="A327" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B327" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C327" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D327" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E327" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F327" s="11" t="n">
         <x:f>SQRT((C327-C326)^2+(D327-D326)^2+(E327-E326)^2)</x:f>
-        <x:v>8.841000000000001</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G327" s="8" t="str">
         <x:v>Current</x:v>
@@ -16296,23 +16775,23 @@
     </x:row>
     <x:row r="328" ht="32" customHeight="1">
       <x:c r="A328" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B328" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C328" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D328" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>11.801347826086957</x:v>
       </x:c>
       <x:c r="E328" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>0.7999999999999998</x:v>
       </x:c>
       <x:c r="F328" s="11" t="n">
         <x:f>SQRT((C328-C327)^2+(D328-D327)^2+(E328-E327)^2)</x:f>
-        <x:v>1.0039999999999996</x:v>
+        <x:v>8.105802435353516</x:v>
       </x:c>
       <x:c r="G328" s="8" t="str">
         <x:v>Current</x:v>
@@ -16320,23 +16799,23 @@
     </x:row>
     <x:row r="329" ht="32" customHeight="1">
       <x:c r="A329" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B329" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C329" s="11" t="n">
-        <x:v>43.535</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D329" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E329" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="F329" s="11" t="n">
         <x:f>SQRT((C329-C328)^2+(D329-D328)^2+(E329-E328)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>2.4013478260869565</x:v>
       </x:c>
       <x:c r="G329" s="8" t="str">
         <x:v>Current</x:v>
@@ -16344,23 +16823,23 @@
     </x:row>
     <x:row r="330" ht="32" customHeight="1">
       <x:c r="A330" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F254</x:v>
       </x:c>
       <x:c r="B330" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C330" s="11" t="n">
-        <x:v>43.455</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D330" s="11" t="n">
-        <x:v>6.950412371134024</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E330" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="F330" s="11" t="n">
         <x:f>SQRT((C330-C329)^2+(D330-D329)^2+(E330-E329)^2)</x:f>
-        <x:v>0.12010804821421249</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G330" s="8" t="str">
         <x:v>Current</x:v>
@@ -16368,23 +16847,23 @@
     </x:row>
     <x:row r="331" ht="32" customHeight="1">
       <x:c r="A331" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B331" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C331" s="11" t="n">
-        <x:v>40.574999999999996</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D331" s="11" t="n">
-        <x:v>9.269999999999994</x:v>
+        <x:v>6.0360000000000005</x:v>
       </x:c>
       <x:c r="E331" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F331" s="11" t="n">
-        <x:f>SQRT((C331-C330)^2+(D331-D330)^2+(E331-E330)^2)</x:f>
-        <x:v>3.6979571073753776</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G331" s="8" t="str">
         <x:v>Current</x:v>
@@ -16392,23 +16871,23 @@
     </x:row>
     <x:row r="332" ht="32" customHeight="1">
       <x:c r="A332" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B332" s="8" t="n">
-        <x:v>14</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C332" s="11" t="n">
-        <x:v>37.695</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D332" s="11" t="n">
-        <x:v>6.950412371134018</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E332" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F332" s="11" t="n">
         <x:f>SQRT((C332-C331)^2+(D332-D331)^2+(E332-E331)^2)</x:f>
-        <x:v>3.697957107375376</x:v>
+        <x:v>1.0039999999999996</x:v>
       </x:c>
       <x:c r="G332" s="8" t="str">
         <x:v>Current</x:v>
@@ -16416,13 +16895,13 @@
     </x:row>
     <x:row r="333" ht="32" customHeight="1">
       <x:c r="A333" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B333" s="8" t="n">
-        <x:v>15</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C333" s="11" t="n">
-        <x:v>37.615</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D333" s="11" t="n">
         <x:v>7.04</x:v>
@@ -16432,7 +16911,7 @@
       </x:c>
       <x:c r="F333" s="11" t="n">
         <x:f>SQRT((C333-C332)^2+(D333-D332)^2+(E333-E332)^2)</x:f>
-        <x:v>0.12010804821421713</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G333" s="8" t="str">
         <x:v>Current</x:v>
@@ -16440,23 +16919,23 @@
     </x:row>
     <x:row r="334" ht="32" customHeight="1">
       <x:c r="A334" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B334" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C334" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D334" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>10.64004347826087</x:v>
       </x:c>
       <x:c r="E334" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>2.3999999999999995</x:v>
       </x:c>
       <x:c r="F334" s="11" t="n">
         <x:f>SQRT((C334-C333)^2+(D334-D333)^2+(E334-E333)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>6.128777451120952</x:v>
       </x:c>
       <x:c r="G334" s="8" t="str">
         <x:v>Current</x:v>
@@ -16464,23 +16943,23 @@
     </x:row>
     <x:row r="335" ht="32" customHeight="1">
       <x:c r="A335" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B335" s="8" t="n">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C335" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>5.32</x:v>
       </x:c>
       <x:c r="D335" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E335" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="F335" s="11" t="n">
         <x:f>SQRT((C335-C334)^2+(D335-D334)^2+(E335-E334)^2)</x:f>
-        <x:v>1.0039999999999996</x:v>
+        <x:v>1.2400434782608691</x:v>
       </x:c>
       <x:c r="G335" s="8" t="str">
         <x:v>Current</x:v>
@@ -16488,23 +16967,23 @@
     </x:row>
     <x:row r="336" ht="32" customHeight="1">
       <x:c r="A336" s="8" t="str">
-        <x:v>trunk:FC1:V1:fan:1</x:v>
+        <x:v>drop:FC1:V1:fan:1:F255</x:v>
       </x:c>
       <x:c r="B336" s="8" t="n">
-        <x:v>18</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C336" s="11" t="n">
         <x:v>5.48</x:v>
       </x:c>
       <x:c r="D336" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E336" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="F336" s="11" t="n">
         <x:f>SQRT((C336-C335)^2+(D336-D335)^2+(E336-E335)^2)</x:f>
-        <x:v>31.495</x:v>
+        <x:v>0.16000000000000014</x:v>
       </x:c>
       <x:c r="G336" s="8" t="str">
         <x:v>Current</x:v>
@@ -16512,19 +16991,19 @@
     </x:row>
     <x:row r="337" ht="32" customHeight="1">
       <x:c r="A337" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>trunk:FC1:V2:fan:-1</x:v>
       </x:c>
       <x:c r="B337" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C337" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D337" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E337" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F337" s="11" t="n">
         <x:f>0</x:f>
@@ -16536,23 +17015,23 @@
     </x:row>
     <x:row r="338" ht="32" customHeight="1">
       <x:c r="A338" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>trunk:FC1:V2:fan:-1</x:v>
       </x:c>
       <x:c r="B338" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C338" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D338" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E338" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F338" s="11" t="n">
         <x:f>SQRT((C338-C337)^2+(D338-D337)^2+(E338-E337)^2)</x:f>
-        <x:v>1.0039999999999996</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G338" s="8" t="str">
         <x:v>Current</x:v>
@@ -16560,23 +17039,23 @@
     </x:row>
     <x:row r="339" ht="32" customHeight="1">
       <x:c r="A339" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>trunk:FC1:V2:fan:-1</x:v>
       </x:c>
       <x:c r="B339" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C339" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D339" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E339" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F339" s="11" t="n">
         <x:f>SQRT((C339-C338)^2+(D339-D338)^2+(E339-E338)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="G339" s="8" t="str">
         <x:v>Current</x:v>
@@ -16584,23 +17063,23 @@
     </x:row>
     <x:row r="340" ht="32" customHeight="1">
       <x:c r="A340" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>trunk:FC1:V2:fan:-1</x:v>
       </x:c>
       <x:c r="B340" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C340" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D340" s="11" t="n">
-        <x:v>11.801347826086957</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E340" s="11" t="n">
-        <x:v>0.7999999999999998</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F340" s="11" t="n">
         <x:f>SQRT((C340-C339)^2+(D340-D339)^2+(E340-E339)^2)</x:f>
-        <x:v>8.105802435353516</x:v>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="G340" s="8" t="str">
         <x:v>Current</x:v>
@@ -16608,23 +17087,23 @@
     </x:row>
     <x:row r="341" ht="32" customHeight="1">
       <x:c r="A341" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>trunk:FC1:V2:fan:-1</x:v>
       </x:c>
       <x:c r="B341" s="8" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C341" s="11" t="n">
-        <x:v>5.32</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D341" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E341" s="11" t="n">
-        <x:v>0.8</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F341" s="11" t="n">
         <x:f>SQRT((C341-C340)^2+(D341-D340)^2+(E341-E340)^2)</x:f>
-        <x:v>2.4013478260869565</x:v>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G341" s="8" t="str">
         <x:v>Current</x:v>
@@ -16632,23 +17111,23 @@
     </x:row>
     <x:row r="342" ht="32" customHeight="1">
       <x:c r="A342" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F254</x:v>
+        <x:v>trunk:FC1:V2:fan:-1</x:v>
       </x:c>
       <x:c r="B342" s="8" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C342" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D342" s="11" t="n">
-        <x:v>9.4</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E342" s="11" t="n">
-        <x:v>0.8</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F342" s="11" t="n">
         <x:f>SQRT((C342-C341)^2+(D342-D341)^2+(E342-E341)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G342" s="8" t="str">
         <x:v>Current</x:v>
@@ -16656,1019 +17135,2363 @@
     </x:row>
     <x:row r="343" ht="32" customHeight="1">
       <x:c r="A343" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
+        <x:v>trunk:FC1:V2:fan:-1</x:v>
       </x:c>
       <x:c r="B343" s="8" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C343" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D343" s="11" t="n">
+        <x:v>6.148000000000001</x:v>
+      </x:c>
+      <x:c r="E343" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F343" s="11" t="n">
+        <x:f>SQRT((C343-C342)^2+(D343-D342)^2+(E343-E342)^2)</x:f>
+        <x:v>1.8180000000000005</x:v>
+      </x:c>
+      <x:c r="G343" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344" ht="32" customHeight="1">
+      <x:c r="A344" s="8" t="str">
+        <x:v>trunk:FC1:V2:fan:-1</x:v>
+      </x:c>
+      <x:c r="B344" s="8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C344" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D344" s="11" t="n">
+        <x:v>6.148000000000001</x:v>
+      </x:c>
+      <x:c r="E344" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F344" s="11" t="n">
+        <x:f>SQRT((C344-C343)^2+(D344-D343)^2+(E344-E343)^2)</x:f>
+        <x:v>4.0600000000000005</x:v>
+      </x:c>
+      <x:c r="G344" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345" ht="32" customHeight="1">
+      <x:c r="A345" s="8" t="str">
+        <x:v>trunk:FC1:V2:fan:-1</x:v>
+      </x:c>
+      <x:c r="B345" s="8" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C345" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D345" s="11" t="n">
+        <x:v>6.148000000000001</x:v>
+      </x:c>
+      <x:c r="E345" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F345" s="11" t="n">
+        <x:f>SQRT((C345-C344)^2+(D345-D344)^2+(E345-E344)^2)</x:f>
+        <x:v>8.841000000000001</x:v>
+      </x:c>
+      <x:c r="G345" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="346" ht="32" customHeight="1">
+      <x:c r="A346" s="8" t="str">
+        <x:v>trunk:FC1:V2:fan:-1</x:v>
+      </x:c>
+      <x:c r="B346" s="8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C346" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D346" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E346" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F346" s="11" t="n">
+        <x:f>SQRT((C346-C345)^2+(D346-D345)^2+(E346-E345)^2)</x:f>
+        <x:v>0.8919999999999995</x:v>
+      </x:c>
+      <x:c r="G346" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347" ht="32" customHeight="1">
+      <x:c r="A347" s="8" t="str">
+        <x:v>trunk:FC1:V2:fan:-1</x:v>
+      </x:c>
+      <x:c r="B347" s="8" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C347" s="11" t="n">
+        <x:v>43.535</x:v>
+      </x:c>
+      <x:c r="D347" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E347" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F347" s="11" t="n">
+        <x:f>SQRT((C347-C346)^2+(D347-D346)^2+(E347-E346)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G347" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348" ht="32" customHeight="1">
+      <x:c r="A348" s="8" t="str">
+        <x:v>trunk:FC1:V2:fan:-1</x:v>
+      </x:c>
+      <x:c r="B348" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C348" s="11" t="n">
+        <x:v>43.455</x:v>
+      </x:c>
+      <x:c r="D348" s="11" t="n">
+        <x:v>6.950412371134024</x:v>
+      </x:c>
+      <x:c r="E348" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F348" s="11" t="n">
+        <x:f>SQRT((C348-C347)^2+(D348-D347)^2+(E348-E347)^2)</x:f>
+        <x:v>0.12010804821421249</x:v>
+      </x:c>
+      <x:c r="G348" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349" ht="32" customHeight="1">
+      <x:c r="A349" s="8" t="str">
+        <x:v>trunk:FC1:V2:fan:-1</x:v>
+      </x:c>
+      <x:c r="B349" s="8" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C349" s="11" t="n">
+        <x:v>40.574999999999996</x:v>
+      </x:c>
+      <x:c r="D349" s="11" t="n">
+        <x:v>9.269999999999994</x:v>
+      </x:c>
+      <x:c r="E349" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F349" s="11" t="n">
+        <x:f>SQRT((C349-C348)^2+(D349-D348)^2+(E349-E348)^2)</x:f>
+        <x:v>3.6979571073753776</x:v>
+      </x:c>
+      <x:c r="G349" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350" ht="32" customHeight="1">
+      <x:c r="A350" s="8" t="str">
+        <x:v>trunk:FC1:V2:fan:-1</x:v>
+      </x:c>
+      <x:c r="B350" s="8" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C350" s="11" t="n">
+        <x:v>39.7</x:v>
+      </x:c>
+      <x:c r="D350" s="11" t="n">
+        <x:v>8.565264175257731</x:v>
+      </x:c>
+      <x:c r="E350" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F350" s="11" t="n">
+        <x:f>SQRT((C350-C349)^2+(D350-D349)^2+(E350-E349)^2)</x:f>
+        <x:v>1.1235112739421647</x:v>
+      </x:c>
+      <x:c r="G350" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351" ht="32" customHeight="1">
+      <x:c r="A351" s="8" t="str">
+        <x:v>drop:FC1:V2:fan:-1:F256</x:v>
+      </x:c>
+      <x:c r="B351" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C343" s="11" t="n">
-        <x:v>5.48</x:v>
-      </x:c>
-      <x:c r="D343" s="11" t="n">
-        <x:v>6.0360000000000005</x:v>
-      </x:c>
-      <x:c r="E343" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F343" s="11" t="n">
+      <x:c r="C351" s="11" t="n">
+        <x:v>39.7</x:v>
+      </x:c>
+      <x:c r="D351" s="11" t="n">
+        <x:v>8.565264175257731</x:v>
+      </x:c>
+      <x:c r="E351" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F351" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G343" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="344" ht="32" customHeight="1">
-      <x:c r="A344" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
-      </x:c>
-      <x:c r="B344" s="8" t="n">
+      <x:c r="G351" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352" ht="32" customHeight="1">
+      <x:c r="A352" s="8" t="str">
+        <x:v>drop:FC1:V2:fan:-1:F256</x:v>
+      </x:c>
+      <x:c r="B352" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C344" s="11" t="n">
-        <x:v>5.48</x:v>
-      </x:c>
-      <x:c r="D344" s="11" t="n">
-        <x:v>7.04</x:v>
-      </x:c>
-      <x:c r="E344" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F344" s="11" t="n">
-        <x:f>SQRT((C344-C343)^2+(D344-D343)^2+(E344-E343)^2)</x:f>
-        <x:v>1.0039999999999996</x:v>
-      </x:c>
-      <x:c r="G344" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="345" ht="32" customHeight="1">
-      <x:c r="A345" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
-      </x:c>
-      <x:c r="B345" s="8" t="n">
+      <x:c r="C352" s="11" t="n">
+        <x:v>39.7</x:v>
+      </x:c>
+      <x:c r="D352" s="11" t="n">
+        <x:v>8.565264175257731</x:v>
+      </x:c>
+      <x:c r="E352" s="11" t="n">
+        <x:v>-13.249</x:v>
+      </x:c>
+      <x:c r="F352" s="11" t="n">
+        <x:f>SQRT((C352-C351)^2+(D352-D351)^2+(E352-E351)^2)</x:f>
+        <x:v>5.889</x:v>
+      </x:c>
+      <x:c r="G352" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353" ht="32" customHeight="1">
+      <x:c r="A353" s="8" t="str">
+        <x:v>drop:FC1:V2:fan:-1:F256</x:v>
+      </x:c>
+      <x:c r="B353" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C345" s="11" t="n">
-        <x:v>5.32</x:v>
-      </x:c>
-      <x:c r="D345" s="11" t="n">
-        <x:v>7.04</x:v>
-      </x:c>
-      <x:c r="E345" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F345" s="11" t="n">
-        <x:f>SQRT((C345-C344)^2+(D345-D344)^2+(E345-E344)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
-      </x:c>
-      <x:c r="G345" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="346" ht="32" customHeight="1">
-      <x:c r="A346" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
-      </x:c>
-      <x:c r="B346" s="8" t="n">
+      <x:c r="C353" s="11" t="n">
+        <x:v>39.7</x:v>
+      </x:c>
+      <x:c r="D353" s="11" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="E353" s="11" t="n">
+        <x:v>-13.249</x:v>
+      </x:c>
+      <x:c r="F353" s="11" t="n">
+        <x:f>SQRT((C353-C352)^2+(D353-D352)^2+(E353-E352)^2)</x:f>
+        <x:v>0.9652641752577313</x:v>
+      </x:c>
+      <x:c r="G353" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354" ht="32" customHeight="1">
+      <x:c r="A354" s="8" t="str">
+        <x:v>drop:FC1:V2:fan:-1:F256</x:v>
+      </x:c>
+      <x:c r="B354" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C346" s="11" t="n">
-        <x:v>5.32</x:v>
-      </x:c>
-      <x:c r="D346" s="11" t="n">
-        <x:v>10.64004347826087</x:v>
-      </x:c>
-      <x:c r="E346" s="11" t="n">
-        <x:v>2.3999999999999995</x:v>
-      </x:c>
-      <x:c r="F346" s="11" t="n">
-        <x:f>SQRT((C346-C345)^2+(D346-D345)^2+(E346-E345)^2)</x:f>
-        <x:v>6.128777451120952</x:v>
-      </x:c>
-      <x:c r="G346" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="347" ht="32" customHeight="1">
-      <x:c r="A347" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
-      </x:c>
-      <x:c r="B347" s="8" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C347" s="11" t="n">
-        <x:v>5.32</x:v>
-      </x:c>
-      <x:c r="D347" s="11" t="n">
-        <x:v>9.4</x:v>
-      </x:c>
-      <x:c r="E347" s="11" t="n">
-        <x:v>2.4</x:v>
-      </x:c>
-      <x:c r="F347" s="11" t="n">
-        <x:f>SQRT((C347-C346)^2+(D347-D346)^2+(E347-E346)^2)</x:f>
-        <x:v>1.2400434782608691</x:v>
-      </x:c>
-      <x:c r="G347" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="348" ht="32" customHeight="1">
-      <x:c r="A348" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F255</x:v>
-      </x:c>
-      <x:c r="B348" s="8" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C348" s="11" t="n">
-        <x:v>5.48</x:v>
-      </x:c>
-      <x:c r="D348" s="11" t="n">
-        <x:v>9.4</x:v>
-      </x:c>
-      <x:c r="E348" s="11" t="n">
-        <x:v>2.4</x:v>
-      </x:c>
-      <x:c r="F348" s="11" t="n">
-        <x:f>SQRT((C348-C347)^2+(D348-D347)^2+(E348-E347)^2)</x:f>
-        <x:v>0.16000000000000014</x:v>
-      </x:c>
-      <x:c r="G348" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="349" ht="32" customHeight="1">
-      <x:c r="A349" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F258</x:v>
-      </x:c>
-      <x:c r="B349" s="8" t="n">
+      <x:c r="C354" s="11" t="n">
+        <x:v>39.7</x:v>
+      </x:c>
+      <x:c r="D354" s="11" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="E354" s="11" t="n">
+        <x:v>-13.13</x:v>
+      </x:c>
+      <x:c r="F354" s="11" t="n">
+        <x:f>SQRT((C354-C353)^2+(D354-D353)^2+(E354-E353)^2)</x:f>
+        <x:v>0.11899999999999977</x:v>
+      </x:c>
+      <x:c r="G354" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355" ht="32" customHeight="1">
+      <x:c r="A355" s="8" t="str">
+        <x:v>drop:FC1:V2:fan:-1:F257</x:v>
+      </x:c>
+      <x:c r="B355" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C349" s="11" t="n">
-        <x:v>39.7</x:v>
-      </x:c>
-      <x:c r="D349" s="11" t="n">
-        <x:v>8.565264175257731</x:v>
-      </x:c>
-      <x:c r="E349" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F349" s="11" t="n">
+      <x:c r="C355" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D355" s="11" t="n">
+        <x:v>8.565264175257724</x:v>
+      </x:c>
+      <x:c r="E355" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F355" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G349" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="350" ht="32" customHeight="1">
-      <x:c r="A350" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F258</x:v>
-      </x:c>
-      <x:c r="B350" s="8" t="n">
+      <x:c r="G355" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356" ht="32" customHeight="1">
+      <x:c r="A356" s="8" t="str">
+        <x:v>drop:FC1:V2:fan:-1:F257</x:v>
+      </x:c>
+      <x:c r="B356" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C350" s="11" t="n">
-        <x:v>39.7</x:v>
-      </x:c>
-      <x:c r="D350" s="11" t="n">
+      <x:c r="C356" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D356" s="11" t="n">
         <x:v>8.565264175257731</x:v>
       </x:c>
-      <x:c r="E350" s="11" t="n">
-        <x:v>13.249</x:v>
-      </x:c>
-      <x:c r="F350" s="11" t="n">
-        <x:f>SQRT((C350-C349)^2+(D350-D349)^2+(E350-E349)^2)</x:f>
+      <x:c r="E356" s="11" t="n">
+        <x:v>-13.249</x:v>
+      </x:c>
+      <x:c r="F356" s="11" t="n">
+        <x:f>SQRT((C356-C355)^2+(D356-D355)^2+(E356-E355)^2)</x:f>
         <x:v>5.889</x:v>
       </x:c>
-      <x:c r="G350" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="351" ht="32" customHeight="1">
-      <x:c r="A351" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F258</x:v>
-      </x:c>
-      <x:c r="B351" s="8" t="n">
+      <x:c r="G356" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357" ht="32" customHeight="1">
+      <x:c r="A357" s="8" t="str">
+        <x:v>drop:FC1:V2:fan:-1:F257</x:v>
+      </x:c>
+      <x:c r="B357" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C351" s="11" t="n">
-        <x:v>39.7</x:v>
-      </x:c>
-      <x:c r="D351" s="11" t="n">
+      <x:c r="C357" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D357" s="11" t="n">
         <x:v>7.6</x:v>
       </x:c>
-      <x:c r="E351" s="11" t="n">
-        <x:v>13.249</x:v>
-      </x:c>
-      <x:c r="F351" s="11" t="n">
-        <x:f>SQRT((C351-C350)^2+(D351-D350)^2+(E351-E350)^2)</x:f>
+      <x:c r="E357" s="11" t="n">
+        <x:v>-13.249</x:v>
+      </x:c>
+      <x:c r="F357" s="11" t="n">
+        <x:f>SQRT((C357-C356)^2+(D357-D356)^2+(E357-E356)^2)</x:f>
         <x:v>0.9652641752577313</x:v>
       </x:c>
-      <x:c r="G351" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="352" ht="32" customHeight="1">
-      <x:c r="A352" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F258</x:v>
-      </x:c>
-      <x:c r="B352" s="8" t="n">
+      <x:c r="G357" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358" ht="32" customHeight="1">
+      <x:c r="A358" s="8" t="str">
+        <x:v>drop:FC1:V2:fan:-1:F257</x:v>
+      </x:c>
+      <x:c r="B358" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C352" s="11" t="n">
-        <x:v>39.7</x:v>
-      </x:c>
-      <x:c r="D352" s="11" t="n">
+      <x:c r="C358" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D358" s="11" t="n">
         <x:v>7.6</x:v>
       </x:c>
-      <x:c r="E352" s="11" t="n">
-        <x:v>13.13</x:v>
-      </x:c>
-      <x:c r="F352" s="11" t="n">
-        <x:f>SQRT((C352-C351)^2+(D352-D351)^2+(E352-E351)^2)</x:f>
+      <x:c r="E358" s="11" t="n">
+        <x:v>-13.13</x:v>
+      </x:c>
+      <x:c r="F358" s="11" t="n">
+        <x:f>SQRT((C358-C357)^2+(D358-D357)^2+(E358-E357)^2)</x:f>
         <x:v>0.11899999999999977</x:v>
       </x:c>
-      <x:c r="G352" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="353" ht="32" customHeight="1">
-      <x:c r="A353" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F259</x:v>
-      </x:c>
-      <x:c r="B353" s="8" t="n">
+      <x:c r="G358" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359" ht="32" customHeight="1">
+      <x:c r="A359" s="8" t="str">
+        <x:v>trunk:FC1:V2:fan:1</x:v>
+      </x:c>
+      <x:c r="B359" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C353" s="11" t="n">
-        <x:v>41.45</x:v>
-      </x:c>
-      <x:c r="D353" s="11" t="n">
-        <x:v>8.565264175257724</x:v>
-      </x:c>
-      <x:c r="E353" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F353" s="11" t="n">
+      <x:c r="C359" s="11" t="n">
+        <x:v>48.895</x:v>
+      </x:c>
+      <x:c r="D359" s="11" t="n">
+        <x:v>1.95</x:v>
+      </x:c>
+      <x:c r="E359" s="11" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="F359" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G353" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="354" ht="32" customHeight="1">
-      <x:c r="A354" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F259</x:v>
-      </x:c>
-      <x:c r="B354" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C354" s="11" t="n">
-        <x:v>41.45</x:v>
-      </x:c>
-      <x:c r="D354" s="11" t="n">
-        <x:v>8.565264175257731</x:v>
-      </x:c>
-      <x:c r="E354" s="11" t="n">
-        <x:v>13.249</x:v>
-      </x:c>
-      <x:c r="F354" s="11" t="n">
-        <x:f>SQRT((C354-C353)^2+(D354-D353)^2+(E354-E353)^2)</x:f>
-        <x:v>5.889</x:v>
-      </x:c>
-      <x:c r="G354" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="355" ht="32" customHeight="1">
-      <x:c r="A355" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F259</x:v>
-      </x:c>
-      <x:c r="B355" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C355" s="11" t="n">
-        <x:v>41.45</x:v>
-      </x:c>
-      <x:c r="D355" s="11" t="n">
-        <x:v>7.6</x:v>
-      </x:c>
-      <x:c r="E355" s="11" t="n">
-        <x:v>13.249</x:v>
-      </x:c>
-      <x:c r="F355" s="11" t="n">
-        <x:f>SQRT((C355-C354)^2+(D355-D354)^2+(E355-E354)^2)</x:f>
-        <x:v>0.9652641752577313</x:v>
-      </x:c>
-      <x:c r="G355" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="356" ht="32" customHeight="1">
-      <x:c r="A356" s="8" t="str">
-        <x:v>drop:FC1:V1:fan:1:F259</x:v>
-      </x:c>
-      <x:c r="B356" s="8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C356" s="11" t="n">
-        <x:v>41.45</x:v>
-      </x:c>
-      <x:c r="D356" s="11" t="n">
-        <x:v>7.6</x:v>
-      </x:c>
-      <x:c r="E356" s="11" t="n">
-        <x:v>13.13</x:v>
-      </x:c>
-      <x:c r="F356" s="11" t="n">
-        <x:f>SQRT((C356-C355)^2+(D356-D355)^2+(E356-E355)^2)</x:f>
-        <x:v>0.11899999999999977</x:v>
-      </x:c>
-      <x:c r="G356" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="357" ht="32" customHeight="1">
-      <x:c r="A357" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
-      </x:c>
-      <x:c r="B357" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C357" s="11" t="n">
-        <x:v>41.2</x:v>
-      </x:c>
-      <x:c r="D357" s="11" t="n">
-        <x:v>8.766617268041228</x:v>
-      </x:c>
-      <x:c r="E357" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F357" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G357" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="358" ht="32" customHeight="1">
-      <x:c r="A358" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
-      </x:c>
-      <x:c r="B358" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C358" s="11" t="n">
-        <x:v>41.2</x:v>
-      </x:c>
-      <x:c r="D358" s="11" t="n">
-        <x:v>8.766617268041237</x:v>
-      </x:c>
-      <x:c r="E358" s="11" t="n">
-        <x:v>-13.249</x:v>
-      </x:c>
-      <x:c r="F358" s="11" t="n">
-        <x:f>SQRT((C358-C357)^2+(D358-D357)^2+(E358-E357)^2)</x:f>
-        <x:v>5.889</x:v>
-      </x:c>
-      <x:c r="G358" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="359" ht="32" customHeight="1">
-      <x:c r="A359" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
-      </x:c>
-      <x:c r="B359" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C359" s="11" t="n">
-        <x:v>41.2</x:v>
-      </x:c>
-      <x:c r="D359" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E359" s="11" t="n">
-        <x:v>-13.249</x:v>
-      </x:c>
-      <x:c r="F359" s="11" t="n">
-        <x:f>SQRT((C359-C358)^2+(D359-D358)^2+(E359-E358)^2)</x:f>
-        <x:v>6.066617268041237</x:v>
-      </x:c>
       <x:c r="G359" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="360" ht="32" customHeight="1">
       <x:c r="A360" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+        <x:v>trunk:FC1:V2:fan:1</x:v>
       </x:c>
       <x:c r="B360" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C360" s="11" t="n">
-        <x:v>41.2</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D360" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E360" s="11" t="n">
-        <x:v>-13.06</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F360" s="11" t="n">
         <x:f>SQRT((C360-C359)^2+(D360-D359)^2+(E360-E359)^2)</x:f>
-        <x:v>0.18900000000000006</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G360" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="361" ht="32" customHeight="1">
       <x:c r="A361" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+        <x:v>trunk:FC1:V2:fan:1</x:v>
       </x:c>
       <x:c r="B361" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C361" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D361" s="11" t="n">
-        <x:v>8.122287371134018</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E361" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F361" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C361-C360)^2+(D361-D360)^2+(E361-E360)^2)</x:f>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="G361" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="362" ht="32" customHeight="1">
       <x:c r="A362" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+        <x:v>trunk:FC1:V2:fan:1</x:v>
       </x:c>
       <x:c r="B362" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C362" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D362" s="11" t="n">
-        <x:v>8.122287371134023</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E362" s="11" t="n">
-        <x:v>-13.249</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F362" s="11" t="n">
         <x:f>SQRT((C362-C361)^2+(D362-D361)^2+(E362-E361)^2)</x:f>
-        <x:v>5.889</x:v>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="G362" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="363" ht="32" customHeight="1">
       <x:c r="A363" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+        <x:v>trunk:FC1:V2:fan:1</x:v>
       </x:c>
       <x:c r="B363" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C363" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D363" s="11" t="n">
-        <x:v>3.5</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E363" s="11" t="n">
-        <x:v>-13.249</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F363" s="11" t="n">
         <x:f>SQRT((C363-C362)^2+(D363-D362)^2+(E363-E362)^2)</x:f>
-        <x:v>4.622287371134023</x:v>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G363" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="364" ht="32" customHeight="1">
       <x:c r="A364" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+        <x:v>trunk:FC1:V2:fan:1</x:v>
       </x:c>
       <x:c r="B364" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C364" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D364" s="11" t="n">
-        <x:v>3.5</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E364" s="11" t="n">
-        <x:v>-13.06</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F364" s="11" t="n">
         <x:f>SQRT((C364-C363)^2+(D364-D363)^2+(E364-E363)^2)</x:f>
-        <x:v>0.18900000000000006</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G364" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="365" ht="32" customHeight="1">
       <x:c r="A365" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+        <x:v>trunk:FC1:V2:fan:1</x:v>
       </x:c>
       <x:c r="B365" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C365" s="11" t="n">
-        <x:v>41.2</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D365" s="11" t="n">
-        <x:v>8.766617268041228</x:v>
+        <x:v>6.148000000000001</x:v>
       </x:c>
       <x:c r="E365" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F365" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C365-C364)^2+(D365-D364)^2+(E365-E364)^2)</x:f>
+        <x:v>1.8180000000000005</x:v>
       </x:c>
       <x:c r="G365" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="366" ht="32" customHeight="1">
       <x:c r="A366" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+        <x:v>trunk:FC1:V2:fan:1</x:v>
       </x:c>
       <x:c r="B366" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C366" s="11" t="n">
-        <x:v>41.2</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D366" s="11" t="n">
-        <x:v>8.766617268041237</x:v>
+        <x:v>6.148000000000001</x:v>
       </x:c>
       <x:c r="E366" s="11" t="n">
-        <x:v>13.249</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F366" s="11" t="n">
         <x:f>SQRT((C366-C365)^2+(D366-D365)^2+(E366-E365)^2)</x:f>
-        <x:v>5.889</x:v>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G366" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="367" ht="32" customHeight="1">
       <x:c r="A367" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+        <x:v>trunk:FC1:V2:fan:1</x:v>
       </x:c>
       <x:c r="B367" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C367" s="11" t="n">
-        <x:v>41.2</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D367" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>6.148000000000001</x:v>
       </x:c>
       <x:c r="E367" s="11" t="n">
-        <x:v>13.249</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F367" s="11" t="n">
         <x:f>SQRT((C367-C366)^2+(D367-D366)^2+(E367-E366)^2)</x:f>
-        <x:v>6.066617268041237</x:v>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G367" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="368" ht="32" customHeight="1">
       <x:c r="A368" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+        <x:v>trunk:FC1:V2:fan:1</x:v>
       </x:c>
       <x:c r="B368" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C368" s="11" t="n">
-        <x:v>41.2</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D368" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E368" s="11" t="n">
-        <x:v>13.06</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F368" s="11" t="n">
         <x:f>SQRT((C368-C367)^2+(D368-D367)^2+(E368-E367)^2)</x:f>
-        <x:v>0.18900000000000006</x:v>
+        <x:v>0.8919999999999995</x:v>
       </x:c>
       <x:c r="G368" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="369" ht="32" customHeight="1">
       <x:c r="A369" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+        <x:v>trunk:FC1:V2:fan:1</x:v>
       </x:c>
       <x:c r="B369" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C369" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D369" s="11" t="n">
-        <x:v>8.122287371134018</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E369" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F369" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C369-C368)^2+(D369-D368)^2+(E369-E368)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G369" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="370" ht="32" customHeight="1">
       <x:c r="A370" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+        <x:v>trunk:FC1:V2:fan:1</x:v>
       </x:c>
       <x:c r="B370" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C370" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D370" s="11" t="n">
-        <x:v>8.122287371134023</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E370" s="11" t="n">
-        <x:v>13.249</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F370" s="11" t="n">
         <x:f>SQRT((C370-C369)^2+(D370-D369)^2+(E370-E369)^2)</x:f>
-        <x:v>5.889</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G370" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="371" ht="32" customHeight="1">
       <x:c r="A371" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+        <x:v>trunk:FC1:V2:fan:1</x:v>
       </x:c>
       <x:c r="B371" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C371" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D371" s="11" t="n">
-        <x:v>3.5</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E371" s="11" t="n">
-        <x:v>13.249</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F371" s="11" t="n">
         <x:f>SQRT((C371-C370)^2+(D371-D370)^2+(E371-E370)^2)</x:f>
-        <x:v>4.622287371134023</x:v>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G371" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="372" ht="32" customHeight="1">
       <x:c r="A372" s="8" t="str">
-        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+        <x:v>trunk:FC1:V2:fan:1</x:v>
       </x:c>
       <x:c r="B372" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C372" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D372" s="11" t="n">
-        <x:v>3.5</x:v>
+        <x:v>8.565264175257731</x:v>
       </x:c>
       <x:c r="E372" s="11" t="n">
-        <x:v>13.06</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F372" s="11" t="n">
         <x:f>SQRT((C372-C371)^2+(D372-D371)^2+(E372-E371)^2)</x:f>
-        <x:v>0.18900000000000006</x:v>
+        <x:v>1.1235112739421647</x:v>
       </x:c>
       <x:c r="G372" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="373" ht="32" customHeight="1">
       <x:c r="A373" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
+        <x:v>drop:FC1:V2:fan:1:F258</x:v>
       </x:c>
       <x:c r="B373" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C373" s="11" t="n">
-        <x:v>39.3</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D373" s="11" t="n">
-        <x:v>8.24309922680412</x:v>
+        <x:v>8.565264175257731</x:v>
       </x:c>
       <x:c r="E373" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F373" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G373" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="374" ht="32" customHeight="1">
       <x:c r="A374" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
+        <x:v>drop:FC1:V2:fan:1:F258</x:v>
       </x:c>
       <x:c r="B374" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C374" s="11" t="n">
-        <x:v>39.3</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D374" s="11" t="n">
-        <x:v>8.24309922680412</x:v>
+        <x:v>8.565264175257731</x:v>
       </x:c>
       <x:c r="E374" s="11" t="n">
-        <x:v>-10.15</x:v>
+        <x:v>13.249</x:v>
       </x:c>
       <x:c r="F374" s="11" t="n">
         <x:f>SQRT((C374-C373)^2+(D374-D373)^2+(E374-E373)^2)</x:f>
-        <x:v>2.79</x:v>
+        <x:v>5.889</x:v>
       </x:c>
       <x:c r="G374" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="375" ht="32" customHeight="1">
       <x:c r="A375" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
+        <x:v>drop:FC1:V2:fan:1:F258</x:v>
       </x:c>
       <x:c r="B375" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C375" s="11" t="n">
-        <x:v>39.3</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="D375" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="E375" s="11" t="n">
-        <x:v>-10.15</x:v>
+        <x:v>13.249</x:v>
       </x:c>
       <x:c r="F375" s="11" t="n">
         <x:f>SQRT((C375-C374)^2+(D375-D374)^2+(E375-E374)^2)</x:f>
-        <x:v>4.94309922680412</x:v>
+        <x:v>0.9652641752577313</x:v>
       </x:c>
       <x:c r="G375" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="376" ht="32" customHeight="1">
       <x:c r="A376" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+        <x:v>drop:FC1:V2:fan:1:F258</x:v>
       </x:c>
       <x:c r="B376" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C376" s="11" t="n">
+        <x:v>39.7</x:v>
+      </x:c>
+      <x:c r="D376" s="11" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="E376" s="11" t="n">
+        <x:v>13.13</x:v>
+      </x:c>
+      <x:c r="F376" s="11" t="n">
+        <x:f>SQRT((C376-C375)^2+(D376-D375)^2+(E376-E375)^2)</x:f>
+        <x:v>0.11899999999999977</x:v>
+      </x:c>
+      <x:c r="G376" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377" ht="32" customHeight="1">
+      <x:c r="A377" s="8" t="str">
+        <x:v>drop:FC1:V2:fan:1:F259</x:v>
+      </x:c>
+      <x:c r="B377" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C376" s="11" t="n">
-        <x:v>41.85</x:v>
-      </x:c>
-      <x:c r="D376" s="11" t="n">
-        <x:v>8.243099226804118</x:v>
-      </x:c>
-      <x:c r="E376" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F376" s="11" t="n">
+      <x:c r="C377" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D377" s="11" t="n">
+        <x:v>8.565264175257724</x:v>
+      </x:c>
+      <x:c r="E377" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F377" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G376" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="377" ht="32" customHeight="1">
-      <x:c r="A377" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
-      </x:c>
-      <x:c r="B377" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C377" s="11" t="n">
-        <x:v>41.85</x:v>
-      </x:c>
-      <x:c r="D377" s="11" t="n">
-        <x:v>8.243099226804125</x:v>
-      </x:c>
-      <x:c r="E377" s="11" t="n">
-        <x:v>-10.15</x:v>
-      </x:c>
-      <x:c r="F377" s="11" t="n">
-        <x:f>SQRT((C377-C376)^2+(D377-D376)^2+(E377-E376)^2)</x:f>
-        <x:v>2.79</x:v>
-      </x:c>
       <x:c r="G377" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="378" ht="32" customHeight="1">
       <x:c r="A378" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+        <x:v>drop:FC1:V2:fan:1:F259</x:v>
       </x:c>
       <x:c r="B378" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C378" s="11" t="n">
-        <x:v>41.85</x:v>
+        <x:v>41.45</x:v>
       </x:c>
       <x:c r="D378" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>8.565264175257731</x:v>
       </x:c>
       <x:c r="E378" s="11" t="n">
-        <x:v>-10.15</x:v>
+        <x:v>13.249</x:v>
       </x:c>
       <x:c r="F378" s="11" t="n">
         <x:f>SQRT((C378-C377)^2+(D378-D377)^2+(E378-E377)^2)</x:f>
-        <x:v>4.943099226804125</x:v>
+        <x:v>5.889</x:v>
       </x:c>
       <x:c r="G378" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="379" ht="32" customHeight="1">
       <x:c r="A379" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F242</x:v>
+        <x:v>drop:FC1:V2:fan:1:F259</x:v>
       </x:c>
       <x:c r="B379" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C379" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D379" s="11" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="E379" s="11" t="n">
+        <x:v>13.249</x:v>
+      </x:c>
+      <x:c r="F379" s="11" t="n">
+        <x:f>SQRT((C379-C378)^2+(D379-D378)^2+(E379-E378)^2)</x:f>
+        <x:v>0.9652641752577313</x:v>
+      </x:c>
+      <x:c r="G379" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="380" ht="32" customHeight="1">
+      <x:c r="A380" s="8" t="str">
+        <x:v>drop:FC1:V2:fan:1:F259</x:v>
+      </x:c>
+      <x:c r="B380" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C380" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D380" s="11" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="E380" s="11" t="n">
+        <x:v>13.13</x:v>
+      </x:c>
+      <x:c r="F380" s="11" t="n">
+        <x:f>SQRT((C380-C379)^2+(D380-D379)^2+(E380-E379)^2)</x:f>
+        <x:v>0.11899999999999977</x:v>
+      </x:c>
+      <x:c r="G380" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381" ht="32" customHeight="1">
+      <x:c r="A381" s="8" t="str">
+        <x:v>trunk:FC1:V3:fan:-1</x:v>
+      </x:c>
+      <x:c r="B381" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C379" s="11" t="n">
-        <x:v>39.3</x:v>
-      </x:c>
-      <x:c r="D379" s="11" t="n">
-        <x:v>8.24309922680412</x:v>
-      </x:c>
-      <x:c r="E379" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F379" s="11" t="n">
+      <x:c r="C381" s="11" t="n">
+        <x:v>48.895</x:v>
+      </x:c>
+      <x:c r="D381" s="11" t="n">
+        <x:v>1.95</x:v>
+      </x:c>
+      <x:c r="E381" s="11" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="F381" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G379" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="380" ht="32" customHeight="1">
-      <x:c r="A380" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F242</x:v>
-      </x:c>
-      <x:c r="B380" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C380" s="11" t="n">
-        <x:v>39.3</x:v>
-      </x:c>
-      <x:c r="D380" s="11" t="n">
-        <x:v>8.24309922680412</x:v>
-      </x:c>
-      <x:c r="E380" s="11" t="n">
-        <x:v>10.15</x:v>
-      </x:c>
-      <x:c r="F380" s="11" t="n">
-        <x:f>SQRT((C380-C379)^2+(D380-D379)^2+(E380-E379)^2)</x:f>
-        <x:v>2.79</x:v>
-      </x:c>
-      <x:c r="G380" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="381" ht="32" customHeight="1">
-      <x:c r="A381" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F242</x:v>
-      </x:c>
-      <x:c r="B381" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C381" s="11" t="n">
-        <x:v>39.3</x:v>
-      </x:c>
-      <x:c r="D381" s="11" t="n">
-        <x:v>3.3</x:v>
-      </x:c>
-      <x:c r="E381" s="11" t="n">
-        <x:v>10.15</x:v>
-      </x:c>
-      <x:c r="F381" s="11" t="n">
-        <x:f>SQRT((C381-C380)^2+(D381-D380)^2+(E381-E380)^2)</x:f>
-        <x:v>4.94309922680412</x:v>
-      </x:c>
       <x:c r="G381" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="382" ht="32" customHeight="1">
       <x:c r="A382" s="8" t="str">
-        <x:v>drop:FC1:F1:fan:1:F243</x:v>
+        <x:v>trunk:FC1:V3:fan:-1</x:v>
       </x:c>
       <x:c r="B382" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C382" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D382" s="11" t="n">
+        <x:v>1.95</x:v>
+      </x:c>
+      <x:c r="E382" s="11" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="F382" s="11" t="n">
+        <x:f>SQRT((C382-C381)^2+(D382-D381)^2+(E382-E381)^2)</x:f>
+        <x:v>0.1600000000000037</x:v>
+      </x:c>
+      <x:c r="G382" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="383" ht="32" customHeight="1">
+      <x:c r="A383" s="8" t="str">
+        <x:v>trunk:FC1:V3:fan:-1</x:v>
+      </x:c>
+      <x:c r="B383" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C383" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D383" s="11" t="n">
+        <x:v>1.95</x:v>
+      </x:c>
+      <x:c r="E383" s="11" t="n">
+        <x:v>-2.24</x:v>
+      </x:c>
+      <x:c r="F383" s="11" t="n">
+        <x:f>SQRT((C383-C382)^2+(D383-D382)^2+(E383-E382)^2)</x:f>
+        <x:v>2.64</x:v>
+      </x:c>
+      <x:c r="G383" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384" ht="32" customHeight="1">
+      <x:c r="A384" s="8" t="str">
+        <x:v>trunk:FC1:V3:fan:-1</x:v>
+      </x:c>
+      <x:c r="B384" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C384" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D384" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E384" s="11" t="n">
+        <x:v>-2.24</x:v>
+      </x:c>
+      <x:c r="F384" s="11" t="n">
+        <x:f>SQRT((C384-C383)^2+(D384-D383)^2+(E384-E383)^2)</x:f>
+        <x:v>2.38</x:v>
+      </x:c>
+      <x:c r="G384" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="385" ht="32" customHeight="1">
+      <x:c r="A385" s="8" t="str">
+        <x:v>trunk:FC1:V3:fan:-1</x:v>
+      </x:c>
+      <x:c r="B385" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C385" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D385" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E385" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F385" s="11" t="n">
+        <x:f>SQRT((C385-C384)^2+(D385-D384)^2+(E385-E384)^2)</x:f>
+        <x:v>1.0599999999999996</x:v>
+      </x:c>
+      <x:c r="G385" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386" ht="32" customHeight="1">
+      <x:c r="A386" s="8" t="str">
+        <x:v>trunk:FC1:V3:fan:-1</x:v>
+      </x:c>
+      <x:c r="B386" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C386" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D386" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E386" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F386" s="11" t="n">
+        <x:f>SQRT((C386-C385)^2+(D386-D385)^2+(E386-E385)^2)</x:f>
+        <x:v>4.280999999999999</x:v>
+      </x:c>
+      <x:c r="G386" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387" ht="32" customHeight="1">
+      <x:c r="A387" s="8" t="str">
+        <x:v>trunk:FC1:V3:fan:-1</x:v>
+      </x:c>
+      <x:c r="B387" s="8" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C387" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D387" s="11" t="n">
+        <x:v>6.156000000000001</x:v>
+      </x:c>
+      <x:c r="E387" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F387" s="11" t="n">
+        <x:f>SQRT((C387-C386)^2+(D387-D386)^2+(E387-E386)^2)</x:f>
+        <x:v>1.8260000000000005</x:v>
+      </x:c>
+      <x:c r="G387" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388" ht="32" customHeight="1">
+      <x:c r="A388" s="8" t="str">
+        <x:v>trunk:FC1:V3:fan:-1</x:v>
+      </x:c>
+      <x:c r="B388" s="8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C388" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D388" s="11" t="n">
+        <x:v>6.156000000000001</x:v>
+      </x:c>
+      <x:c r="E388" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F388" s="11" t="n">
+        <x:f>SQRT((C388-C387)^2+(D388-D387)^2+(E388-E387)^2)</x:f>
+        <x:v>4.0600000000000005</x:v>
+      </x:c>
+      <x:c r="G388" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389" ht="32" customHeight="1">
+      <x:c r="A389" s="8" t="str">
+        <x:v>drop:FC1:V3:fan:-1:F260</x:v>
+      </x:c>
+      <x:c r="B389" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C382" s="11" t="n">
-        <x:v>41.85</x:v>
-      </x:c>
-      <x:c r="D382" s="11" t="n">
-        <x:v>8.243099226804118</x:v>
-      </x:c>
-      <x:c r="E382" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F382" s="11" t="n">
+      <x:c r="C389" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D389" s="11" t="n">
+        <x:v>6.156000000000001</x:v>
+      </x:c>
+      <x:c r="E389" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F389" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G382" s="8" t="str">
+      <x:c r="G389" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390" ht="32" customHeight="1">
+      <x:c r="A390" s="8" t="str">
+        <x:v>drop:FC1:V3:fan:-1:F260</x:v>
+      </x:c>
+      <x:c r="B390" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C390" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D390" s="11" t="n">
+        <x:v>6.156000000000001</x:v>
+      </x:c>
+      <x:c r="E390" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F390" s="11" t="n">
+        <x:f>SQRT((C390-C389)^2+(D390-D389)^2+(E390-E389)^2)</x:f>
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="G390" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391" ht="32" customHeight="1">
+      <x:c r="A391" s="8" t="str">
+        <x:v>drop:FC1:V3:fan:-1:F260</x:v>
+      </x:c>
+      <x:c r="B391" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C391" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D391" s="11" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="E391" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F391" s="11" t="n">
+        <x:f>SQRT((C391-C390)^2+(D391-D390)^2+(E391-E390)^2)</x:f>
+        <x:v>2.8560000000000008</x:v>
+      </x:c>
+      <x:c r="G391" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392" ht="32" customHeight="1">
+      <x:c r="A392" s="8" t="str">
+        <x:v>drop:FC1:V3:fan:-1:F260</x:v>
+      </x:c>
+      <x:c r="B392" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C392" s="11" t="n">
+        <x:v>53.12</x:v>
+      </x:c>
+      <x:c r="D392" s="11" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="E392" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F392" s="11" t="n">
+        <x:f>SQRT((C392-C391)^2+(D392-D391)^2+(E392-E391)^2)</x:f>
+        <x:v>0.1039999999999992</x:v>
+      </x:c>
+      <x:c r="G392" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393" ht="32" customHeight="1">
+      <x:c r="A393" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+      </x:c>
+      <x:c r="B393" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C393" s="11" t="n">
+        <x:v>39.7</x:v>
+      </x:c>
+      <x:c r="D393" s="11" t="n">
+        <x:v>8.565264175257731</x:v>
+      </x:c>
+      <x:c r="E393" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F393" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G393" s="8" t="str">
         <x:v>Retired</x:v>
       </x:c>
     </x:row>
-    <x:row r="383" ht="32" customHeight="1">
-      <x:c r="A383" s="8" t="str">
+    <x:row r="394" ht="32" customHeight="1">
+      <x:c r="A394" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+      </x:c>
+      <x:c r="B394" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C394" s="11" t="n">
+        <x:v>39.7</x:v>
+      </x:c>
+      <x:c r="D394" s="11" t="n">
+        <x:v>8.565264175257731</x:v>
+      </x:c>
+      <x:c r="E394" s="11" t="n">
+        <x:v>-13.249</x:v>
+      </x:c>
+      <x:c r="F394" s="11" t="n">
+        <x:f>SQRT((C394-C393)^2+(D394-D393)^2+(E394-E393)^2)</x:f>
+        <x:v>5.889</x:v>
+      </x:c>
+      <x:c r="G394" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395" ht="32" customHeight="1">
+      <x:c r="A395" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+      </x:c>
+      <x:c r="B395" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C395" s="11" t="n">
+        <x:v>39.7</x:v>
+      </x:c>
+      <x:c r="D395" s="11" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="E395" s="11" t="n">
+        <x:v>-13.249</x:v>
+      </x:c>
+      <x:c r="F395" s="11" t="n">
+        <x:f>SQRT((C395-C394)^2+(D395-D394)^2+(E395-E394)^2)</x:f>
+        <x:v>0.9652641752577313</x:v>
+      </x:c>
+      <x:c r="G395" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396" ht="32" customHeight="1">
+      <x:c r="A396" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F256</x:v>
+      </x:c>
+      <x:c r="B396" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C396" s="11" t="n">
+        <x:v>39.7</x:v>
+      </x:c>
+      <x:c r="D396" s="11" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="E396" s="11" t="n">
+        <x:v>-13.13</x:v>
+      </x:c>
+      <x:c r="F396" s="11" t="n">
+        <x:f>SQRT((C396-C395)^2+(D396-D395)^2+(E396-E395)^2)</x:f>
+        <x:v>0.11899999999999977</x:v>
+      </x:c>
+      <x:c r="G396" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397" ht="32" customHeight="1">
+      <x:c r="A397" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
+      </x:c>
+      <x:c r="B397" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C397" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D397" s="11" t="n">
+        <x:v>8.565264175257724</x:v>
+      </x:c>
+      <x:c r="E397" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F397" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G397" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398" ht="32" customHeight="1">
+      <x:c r="A398" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
+      </x:c>
+      <x:c r="B398" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C398" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D398" s="11" t="n">
+        <x:v>8.565264175257731</x:v>
+      </x:c>
+      <x:c r="E398" s="11" t="n">
+        <x:v>-13.249</x:v>
+      </x:c>
+      <x:c r="F398" s="11" t="n">
+        <x:f>SQRT((C398-C397)^2+(D398-D397)^2+(E398-E397)^2)</x:f>
+        <x:v>5.889</x:v>
+      </x:c>
+      <x:c r="G398" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399" ht="32" customHeight="1">
+      <x:c r="A399" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
+      </x:c>
+      <x:c r="B399" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C399" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D399" s="11" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="E399" s="11" t="n">
+        <x:v>-13.249</x:v>
+      </x:c>
+      <x:c r="F399" s="11" t="n">
+        <x:f>SQRT((C399-C398)^2+(D399-D398)^2+(E399-E398)^2)</x:f>
+        <x:v>0.9652641752577313</x:v>
+      </x:c>
+      <x:c r="G399" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400" ht="32" customHeight="1">
+      <x:c r="A400" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F257</x:v>
+      </x:c>
+      <x:c r="B400" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C400" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D400" s="11" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="E400" s="11" t="n">
+        <x:v>-13.13</x:v>
+      </x:c>
+      <x:c r="F400" s="11" t="n">
+        <x:f>SQRT((C400-C399)^2+(D400-D399)^2+(E400-E399)^2)</x:f>
+        <x:v>0.11899999999999977</x:v>
+      </x:c>
+      <x:c r="G400" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401" ht="32" customHeight="1">
+      <x:c r="A401" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
+      </x:c>
+      <x:c r="B401" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C401" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D401" s="11" t="n">
+        <x:v>6.0360000000000005</x:v>
+      </x:c>
+      <x:c r="E401" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F401" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G401" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402" ht="32" customHeight="1">
+      <x:c r="A402" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
+      </x:c>
+      <x:c r="B402" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C402" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D402" s="11" t="n">
+        <x:v>6.0360000000000005</x:v>
+      </x:c>
+      <x:c r="E402" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F402" s="11" t="n">
+        <x:f>SQRT((C402-C401)^2+(D402-D401)^2+(E402-E401)^2)</x:f>
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="G402" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403" ht="32" customHeight="1">
+      <x:c r="A403" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
+      </x:c>
+      <x:c r="B403" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C403" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D403" s="11" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="E403" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F403" s="11" t="n">
+        <x:f>SQRT((C403-C402)^2+(D403-D402)^2+(E403-E402)^2)</x:f>
+        <x:v>2.7360000000000007</x:v>
+      </x:c>
+      <x:c r="G403" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404" ht="32" customHeight="1">
+      <x:c r="A404" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:-1:F260</x:v>
+      </x:c>
+      <x:c r="B404" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C404" s="11" t="n">
+        <x:v>53.12</x:v>
+      </x:c>
+      <x:c r="D404" s="11" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="E404" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F404" s="11" t="n">
+        <x:f>SQRT((C404-C403)^2+(D404-D403)^2+(E404-E403)^2)</x:f>
+        <x:v>0.1039999999999992</x:v>
+      </x:c>
+      <x:c r="G404" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405" ht="32" customHeight="1">
+      <x:c r="A405" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F258</x:v>
+      </x:c>
+      <x:c r="B405" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C405" s="11" t="n">
+        <x:v>39.7</x:v>
+      </x:c>
+      <x:c r="D405" s="11" t="n">
+        <x:v>8.565264175257731</x:v>
+      </x:c>
+      <x:c r="E405" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F405" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G405" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406" ht="32" customHeight="1">
+      <x:c r="A406" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F258</x:v>
+      </x:c>
+      <x:c r="B406" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C406" s="11" t="n">
+        <x:v>39.7</x:v>
+      </x:c>
+      <x:c r="D406" s="11" t="n">
+        <x:v>8.565264175257731</x:v>
+      </x:c>
+      <x:c r="E406" s="11" t="n">
+        <x:v>13.249</x:v>
+      </x:c>
+      <x:c r="F406" s="11" t="n">
+        <x:f>SQRT((C406-C405)^2+(D406-D405)^2+(E406-E405)^2)</x:f>
+        <x:v>5.889</x:v>
+      </x:c>
+      <x:c r="G406" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407" ht="32" customHeight="1">
+      <x:c r="A407" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F258</x:v>
+      </x:c>
+      <x:c r="B407" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C407" s="11" t="n">
+        <x:v>39.7</x:v>
+      </x:c>
+      <x:c r="D407" s="11" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="E407" s="11" t="n">
+        <x:v>13.249</x:v>
+      </x:c>
+      <x:c r="F407" s="11" t="n">
+        <x:f>SQRT((C407-C406)^2+(D407-D406)^2+(E407-E406)^2)</x:f>
+        <x:v>0.9652641752577313</x:v>
+      </x:c>
+      <x:c r="G407" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408" ht="32" customHeight="1">
+      <x:c r="A408" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F258</x:v>
+      </x:c>
+      <x:c r="B408" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C408" s="11" t="n">
+        <x:v>39.7</x:v>
+      </x:c>
+      <x:c r="D408" s="11" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="E408" s="11" t="n">
+        <x:v>13.13</x:v>
+      </x:c>
+      <x:c r="F408" s="11" t="n">
+        <x:f>SQRT((C408-C407)^2+(D408-D407)^2+(E408-E407)^2)</x:f>
+        <x:v>0.11899999999999977</x:v>
+      </x:c>
+      <x:c r="G408" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" ht="32" customHeight="1">
+      <x:c r="A409" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F259</x:v>
+      </x:c>
+      <x:c r="B409" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C409" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D409" s="11" t="n">
+        <x:v>8.565264175257724</x:v>
+      </x:c>
+      <x:c r="E409" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F409" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G409" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410" ht="32" customHeight="1">
+      <x:c r="A410" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F259</x:v>
+      </x:c>
+      <x:c r="B410" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C410" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D410" s="11" t="n">
+        <x:v>8.565264175257731</x:v>
+      </x:c>
+      <x:c r="E410" s="11" t="n">
+        <x:v>13.249</x:v>
+      </x:c>
+      <x:c r="F410" s="11" t="n">
+        <x:f>SQRT((C410-C409)^2+(D410-D409)^2+(E410-E409)^2)</x:f>
+        <x:v>5.889</x:v>
+      </x:c>
+      <x:c r="G410" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411" ht="32" customHeight="1">
+      <x:c r="A411" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F259</x:v>
+      </x:c>
+      <x:c r="B411" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C411" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D411" s="11" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="E411" s="11" t="n">
+        <x:v>13.249</x:v>
+      </x:c>
+      <x:c r="F411" s="11" t="n">
+        <x:f>SQRT((C411-C410)^2+(D411-D410)^2+(E411-E410)^2)</x:f>
+        <x:v>0.9652641752577313</x:v>
+      </x:c>
+      <x:c r="G411" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412" ht="32" customHeight="1">
+      <x:c r="A412" s="8" t="str">
+        <x:v>drop:FC1:V1:fan:1:F259</x:v>
+      </x:c>
+      <x:c r="B412" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C412" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="D412" s="11" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="E412" s="11" t="n">
+        <x:v>13.13</x:v>
+      </x:c>
+      <x:c r="F412" s="11" t="n">
+        <x:f>SQRT((C412-C411)^2+(D412-D411)^2+(E412-E411)^2)</x:f>
+        <x:v>0.11899999999999977</x:v>
+      </x:c>
+      <x:c r="G412" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413" ht="32" customHeight="1">
+      <x:c r="A413" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+      </x:c>
+      <x:c r="B413" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C413" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="D413" s="11" t="n">
+        <x:v>8.766617268041228</x:v>
+      </x:c>
+      <x:c r="E413" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F413" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G413" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414" ht="32" customHeight="1">
+      <x:c r="A414" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+      </x:c>
+      <x:c r="B414" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C414" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="D414" s="11" t="n">
+        <x:v>8.766617268041237</x:v>
+      </x:c>
+      <x:c r="E414" s="11" t="n">
+        <x:v>-13.249</x:v>
+      </x:c>
+      <x:c r="F414" s="11" t="n">
+        <x:f>SQRT((C414-C413)^2+(D414-D413)^2+(E414-E413)^2)</x:f>
+        <x:v>5.889</x:v>
+      </x:c>
+      <x:c r="G414" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415" ht="32" customHeight="1">
+      <x:c r="A415" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+      </x:c>
+      <x:c r="B415" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C415" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="D415" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E415" s="11" t="n">
+        <x:v>-13.249</x:v>
+      </x:c>
+      <x:c r="F415" s="11" t="n">
+        <x:f>SQRT((C415-C414)^2+(D415-D414)^2+(E415-E414)^2)</x:f>
+        <x:v>6.066617268041237</x:v>
+      </x:c>
+      <x:c r="G415" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416" ht="32" customHeight="1">
+      <x:c r="A416" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-3</x:v>
+      </x:c>
+      <x:c r="B416" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C416" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="D416" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E416" s="11" t="n">
+        <x:v>-13.06</x:v>
+      </x:c>
+      <x:c r="F416" s="11" t="n">
+        <x:f>SQRT((C416-C415)^2+(D416-D415)^2+(E416-E415)^2)</x:f>
+        <x:v>0.18900000000000006</x:v>
+      </x:c>
+      <x:c r="G416" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417" ht="32" customHeight="1">
+      <x:c r="A417" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+      </x:c>
+      <x:c r="B417" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C417" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D417" s="11" t="n">
+        <x:v>8.122287371134018</x:v>
+      </x:c>
+      <x:c r="E417" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F417" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G417" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418" ht="32" customHeight="1">
+      <x:c r="A418" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+      </x:c>
+      <x:c r="B418" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C418" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D418" s="11" t="n">
+        <x:v>8.122287371134023</x:v>
+      </x:c>
+      <x:c r="E418" s="11" t="n">
+        <x:v>-13.249</x:v>
+      </x:c>
+      <x:c r="F418" s="11" t="n">
+        <x:f>SQRT((C418-C417)^2+(D418-D417)^2+(E418-E417)^2)</x:f>
+        <x:v>5.889</x:v>
+      </x:c>
+      <x:c r="G418" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419" ht="32" customHeight="1">
+      <x:c r="A419" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+      </x:c>
+      <x:c r="B419" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C419" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D419" s="11" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="E419" s="11" t="n">
+        <x:v>-13.249</x:v>
+      </x:c>
+      <x:c r="F419" s="11" t="n">
+        <x:f>SQRT((C419-C418)^2+(D419-D418)^2+(E419-E418)^2)</x:f>
+        <x:v>4.622287371134023</x:v>
+      </x:c>
+      <x:c r="G419" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420" ht="32" customHeight="1">
+      <x:c r="A420" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:-1:F-WING-B-4</x:v>
+      </x:c>
+      <x:c r="B420" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C420" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D420" s="11" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="E420" s="11" t="n">
+        <x:v>-13.06</x:v>
+      </x:c>
+      <x:c r="F420" s="11" t="n">
+        <x:f>SQRT((C420-C419)^2+(D420-D419)^2+(E420-E419)^2)</x:f>
+        <x:v>0.18900000000000006</x:v>
+      </x:c>
+      <x:c r="G420" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421" ht="32" customHeight="1">
+      <x:c r="A421" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+      </x:c>
+      <x:c r="B421" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C421" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="D421" s="11" t="n">
+        <x:v>8.766617268041228</x:v>
+      </x:c>
+      <x:c r="E421" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F421" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G421" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422" ht="32" customHeight="1">
+      <x:c r="A422" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+      </x:c>
+      <x:c r="B422" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C422" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="D422" s="11" t="n">
+        <x:v>8.766617268041237</x:v>
+      </x:c>
+      <x:c r="E422" s="11" t="n">
+        <x:v>13.249</x:v>
+      </x:c>
+      <x:c r="F422" s="11" t="n">
+        <x:f>SQRT((C422-C421)^2+(D422-D421)^2+(E422-E421)^2)</x:f>
+        <x:v>5.889</x:v>
+      </x:c>
+      <x:c r="G422" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423" ht="32" customHeight="1">
+      <x:c r="A423" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+      </x:c>
+      <x:c r="B423" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C423" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="D423" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E423" s="11" t="n">
+        <x:v>13.249</x:v>
+      </x:c>
+      <x:c r="F423" s="11" t="n">
+        <x:f>SQRT((C423-C422)^2+(D423-D422)^2+(E423-E422)^2)</x:f>
+        <x:v>6.066617268041237</x:v>
+      </x:c>
+      <x:c r="G423" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424" ht="32" customHeight="1">
+      <x:c r="A424" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-3</x:v>
+      </x:c>
+      <x:c r="B424" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C424" s="11" t="n">
+        <x:v>41.2</x:v>
+      </x:c>
+      <x:c r="D424" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E424" s="11" t="n">
+        <x:v>13.06</x:v>
+      </x:c>
+      <x:c r="F424" s="11" t="n">
+        <x:f>SQRT((C424-C423)^2+(D424-D423)^2+(E424-E423)^2)</x:f>
+        <x:v>0.18900000000000006</x:v>
+      </x:c>
+      <x:c r="G424" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425" ht="32" customHeight="1">
+      <x:c r="A425" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+      </x:c>
+      <x:c r="B425" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C425" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D425" s="11" t="n">
+        <x:v>8.122287371134018</x:v>
+      </x:c>
+      <x:c r="E425" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F425" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G425" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426" ht="32" customHeight="1">
+      <x:c r="A426" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+      </x:c>
+      <x:c r="B426" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C426" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D426" s="11" t="n">
+        <x:v>8.122287371134023</x:v>
+      </x:c>
+      <x:c r="E426" s="11" t="n">
+        <x:v>13.249</x:v>
+      </x:c>
+      <x:c r="F426" s="11" t="n">
+        <x:f>SQRT((C426-C425)^2+(D426-D425)^2+(E426-E425)^2)</x:f>
+        <x:v>5.889</x:v>
+      </x:c>
+      <x:c r="G426" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="427" ht="32" customHeight="1">
+      <x:c r="A427" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+      </x:c>
+      <x:c r="B427" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C427" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D427" s="11" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="E427" s="11" t="n">
+        <x:v>13.249</x:v>
+      </x:c>
+      <x:c r="F427" s="11" t="n">
+        <x:f>SQRT((C427-C426)^2+(D427-D426)^2+(E427-E426)^2)</x:f>
+        <x:v>4.622287371134023</x:v>
+      </x:c>
+      <x:c r="G427" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428" ht="32" customHeight="1">
+      <x:c r="A428" s="8" t="str">
+        <x:v>drop:FC1:F5:fan:1:F-WING-H-4</x:v>
+      </x:c>
+      <x:c r="B428" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C428" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D428" s="11" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="E428" s="11" t="n">
+        <x:v>13.06</x:v>
+      </x:c>
+      <x:c r="F428" s="11" t="n">
+        <x:f>SQRT((C428-C427)^2+(D428-D427)^2+(E428-E427)^2)</x:f>
+        <x:v>0.18900000000000006</x:v>
+      </x:c>
+      <x:c r="G428" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429" ht="32" customHeight="1">
+      <x:c r="A429" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
+      </x:c>
+      <x:c r="B429" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C429" s="11" t="n">
+        <x:v>39.3</x:v>
+      </x:c>
+      <x:c r="D429" s="11" t="n">
+        <x:v>8.24309922680412</x:v>
+      </x:c>
+      <x:c r="E429" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F429" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G429" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430" ht="32" customHeight="1">
+      <x:c r="A430" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
+      </x:c>
+      <x:c r="B430" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C430" s="11" t="n">
+        <x:v>39.3</x:v>
+      </x:c>
+      <x:c r="D430" s="11" t="n">
+        <x:v>8.24309922680412</x:v>
+      </x:c>
+      <x:c r="E430" s="11" t="n">
+        <x:v>-10.15</x:v>
+      </x:c>
+      <x:c r="F430" s="11" t="n">
+        <x:f>SQRT((C430-C429)^2+(D430-D429)^2+(E430-E429)^2)</x:f>
+        <x:v>2.79</x:v>
+      </x:c>
+      <x:c r="G430" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431" ht="32" customHeight="1">
+      <x:c r="A431" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:-1:F240</x:v>
+      </x:c>
+      <x:c r="B431" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C431" s="11" t="n">
+        <x:v>39.3</x:v>
+      </x:c>
+      <x:c r="D431" s="11" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="E431" s="11" t="n">
+        <x:v>-10.15</x:v>
+      </x:c>
+      <x:c r="F431" s="11" t="n">
+        <x:f>SQRT((C431-C430)^2+(D431-D430)^2+(E431-E430)^2)</x:f>
+        <x:v>4.94309922680412</x:v>
+      </x:c>
+      <x:c r="G431" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432" ht="32" customHeight="1">
+      <x:c r="A432" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+      </x:c>
+      <x:c r="B432" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C432" s="11" t="n">
+        <x:v>41.85</x:v>
+      </x:c>
+      <x:c r="D432" s="11" t="n">
+        <x:v>8.243099226804118</x:v>
+      </x:c>
+      <x:c r="E432" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F432" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G432" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433" ht="32" customHeight="1">
+      <x:c r="A433" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+      </x:c>
+      <x:c r="B433" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C433" s="11" t="n">
+        <x:v>41.85</x:v>
+      </x:c>
+      <x:c r="D433" s="11" t="n">
+        <x:v>8.243099226804125</x:v>
+      </x:c>
+      <x:c r="E433" s="11" t="n">
+        <x:v>-10.15</x:v>
+      </x:c>
+      <x:c r="F433" s="11" t="n">
+        <x:f>SQRT((C433-C432)^2+(D433-D432)^2+(E433-E432)^2)</x:f>
+        <x:v>2.79</x:v>
+      </x:c>
+      <x:c r="G433" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434" ht="32" customHeight="1">
+      <x:c r="A434" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:-1:F241</x:v>
+      </x:c>
+      <x:c r="B434" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C434" s="11" t="n">
+        <x:v>41.85</x:v>
+      </x:c>
+      <x:c r="D434" s="11" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="E434" s="11" t="n">
+        <x:v>-10.15</x:v>
+      </x:c>
+      <x:c r="F434" s="11" t="n">
+        <x:f>SQRT((C434-C433)^2+(D434-D433)^2+(E434-E433)^2)</x:f>
+        <x:v>4.943099226804125</x:v>
+      </x:c>
+      <x:c r="G434" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="435" ht="32" customHeight="1">
+      <x:c r="A435" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:1:F242</x:v>
+      </x:c>
+      <x:c r="B435" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C435" s="11" t="n">
+        <x:v>39.3</x:v>
+      </x:c>
+      <x:c r="D435" s="11" t="n">
+        <x:v>8.24309922680412</x:v>
+      </x:c>
+      <x:c r="E435" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F435" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G435" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436" ht="32" customHeight="1">
+      <x:c r="A436" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:1:F242</x:v>
+      </x:c>
+      <x:c r="B436" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C436" s="11" t="n">
+        <x:v>39.3</x:v>
+      </x:c>
+      <x:c r="D436" s="11" t="n">
+        <x:v>8.24309922680412</x:v>
+      </x:c>
+      <x:c r="E436" s="11" t="n">
+        <x:v>10.15</x:v>
+      </x:c>
+      <x:c r="F436" s="11" t="n">
+        <x:f>SQRT((C436-C435)^2+(D436-D435)^2+(E436-E435)^2)</x:f>
+        <x:v>2.79</x:v>
+      </x:c>
+      <x:c r="G436" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="437" ht="32" customHeight="1">
+      <x:c r="A437" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:1:F242</x:v>
+      </x:c>
+      <x:c r="B437" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C437" s="11" t="n">
+        <x:v>39.3</x:v>
+      </x:c>
+      <x:c r="D437" s="11" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="E437" s="11" t="n">
+        <x:v>10.15</x:v>
+      </x:c>
+      <x:c r="F437" s="11" t="n">
+        <x:f>SQRT((C437-C436)^2+(D437-D436)^2+(E437-E436)^2)</x:f>
+        <x:v>4.94309922680412</x:v>
+      </x:c>
+      <x:c r="G437" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="438" ht="32" customHeight="1">
+      <x:c r="A438" s="8" t="str">
         <x:v>drop:FC1:F1:fan:1:F243</x:v>
       </x:c>
-      <x:c r="B383" s="8" t="n">
+      <x:c r="B438" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C438" s="11" t="n">
+        <x:v>41.85</x:v>
+      </x:c>
+      <x:c r="D438" s="11" t="n">
+        <x:v>8.243099226804118</x:v>
+      </x:c>
+      <x:c r="E438" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F438" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G438" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="439" ht="32" customHeight="1">
+      <x:c r="A439" s="8" t="str">
+        <x:v>drop:FC1:F1:fan:1:F243</x:v>
+      </x:c>
+      <x:c r="B439" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C383" s="11" t="n">
+      <x:c r="C439" s="11" t="n">
         <x:v>41.85</x:v>
       </x:c>
-      <x:c r="D383" s="11" t="n">
+      <x:c r="D439" s="11" t="n">
         <x:v>8.243099226804125</x:v>
       </x:c>
-      <x:c r="E383" s="11" t="n">
+      <x:c r="E439" s="11" t="n">
         <x:v>10.15</x:v>
       </x:c>
-      <x:c r="F383" s="11" t="n">
-        <x:f>SQRT((C383-C382)^2+(D383-D382)^2+(E383-E382)^2)</x:f>
+      <x:c r="F439" s="11" t="n">
+        <x:f>SQRT((C439-C438)^2+(D439-D438)^2+(E439-E438)^2)</x:f>
         <x:v>2.79</x:v>
       </x:c>
-      <x:c r="G383" s="8" t="str">
+      <x:c r="G439" s="8" t="str">
         <x:v>Retired</x:v>
       </x:c>
     </x:row>
-    <x:row r="384" ht="32" customHeight="1">
-      <x:c r="A384" s="8" t="str">
+    <x:row r="440" ht="32" customHeight="1">
+      <x:c r="A440" s="8" t="str">
         <x:v>drop:FC1:F1:fan:1:F243</x:v>
       </x:c>
-      <x:c r="B384" s="8" t="n">
+      <x:c r="B440" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C384" s="11" t="n">
+      <x:c r="C440" s="11" t="n">
         <x:v>41.85</x:v>
       </x:c>
-      <x:c r="D384" s="11" t="n">
+      <x:c r="D440" s="11" t="n">
         <x:v>3.3</x:v>
       </x:c>
-      <x:c r="E384" s="11" t="n">
+      <x:c r="E440" s="11" t="n">
         <x:v>10.15</x:v>
       </x:c>
-      <x:c r="F384" s="11" t="n">
-        <x:f>SQRT((C384-C383)^2+(D384-D383)^2+(E384-E383)^2)</x:f>
+      <x:c r="F440" s="11" t="n">
+        <x:f>SQRT((C440-C439)^2+(D440-D439)^2+(E440-E439)^2)</x:f>
         <x:v>4.943099226804125</x:v>
       </x:c>
-      <x:c r="G384" s="8" t="str">
+      <x:c r="G440" s="8" t="str">
         <x:v>Retired</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G7:G384">
+  <x:conditionalFormatting sqref="G7:G440">
     <x:cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R864a6eb57cc040ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b4d9f05bdba4863"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R7dc70ed54dae453a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re5a02f525b014727"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R5e2a2d9156f54ec9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rdebbbf2f02314341"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R26b335b8dff84aed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R321d589644ef41f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R09d4d7bf59f34975"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R9e93640e7849483b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-17T21:33:54.811Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-19T08:15:40.780Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>40c0fb48adb616822d2737a378024e64d46f211fcc43ca75ea298cd2570965f8</x:v>
+        <x:v>377a9614312a02f792043db75f19539177eac31dbb6fbce22ffc70cc36f6d6f9</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>e8507810679907dc3354f9387ce0b6d5f3b3e307d5939a52680f19a914a4cd86</x:v>
+        <x:v>7407c92e37c8f0d1299afa3b00360d1b00fbe1db0f067d0666f57047093f1960</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5895ed09e7004630"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60c472f1fe784b7c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde232074433d482e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R474402d52f614a41"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19491,7 +19491,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b4d9f05bdba4863"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5eee79d04451493b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R26b335b8dff84aed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R321d589644ef41f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R09d4d7bf59f34975"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R9e93640e7849483b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rffbe048ca8984572"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R722866d7ead046e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R1d6333806d1a465d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rafd8bb5fb0c44a47"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-19T08:15:40.780Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-19T08:50:48.752Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>377a9614312a02f792043db75f19539177eac31dbb6fbce22ffc70cc36f6d6f9</x:v>
+        <x:v>5f987e29647ab0b5cedad770eae700cb80b204e95ea85d8a400edb95c4d1128d</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60c472f1fe784b7c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raff5e57ccc324271"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R474402d52f614a41"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3dee4c37a7fc4c8f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19491,7 +19491,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5eee79d04451493b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R586d854a0a5843d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rffbe048ca8984572"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R722866d7ead046e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R1d6333806d1a465d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rafd8bb5fb0c44a47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R9f74d8370b2d4e92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R3290e164e2bf459e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rdcc57228c09344fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rfdcbf1d94ff94361"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-19T08:50:48.752Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-19T11:17:33.830Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5f987e29647ab0b5cedad770eae700cb80b204e95ea85d8a400edb95c4d1128d</x:v>
+        <x:v>76909d79225afb700a61e3530abc09d363cc6e053b648e6ff87757a6c3bc33f9</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>7407c92e37c8f0d1299afa3b00360d1b00fbe1db0f067d0666f57047093f1960</x:v>
+        <x:v>5c2b7909fdbf3eab73054e0a16a6cfe55decd4f3c81b9a88867863ffd7c0fef1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raff5e57ccc324271"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29db7f436e504aec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3dee4c37a7fc4c8f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50e5e48400884070"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19491,7 +19491,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R586d854a0a5843d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a0765d8084b4bb9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R87a00a19307e48b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rfbfa7fed3f6648ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R6ea773f956fa4d8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R00a56819caa047d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R4acaf98294bf4c3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R77575370518d4086"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rac019a69759a494b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rcbd0170f0e704bce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-19T13:14:34.808Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-23T23:29:38.571Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5e78147eff2f4a61ae97936ba8b51920b75ba77bd982e40a1cae0206f908332c</x:v>
+        <x:v>19eb3af4e9e190d44f45651a83746b308f3bc351650fff669ae77f5ce0cb3e9d</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>7a659950a4bf89cc57551f6d9714dbafa89ad76ea9820ddefb4bbc73056b5b2e</x:v>
+        <x:v>ec7eed586921cecf1c820f16f5ebefd971b44f66cd4eae78e00a7540b47ad9d9</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34003bcc69fb4bac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a38163d880445b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf241ac41d2634534"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3e96af78238438e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20067,7 +20067,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a31eaa0cdeb46b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb070a2041729469d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R4acaf98294bf4c3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R77575370518d4086"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rac019a69759a494b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rcbd0170f0e704bce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R1a666807ce3749bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re0ff672eed654923"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R71dba90629ec491f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rf72ebae4f0114e8e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-23T23:29:38.571Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T00:39:01.684Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>19eb3af4e9e190d44f45651a83746b308f3bc351650fff669ae77f5ce0cb3e9d</x:v>
+        <x:v>146da28a773b5232adb7a991941b4c52312ffa1c721c3656a3930b7eeac1bb23</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>ec7eed586921cecf1c820f16f5ebefd971b44f66cd4eae78e00a7540b47ad9d9</x:v>
+        <x:v>c2461516b6454aa96dec6678dad1bc8b977620d5c08160037ef8b86f7f230532</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a38163d880445b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R369f136dec9248ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3e96af78238438e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda506af14be94be5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20067,7 +20067,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb070a2041729469d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86edf94664fc4524"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R1a666807ce3749bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re0ff672eed654923"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R71dba90629ec491f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rf72ebae4f0114e8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R5e08d02365c54bb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R4a8beb66ffd94c40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R434da2d133f74ec0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R775f1579ffcb40aa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T00:39:01.684Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T16:03:51.012Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>146da28a773b5232adb7a991941b4c52312ffa1c721c3656a3930b7eeac1bb23</x:v>
+        <x:v>5426ce45cb04f814d5dd0210f8e96b572936a920fad8790c50d7c5cfa6b6676e</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>c2461516b6454aa96dec6678dad1bc8b977620d5c08160037ef8b86f7f230532</x:v>
+        <x:v>b17314130617491f3e73a772bab5720c8ffe36baa24ed5a5cc2512f8640338ef</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R369f136dec9248ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d7b5caea31b42f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda506af14be94be5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3901d5f980d4a9e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20067,7 +20067,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86edf94664fc4524"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3328f4c44b8d4a22"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R5e08d02365c54bb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R4a8beb66ffd94c40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R434da2d133f74ec0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R775f1579ffcb40aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R241479cb06ae4989"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re106657a02134560"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rcbbe33de39cb4b2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R798eb52dc5d142f4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T16:03:51.012Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T16:44:17.712Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5426ce45cb04f814d5dd0210f8e96b572936a920fad8790c50d7c5cfa6b6676e</x:v>
+        <x:v>c5d56493e89032b01436ecaed120866a09d5872d997065e2e10f3c09d0d21e41</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>b17314130617491f3e73a772bab5720c8ffe36baa24ed5a5cc2512f8640338ef</x:v>
+        <x:v>10d6d18e117107f62a3d3e48f08d9f8d9df9954b8ce3c3d85d06553452833a75</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d7b5caea31b42f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8be6b8e8001c4afc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3901d5f980d4a9e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0190e00caaf348da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20067,7 +20067,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3328f4c44b8d4a22"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49a33d9f6e414be7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R241479cb06ae4989"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re106657a02134560"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rcbbe33de39cb4b2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R798eb52dc5d142f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rf96fc544ac384f30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R71dbe10c8f7849fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Ra746be27e5e64e46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R3ea1ad2469114ba2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T16:44:17.712Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T17:01:56.972Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>c5d56493e89032b01436ecaed120866a09d5872d997065e2e10f3c09d0d21e41</x:v>
+        <x:v>13047932f1698050c4ec862686991828799970abdcdf394a64d82404d1fcbee8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>10d6d18e117107f62a3d3e48f08d9f8d9df9954b8ce3c3d85d06553452833a75</x:v>
+        <x:v>2faac8500a07543b677dc990e5aad2b96fa69acb639f440c57dab2001fa28053</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -2217,7 +2217,7 @@
         <x:v>14.475</x:v>
       </x:c>
       <x:c r="G25" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="H25" s="11" t="n">
         <x:v>-7.07</x:v>
@@ -2286,7 +2286,7 @@
         <x:v>14.475</x:v>
       </x:c>
       <x:c r="G26" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="H26" s="11" t="n">
         <x:v>7.07</x:v>
@@ -2355,7 +2355,7 @@
         <x:v>23.475</x:v>
       </x:c>
       <x:c r="G27" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="H27" s="11" t="n">
         <x:v>-7.07</x:v>
@@ -2424,7 +2424,7 @@
         <x:v>23.475</x:v>
       </x:c>
       <x:c r="G28" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="H28" s="11" t="n">
         <x:v>7.07</x:v>
@@ -2493,7 +2493,7 @@
         <x:v>32.475</x:v>
       </x:c>
       <x:c r="G29" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="H29" s="11" t="n">
         <x:v>-7.07</x:v>
@@ -2562,7 +2562,7 @@
         <x:v>32.475</x:v>
       </x:c>
       <x:c r="G30" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="H30" s="11" t="n">
         <x:v>7.07</x:v>
@@ -3390,7 +3390,7 @@
         <x:v>5.475</x:v>
       </x:c>
       <x:c r="G42" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="H42" s="11" t="n">
         <x:v>-7.07</x:v>
@@ -3459,7 +3459,7 @@
         <x:v>5.475</x:v>
       </x:c>
       <x:c r="G43" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="H43" s="11" t="n">
         <x:v>7.07</x:v>
@@ -3528,7 +3528,7 @@
         <x:v>9.975</x:v>
       </x:c>
       <x:c r="G44" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="H44" s="11" t="n">
         <x:v>-7.07</x:v>
@@ -3597,7 +3597,7 @@
         <x:v>9.975</x:v>
       </x:c>
       <x:c r="G45" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="H45" s="11" t="n">
         <x:v>7.07</x:v>
@@ -3666,7 +3666,7 @@
         <x:v>18.975</x:v>
       </x:c>
       <x:c r="G46" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="H46" s="11" t="n">
         <x:v>-7.07</x:v>
@@ -3735,7 +3735,7 @@
         <x:v>18.975</x:v>
       </x:c>
       <x:c r="G47" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="H47" s="11" t="n">
         <x:v>7.07</x:v>
@@ -3804,7 +3804,7 @@
         <x:v>27.975</x:v>
       </x:c>
       <x:c r="G48" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="H48" s="11" t="n">
         <x:v>-7.07</x:v>
@@ -3873,7 +3873,7 @@
         <x:v>27.975</x:v>
       </x:c>
       <x:c r="G49" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="H49" s="11" t="n">
         <x:v>7.07</x:v>
@@ -3942,7 +3942,7 @@
         <x:v>36.975</x:v>
       </x:c>
       <x:c r="G50" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="H50" s="11" t="n">
         <x:v>-7.07</x:v>
@@ -4011,7 +4011,7 @@
         <x:v>36.975</x:v>
       </x:c>
       <x:c r="G51" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="H51" s="11" t="n">
         <x:v>7.07</x:v>
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8be6b8e8001c4afc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fa9a139d02045c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6062,7 +6062,7 @@
       </x:c>
       <x:c r="I30" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A30,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>0.7520000000000007</x:v>
+        <x:v>2.202000000000001</x:v>
       </x:c>
       <x:c r="J30" s="11"/>
       <x:c r="K30" s="11" t="str">
@@ -6123,7 +6123,7 @@
       </x:c>
       <x:c r="I31" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A31,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>0.7520000000000007</x:v>
+        <x:v>2.202000000000001</x:v>
       </x:c>
       <x:c r="J31" s="11"/>
       <x:c r="K31" s="11" t="str">
@@ -6184,7 +6184,7 @@
       </x:c>
       <x:c r="I32" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A32,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>0.7520000000000007</x:v>
+        <x:v>2.202000000000001</x:v>
       </x:c>
       <x:c r="J32" s="11"/>
       <x:c r="K32" s="11" t="str">
@@ -6245,7 +6245,7 @@
       </x:c>
       <x:c r="I33" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A33,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>0.7520000000000007</x:v>
+        <x:v>2.202000000000001</x:v>
       </x:c>
       <x:c r="J33" s="11"/>
       <x:c r="K33" s="11" t="str">
@@ -6306,7 +6306,7 @@
       </x:c>
       <x:c r="I34" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A34,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>0.7520000000000007</x:v>
+        <x:v>2.202000000000001</x:v>
       </x:c>
       <x:c r="J34" s="11"/>
       <x:c r="K34" s="11" t="str">
@@ -6367,7 +6367,7 @@
       </x:c>
       <x:c r="I35" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A35,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>0.7520000000000007</x:v>
+        <x:v>2.202000000000001</x:v>
       </x:c>
       <x:c r="J35" s="11"/>
       <x:c r="K35" s="11" t="str">
@@ -6428,7 +6428,7 @@
       </x:c>
       <x:c r="I36" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A36,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>0.7520000000000007</x:v>
+        <x:v>2.202000000000001</x:v>
       </x:c>
       <x:c r="J36" s="11"/>
       <x:c r="K36" s="11" t="str">
@@ -6489,7 +6489,7 @@
       </x:c>
       <x:c r="I37" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A37,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>0.7520000000000007</x:v>
+        <x:v>2.202000000000001</x:v>
       </x:c>
       <x:c r="J37" s="11"/>
       <x:c r="K37" s="11" t="str">
@@ -6616,7 +6616,7 @@
       </x:c>
       <x:c r="I39" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A39,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>0.7520000000000007</x:v>
+        <x:v>2.202000000000001</x:v>
       </x:c>
       <x:c r="J39" s="11"/>
       <x:c r="K39" s="11" t="str">
@@ -6677,7 +6677,7 @@
       </x:c>
       <x:c r="I40" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A40,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>0.7520000000000007</x:v>
+        <x:v>2.202000000000001</x:v>
       </x:c>
       <x:c r="J40" s="11"/>
       <x:c r="K40" s="11" t="str">
@@ -6738,7 +6738,7 @@
       </x:c>
       <x:c r="I41" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A41,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>0.7520000000000007</x:v>
+        <x:v>2.202000000000001</x:v>
       </x:c>
       <x:c r="J41" s="11"/>
       <x:c r="K41" s="11" t="str">
@@ -6799,7 +6799,7 @@
       </x:c>
       <x:c r="I42" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A42,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>0.7520000000000007</x:v>
+        <x:v>2.202000000000001</x:v>
       </x:c>
       <x:c r="J42" s="11"/>
       <x:c r="K42" s="11" t="str">
@@ -6860,7 +6860,7 @@
       </x:c>
       <x:c r="I43" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A43,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>0.7520000000000007</x:v>
+        <x:v>2.202000000000001</x:v>
       </x:c>
       <x:c r="J43" s="11"/>
       <x:c r="K43" s="11" t="str">
@@ -6921,7 +6921,7 @@
       </x:c>
       <x:c r="I44" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A44,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>0.7520000000000007</x:v>
+        <x:v>2.202000000000001</x:v>
       </x:c>
       <x:c r="J44" s="11"/>
       <x:c r="K44" s="11" t="str">
@@ -6982,7 +6982,7 @@
       </x:c>
       <x:c r="I45" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A45,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>0.7520000000000007</x:v>
+        <x:v>2.202000000000001</x:v>
       </x:c>
       <x:c r="J45" s="11"/>
       <x:c r="K45" s="11" t="str">
@@ -7043,7 +7043,7 @@
       </x:c>
       <x:c r="I46" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A46,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>0.7520000000000007</x:v>
+        <x:v>2.202000000000001</x:v>
       </x:c>
       <x:c r="J46" s="11"/>
       <x:c r="K46" s="11" t="str">
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0190e00caaf348da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d25a7fe267743b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14048,14 +14048,14 @@
         <x:v>14.475000000000001</x:v>
       </x:c>
       <x:c r="D214" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E214" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F214" s="11" t="n">
         <x:f>SQRT((C214-C213)^2+(D214-D213)^2+(E214-E213)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>1.9120000000000008</x:v>
       </x:c>
       <x:c r="G214" s="8" t="str">
         <x:v>Current</x:v>
@@ -14072,7 +14072,7 @@
         <x:v>14.475</x:v>
       </x:c>
       <x:c r="D215" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E215" s="11" t="n">
         <x:v>-7.07</x:v>
@@ -14120,14 +14120,14 @@
         <x:v>23.475</x:v>
       </x:c>
       <x:c r="D217" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E217" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F217" s="11" t="n">
         <x:f>SQRT((C217-C216)^2+(D217-D216)^2+(E217-E216)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>1.9120000000000008</x:v>
       </x:c>
       <x:c r="G217" s="8" t="str">
         <x:v>Current</x:v>
@@ -14144,7 +14144,7 @@
         <x:v>23.475</x:v>
       </x:c>
       <x:c r="D218" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E218" s="11" t="n">
         <x:v>-7.07</x:v>
@@ -14192,14 +14192,14 @@
         <x:v>32.475</x:v>
       </x:c>
       <x:c r="D220" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E220" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F220" s="11" t="n">
         <x:f>SQRT((C220-C219)^2+(D220-D219)^2+(E220-E219)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>1.9120000000000008</x:v>
       </x:c>
       <x:c r="G220" s="8" t="str">
         <x:v>Current</x:v>
@@ -14216,7 +14216,7 @@
         <x:v>32.475</x:v>
       </x:c>
       <x:c r="D221" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E221" s="11" t="n">
         <x:v>-7.07</x:v>
@@ -14264,14 +14264,14 @@
         <x:v>5.475000000000001</x:v>
       </x:c>
       <x:c r="D223" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E223" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F223" s="11" t="n">
         <x:f>SQRT((C223-C222)^2+(D223-D222)^2+(E223-E222)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>1.9120000000000008</x:v>
       </x:c>
       <x:c r="G223" s="8" t="str">
         <x:v>Current</x:v>
@@ -14288,7 +14288,7 @@
         <x:v>5.475</x:v>
       </x:c>
       <x:c r="D224" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E224" s="11" t="n">
         <x:v>-7.07</x:v>
@@ -14336,14 +14336,14 @@
         <x:v>9.975000000000001</x:v>
       </x:c>
       <x:c r="D226" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E226" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F226" s="11" t="n">
         <x:f>SQRT((C226-C225)^2+(D226-D225)^2+(E226-E225)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>1.9120000000000008</x:v>
       </x:c>
       <x:c r="G226" s="8" t="str">
         <x:v>Current</x:v>
@@ -14360,7 +14360,7 @@
         <x:v>9.975</x:v>
       </x:c>
       <x:c r="D227" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E227" s="11" t="n">
         <x:v>-7.07</x:v>
@@ -14408,14 +14408,14 @@
         <x:v>18.975</x:v>
       </x:c>
       <x:c r="D229" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E229" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F229" s="11" t="n">
         <x:f>SQRT((C229-C228)^2+(D229-D228)^2+(E229-E228)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>1.9120000000000008</x:v>
       </x:c>
       <x:c r="G229" s="8" t="str">
         <x:v>Current</x:v>
@@ -14432,7 +14432,7 @@
         <x:v>18.975</x:v>
       </x:c>
       <x:c r="D230" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E230" s="11" t="n">
         <x:v>-7.07</x:v>
@@ -14480,14 +14480,14 @@
         <x:v>27.975</x:v>
       </x:c>
       <x:c r="D232" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E232" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F232" s="11" t="n">
         <x:f>SQRT((C232-C231)^2+(D232-D231)^2+(E232-E231)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>1.9120000000000008</x:v>
       </x:c>
       <x:c r="G232" s="8" t="str">
         <x:v>Current</x:v>
@@ -14504,7 +14504,7 @@
         <x:v>27.975</x:v>
       </x:c>
       <x:c r="D233" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E233" s="11" t="n">
         <x:v>-7.07</x:v>
@@ -14552,14 +14552,14 @@
         <x:v>36.975</x:v>
       </x:c>
       <x:c r="D235" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E235" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F235" s="11" t="n">
         <x:f>SQRT((C235-C234)^2+(D235-D234)^2+(E235-E234)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>1.9120000000000008</x:v>
       </x:c>
       <x:c r="G235" s="8" t="str">
         <x:v>Current</x:v>
@@ -14576,7 +14576,7 @@
         <x:v>36.975</x:v>
       </x:c>
       <x:c r="D236" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E236" s="11" t="n">
         <x:v>-7.07</x:v>
@@ -15056,14 +15056,14 @@
         <x:v>14.475000000000001</x:v>
       </x:c>
       <x:c r="D256" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E256" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F256" s="11" t="n">
         <x:f>SQRT((C256-C255)^2+(D256-D255)^2+(E256-E255)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>1.9120000000000008</x:v>
       </x:c>
       <x:c r="G256" s="8" t="str">
         <x:v>Current</x:v>
@@ -15080,7 +15080,7 @@
         <x:v>14.475</x:v>
       </x:c>
       <x:c r="D257" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E257" s="11" t="n">
         <x:v>7.07</x:v>
@@ -15128,14 +15128,14 @@
         <x:v>23.475</x:v>
       </x:c>
       <x:c r="D259" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E259" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F259" s="11" t="n">
         <x:f>SQRT((C259-C258)^2+(D259-D258)^2+(E259-E258)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>1.9120000000000008</x:v>
       </x:c>
       <x:c r="G259" s="8" t="str">
         <x:v>Current</x:v>
@@ -15152,7 +15152,7 @@
         <x:v>23.475</x:v>
       </x:c>
       <x:c r="D260" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E260" s="11" t="n">
         <x:v>7.07</x:v>
@@ -15200,14 +15200,14 @@
         <x:v>32.475</x:v>
       </x:c>
       <x:c r="D262" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E262" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F262" s="11" t="n">
         <x:f>SQRT((C262-C261)^2+(D262-D261)^2+(E262-E261)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>1.9120000000000008</x:v>
       </x:c>
       <x:c r="G262" s="8" t="str">
         <x:v>Current</x:v>
@@ -15224,7 +15224,7 @@
         <x:v>32.475</x:v>
       </x:c>
       <x:c r="D263" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E263" s="11" t="n">
         <x:v>7.07</x:v>
@@ -15272,14 +15272,14 @@
         <x:v>5.475000000000001</x:v>
       </x:c>
       <x:c r="D265" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E265" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F265" s="11" t="n">
         <x:f>SQRT((C265-C264)^2+(D265-D264)^2+(E265-E264)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>1.9120000000000008</x:v>
       </x:c>
       <x:c r="G265" s="8" t="str">
         <x:v>Current</x:v>
@@ -15296,7 +15296,7 @@
         <x:v>5.475</x:v>
       </x:c>
       <x:c r="D266" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E266" s="11" t="n">
         <x:v>7.07</x:v>
@@ -15344,14 +15344,14 @@
         <x:v>9.975000000000001</x:v>
       </x:c>
       <x:c r="D268" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E268" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F268" s="11" t="n">
         <x:f>SQRT((C268-C267)^2+(D268-D267)^2+(E268-E267)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>1.9120000000000008</x:v>
       </x:c>
       <x:c r="G268" s="8" t="str">
         <x:v>Current</x:v>
@@ -15368,7 +15368,7 @@
         <x:v>9.975</x:v>
       </x:c>
       <x:c r="D269" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E269" s="11" t="n">
         <x:v>7.07</x:v>
@@ -15416,14 +15416,14 @@
         <x:v>18.975</x:v>
       </x:c>
       <x:c r="D271" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E271" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F271" s="11" t="n">
         <x:f>SQRT((C271-C270)^2+(D271-D270)^2+(E271-E270)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>1.9120000000000008</x:v>
       </x:c>
       <x:c r="G271" s="8" t="str">
         <x:v>Current</x:v>
@@ -15440,7 +15440,7 @@
         <x:v>18.975</x:v>
       </x:c>
       <x:c r="D272" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E272" s="11" t="n">
         <x:v>7.07</x:v>
@@ -15488,14 +15488,14 @@
         <x:v>27.975</x:v>
       </x:c>
       <x:c r="D274" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E274" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F274" s="11" t="n">
         <x:f>SQRT((C274-C273)^2+(D274-D273)^2+(E274-E273)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>1.9120000000000008</x:v>
       </x:c>
       <x:c r="G274" s="8" t="str">
         <x:v>Current</x:v>
@@ -15512,7 +15512,7 @@
         <x:v>27.975</x:v>
       </x:c>
       <x:c r="D275" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E275" s="11" t="n">
         <x:v>7.07</x:v>
@@ -15560,14 +15560,14 @@
         <x:v>36.975</x:v>
       </x:c>
       <x:c r="D277" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E277" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F277" s="11" t="n">
         <x:f>SQRT((C277-C276)^2+(D277-D276)^2+(E277-E276)^2)</x:f>
-        <x:v>0.46200000000000063</x:v>
+        <x:v>1.9120000000000008</x:v>
       </x:c>
       <x:c r="G277" s="8" t="str">
         <x:v>Current</x:v>
@@ -15584,7 +15584,7 @@
         <x:v>36.975</x:v>
       </x:c>
       <x:c r="D278" s="11" t="n">
-        <x:v>5.55</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E278" s="11" t="n">
         <x:v>7.07</x:v>
@@ -20067,7 +20067,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49a33d9f6e414be7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23e55596a7674052"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rf96fc544ac384f30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R71dbe10c8f7849fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Ra746be27e5e64e46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R3ea1ad2469114ba2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rc1b0cd46d332401a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R7830d96efff246f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rb76c38d9a7354b6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R1cddc4a20d7e4ee0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T17:01:56.972Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T17:09:33.226Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>13047932f1698050c4ec862686991828799970abdcdf394a64d82404d1fcbee8</x:v>
+        <x:v>8494709266c989cc26ec0f16481a494804ce05b0210fea7ddf78e6004c0e1614</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>2faac8500a07543b677dc990e5aad2b96fa69acb639f440c57dab2001fa28053</x:v>
+        <x:v>760fbab99b5e7a6f8a94c497e4a9254bf06be7fb81bd104e0e2b4126c9fde701</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fa9a139d02045c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a3c1dc1a06a4bf0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d25a7fe267743b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99ee66b229094d7f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20067,7 +20067,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23e55596a7674052"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R523cd2fe39824bd9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rc1b0cd46d332401a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R7830d96efff246f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rb76c38d9a7354b6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R1cddc4a20d7e4ee0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R73ddbcae28eb440e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re9c634fa4f7c412f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R2c42817276af4982"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R072f1dd5135441aa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T17:09:33.226Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T17:42:22.582Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>8494709266c989cc26ec0f16481a494804ce05b0210fea7ddf78e6004c0e1614</x:v>
+        <x:v>94f37cc477b452b68afd0631937580a0b9412b859965e9046c49f59c64746a3f</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>760fbab99b5e7a6f8a94c497e4a9254bf06be7fb81bd104e0e2b4126c9fde701</x:v>
+        <x:v>1c162288ea3d9215a1f3a3feb59b009079a72c6a8a777f9f9044923d3b18ad31</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a3c1dc1a06a4bf0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce15e2f752c14c5d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99ee66b229094d7f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42ad60fe4c7343e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20067,7 +20067,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R523cd2fe39824bd9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc66f3caeb824261"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R73ddbcae28eb440e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re9c634fa4f7c412f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R2c42817276af4982"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R072f1dd5135441aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R389e5f9f7d6042b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Ra44865582fab4b35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rcfd8ccc75c40462c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rc14c08c789a54fbd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T17:42:22.582Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T17:49:59.196Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>94f37cc477b452b68afd0631937580a0b9412b859965e9046c49f59c64746a3f</x:v>
+        <x:v>88062f7a6e23d78621ee2f69e0c94047babf12437db78098dd47d3bedd6e18e8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>1c162288ea3d9215a1f3a3feb59b009079a72c6a8a777f9f9044923d3b18ad31</x:v>
+        <x:v>fb798ccf47bd62d17275121a5ca1021b3ed9a80358d236bd57d75a7be070b894</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce15e2f752c14c5d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ccc4e3c6b724e0e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7104,7 +7104,7 @@
       </x:c>
       <x:c r="I47" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A47,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>12.517</x:v>
+        <x:v>26.797</x:v>
       </x:c>
       <x:c r="J47" s="11"/>
       <x:c r="K47" s="11" t="str">
@@ -7224,7 +7224,7 @@
       </x:c>
       <x:c r="I49" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A49,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>19.117</x:v>
+        <x:v>12.077000000000002</x:v>
       </x:c>
       <x:c r="J49" s="11"/>
       <x:c r="K49" s="11" t="str">
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42ad60fe4c7343e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9ab5ebf93f2413d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15605,13 +15605,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C279" s="11" t="n">
-        <x:v>2.73</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D279" s="11" t="n">
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="E279" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="F279" s="11" t="n">
         <x:f>0</x:f>
@@ -15635,11 +15635,11 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="E280" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="F280" s="11" t="n">
         <x:f>SQRT((C280-C279)^2+(D280-D279)^2+(E280-E279)^2)</x:f>
-        <x:v>0.3799999999999999</x:v>
+        <x:v>2.1100000000000003</x:v>
       </x:c>
       <x:c r="G280" s="8" t="str">
         <x:v>Current</x:v>
@@ -15659,7 +15659,7 @@
         <x:v>7.65</x:v>
       </x:c>
       <x:c r="E281" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="F281" s="11" t="n">
         <x:f>SQRT((C281-C280)^2+(D281-D280)^2+(E281-E280)^2)</x:f>
@@ -15687,7 +15687,7 @@
       </x:c>
       <x:c r="F282" s="11" t="n">
         <x:f>SQRT((C282-C281)^2+(D282-D281)^2+(E282-E281)^2)</x:f>
-        <x:v>4.0600000000000005</x:v>
+        <x:v>16.61</x:v>
       </x:c>
       <x:c r="G282" s="8" t="str">
         <x:v>Current</x:v>
@@ -15869,13 +15869,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C290" s="11" t="n">
-        <x:v>2.73</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D290" s="11" t="n">
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="E290" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="F290" s="11" t="n">
         <x:f>0</x:f>
@@ -15899,11 +15899,11 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="E291" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="F291" s="11" t="n">
         <x:f>SQRT((C291-C290)^2+(D291-D290)^2+(E291-E290)^2)</x:f>
-        <x:v>0.3799999999999999</x:v>
+        <x:v>2.1100000000000003</x:v>
       </x:c>
       <x:c r="G291" s="8" t="str">
         <x:v>Current</x:v>
@@ -15923,7 +15923,7 @@
         <x:v>7.65</x:v>
       </x:c>
       <x:c r="E292" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="F292" s="11" t="n">
         <x:f>SQRT((C292-C291)^2+(D292-D291)^2+(E292-E291)^2)</x:f>
@@ -15951,7 +15951,7 @@
       </x:c>
       <x:c r="F293" s="11" t="n">
         <x:f>SQRT((C293-C292)^2+(D293-D292)^2+(E293-E292)^2)</x:f>
-        <x:v>10.66</x:v>
+        <x:v>1.8899999999999997</x:v>
       </x:c>
       <x:c r="G293" s="8" t="str">
         <x:v>Current</x:v>
@@ -20067,7 +20067,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc66f3caeb824261"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10538ca727674d9e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R389e5f9f7d6042b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Ra44865582fab4b35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rcfd8ccc75c40462c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rc14c08c789a54fbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R9efe0ad8efd7406d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rb850016c60604df4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R1954c5ae925c43d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rc43ec3a575cc4786"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T17:49:59.196Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T18:07:55.978Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>88062f7a6e23d78621ee2f69e0c94047babf12437db78098dd47d3bedd6e18e8</x:v>
+        <x:v>5385d4f4cf361a2e56db9b88d4a9952e6d93bf5f83f0834cb083bcdd6684e517</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>fb798ccf47bd62d17275121a5ca1021b3ed9a80358d236bd57d75a7be070b894</x:v>
+        <x:v>d50c68edff009ac84589ad37b15985dac299e304fb4daa2752ebe808d92740fd</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ccc4e3c6b724e0e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra525fc5b7d8a4b8b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9ab5ebf93f2413d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ae1a096c90d455d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20067,7 +20067,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10538ca727674d9e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb75c4dd1022c4b00"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R9efe0ad8efd7406d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rb850016c60604df4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R1954c5ae925c43d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rc43ec3a575cc4786"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R4ee5a53728384111"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R1b6fb52a3a074e00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R39214289c12c4832"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rf734f7aea25e44b3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T18:07:55.978Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T18:15:14.532Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5385d4f4cf361a2e56db9b88d4a9952e6d93bf5f83f0834cb083bcdd6684e517</x:v>
+        <x:v>944ecbe81a903e81a65ffa487f20c3a417603b0749843148bbf77414d42d60b4</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra525fc5b7d8a4b8b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1d407e7756a4717"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ae1a096c90d455d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd265785bb79d4d1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20067,7 +20067,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb75c4dd1022c4b00"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a9968331c894f20"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R4ee5a53728384111"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R1b6fb52a3a074e00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R39214289c12c4832"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rf734f7aea25e44b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Re927aaa823004a33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rc5055d3582524cff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Re6583ee8635243d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R97149a45f9d14cc5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T18:15:14.532Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T22:22:25.930Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>944ecbe81a903e81a65ffa487f20c3a417603b0749843148bbf77414d42d60b4</x:v>
+        <x:v>325f8ef8696abef155a85a11a511a71ee5bbd155d28b2e0bfd11928b39ade4e3</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>d50c68edff009ac84589ad37b15985dac299e304fb4daa2752ebe808d92740fd</x:v>
+        <x:v>75fa53533f9758516132ea54608152663cd0f407a24b0e6a3e030bc743a6ab27</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1d407e7756a4717"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c36dc8fb6ee4301"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd265785bb79d4d1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbcbb12a1afb04b05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20067,7 +20067,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a9968331c894f20"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re00faecb40b14f37"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Re927aaa823004a33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rc5055d3582524cff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Re6583ee8635243d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R97149a45f9d14cc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R543bd546a0b44317"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R19c72c866deb43dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R770fc7b652414a99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R161c03404f8a4379"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-24T22:22:25.930Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-25T11:43:35.202Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>325f8ef8696abef155a85a11a511a71ee5bbd155d28b2e0bfd11928b39ade4e3</x:v>
+        <x:v>8794d15eced755667fbb94a78904d0b24ab39e7c75d28fc3bbe150bece4e8ceb</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>75fa53533f9758516132ea54608152663cd0f407a24b0e6a3e030bc743a6ab27</x:v>
+        <x:v>fa54e193a88aab1a463c7e9a9d929aac8295554193f697131ae924624c8c3635</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c36dc8fb6ee4301"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd28b87849b534b27"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbcbb12a1afb04b05"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc691b719c0e4119"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20067,7 +20067,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re00faecb40b14f37"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8af791a015d9468d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R543bd546a0b44317"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R19c72c866deb43dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R770fc7b652414a99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R161c03404f8a4379"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R2cb503c86bae4af5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R6096f9c42d084a30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R69a9cf476106426b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R56e4a19de4a24a4a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-25T11:43:35.202Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-25T12:31:42.928Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>8794d15eced755667fbb94a78904d0b24ab39e7c75d28fc3bbe150bece4e8ceb</x:v>
+        <x:v>6638c6d858c0c15d03f1b8c7f8d4371e61b16cbc58edb9c36dd4e72b917f5303</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>fa54e193a88aab1a463c7e9a9d929aac8295554193f697131ae924624c8c3635</x:v>
+        <x:v>8efd0e5d2f1745401819248f5cd349c1ca2995df2b2938bff0ddd27c9679b4c8</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd28b87849b534b27"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcebc72e9f2794379"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc691b719c0e4119"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re98b49e322b44561"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20067,7 +20067,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8af791a015d9468d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd4197711d6b4025"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R2cb503c86bae4af5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R6096f9c42d084a30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R69a9cf476106426b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R56e4a19de4a24a4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3939da11bb3b42b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rc48a2bef8c504d2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R9e252174ba4b4f97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R9ad2e6762346419b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-25T12:31:42.928Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-31T15:58:16.965Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>6638c6d858c0c15d03f1b8c7f8d4371e61b16cbc58edb9c36dd4e72b917f5303</x:v>
+        <x:v>7958b4809b6199a78823ea47abdd37329f78f9de03404b0f973483495d74be9e</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>8efd0e5d2f1745401819248f5cd349c1ca2995df2b2938bff0ddd27c9679b4c8</x:v>
+        <x:v>de942b6ea94208f140cd0ec1bb6d7282f467a001cb150dd4c584a870ba9c4c2b</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcebc72e9f2794379"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdd387e9856944f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re98b49e322b44561"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd2e7da50bec43b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20067,7 +20067,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd4197711d6b4025"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea6d289706b640cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3939da11bb3b42b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rc48a2bef8c504d2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R9e252174ba4b4f97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R9ad2e6762346419b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R0ddadd2ed65f4cbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rb67909cdf56f4fb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rc209a110d80d4ef1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R0251919ba7d740e4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-31T15:58:16.965Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-31T16:19:36.678Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>7958b4809b6199a78823ea47abdd37329f78f9de03404b0f973483495d74be9e</x:v>
+        <x:v>3cdbadaba0ffc908418f454ec3a56c6c112739ccae548d5038c524ed0fb572ae</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>de942b6ea94208f140cd0ec1bb6d7282f467a001cb150dd4c584a870ba9c4c2b</x:v>
+        <x:v>19f49808ff7b94351ad8e2bad9b30d5c978e8d5e96c5f164a91146ca0afcd5ac</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdd387e9856944f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6cd4eaeb3594562"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd2e7da50bec43b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67a91ed5cb7d4f65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20067,7 +20067,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea6d289706b640cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b9896d63b0143d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R0ddadd2ed65f4cbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rb67909cdf56f4fb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rc209a110d80d4ef1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R0251919ba7d740e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3cf2e96442ff4527"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R3f0090f1fcc24023"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R628374fe465843cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rcc8ab1d9fbbc4d6b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-31T16:19:36.678Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-11-01T00:50:08.502Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>3cdbadaba0ffc908418f454ec3a56c6c112739ccae548d5038c524ed0fb572ae</x:v>
+        <x:v>b59c831ec1c00c49183c1e83c86ee8d801e0152690935057f3be6f551a8b788b</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>19f49808ff7b94351ad8e2bad9b30d5c978e8d5e96c5f164a91146ca0afcd5ac</x:v>
+        <x:v>2a343075b78e07a39b50033e252aeaec71194df376aa048789dba03e95d6e972</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -2628,7 +2628,7 @@
         <x:v>F4</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>5.4799999999999995</x:v>
       </x:c>
       <x:c r="G31" s="11" t="n">
         <x:v>6</x:v>
@@ -2697,7 +2697,7 @@
         <x:v>F4</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>5.4799999999999995</x:v>
       </x:c>
       <x:c r="G32" s="11" t="n">
         <x:v>6</x:v>
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6cd4eaeb3594562"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7da132423194fda"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7104,7 +7104,7 @@
       </x:c>
       <x:c r="I47" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A47,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>26.797</x:v>
+        <x:v>29.622</x:v>
       </x:c>
       <x:c r="J47" s="11"/>
       <x:c r="K47" s="11" t="str">
@@ -7163,7 +7163,7 @@
       </x:c>
       <x:c r="I48" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A48,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>7.91542691446789</x:v>
+        <x:v>17.218000000000004</x:v>
       </x:c>
       <x:c r="J48" s="11"/>
       <x:c r="K48" s="11" t="str">
@@ -7180,7 +7180,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P48" s="8" t="str">
-        <x:v>Concealed entrance wall band, solid pier and local termination.</x:v>
+        <x:v>Proposed underfloor return; this location needs a concealed local riser / connection design.</x:v>
       </x:c>
       <x:c r="Q48" s="9"/>
       <x:c r="R48" s="9"/>
@@ -7224,7 +7224,7 @@
       </x:c>
       <x:c r="I49" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A49,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>12.077000000000002</x:v>
+        <x:v>14.902000000000001</x:v>
       </x:c>
       <x:c r="J49" s="11"/>
       <x:c r="K49" s="11" t="str">
@@ -7283,7 +7283,7 @@
       </x:c>
       <x:c r="I50" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$464,A50,'Route Points'!$F$7:$F$464)</x:f>
-        <x:v>7.91542691446789</x:v>
+        <x:v>17.218000000000004</x:v>
       </x:c>
       <x:c r="J50" s="11"/>
       <x:c r="K50" s="11" t="str">
@@ -7300,7 +7300,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P50" s="8" t="str">
-        <x:v>Concealed entrance wall band, solid pier and local termination.</x:v>
+        <x:v>Proposed underfloor return; this location needs a concealed local riser / connection design.</x:v>
       </x:c>
       <x:c r="Q50" s="9"/>
       <x:c r="R50" s="9"/>
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67a91ed5cb7d4f65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e77e97b8c714262"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15725,7 +15725,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C284" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>5.475</x:v>
       </x:c>
       <x:c r="D284" s="11" t="n">
         <x:v>6.0280000000000005</x:v>
@@ -15735,7 +15735,7 @@
       </x:c>
       <x:c r="F284" s="11" t="n">
         <x:f>SQRT((C284-C283)^2+(D284-D283)^2+(E284-E283)^2)</x:f>
-        <x:v>0.3049999999999997</x:v>
+        <x:v>3.1249999999999996</x:v>
       </x:c>
       <x:c r="G284" s="8" t="str">
         <x:v>Current</x:v>
@@ -15743,13 +15743,13 @@
     </x:row>
     <x:row r="285" ht="32" customHeight="1">
       <x:c r="A285" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:-1:F250</x:v>
+        <x:v>trunk:DB2:F4:fan:-1</x:v>
       </x:c>
       <x:c r="B285" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C285" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>5.4799999999999995</x:v>
       </x:c>
       <x:c r="D285" s="11" t="n">
         <x:v>6.0280000000000005</x:v>
@@ -15758,8 +15758,8 @@
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F285" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C285-C284)^2+(D285-D284)^2+(E285-E284)^2)</x:f>
+        <x:v>0.004999999999999893</x:v>
       </x:c>
       <x:c r="G285" s="8" t="str">
         <x:v>Current</x:v>
@@ -15770,20 +15770,20 @@
         <x:v>drop:DB2:F4:fan:-1:F250</x:v>
       </x:c>
       <x:c r="B286" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C286" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>5.4799999999999995</x:v>
       </x:c>
       <x:c r="D286" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>6.0280000000000005</x:v>
       </x:c>
       <x:c r="E286" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F286" s="11" t="n">
-        <x:f>SQRT((C286-C285)^2+(D286-D285)^2+(E286-E285)^2)</x:f>
-        <x:v>1.6504269144678898</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G286" s="8" t="str">
         <x:v>Current</x:v>
@@ -15794,20 +15794,20 @@
         <x:v>drop:DB2:F4:fan:-1:F250</x:v>
       </x:c>
       <x:c r="B287" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C287" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>5.4799999999999995</x:v>
       </x:c>
       <x:c r="D287" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="E287" s="11" t="n">
-        <x:v>-3.05</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F287" s="11" t="n">
         <x:f>SQRT((C287-C286)^2+(D287-D286)^2+(E287-E286)^2)</x:f>
-        <x:v>4.3100000000000005</x:v>
+        <x:v>6.468000000000001</x:v>
       </x:c>
       <x:c r="G287" s="8" t="str">
         <x:v>Current</x:v>
@@ -15818,20 +15818,20 @@
         <x:v>drop:DB2:F4:fan:-1:F250</x:v>
       </x:c>
       <x:c r="B288" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C288" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>5.4799999999999995</x:v>
       </x:c>
       <x:c r="D288" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="E288" s="11" t="n">
         <x:v>-3.05</x:v>
       </x:c>
       <x:c r="F288" s="11" t="n">
         <x:f>SQRT((C288-C287)^2+(D288-D287)^2+(E288-E287)^2)</x:f>
-        <x:v>1.6500000000000004</x:v>
+        <x:v>4.3100000000000005</x:v>
       </x:c>
       <x:c r="G288" s="8" t="str">
         <x:v>Current</x:v>
@@ -15842,10 +15842,10 @@
         <x:v>drop:DB2:F4:fan:-1:F250</x:v>
       </x:c>
       <x:c r="B289" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C289" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>5.4799999999999995</x:v>
       </x:c>
       <x:c r="D289" s="11" t="n">
         <x:v>6</x:v>
@@ -15855,7 +15855,7 @@
       </x:c>
       <x:c r="F289" s="11" t="n">
         <x:f>SQRT((C289-C288)^2+(D289-D288)^2+(E289-E288)^2)</x:f>
-        <x:v>0.3049999999999997</x:v>
+        <x:v>6.44</x:v>
       </x:c>
       <x:c r="G289" s="8" t="str">
         <x:v>Current</x:v>
@@ -15989,7 +15989,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C295" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>5.475</x:v>
       </x:c>
       <x:c r="D295" s="11" t="n">
         <x:v>6.0280000000000005</x:v>
@@ -15999,7 +15999,7 @@
       </x:c>
       <x:c r="F295" s="11" t="n">
         <x:f>SQRT((C295-C294)^2+(D295-D294)^2+(E295-E294)^2)</x:f>
-        <x:v>0.3049999999999997</x:v>
+        <x:v>3.1249999999999996</x:v>
       </x:c>
       <x:c r="G295" s="8" t="str">
         <x:v>Current</x:v>
@@ -16007,13 +16007,13 @@
     </x:row>
     <x:row r="296" ht="32" customHeight="1">
       <x:c r="A296" s="8" t="str">
-        <x:v>drop:DB2:F4:fan:1:F251</x:v>
+        <x:v>trunk:DB2:F4:fan:1</x:v>
       </x:c>
       <x:c r="B296" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C296" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>5.4799999999999995</x:v>
       </x:c>
       <x:c r="D296" s="11" t="n">
         <x:v>6.0280000000000005</x:v>
@@ -16022,8 +16022,8 @@
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F296" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C296-C295)^2+(D296-D295)^2+(E296-E295)^2)</x:f>
+        <x:v>0.004999999999999893</x:v>
       </x:c>
       <x:c r="G296" s="8" t="str">
         <x:v>Current</x:v>
@@ -16034,20 +16034,20 @@
         <x:v>drop:DB2:F4:fan:1:F251</x:v>
       </x:c>
       <x:c r="B297" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C297" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>5.4799999999999995</x:v>
       </x:c>
       <x:c r="D297" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>6.0280000000000005</x:v>
       </x:c>
       <x:c r="E297" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F297" s="11" t="n">
-        <x:f>SQRT((C297-C296)^2+(D297-D296)^2+(E297-E296)^2)</x:f>
-        <x:v>1.6504269144678898</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G297" s="8" t="str">
         <x:v>Current</x:v>
@@ -16058,20 +16058,20 @@
         <x:v>drop:DB2:F4:fan:1:F251</x:v>
       </x:c>
       <x:c r="B298" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C298" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>5.4799999999999995</x:v>
       </x:c>
       <x:c r="D298" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="E298" s="11" t="n">
-        <x:v>3.05</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F298" s="11" t="n">
         <x:f>SQRT((C298-C297)^2+(D298-D297)^2+(E298-E297)^2)</x:f>
-        <x:v>4.3100000000000005</x:v>
+        <x:v>6.468000000000001</x:v>
       </x:c>
       <x:c r="G298" s="8" t="str">
         <x:v>Current</x:v>
@@ -16082,20 +16082,20 @@
         <x:v>drop:DB2:F4:fan:1:F251</x:v>
       </x:c>
       <x:c r="B299" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C299" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>5.4799999999999995</x:v>
       </x:c>
       <x:c r="D299" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="E299" s="11" t="n">
         <x:v>3.05</x:v>
       </x:c>
       <x:c r="F299" s="11" t="n">
         <x:f>SQRT((C299-C298)^2+(D299-D298)^2+(E299-E298)^2)</x:f>
-        <x:v>1.6500000000000004</x:v>
+        <x:v>4.3100000000000005</x:v>
       </x:c>
       <x:c r="G299" s="8" t="str">
         <x:v>Current</x:v>
@@ -16106,10 +16106,10 @@
         <x:v>drop:DB2:F4:fan:1:F251</x:v>
       </x:c>
       <x:c r="B300" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C300" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>5.4799999999999995</x:v>
       </x:c>
       <x:c r="D300" s="11" t="n">
         <x:v>6</x:v>
@@ -16119,7 +16119,7 @@
       </x:c>
       <x:c r="F300" s="11" t="n">
         <x:f>SQRT((C300-C299)^2+(D300-D299)^2+(E300-E299)^2)</x:f>
-        <x:v>0.3049999999999997</x:v>
+        <x:v>6.44</x:v>
       </x:c>
       <x:c r="G300" s="8" t="str">
         <x:v>Current</x:v>
@@ -20067,7 +20067,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b9896d63b0143d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77236972b87c4aec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/air-system/register.xlsx
+++ b/docs/electrical-grid/categories/air-system/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R0ddadd2ed65f4cbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rb67909cdf56f4fb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rc209a110d80d4ef1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R0251919ba7d740e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rc8a6cf48b3a74beb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R86ebbe4f24744885"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R38b46c54656445a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R656cdd4cb6b048a4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-10-31T16:19:36.678Z.</x:v>
+        <x:v>Fans and ventilation. Ceiling, wall, entrance and exhaust fans for air movement and ventilation. Model snapshot: 2026-11-01T01:42:20.339Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>3cdbadaba0ffc908418f454ec3a56c6c112739ccae548d5038c524ed0fb572ae</x:v>
+        <x:v>50118e5af402ff0efaabf2d570ac3f0129d03efc89e10e7eeb51b8d67485750c</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>19f49808ff7b94351ad8e2bad9b30d5c978e8d5e96c5f164a91146ca0afcd5ac</x:v>
+        <x:v>0fb0ba42a427dbbe355fa325c0efcf0641bfb0dae62bd4f360bc65584cfd7d81</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4356,7 +4356,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6cd4eaeb3594562"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4bc28c8f64e4a81"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8975,7 +8975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67a91ed5cb7d4f65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a659d9ded1d4ffc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20067,7 +20067,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b9896d63b0143d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4eef80c39cb94efe"/>
   </x:tableParts>
 </x:worksheet>
 </file>